--- a/SlotTemplate_AudioSpec.xlsx
+++ b/SlotTemplate_AudioSpec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valsamp/Documents/GitHub/igtinteractive/slot-template-audio-howler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6D065B-6CE1-3D47-8930-D3E0028DABA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F96D657-E738-F647-92A4-70417313FC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-21140" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Audio Spec" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="546">
   <si>
     <t>EVENT</t>
   </si>
@@ -1127,12 +1127,6 @@
   </si>
   <si>
     <t>onRollupEnd</t>
-  </si>
-  <si>
-    <t>Rollup</t>
-  </si>
-  <si>
-    <t>RollupEnd</t>
   </si>
   <si>
     <t>Rollup2</t>
@@ -1775,6 +1769,18 @@
   </si>
   <si>
     <t>BonusSymbolS11</t>
+  </si>
+  <si>
+    <t>onRollup1End</t>
+  </si>
+  <si>
+    <t>onRollup1Start</t>
+  </si>
+  <si>
+    <t>Rollup1</t>
+  </si>
+  <si>
+    <t>Rollup1End</t>
   </si>
 </sst>
 </file>
@@ -2339,7 +2345,7 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2586,6 +2592,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2595,25 +2616,7 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3814,7 +3817,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IW163"/>
+  <dimension ref="A1:IW165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.1640625" style="77" bestFit="1" customWidth="1"/>
@@ -3842,10 +3845,10 @@
         <v>246</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E1" s="38" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F1" s="38" t="s">
         <v>280</v>
@@ -4110,7 +4113,7 @@
     </row>
     <row r="2" spans="1:257" ht="16" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42" t="s">
@@ -4118,10 +4121,10 @@
       </c>
       <c r="D2" s="42"/>
       <c r="E2" s="43" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>251</v>
@@ -4377,9 +4380,9 @@
       <c r="IV2" s="39"/>
       <c r="IW2" s="47"/>
     </row>
-    <row r="3" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="42" t="s">
@@ -4387,7 +4390,7 @@
       </c>
       <c r="D3" s="42"/>
       <c r="E3" s="43" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F3" s="42" t="s">
         <v>53</v>
@@ -4648,18 +4651,18 @@
     </row>
     <row r="4" spans="1:257" ht="16" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="96"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="43" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>251</v>
@@ -4915,20 +4918,20 @@
       <c r="IV4" s="39"/>
       <c r="IW4" s="47"/>
     </row>
-    <row r="5" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="96"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="43" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>251</v>
@@ -5190,21 +5193,21 @@
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="48" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="45" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J6" s="46"/>
       <c r="K6" s="46"/>
@@ -5461,14 +5464,14 @@
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="43" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>251</v>
@@ -5736,7 +5739,7 @@
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="43" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>102</v>
@@ -6005,10 +6008,10 @@
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="F9" s="42" t="s">
         <v>398</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>400</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>251</v>
@@ -6270,21 +6273,21 @@
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="57" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D10" s="42"/>
       <c r="E10" s="48" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H10" s="44"/>
       <c r="I10" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J10" s="46"/>
       <c r="K10" s="46"/>
@@ -6541,14 +6544,14 @@
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="57" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="48" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G11" s="44" t="s">
         <v>251</v>
@@ -6810,14 +6813,14 @@
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="57" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="48" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G12" s="44" t="s">
         <v>251</v>
@@ -7079,14 +7082,14 @@
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="57" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="48" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G13" s="44" t="s">
         <v>251</v>
@@ -7348,14 +7351,14 @@
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="57" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="48" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G14" s="44" t="s">
         <v>251</v>
@@ -8964,7 +8967,7 @@
       <c r="C20" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="96"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="43" t="s">
         <v>352</v>
       </c>
@@ -9231,14 +9234,14 @@
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="96"/>
-      <c r="E21" s="48" t="s">
-        <v>337</v>
+        <v>542</v>
+      </c>
+      <c r="D21" s="93"/>
+      <c r="E21" s="43" t="s">
+        <v>545</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G21" s="44" t="s">
         <v>251</v>
@@ -9494,20 +9497,20 @@
       <c r="IV21" s="51"/>
       <c r="IW21" s="52"/>
     </row>
-    <row r="22" spans="1:257" s="53" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:257" s="53" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="62" t="s">
         <v>247</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42" t="s">
-        <v>97</v>
+        <v>543</v>
       </c>
       <c r="D22" s="42"/>
-      <c r="E22" s="48" t="s">
-        <v>357</v>
+      <c r="E22" s="43" t="s">
+        <v>544</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G22" s="44" t="s">
         <v>251</v>
@@ -9769,14 +9772,14 @@
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42" t="s">
-        <v>354</v>
+        <v>99</v>
       </c>
       <c r="D23" s="42"/>
-      <c r="E23" s="43" t="s">
-        <v>356</v>
+      <c r="E23" s="48" t="s">
+        <v>337</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G23" s="44" t="s">
         <v>251</v>
@@ -10038,14 +10041,14 @@
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42" t="s">
-        <v>359</v>
+        <v>97</v>
       </c>
       <c r="D24" s="42"/>
-      <c r="E24" s="43" t="s">
-        <v>358</v>
+      <c r="E24" s="48" t="s">
+        <v>355</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>360</v>
+        <v>98</v>
       </c>
       <c r="G24" s="44" t="s">
         <v>251</v>
@@ -10307,14 +10310,14 @@
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="43" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="G25" s="44" t="s">
         <v>251</v>
@@ -10576,14 +10579,14 @@
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="43" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G26" s="44" t="s">
         <v>251</v>
@@ -10839,7 +10842,7 @@
       <c r="IV26" s="51"/>
       <c r="IW26" s="52"/>
     </row>
-    <row r="27" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:257" s="53" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="56" t="s">
         <v>248</v>
       </c>
@@ -10847,535 +10850,535 @@
       <c r="C27" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="D27" s="98"/>
+      <c r="D27" s="92"/>
       <c r="E27" s="42" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G27" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H27" s="44"/>
       <c r="I27" s="58"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
-      <c r="AA27" s="46"/>
-      <c r="AB27" s="46"/>
-      <c r="AC27" s="46"/>
-      <c r="AD27" s="46"/>
-      <c r="AE27" s="46"/>
-      <c r="AF27" s="46"/>
-      <c r="AG27" s="46"/>
-      <c r="AH27" s="46"/>
-      <c r="AI27" s="46"/>
-      <c r="AJ27" s="46"/>
-      <c r="AK27" s="46"/>
-      <c r="AL27" s="46"/>
-      <c r="AM27" s="46"/>
-      <c r="AN27" s="46"/>
-      <c r="AO27" s="46"/>
-      <c r="AP27" s="46"/>
-      <c r="AQ27" s="46"/>
-      <c r="AR27" s="46"/>
-      <c r="AS27" s="46"/>
-      <c r="AT27" s="46"/>
-      <c r="AU27" s="46"/>
-      <c r="AV27" s="46"/>
-      <c r="AW27" s="46"/>
-      <c r="AX27" s="46"/>
-      <c r="AY27" s="46"/>
-      <c r="AZ27" s="46"/>
-      <c r="BA27" s="46"/>
-      <c r="BB27" s="46"/>
-      <c r="BC27" s="46"/>
-      <c r="BD27" s="46"/>
-      <c r="BE27" s="46"/>
-      <c r="BF27" s="46"/>
-      <c r="BG27" s="46"/>
-      <c r="BH27" s="46"/>
-      <c r="BI27" s="46"/>
-      <c r="BJ27" s="46"/>
-      <c r="BK27" s="46"/>
-      <c r="BL27" s="46"/>
-      <c r="BM27" s="46"/>
-      <c r="BN27" s="46"/>
-      <c r="BO27" s="46"/>
-      <c r="BP27" s="46"/>
-      <c r="BQ27" s="46"/>
-      <c r="BR27" s="46"/>
-      <c r="BS27" s="46"/>
-      <c r="BT27" s="46"/>
-      <c r="BU27" s="46"/>
-      <c r="BV27" s="46"/>
-      <c r="BW27" s="46"/>
-      <c r="BX27" s="46"/>
-      <c r="BY27" s="46"/>
-      <c r="BZ27" s="46"/>
-      <c r="CA27" s="46"/>
-      <c r="CB27" s="46"/>
-      <c r="CC27" s="46"/>
-      <c r="CD27" s="46"/>
-      <c r="CE27" s="46"/>
-      <c r="CF27" s="46"/>
-      <c r="CG27" s="46"/>
-      <c r="CH27" s="46"/>
-      <c r="CI27" s="46"/>
-      <c r="CJ27" s="46"/>
-      <c r="CK27" s="46"/>
-      <c r="CL27" s="46"/>
-      <c r="CM27" s="46"/>
-      <c r="CN27" s="46"/>
-      <c r="CO27" s="46"/>
-      <c r="CP27" s="46"/>
-      <c r="CQ27" s="46"/>
-      <c r="CR27" s="46"/>
-      <c r="CS27" s="46"/>
-      <c r="CT27" s="46"/>
-      <c r="CU27" s="46"/>
-      <c r="CV27" s="46"/>
-      <c r="CW27" s="46"/>
-      <c r="CX27" s="46"/>
-      <c r="CY27" s="46"/>
-      <c r="CZ27" s="46"/>
-      <c r="DA27" s="46"/>
-      <c r="DB27" s="46"/>
-      <c r="DC27" s="46"/>
-      <c r="DD27" s="46"/>
-      <c r="DE27" s="46"/>
-      <c r="DF27" s="46"/>
-      <c r="DG27" s="46"/>
-      <c r="DH27" s="46"/>
-      <c r="DI27" s="46"/>
-      <c r="DJ27" s="46"/>
-      <c r="DK27" s="46"/>
-      <c r="DL27" s="46"/>
-      <c r="DM27" s="46"/>
-      <c r="DN27" s="46"/>
-      <c r="DO27" s="46"/>
-      <c r="DP27" s="46"/>
-      <c r="DQ27" s="46"/>
-      <c r="DR27" s="46"/>
-      <c r="DS27" s="46"/>
-      <c r="DT27" s="46"/>
-      <c r="DU27" s="46"/>
-      <c r="DV27" s="46"/>
-      <c r="DW27" s="46"/>
-      <c r="DX27" s="46"/>
-      <c r="DY27" s="46"/>
-      <c r="DZ27" s="46"/>
-      <c r="EA27" s="46"/>
-      <c r="EB27" s="46"/>
-      <c r="EC27" s="46"/>
-      <c r="ED27" s="46"/>
-      <c r="EE27" s="46"/>
-      <c r="EF27" s="46"/>
-      <c r="EG27" s="46"/>
-      <c r="EH27" s="46"/>
-      <c r="EI27" s="46"/>
-      <c r="EJ27" s="46"/>
-      <c r="EK27" s="46"/>
-      <c r="EL27" s="46"/>
-      <c r="EM27" s="46"/>
-      <c r="EN27" s="46"/>
-      <c r="EO27" s="46"/>
-      <c r="EP27" s="46"/>
-      <c r="EQ27" s="46"/>
-      <c r="ER27" s="46"/>
-      <c r="ES27" s="46"/>
-      <c r="ET27" s="46"/>
-      <c r="EU27" s="46"/>
-      <c r="EV27" s="46"/>
-      <c r="EW27" s="46"/>
-      <c r="EX27" s="46"/>
-      <c r="EY27" s="46"/>
-      <c r="EZ27" s="46"/>
-      <c r="FA27" s="46"/>
-      <c r="FB27" s="46"/>
-      <c r="FC27" s="46"/>
-      <c r="FD27" s="46"/>
-      <c r="FE27" s="46"/>
-      <c r="FF27" s="46"/>
-      <c r="FG27" s="46"/>
-      <c r="FH27" s="46"/>
-      <c r="FI27" s="46"/>
-      <c r="FJ27" s="46"/>
-      <c r="FK27" s="46"/>
-      <c r="FL27" s="46"/>
-      <c r="FM27" s="46"/>
-      <c r="FN27" s="46"/>
-      <c r="FO27" s="46"/>
-      <c r="FP27" s="46"/>
-      <c r="FQ27" s="46"/>
-      <c r="FR27" s="46"/>
-      <c r="FS27" s="46"/>
-      <c r="FT27" s="46"/>
-      <c r="FU27" s="46"/>
-      <c r="FV27" s="46"/>
-      <c r="FW27" s="46"/>
-      <c r="FX27" s="46"/>
-      <c r="FY27" s="46"/>
-      <c r="FZ27" s="46"/>
-      <c r="GA27" s="46"/>
-      <c r="GB27" s="46"/>
-      <c r="GC27" s="46"/>
-      <c r="GD27" s="46"/>
-      <c r="GE27" s="46"/>
-      <c r="GF27" s="46"/>
-      <c r="GG27" s="46"/>
-      <c r="GH27" s="46"/>
-      <c r="GI27" s="46"/>
-      <c r="GJ27" s="46"/>
-      <c r="GK27" s="46"/>
-      <c r="GL27" s="46"/>
-      <c r="GM27" s="46"/>
-      <c r="GN27" s="46"/>
-      <c r="GO27" s="46"/>
-      <c r="GP27" s="46"/>
-      <c r="GQ27" s="46"/>
-      <c r="GR27" s="46"/>
-      <c r="GS27" s="46"/>
-      <c r="GT27" s="46"/>
-      <c r="GU27" s="46"/>
-      <c r="GV27" s="46"/>
-      <c r="GW27" s="46"/>
-      <c r="GX27" s="46"/>
-      <c r="GY27" s="46"/>
-      <c r="GZ27" s="46"/>
-      <c r="HA27" s="46"/>
-      <c r="HB27" s="46"/>
-      <c r="HC27" s="46"/>
-      <c r="HD27" s="46"/>
-      <c r="HE27" s="46"/>
-      <c r="HF27" s="46"/>
-      <c r="HG27" s="46"/>
-      <c r="HH27" s="46"/>
-      <c r="HI27" s="46"/>
-      <c r="HJ27" s="46"/>
-      <c r="HK27" s="46"/>
-      <c r="HL27" s="46"/>
-      <c r="HM27" s="46"/>
-      <c r="HN27" s="46"/>
-      <c r="HO27" s="46"/>
-      <c r="HP27" s="46"/>
-      <c r="HQ27" s="46"/>
-      <c r="HR27" s="46"/>
-      <c r="HS27" s="46"/>
-      <c r="HT27" s="46"/>
-      <c r="HU27" s="46"/>
-      <c r="HV27" s="46"/>
-      <c r="HW27" s="46"/>
-      <c r="HX27" s="46"/>
-      <c r="HY27" s="46"/>
-      <c r="HZ27" s="46"/>
-      <c r="IA27" s="46"/>
-      <c r="IB27" s="46"/>
-      <c r="IC27" s="46"/>
-      <c r="ID27" s="46"/>
-      <c r="IE27" s="46"/>
-      <c r="IF27" s="46"/>
-      <c r="IG27" s="46"/>
-      <c r="IH27" s="46"/>
-      <c r="II27" s="46"/>
-      <c r="IJ27" s="46"/>
-      <c r="IK27" s="46"/>
-      <c r="IL27" s="46"/>
-      <c r="IM27" s="46"/>
-      <c r="IN27" s="39"/>
-      <c r="IO27" s="39"/>
-      <c r="IP27" s="39"/>
-      <c r="IQ27" s="39"/>
-      <c r="IR27" s="39"/>
-      <c r="IS27" s="39"/>
-      <c r="IT27" s="39"/>
-      <c r="IU27" s="39"/>
-      <c r="IV27" s="39"/>
-      <c r="IW27" s="47"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
+      <c r="AF27" s="50"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
+      <c r="AL27" s="50"/>
+      <c r="AM27" s="50"/>
+      <c r="AN27" s="50"/>
+      <c r="AO27" s="50"/>
+      <c r="AP27" s="50"/>
+      <c r="AQ27" s="50"/>
+      <c r="AR27" s="50"/>
+      <c r="AS27" s="50"/>
+      <c r="AT27" s="50"/>
+      <c r="AU27" s="50"/>
+      <c r="AV27" s="50"/>
+      <c r="AW27" s="50"/>
+      <c r="AX27" s="50"/>
+      <c r="AY27" s="50"/>
+      <c r="AZ27" s="50"/>
+      <c r="BA27" s="50"/>
+      <c r="BB27" s="50"/>
+      <c r="BC27" s="50"/>
+      <c r="BD27" s="50"/>
+      <c r="BE27" s="50"/>
+      <c r="BF27" s="50"/>
+      <c r="BG27" s="50"/>
+      <c r="BH27" s="50"/>
+      <c r="BI27" s="50"/>
+      <c r="BJ27" s="50"/>
+      <c r="BK27" s="50"/>
+      <c r="BL27" s="50"/>
+      <c r="BM27" s="50"/>
+      <c r="BN27" s="50"/>
+      <c r="BO27" s="50"/>
+      <c r="BP27" s="50"/>
+      <c r="BQ27" s="50"/>
+      <c r="BR27" s="50"/>
+      <c r="BS27" s="50"/>
+      <c r="BT27" s="50"/>
+      <c r="BU27" s="50"/>
+      <c r="BV27" s="50"/>
+      <c r="BW27" s="50"/>
+      <c r="BX27" s="50"/>
+      <c r="BY27" s="50"/>
+      <c r="BZ27" s="50"/>
+      <c r="CA27" s="50"/>
+      <c r="CB27" s="50"/>
+      <c r="CC27" s="50"/>
+      <c r="CD27" s="50"/>
+      <c r="CE27" s="50"/>
+      <c r="CF27" s="50"/>
+      <c r="CG27" s="50"/>
+      <c r="CH27" s="50"/>
+      <c r="CI27" s="50"/>
+      <c r="CJ27" s="50"/>
+      <c r="CK27" s="50"/>
+      <c r="CL27" s="50"/>
+      <c r="CM27" s="50"/>
+      <c r="CN27" s="50"/>
+      <c r="CO27" s="50"/>
+      <c r="CP27" s="50"/>
+      <c r="CQ27" s="50"/>
+      <c r="CR27" s="50"/>
+      <c r="CS27" s="50"/>
+      <c r="CT27" s="50"/>
+      <c r="CU27" s="50"/>
+      <c r="CV27" s="50"/>
+      <c r="CW27" s="50"/>
+      <c r="CX27" s="50"/>
+      <c r="CY27" s="50"/>
+      <c r="CZ27" s="50"/>
+      <c r="DA27" s="50"/>
+      <c r="DB27" s="50"/>
+      <c r="DC27" s="50"/>
+      <c r="DD27" s="50"/>
+      <c r="DE27" s="50"/>
+      <c r="DF27" s="50"/>
+      <c r="DG27" s="50"/>
+      <c r="DH27" s="50"/>
+      <c r="DI27" s="50"/>
+      <c r="DJ27" s="50"/>
+      <c r="DK27" s="50"/>
+      <c r="DL27" s="50"/>
+      <c r="DM27" s="50"/>
+      <c r="DN27" s="50"/>
+      <c r="DO27" s="50"/>
+      <c r="DP27" s="50"/>
+      <c r="DQ27" s="50"/>
+      <c r="DR27" s="50"/>
+      <c r="DS27" s="50"/>
+      <c r="DT27" s="50"/>
+      <c r="DU27" s="50"/>
+      <c r="DV27" s="50"/>
+      <c r="DW27" s="50"/>
+      <c r="DX27" s="50"/>
+      <c r="DY27" s="50"/>
+      <c r="DZ27" s="50"/>
+      <c r="EA27" s="50"/>
+      <c r="EB27" s="50"/>
+      <c r="EC27" s="50"/>
+      <c r="ED27" s="50"/>
+      <c r="EE27" s="50"/>
+      <c r="EF27" s="50"/>
+      <c r="EG27" s="50"/>
+      <c r="EH27" s="50"/>
+      <c r="EI27" s="50"/>
+      <c r="EJ27" s="50"/>
+      <c r="EK27" s="50"/>
+      <c r="EL27" s="50"/>
+      <c r="EM27" s="50"/>
+      <c r="EN27" s="50"/>
+      <c r="EO27" s="50"/>
+      <c r="EP27" s="50"/>
+      <c r="EQ27" s="50"/>
+      <c r="ER27" s="50"/>
+      <c r="ES27" s="50"/>
+      <c r="ET27" s="50"/>
+      <c r="EU27" s="50"/>
+      <c r="EV27" s="50"/>
+      <c r="EW27" s="50"/>
+      <c r="EX27" s="50"/>
+      <c r="EY27" s="50"/>
+      <c r="EZ27" s="50"/>
+      <c r="FA27" s="50"/>
+      <c r="FB27" s="50"/>
+      <c r="FC27" s="50"/>
+      <c r="FD27" s="50"/>
+      <c r="FE27" s="50"/>
+      <c r="FF27" s="50"/>
+      <c r="FG27" s="50"/>
+      <c r="FH27" s="50"/>
+      <c r="FI27" s="50"/>
+      <c r="FJ27" s="50"/>
+      <c r="FK27" s="50"/>
+      <c r="FL27" s="50"/>
+      <c r="FM27" s="50"/>
+      <c r="FN27" s="50"/>
+      <c r="FO27" s="50"/>
+      <c r="FP27" s="50"/>
+      <c r="FQ27" s="50"/>
+      <c r="FR27" s="50"/>
+      <c r="FS27" s="50"/>
+      <c r="FT27" s="50"/>
+      <c r="FU27" s="50"/>
+      <c r="FV27" s="50"/>
+      <c r="FW27" s="50"/>
+      <c r="FX27" s="50"/>
+      <c r="FY27" s="50"/>
+      <c r="FZ27" s="50"/>
+      <c r="GA27" s="50"/>
+      <c r="GB27" s="50"/>
+      <c r="GC27" s="50"/>
+      <c r="GD27" s="50"/>
+      <c r="GE27" s="50"/>
+      <c r="GF27" s="50"/>
+      <c r="GG27" s="50"/>
+      <c r="GH27" s="50"/>
+      <c r="GI27" s="50"/>
+      <c r="GJ27" s="50"/>
+      <c r="GK27" s="50"/>
+      <c r="GL27" s="50"/>
+      <c r="GM27" s="50"/>
+      <c r="GN27" s="50"/>
+      <c r="GO27" s="50"/>
+      <c r="GP27" s="50"/>
+      <c r="GQ27" s="50"/>
+      <c r="GR27" s="50"/>
+      <c r="GS27" s="50"/>
+      <c r="GT27" s="50"/>
+      <c r="GU27" s="50"/>
+      <c r="GV27" s="50"/>
+      <c r="GW27" s="50"/>
+      <c r="GX27" s="50"/>
+      <c r="GY27" s="50"/>
+      <c r="GZ27" s="50"/>
+      <c r="HA27" s="50"/>
+      <c r="HB27" s="50"/>
+      <c r="HC27" s="50"/>
+      <c r="HD27" s="50"/>
+      <c r="HE27" s="50"/>
+      <c r="HF27" s="50"/>
+      <c r="HG27" s="50"/>
+      <c r="HH27" s="50"/>
+      <c r="HI27" s="50"/>
+      <c r="HJ27" s="50"/>
+      <c r="HK27" s="50"/>
+      <c r="HL27" s="50"/>
+      <c r="HM27" s="50"/>
+      <c r="HN27" s="50"/>
+      <c r="HO27" s="50"/>
+      <c r="HP27" s="50"/>
+      <c r="HQ27" s="50"/>
+      <c r="HR27" s="50"/>
+      <c r="HS27" s="50"/>
+      <c r="HT27" s="50"/>
+      <c r="HU27" s="50"/>
+      <c r="HV27" s="50"/>
+      <c r="HW27" s="50"/>
+      <c r="HX27" s="50"/>
+      <c r="HY27" s="50"/>
+      <c r="HZ27" s="50"/>
+      <c r="IA27" s="50"/>
+      <c r="IB27" s="50"/>
+      <c r="IC27" s="50"/>
+      <c r="ID27" s="50"/>
+      <c r="IE27" s="50"/>
+      <c r="IF27" s="50"/>
+      <c r="IG27" s="50"/>
+      <c r="IH27" s="50"/>
+      <c r="II27" s="50"/>
+      <c r="IJ27" s="50"/>
+      <c r="IK27" s="50"/>
+      <c r="IL27" s="50"/>
+      <c r="IM27" s="50"/>
+      <c r="IN27" s="51"/>
+      <c r="IO27" s="51"/>
+      <c r="IP27" s="51"/>
+      <c r="IQ27" s="51"/>
+      <c r="IR27" s="51"/>
+      <c r="IS27" s="51"/>
+      <c r="IT27" s="51"/>
+      <c r="IU27" s="51"/>
+      <c r="IV27" s="51"/>
+      <c r="IW27" s="52"/>
     </row>
-    <row r="28" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:257" s="53" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="D28" s="92"/>
+      <c r="E28" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="F28" s="42" t="s">
         <v>499</v>
-      </c>
-      <c r="D28" s="95"/>
-      <c r="E28" s="42" t="s">
-        <v>364</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>501</v>
       </c>
       <c r="G28" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H28" s="44"/>
       <c r="I28" s="58"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="46"/>
-      <c r="AA28" s="46"/>
-      <c r="AB28" s="46"/>
-      <c r="AC28" s="46"/>
-      <c r="AD28" s="46"/>
-      <c r="AE28" s="46"/>
-      <c r="AF28" s="46"/>
-      <c r="AG28" s="46"/>
-      <c r="AH28" s="46"/>
-      <c r="AI28" s="46"/>
-      <c r="AJ28" s="46"/>
-      <c r="AK28" s="46"/>
-      <c r="AL28" s="46"/>
-      <c r="AM28" s="46"/>
-      <c r="AN28" s="46"/>
-      <c r="AO28" s="46"/>
-      <c r="AP28" s="46"/>
-      <c r="AQ28" s="46"/>
-      <c r="AR28" s="46"/>
-      <c r="AS28" s="46"/>
-      <c r="AT28" s="46"/>
-      <c r="AU28" s="46"/>
-      <c r="AV28" s="46"/>
-      <c r="AW28" s="46"/>
-      <c r="AX28" s="46"/>
-      <c r="AY28" s="46"/>
-      <c r="AZ28" s="46"/>
-      <c r="BA28" s="46"/>
-      <c r="BB28" s="46"/>
-      <c r="BC28" s="46"/>
-      <c r="BD28" s="46"/>
-      <c r="BE28" s="46"/>
-      <c r="BF28" s="46"/>
-      <c r="BG28" s="46"/>
-      <c r="BH28" s="46"/>
-      <c r="BI28" s="46"/>
-      <c r="BJ28" s="46"/>
-      <c r="BK28" s="46"/>
-      <c r="BL28" s="46"/>
-      <c r="BM28" s="46"/>
-      <c r="BN28" s="46"/>
-      <c r="BO28" s="46"/>
-      <c r="BP28" s="46"/>
-      <c r="BQ28" s="46"/>
-      <c r="BR28" s="46"/>
-      <c r="BS28" s="46"/>
-      <c r="BT28" s="46"/>
-      <c r="BU28" s="46"/>
-      <c r="BV28" s="46"/>
-      <c r="BW28" s="46"/>
-      <c r="BX28" s="46"/>
-      <c r="BY28" s="46"/>
-      <c r="BZ28" s="46"/>
-      <c r="CA28" s="46"/>
-      <c r="CB28" s="46"/>
-      <c r="CC28" s="46"/>
-      <c r="CD28" s="46"/>
-      <c r="CE28" s="46"/>
-      <c r="CF28" s="46"/>
-      <c r="CG28" s="46"/>
-      <c r="CH28" s="46"/>
-      <c r="CI28" s="46"/>
-      <c r="CJ28" s="46"/>
-      <c r="CK28" s="46"/>
-      <c r="CL28" s="46"/>
-      <c r="CM28" s="46"/>
-      <c r="CN28" s="46"/>
-      <c r="CO28" s="46"/>
-      <c r="CP28" s="46"/>
-      <c r="CQ28" s="46"/>
-      <c r="CR28" s="46"/>
-      <c r="CS28" s="46"/>
-      <c r="CT28" s="46"/>
-      <c r="CU28" s="46"/>
-      <c r="CV28" s="46"/>
-      <c r="CW28" s="46"/>
-      <c r="CX28" s="46"/>
-      <c r="CY28" s="46"/>
-      <c r="CZ28" s="46"/>
-      <c r="DA28" s="46"/>
-      <c r="DB28" s="46"/>
-      <c r="DC28" s="46"/>
-      <c r="DD28" s="46"/>
-      <c r="DE28" s="46"/>
-      <c r="DF28" s="46"/>
-      <c r="DG28" s="46"/>
-      <c r="DH28" s="46"/>
-      <c r="DI28" s="46"/>
-      <c r="DJ28" s="46"/>
-      <c r="DK28" s="46"/>
-      <c r="DL28" s="46"/>
-      <c r="DM28" s="46"/>
-      <c r="DN28" s="46"/>
-      <c r="DO28" s="46"/>
-      <c r="DP28" s="46"/>
-      <c r="DQ28" s="46"/>
-      <c r="DR28" s="46"/>
-      <c r="DS28" s="46"/>
-      <c r="DT28" s="46"/>
-      <c r="DU28" s="46"/>
-      <c r="DV28" s="46"/>
-      <c r="DW28" s="46"/>
-      <c r="DX28" s="46"/>
-      <c r="DY28" s="46"/>
-      <c r="DZ28" s="46"/>
-      <c r="EA28" s="46"/>
-      <c r="EB28" s="46"/>
-      <c r="EC28" s="46"/>
-      <c r="ED28" s="46"/>
-      <c r="EE28" s="46"/>
-      <c r="EF28" s="46"/>
-      <c r="EG28" s="46"/>
-      <c r="EH28" s="46"/>
-      <c r="EI28" s="46"/>
-      <c r="EJ28" s="46"/>
-      <c r="EK28" s="46"/>
-      <c r="EL28" s="46"/>
-      <c r="EM28" s="46"/>
-      <c r="EN28" s="46"/>
-      <c r="EO28" s="46"/>
-      <c r="EP28" s="46"/>
-      <c r="EQ28" s="46"/>
-      <c r="ER28" s="46"/>
-      <c r="ES28" s="46"/>
-      <c r="ET28" s="46"/>
-      <c r="EU28" s="46"/>
-      <c r="EV28" s="46"/>
-      <c r="EW28" s="46"/>
-      <c r="EX28" s="46"/>
-      <c r="EY28" s="46"/>
-      <c r="EZ28" s="46"/>
-      <c r="FA28" s="46"/>
-      <c r="FB28" s="46"/>
-      <c r="FC28" s="46"/>
-      <c r="FD28" s="46"/>
-      <c r="FE28" s="46"/>
-      <c r="FF28" s="46"/>
-      <c r="FG28" s="46"/>
-      <c r="FH28" s="46"/>
-      <c r="FI28" s="46"/>
-      <c r="FJ28" s="46"/>
-      <c r="FK28" s="46"/>
-      <c r="FL28" s="46"/>
-      <c r="FM28" s="46"/>
-      <c r="FN28" s="46"/>
-      <c r="FO28" s="46"/>
-      <c r="FP28" s="46"/>
-      <c r="FQ28" s="46"/>
-      <c r="FR28" s="46"/>
-      <c r="FS28" s="46"/>
-      <c r="FT28" s="46"/>
-      <c r="FU28" s="46"/>
-      <c r="FV28" s="46"/>
-      <c r="FW28" s="46"/>
-      <c r="FX28" s="46"/>
-      <c r="FY28" s="46"/>
-      <c r="FZ28" s="46"/>
-      <c r="GA28" s="46"/>
-      <c r="GB28" s="46"/>
-      <c r="GC28" s="46"/>
-      <c r="GD28" s="46"/>
-      <c r="GE28" s="46"/>
-      <c r="GF28" s="46"/>
-      <c r="GG28" s="46"/>
-      <c r="GH28" s="46"/>
-      <c r="GI28" s="46"/>
-      <c r="GJ28" s="46"/>
-      <c r="GK28" s="46"/>
-      <c r="GL28" s="46"/>
-      <c r="GM28" s="46"/>
-      <c r="GN28" s="46"/>
-      <c r="GO28" s="46"/>
-      <c r="GP28" s="46"/>
-      <c r="GQ28" s="46"/>
-      <c r="GR28" s="46"/>
-      <c r="GS28" s="46"/>
-      <c r="GT28" s="46"/>
-      <c r="GU28" s="46"/>
-      <c r="GV28" s="46"/>
-      <c r="GW28" s="46"/>
-      <c r="GX28" s="46"/>
-      <c r="GY28" s="46"/>
-      <c r="GZ28" s="46"/>
-      <c r="HA28" s="46"/>
-      <c r="HB28" s="46"/>
-      <c r="HC28" s="46"/>
-      <c r="HD28" s="46"/>
-      <c r="HE28" s="46"/>
-      <c r="HF28" s="46"/>
-      <c r="HG28" s="46"/>
-      <c r="HH28" s="46"/>
-      <c r="HI28" s="46"/>
-      <c r="HJ28" s="46"/>
-      <c r="HK28" s="46"/>
-      <c r="HL28" s="46"/>
-      <c r="HM28" s="46"/>
-      <c r="HN28" s="46"/>
-      <c r="HO28" s="46"/>
-      <c r="HP28" s="46"/>
-      <c r="HQ28" s="46"/>
-      <c r="HR28" s="46"/>
-      <c r="HS28" s="46"/>
-      <c r="HT28" s="46"/>
-      <c r="HU28" s="46"/>
-      <c r="HV28" s="46"/>
-      <c r="HW28" s="46"/>
-      <c r="HX28" s="46"/>
-      <c r="HY28" s="46"/>
-      <c r="HZ28" s="46"/>
-      <c r="IA28" s="46"/>
-      <c r="IB28" s="46"/>
-      <c r="IC28" s="46"/>
-      <c r="ID28" s="46"/>
-      <c r="IE28" s="46"/>
-      <c r="IF28" s="46"/>
-      <c r="IG28" s="46"/>
-      <c r="IH28" s="46"/>
-      <c r="II28" s="46"/>
-      <c r="IJ28" s="46"/>
-      <c r="IK28" s="46"/>
-      <c r="IL28" s="46"/>
-      <c r="IM28" s="46"/>
-      <c r="IN28" s="39"/>
-      <c r="IO28" s="39"/>
-      <c r="IP28" s="39"/>
-      <c r="IQ28" s="39"/>
-      <c r="IR28" s="39"/>
-      <c r="IS28" s="39"/>
-      <c r="IT28" s="39"/>
-      <c r="IU28" s="39"/>
-      <c r="IV28" s="39"/>
-      <c r="IW28" s="47"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
+      <c r="AF28" s="50"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
+      <c r="AL28" s="50"/>
+      <c r="AM28" s="50"/>
+      <c r="AN28" s="50"/>
+      <c r="AO28" s="50"/>
+      <c r="AP28" s="50"/>
+      <c r="AQ28" s="50"/>
+      <c r="AR28" s="50"/>
+      <c r="AS28" s="50"/>
+      <c r="AT28" s="50"/>
+      <c r="AU28" s="50"/>
+      <c r="AV28" s="50"/>
+      <c r="AW28" s="50"/>
+      <c r="AX28" s="50"/>
+      <c r="AY28" s="50"/>
+      <c r="AZ28" s="50"/>
+      <c r="BA28" s="50"/>
+      <c r="BB28" s="50"/>
+      <c r="BC28" s="50"/>
+      <c r="BD28" s="50"/>
+      <c r="BE28" s="50"/>
+      <c r="BF28" s="50"/>
+      <c r="BG28" s="50"/>
+      <c r="BH28" s="50"/>
+      <c r="BI28" s="50"/>
+      <c r="BJ28" s="50"/>
+      <c r="BK28" s="50"/>
+      <c r="BL28" s="50"/>
+      <c r="BM28" s="50"/>
+      <c r="BN28" s="50"/>
+      <c r="BO28" s="50"/>
+      <c r="BP28" s="50"/>
+      <c r="BQ28" s="50"/>
+      <c r="BR28" s="50"/>
+      <c r="BS28" s="50"/>
+      <c r="BT28" s="50"/>
+      <c r="BU28" s="50"/>
+      <c r="BV28" s="50"/>
+      <c r="BW28" s="50"/>
+      <c r="BX28" s="50"/>
+      <c r="BY28" s="50"/>
+      <c r="BZ28" s="50"/>
+      <c r="CA28" s="50"/>
+      <c r="CB28" s="50"/>
+      <c r="CC28" s="50"/>
+      <c r="CD28" s="50"/>
+      <c r="CE28" s="50"/>
+      <c r="CF28" s="50"/>
+      <c r="CG28" s="50"/>
+      <c r="CH28" s="50"/>
+      <c r="CI28" s="50"/>
+      <c r="CJ28" s="50"/>
+      <c r="CK28" s="50"/>
+      <c r="CL28" s="50"/>
+      <c r="CM28" s="50"/>
+      <c r="CN28" s="50"/>
+      <c r="CO28" s="50"/>
+      <c r="CP28" s="50"/>
+      <c r="CQ28" s="50"/>
+      <c r="CR28" s="50"/>
+      <c r="CS28" s="50"/>
+      <c r="CT28" s="50"/>
+      <c r="CU28" s="50"/>
+      <c r="CV28" s="50"/>
+      <c r="CW28" s="50"/>
+      <c r="CX28" s="50"/>
+      <c r="CY28" s="50"/>
+      <c r="CZ28" s="50"/>
+      <c r="DA28" s="50"/>
+      <c r="DB28" s="50"/>
+      <c r="DC28" s="50"/>
+      <c r="DD28" s="50"/>
+      <c r="DE28" s="50"/>
+      <c r="DF28" s="50"/>
+      <c r="DG28" s="50"/>
+      <c r="DH28" s="50"/>
+      <c r="DI28" s="50"/>
+      <c r="DJ28" s="50"/>
+      <c r="DK28" s="50"/>
+      <c r="DL28" s="50"/>
+      <c r="DM28" s="50"/>
+      <c r="DN28" s="50"/>
+      <c r="DO28" s="50"/>
+      <c r="DP28" s="50"/>
+      <c r="DQ28" s="50"/>
+      <c r="DR28" s="50"/>
+      <c r="DS28" s="50"/>
+      <c r="DT28" s="50"/>
+      <c r="DU28" s="50"/>
+      <c r="DV28" s="50"/>
+      <c r="DW28" s="50"/>
+      <c r="DX28" s="50"/>
+      <c r="DY28" s="50"/>
+      <c r="DZ28" s="50"/>
+      <c r="EA28" s="50"/>
+      <c r="EB28" s="50"/>
+      <c r="EC28" s="50"/>
+      <c r="ED28" s="50"/>
+      <c r="EE28" s="50"/>
+      <c r="EF28" s="50"/>
+      <c r="EG28" s="50"/>
+      <c r="EH28" s="50"/>
+      <c r="EI28" s="50"/>
+      <c r="EJ28" s="50"/>
+      <c r="EK28" s="50"/>
+      <c r="EL28" s="50"/>
+      <c r="EM28" s="50"/>
+      <c r="EN28" s="50"/>
+      <c r="EO28" s="50"/>
+      <c r="EP28" s="50"/>
+      <c r="EQ28" s="50"/>
+      <c r="ER28" s="50"/>
+      <c r="ES28" s="50"/>
+      <c r="ET28" s="50"/>
+      <c r="EU28" s="50"/>
+      <c r="EV28" s="50"/>
+      <c r="EW28" s="50"/>
+      <c r="EX28" s="50"/>
+      <c r="EY28" s="50"/>
+      <c r="EZ28" s="50"/>
+      <c r="FA28" s="50"/>
+      <c r="FB28" s="50"/>
+      <c r="FC28" s="50"/>
+      <c r="FD28" s="50"/>
+      <c r="FE28" s="50"/>
+      <c r="FF28" s="50"/>
+      <c r="FG28" s="50"/>
+      <c r="FH28" s="50"/>
+      <c r="FI28" s="50"/>
+      <c r="FJ28" s="50"/>
+      <c r="FK28" s="50"/>
+      <c r="FL28" s="50"/>
+      <c r="FM28" s="50"/>
+      <c r="FN28" s="50"/>
+      <c r="FO28" s="50"/>
+      <c r="FP28" s="50"/>
+      <c r="FQ28" s="50"/>
+      <c r="FR28" s="50"/>
+      <c r="FS28" s="50"/>
+      <c r="FT28" s="50"/>
+      <c r="FU28" s="50"/>
+      <c r="FV28" s="50"/>
+      <c r="FW28" s="50"/>
+      <c r="FX28" s="50"/>
+      <c r="FY28" s="50"/>
+      <c r="FZ28" s="50"/>
+      <c r="GA28" s="50"/>
+      <c r="GB28" s="50"/>
+      <c r="GC28" s="50"/>
+      <c r="GD28" s="50"/>
+      <c r="GE28" s="50"/>
+      <c r="GF28" s="50"/>
+      <c r="GG28" s="50"/>
+      <c r="GH28" s="50"/>
+      <c r="GI28" s="50"/>
+      <c r="GJ28" s="50"/>
+      <c r="GK28" s="50"/>
+      <c r="GL28" s="50"/>
+      <c r="GM28" s="50"/>
+      <c r="GN28" s="50"/>
+      <c r="GO28" s="50"/>
+      <c r="GP28" s="50"/>
+      <c r="GQ28" s="50"/>
+      <c r="GR28" s="50"/>
+      <c r="GS28" s="50"/>
+      <c r="GT28" s="50"/>
+      <c r="GU28" s="50"/>
+      <c r="GV28" s="50"/>
+      <c r="GW28" s="50"/>
+      <c r="GX28" s="50"/>
+      <c r="GY28" s="50"/>
+      <c r="GZ28" s="50"/>
+      <c r="HA28" s="50"/>
+      <c r="HB28" s="50"/>
+      <c r="HC28" s="50"/>
+      <c r="HD28" s="50"/>
+      <c r="HE28" s="50"/>
+      <c r="HF28" s="50"/>
+      <c r="HG28" s="50"/>
+      <c r="HH28" s="50"/>
+      <c r="HI28" s="50"/>
+      <c r="HJ28" s="50"/>
+      <c r="HK28" s="50"/>
+      <c r="HL28" s="50"/>
+      <c r="HM28" s="50"/>
+      <c r="HN28" s="50"/>
+      <c r="HO28" s="50"/>
+      <c r="HP28" s="50"/>
+      <c r="HQ28" s="50"/>
+      <c r="HR28" s="50"/>
+      <c r="HS28" s="50"/>
+      <c r="HT28" s="50"/>
+      <c r="HU28" s="50"/>
+      <c r="HV28" s="50"/>
+      <c r="HW28" s="50"/>
+      <c r="HX28" s="50"/>
+      <c r="HY28" s="50"/>
+      <c r="HZ28" s="50"/>
+      <c r="IA28" s="50"/>
+      <c r="IB28" s="50"/>
+      <c r="IC28" s="50"/>
+      <c r="ID28" s="50"/>
+      <c r="IE28" s="50"/>
+      <c r="IF28" s="50"/>
+      <c r="IG28" s="50"/>
+      <c r="IH28" s="50"/>
+      <c r="II28" s="50"/>
+      <c r="IJ28" s="50"/>
+      <c r="IK28" s="50"/>
+      <c r="IL28" s="50"/>
+      <c r="IM28" s="50"/>
+      <c r="IN28" s="51"/>
+      <c r="IO28" s="51"/>
+      <c r="IP28" s="51"/>
+      <c r="IQ28" s="51"/>
+      <c r="IR28" s="51"/>
+      <c r="IS28" s="51"/>
+      <c r="IT28" s="51"/>
+      <c r="IU28" s="51"/>
+      <c r="IV28" s="51"/>
+      <c r="IW28" s="52"/>
     </row>
     <row r="29" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A29" s="56" t="s">
@@ -11383,14 +11386,14 @@
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="59" t="s">
-        <v>391</v>
-      </c>
-      <c r="D29" s="61"/>
+        <v>389</v>
+      </c>
+      <c r="D29" s="100"/>
       <c r="E29" s="43" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G29" s="44" t="s">
         <v>251</v>
@@ -11652,14 +11655,14 @@
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="59" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D30" s="61"/>
       <c r="E30" s="43" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G30" s="44" t="s">
         <v>251</v>
@@ -11921,14 +11924,14 @@
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="59" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D31" s="61"/>
       <c r="E31" s="43" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G31" s="44" t="s">
         <v>251</v>
@@ -12190,14 +12193,14 @@
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="43" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G32" s="44" t="s">
         <v>251</v>
@@ -12459,14 +12462,14 @@
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42" t="s">
-        <v>468</v>
-      </c>
-      <c r="D33" s="95"/>
+        <v>466</v>
+      </c>
+      <c r="D33" s="92"/>
       <c r="E33" s="48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>251</v>
@@ -12728,14 +12731,14 @@
       </c>
       <c r="B34" s="42"/>
       <c r="C34" s="42" t="s">
-        <v>469</v>
-      </c>
-      <c r="D34" s="95"/>
+        <v>467</v>
+      </c>
+      <c r="D34" s="92"/>
       <c r="E34" s="48" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G34" s="44" t="s">
         <v>251</v>
@@ -12997,14 +13000,14 @@
       </c>
       <c r="B35" s="60"/>
       <c r="C35" s="42" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D35" s="42"/>
       <c r="E35" s="49" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G35" s="44" t="s">
         <v>251</v>
@@ -13266,14 +13269,14 @@
       </c>
       <c r="B36" s="42"/>
       <c r="C36" s="42" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D36" s="42"/>
       <c r="E36" s="43" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G36" s="44" t="s">
         <v>251</v>
@@ -13537,14 +13540,14 @@
       </c>
       <c r="B37" s="42"/>
       <c r="C37" s="42" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D37" s="42"/>
       <c r="E37" s="43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G37" s="44" t="s">
         <v>251</v>
@@ -13806,14 +13809,14 @@
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="42" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D38" s="42"/>
       <c r="E38" s="43" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G38" s="44" t="s">
         <v>251</v>
@@ -14075,14 +14078,14 @@
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="42" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D39" s="42"/>
       <c r="E39" s="43" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G39" s="44" t="s">
         <v>251</v>
@@ -14344,14 +14347,14 @@
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D40" s="42"/>
       <c r="E40" s="43" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G40" s="44" t="s">
         <v>251</v>
@@ -14613,14 +14616,14 @@
       </c>
       <c r="B41" s="42"/>
       <c r="C41" s="42" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="43" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G41" s="44" t="s">
         <v>251</v>
@@ -14882,14 +14885,14 @@
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="42" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D42" s="42"/>
       <c r="E42" s="43" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G42" s="44" t="s">
         <v>251</v>
@@ -15151,14 +15154,14 @@
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="42" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D43" s="42"/>
       <c r="E43" s="43" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F43" s="42" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G43" s="44" t="s">
         <v>251</v>
@@ -15420,14 +15423,14 @@
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="42" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D44" s="42"/>
       <c r="E44" s="43" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F44" s="42" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G44" s="44" t="s">
         <v>251</v>
@@ -15689,14 +15692,14 @@
       </c>
       <c r="B45" s="42"/>
       <c r="C45" s="42" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D45" s="42"/>
       <c r="E45" s="43" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G45" s="44" t="s">
         <v>251</v>
@@ -15958,14 +15961,14 @@
       </c>
       <c r="B46" s="42"/>
       <c r="C46" s="42" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D46" s="42"/>
       <c r="E46" s="43" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G46" s="44" t="s">
         <v>251</v>
@@ -16227,14 +16230,14 @@
       </c>
       <c r="B47" s="42"/>
       <c r="C47" s="42" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D47" s="42"/>
       <c r="E47" s="48" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G47" s="44" t="s">
         <v>251</v>
@@ -16496,14 +16499,14 @@
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="57" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D48" s="42"/>
       <c r="E48" s="48" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G48" s="44" t="s">
         <v>251</v>
@@ -16772,7 +16775,7 @@
         <v>350</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G49" s="44" t="s">
         <v>251</v>
@@ -17034,14 +17037,14 @@
       </c>
       <c r="B50" s="42"/>
       <c r="C50" s="42" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D50" s="42"/>
       <c r="E50" s="48" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G50" s="44" t="s">
         <v>251</v>
@@ -17301,16 +17304,18 @@
       <c r="A51" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B51" s="42"/>
+      <c r="B51" s="42" t="s">
+        <v>136</v>
+      </c>
       <c r="C51" s="42" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D51" s="42"/>
       <c r="E51" s="48" t="s">
-        <v>512</v>
+        <v>377</v>
       </c>
       <c r="F51" s="42" t="s">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="G51" s="44" t="s">
         <v>251</v>
@@ -17570,16 +17575,18 @@
       <c r="A52" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="42"/>
+      <c r="B52" s="42" t="s">
+        <v>128</v>
+      </c>
       <c r="C52" s="42" t="s">
-        <v>506</v>
+        <v>378</v>
       </c>
       <c r="D52" s="42"/>
       <c r="E52" s="48" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>507</v>
+        <v>130</v>
       </c>
       <c r="G52" s="44" t="s">
         <v>251</v>
@@ -17839,22 +17846,24 @@
       <c r="A53" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="42"/>
+      <c r="B53" s="42" t="s">
+        <v>128</v>
+      </c>
       <c r="C53" s="42" t="s">
-        <v>508</v>
+        <v>372</v>
       </c>
       <c r="D53" s="42"/>
-      <c r="E53" s="43" t="s">
-        <v>372</v>
+      <c r="E53" s="48" t="s">
+        <v>374</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>509</v>
+        <v>130</v>
       </c>
       <c r="G53" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H53" s="44"/>
-      <c r="I53" s="63"/>
+      <c r="I53" s="45"/>
       <c r="J53" s="46"/>
       <c r="K53" s="46"/>
       <c r="L53" s="46"/>
@@ -18104,22 +18113,22 @@
       <c r="IV53" s="39"/>
       <c r="IW53" s="47"/>
     </row>
-    <row r="54" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A54" s="62" t="s">
         <v>122</v>
       </c>
       <c r="B54" s="42" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>510</v>
+        <v>375</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="48" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G54" s="44" t="s">
         <v>251</v>
@@ -18375,7 +18384,7 @@
       <c r="IV54" s="39"/>
       <c r="IW54" s="47"/>
     </row>
-    <row r="55" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A55" s="62" t="s">
         <v>122</v>
       </c>
@@ -18383,11 +18392,11 @@
         <v>128</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="48" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F55" s="42" t="s">
         <v>130</v>
@@ -18646,22 +18655,20 @@
       <c r="IV55" s="39"/>
       <c r="IW55" s="47"/>
     </row>
-    <row r="56" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B56" s="42" t="s">
-        <v>128</v>
-      </c>
+      <c r="B56" s="42"/>
       <c r="C56" s="42" t="s">
-        <v>374</v>
+        <v>509</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="48" t="s">
-        <v>376</v>
+        <v>510</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>130</v>
+        <v>512</v>
       </c>
       <c r="G56" s="44" t="s">
         <v>251</v>
@@ -18921,18 +18928,16 @@
       <c r="A57" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="42" t="s">
-        <v>128</v>
-      </c>
+      <c r="B57" s="42"/>
       <c r="C57" s="42" t="s">
-        <v>377</v>
+        <v>504</v>
       </c>
       <c r="D57" s="42"/>
       <c r="E57" s="48" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>130</v>
+        <v>505</v>
       </c>
       <c r="G57" s="44" t="s">
         <v>251</v>
@@ -19188,28 +19193,26 @@
       <c r="IV57" s="39"/>
       <c r="IW57" s="47"/>
     </row>
-    <row r="58" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A58" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="42" t="s">
-        <v>128</v>
-      </c>
+      <c r="B58" s="42"/>
       <c r="C58" s="42" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
       <c r="D58" s="42"/>
-      <c r="E58" s="48" t="s">
-        <v>375</v>
+      <c r="E58" s="43" t="s">
+        <v>370</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>130</v>
+        <v>507</v>
       </c>
       <c r="G58" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H58" s="44"/>
-      <c r="I58" s="45"/>
+      <c r="I58" s="63"/>
       <c r="J58" s="46"/>
       <c r="K58" s="46"/>
       <c r="L58" s="46"/>
@@ -19459,7 +19462,7 @@
       <c r="IV58" s="39"/>
       <c r="IW58" s="47"/>
     </row>
-    <row r="59" spans="1:257" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A59" s="62" t="s">
         <v>122</v>
       </c>
@@ -19471,7 +19474,7 @@
       </c>
       <c r="D59" s="42"/>
       <c r="E59" s="48" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F59" s="42" t="s">
         <v>109</v>
@@ -19730,22 +19733,22 @@
       <c r="IV59" s="39"/>
       <c r="IW59" s="47"/>
     </row>
-    <row r="60" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="64" t="s">
-        <v>515</v>
+        <v>388</v>
       </c>
       <c r="B60" s="42" t="s">
         <v>131</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>132</v>
+        <v>514</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="48" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F60" s="42" t="s">
-        <v>133</v>
+        <v>515</v>
       </c>
       <c r="G60" s="44" t="s">
         <v>251</v>
@@ -20001,9 +20004,9 @@
       <c r="IV60" s="39"/>
       <c r="IW60" s="47"/>
     </row>
-    <row r="61" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:257" ht="31" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>131</v>
@@ -20016,7 +20019,7 @@
         <v>394</v>
       </c>
       <c r="F61" s="42" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G61" s="44" t="s">
         <v>251</v>
@@ -20272,22 +20275,22 @@
       <c r="IV61" s="39"/>
       <c r="IW61" s="47"/>
     </row>
-    <row r="62" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B62" s="42" t="s">
         <v>131</v>
       </c>
       <c r="C62" s="42" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D62" s="42"/>
       <c r="E62" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F62" s="42" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G62" s="44" t="s">
         <v>251</v>
@@ -20543,28 +20546,28 @@
       <c r="IV62" s="39"/>
       <c r="IW62" s="47"/>
     </row>
-    <row r="63" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:257" ht="60" x14ac:dyDescent="0.15">
       <c r="A63" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B63" s="42" t="s">
-        <v>131</v>
+        <v>380</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D63" s="42"/>
       <c r="E63" s="48" t="s">
-        <v>395</v>
+        <v>531</v>
       </c>
       <c r="F63" s="42" t="s">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="G63" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H63" s="44"/>
-      <c r="I63" s="45"/>
+      <c r="I63" s="58"/>
       <c r="J63" s="46"/>
       <c r="K63" s="46"/>
       <c r="L63" s="46"/>
@@ -20814,22 +20817,22 @@
       <c r="IV63" s="39"/>
       <c r="IW63" s="47"/>
     </row>
-    <row r="64" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B64" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C64" s="42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D64" s="42"/>
       <c r="E64" s="48" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F64" s="42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G64" s="44" t="s">
         <v>251</v>
@@ -21087,20 +21090,20 @@
     </row>
     <row r="65" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B65" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D65" s="42"/>
       <c r="E65" s="48" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F65" s="42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" s="44" t="s">
         <v>251</v>
@@ -21358,20 +21361,20 @@
     </row>
     <row r="66" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B66" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G66" s="44" t="s">
         <v>251</v>
@@ -21629,20 +21632,20 @@
     </row>
     <row r="67" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B67" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C67" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D67" s="42"/>
       <c r="E67" s="48" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F67" s="42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G67" s="44" t="s">
         <v>251</v>
@@ -21900,20 +21903,20 @@
     </row>
     <row r="68" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B68" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D68" s="42"/>
       <c r="E68" s="48" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F68" s="42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G68" s="44" t="s">
         <v>251</v>
@@ -22171,20 +22174,20 @@
     </row>
     <row r="69" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B69" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D69" s="42"/>
       <c r="E69" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G69" s="44" t="s">
         <v>251</v>
@@ -22442,20 +22445,20 @@
     </row>
     <row r="70" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B70" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D70" s="42"/>
       <c r="E70" s="48" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F70" s="42" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G70" s="44" t="s">
         <v>251</v>
@@ -22713,20 +22716,20 @@
     </row>
     <row r="71" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B71" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D71" s="42"/>
       <c r="E71" s="48" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F71" s="42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G71" s="44" t="s">
         <v>251</v>
@@ -22984,20 +22987,20 @@
     </row>
     <row r="72" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B72" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D72" s="42"/>
       <c r="E72" s="48" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G72" s="44" t="s">
         <v>251</v>
@@ -23255,20 +23258,20 @@
     </row>
     <row r="73" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B73" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C73" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D73" s="42"/>
       <c r="E73" s="48" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F73" s="42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G73" s="44" t="s">
         <v>251</v>
@@ -23525,27 +23528,29 @@
       <c r="IW73" s="47"/>
     </row>
     <row r="74" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A74" s="64" t="s">
-        <v>390</v>
-      </c>
-      <c r="B74" s="42" t="s">
-        <v>382</v>
-      </c>
+      <c r="A74" s="41" t="s">
+        <v>459</v>
+      </c>
+      <c r="B74" s="42"/>
       <c r="C74" s="42" t="s">
-        <v>532</v>
-      </c>
-      <c r="D74" s="42"/>
+        <v>152</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>369</v>
+      </c>
       <c r="E74" s="48" t="s">
-        <v>543</v>
+        <v>430</v>
       </c>
       <c r="F74" s="42" t="s">
-        <v>90</v>
+        <v>418</v>
       </c>
       <c r="G74" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H74" s="44"/>
-      <c r="I74" s="58"/>
+      <c r="I74" s="45" t="s">
+        <v>431</v>
+      </c>
       <c r="J74" s="46"/>
       <c r="K74" s="46"/>
       <c r="L74" s="46"/>
@@ -23795,30 +23800,28 @@
       <c r="IV74" s="39"/>
       <c r="IW74" s="47"/>
     </row>
-    <row r="75" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A75" s="41" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B75" s="42"/>
       <c r="C75" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="E75" s="48" t="s">
-        <v>432</v>
+        <v>59</v>
+      </c>
+      <c r="D75" s="42"/>
+      <c r="E75" s="43" t="s">
+        <v>395</v>
       </c>
       <c r="F75" s="42" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G75" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H75" s="44"/>
-      <c r="I75" s="45" t="s">
-        <v>433</v>
-      </c>
+      <c r="H75" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I75" s="45"/>
       <c r="J75" s="46"/>
       <c r="K75" s="46"/>
       <c r="L75" s="46"/>
@@ -24068,27 +24071,25 @@
       <c r="IV75" s="39"/>
       <c r="IW75" s="47"/>
     </row>
-    <row r="76" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:257" ht="75" x14ac:dyDescent="0.15">
       <c r="A76" s="41" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B76" s="42"/>
-      <c r="C76" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D76" s="96"/>
-      <c r="E76" s="43" t="s">
-        <v>397</v>
+      <c r="C76" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="42"/>
+      <c r="E76" s="48" t="s">
+        <v>351</v>
       </c>
       <c r="F76" s="42" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="G76" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H76" s="44" t="s">
-        <v>251</v>
-      </c>
+      <c r="H76" s="44"/>
       <c r="I76" s="45"/>
       <c r="J76" s="46"/>
       <c r="K76" s="46"/>
@@ -24339,20 +24340,20 @@
       <c r="IV76" s="39"/>
       <c r="IW76" s="47"/>
     </row>
-    <row r="77" spans="1:257" ht="75" x14ac:dyDescent="0.15">
-      <c r="A77" s="41" t="s">
-        <v>461</v>
+    <row r="77" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A77" s="62" t="s">
+        <v>459</v>
       </c>
       <c r="B77" s="42"/>
-      <c r="C77" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="D77" s="96"/>
-      <c r="E77" s="48" t="s">
-        <v>351</v>
+      <c r="C77" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="D77" s="42"/>
+      <c r="E77" s="43" t="s">
+        <v>545</v>
       </c>
       <c r="F77" s="42" t="s">
-        <v>401</v>
+        <v>96</v>
       </c>
       <c r="G77" s="44" t="s">
         <v>251</v>
@@ -24608,26 +24609,26 @@
       <c r="IV77" s="39"/>
       <c r="IW77" s="47"/>
     </row>
-    <row r="78" spans="1:257" ht="34" x14ac:dyDescent="0.15">
-      <c r="A78" s="99" t="s">
-        <v>465</v>
-      </c>
-      <c r="B78" s="100"/>
-      <c r="C78" s="100" t="s">
-        <v>76</v>
-      </c>
-      <c r="D78" s="101"/>
-      <c r="E78" s="100" t="s">
-        <v>464</v>
-      </c>
-      <c r="F78" s="100" t="s">
-        <v>444</v>
+    <row r="78" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A78" s="62" t="s">
+        <v>459</v>
+      </c>
+      <c r="B78" s="42"/>
+      <c r="C78" s="42" t="s">
+        <v>353</v>
+      </c>
+      <c r="D78" s="93"/>
+      <c r="E78" s="43" t="s">
+        <v>544</v>
+      </c>
+      <c r="F78" s="42" t="s">
+        <v>95</v>
       </c>
       <c r="G78" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H78" s="99"/>
-      <c r="I78" s="100"/>
+      <c r="H78" s="44"/>
+      <c r="I78" s="45"/>
       <c r="J78" s="46"/>
       <c r="K78" s="46"/>
       <c r="L78" s="46"/>
@@ -24877,22 +24878,22 @@
       <c r="IV78" s="39"/>
       <c r="IW78" s="47"/>
     </row>
-    <row r="79" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B79" s="42"/>
       <c r="C79" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="D79" s="42" t="s">
-        <v>365</v>
+      <c r="D79" s="93" t="s">
+        <v>363</v>
       </c>
       <c r="E79" s="48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F79" s="42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G79" s="44" t="s">
         <v>251</v>
@@ -25148,22 +25149,22 @@
       <c r="IV79" s="39"/>
       <c r="IW79" s="47"/>
     </row>
-    <row r="80" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B80" s="42"/>
       <c r="C80" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="D80" s="42" t="s">
-        <v>366</v>
+      <c r="D80" s="93" t="s">
+        <v>364</v>
       </c>
       <c r="E80" s="48" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F80" s="42" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G80" s="44" t="s">
         <v>251</v>
@@ -25421,20 +25422,20 @@
     </row>
     <row r="81" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A81" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B81" s="42"/>
       <c r="C81" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D81" s="42" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E81" s="48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F81" s="42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G81" s="44" t="s">
         <v>251</v>
@@ -25690,22 +25691,22 @@
       <c r="IV81" s="39"/>
       <c r="IW81" s="47"/>
     </row>
-    <row r="82" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B82" s="42"/>
       <c r="C82" s="57" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D82" s="42" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E82" s="48" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F82" s="42" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G82" s="44" t="s">
         <v>251</v>
@@ -25963,20 +25964,20 @@
     </row>
     <row r="83" spans="1:257" ht="75" x14ac:dyDescent="0.15">
       <c r="A83" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B83" s="42"/>
       <c r="C83" s="59" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D83" s="42" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E83" s="48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F83" s="42" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G83" s="44" t="s">
         <v>251</v>
@@ -26234,18 +26235,18 @@
     </row>
     <row r="84" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A84" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B84" s="42"/>
       <c r="C84" s="59" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D84" s="42"/>
       <c r="E84" s="48" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F84" s="42" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G84" s="44" t="s">
         <v>251</v>
@@ -26503,18 +26504,18 @@
     </row>
     <row r="85" spans="1:257" ht="75" x14ac:dyDescent="0.15">
       <c r="A85" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B85" s="60"/>
       <c r="C85" s="42" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D85" s="42"/>
       <c r="E85" s="49" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F85" s="42" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G85" s="44" t="s">
         <v>251</v>
@@ -26770,26 +26771,26 @@
       <c r="IV85" s="39"/>
       <c r="IW85" s="47"/>
     </row>
-    <row r="86" spans="1:257" ht="45" x14ac:dyDescent="0.15">
-      <c r="A86" s="56" t="s">
-        <v>465</v>
-      </c>
-      <c r="B86" s="42"/>
-      <c r="C86" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="D86" s="42"/>
-      <c r="E86" s="43" t="s">
-        <v>484</v>
-      </c>
-      <c r="F86" s="42" t="s">
-        <v>445</v>
+    <row r="86" spans="1:257" ht="34" x14ac:dyDescent="0.15">
+      <c r="A86" s="95" t="s">
+        <v>463</v>
+      </c>
+      <c r="B86" s="96"/>
+      <c r="C86" s="96" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" s="96"/>
+      <c r="E86" s="96" t="s">
+        <v>462</v>
+      </c>
+      <c r="F86" s="96" t="s">
+        <v>442</v>
       </c>
       <c r="G86" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H86" s="44"/>
-      <c r="I86" s="58"/>
+      <c r="H86" s="95"/>
+      <c r="I86" s="96"/>
       <c r="J86" s="46"/>
       <c r="K86" s="46"/>
       <c r="L86" s="46"/>
@@ -27039,20 +27040,20 @@
       <c r="IV86" s="39"/>
       <c r="IW86" s="47"/>
     </row>
-    <row r="87" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A87" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B87" s="42"/>
       <c r="C87" s="42" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="43" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F87" s="42" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G87" s="44" t="s">
         <v>251</v>
@@ -27308,28 +27309,26 @@
       <c r="IV87" s="39"/>
       <c r="IW87" s="47"/>
     </row>
-    <row r="88" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A88" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B88" s="42"/>
       <c r="C88" s="42" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="43" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F88" s="42" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G88" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H88" s="44"/>
-      <c r="I88" s="58" t="s">
-        <v>78</v>
-      </c>
+      <c r="I88" s="58"/>
       <c r="J88" s="46"/>
       <c r="K88" s="46"/>
       <c r="L88" s="46"/>
@@ -27579,26 +27578,28 @@
       <c r="IV88" s="39"/>
       <c r="IW88" s="47"/>
     </row>
-    <row r="89" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:257" ht="60" x14ac:dyDescent="0.15">
       <c r="A89" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B89" s="42"/>
       <c r="C89" s="42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D89" s="42"/>
       <c r="E89" s="43" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F89" s="42" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G89" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H89" s="44"/>
-      <c r="I89" s="58"/>
+      <c r="I89" s="58" t="s">
+        <v>78</v>
+      </c>
       <c r="J89" s="46"/>
       <c r="K89" s="46"/>
       <c r="L89" s="46"/>
@@ -27850,18 +27851,18 @@
     </row>
     <row r="90" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A90" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B90" s="42"/>
       <c r="C90" s="42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D90" s="42"/>
       <c r="E90" s="43" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F90" s="42" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G90" s="44" t="s">
         <v>251</v>
@@ -28119,18 +28120,18 @@
     </row>
     <row r="91" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A91" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B91" s="42"/>
       <c r="C91" s="42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D91" s="42"/>
       <c r="E91" s="43" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F91" s="42" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G91" s="44" t="s">
         <v>251</v>
@@ -28388,18 +28389,18 @@
     </row>
     <row r="92" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A92" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B92" s="42"/>
       <c r="C92" s="42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D92" s="42"/>
       <c r="E92" s="43" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F92" s="42" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G92" s="44" t="s">
         <v>251</v>
@@ -28657,18 +28658,18 @@
     </row>
     <row r="93" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A93" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B93" s="42"/>
       <c r="C93" s="42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D93" s="42"/>
       <c r="E93" s="43" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F93" s="42" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G93" s="44" t="s">
         <v>251</v>
@@ -28926,18 +28927,18 @@
     </row>
     <row r="94" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A94" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B94" s="42"/>
       <c r="C94" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D94" s="42"/>
       <c r="E94" s="43" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F94" s="42" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G94" s="44" t="s">
         <v>251</v>
@@ -29195,18 +29196,18 @@
     </row>
     <row r="95" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A95" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B95" s="42"/>
       <c r="C95" s="42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D95" s="42"/>
       <c r="E95" s="43" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F95" s="42" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G95" s="44" t="s">
         <v>251</v>
@@ -29464,18 +29465,18 @@
     </row>
     <row r="96" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A96" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B96" s="42"/>
       <c r="C96" s="42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D96" s="42"/>
       <c r="E96" s="43" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F96" s="42" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G96" s="44" t="s">
         <v>251</v>
@@ -29733,18 +29734,18 @@
     </row>
     <row r="97" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A97" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B97" s="42"/>
       <c r="C97" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D97" s="42"/>
       <c r="E97" s="43" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F97" s="42" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G97" s="44" t="s">
         <v>251</v>
@@ -30002,18 +30003,18 @@
     </row>
     <row r="98" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A98" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B98" s="42"/>
       <c r="C98" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D98" s="42"/>
       <c r="E98" s="43" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F98" s="42" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G98" s="44" t="s">
         <v>251</v>
@@ -30271,18 +30272,18 @@
     </row>
     <row r="99" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A99" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B99" s="42"/>
       <c r="C99" s="42" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D99" s="42"/>
-      <c r="E99" s="48" t="s">
-        <v>498</v>
+      <c r="E99" s="43" t="s">
+        <v>495</v>
       </c>
       <c r="F99" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G99" s="44" t="s">
         <v>251</v>
@@ -30540,18 +30541,18 @@
     </row>
     <row r="100" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A100" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B100" s="42"/>
       <c r="C100" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="D100" s="97"/>
+        <v>75</v>
+      </c>
+      <c r="D100" s="42"/>
       <c r="E100" s="48" t="s">
-        <v>363</v>
+        <v>496</v>
       </c>
       <c r="F100" s="42" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="G100" s="44" t="s">
         <v>251</v>
@@ -30807,20 +30808,20 @@
       <c r="IV100" s="39"/>
       <c r="IW100" s="47"/>
     </row>
-    <row r="101" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A101" s="56" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B101" s="42"/>
       <c r="C101" s="42" t="s">
-        <v>364</v>
-      </c>
-      <c r="D101" s="97"/>
+        <v>361</v>
+      </c>
+      <c r="D101" s="94"/>
       <c r="E101" s="48" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F101" s="42" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G101" s="44" t="s">
         <v>251</v>
@@ -31077,25 +31078,25 @@
       <c r="IW101" s="47"/>
     </row>
     <row r="102" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A102" s="62" t="s">
-        <v>504</v>
+      <c r="A102" s="56" t="s">
+        <v>463</v>
       </c>
       <c r="B102" s="42"/>
       <c r="C102" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="D102" s="42"/>
+        <v>362</v>
+      </c>
+      <c r="D102" s="94"/>
       <c r="E102" s="48" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="F102" s="42" t="s">
-        <v>505</v>
+        <v>423</v>
       </c>
       <c r="G102" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H102" s="44"/>
-      <c r="I102" s="63"/>
+      <c r="I102" s="58"/>
       <c r="J102" s="46"/>
       <c r="K102" s="46"/>
       <c r="L102" s="46"/>
@@ -31347,24 +31348,24 @@
     </row>
     <row r="103" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A103" s="62" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B103" s="42"/>
       <c r="C103" s="42" t="s">
-        <v>127</v>
+        <v>385</v>
       </c>
       <c r="D103" s="42"/>
       <c r="E103" s="48" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F103" s="42" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G103" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H103" s="44"/>
-      <c r="I103" s="45"/>
+      <c r="I103" s="63"/>
       <c r="J103" s="46"/>
       <c r="K103" s="46"/>
       <c r="L103" s="46"/>
@@ -31616,24 +31617,24 @@
     </row>
     <row r="104" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A104" s="62" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B104" s="42"/>
       <c r="C104" s="42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D104" s="42"/>
-      <c r="E104" s="43" t="s">
-        <v>372</v>
+      <c r="E104" s="48" t="s">
+        <v>368</v>
       </c>
       <c r="F104" s="42" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G104" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H104" s="44"/>
-      <c r="I104" s="63"/>
+      <c r="I104" s="45"/>
       <c r="J104" s="46"/>
       <c r="K104" s="46"/>
       <c r="L104" s="46"/>
@@ -31883,28 +31884,26 @@
       <c r="IV104" s="39"/>
       <c r="IW104" s="47"/>
     </row>
-    <row r="105" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A105" s="62" t="s">
-        <v>504</v>
-      </c>
-      <c r="B105" s="42" t="s">
-        <v>136</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="B105" s="42"/>
       <c r="C105" s="42" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D105" s="42"/>
-      <c r="E105" s="48" t="s">
-        <v>379</v>
+      <c r="E105" s="43" t="s">
+        <v>370</v>
       </c>
       <c r="F105" s="42" t="s">
-        <v>138</v>
+        <v>507</v>
       </c>
       <c r="G105" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H105" s="44"/>
-      <c r="I105" s="45"/>
+      <c r="I105" s="63"/>
       <c r="J105" s="46"/>
       <c r="K105" s="46"/>
       <c r="L105" s="46"/>
@@ -32154,28 +32153,28 @@
       <c r="IV105" s="39"/>
       <c r="IW105" s="47"/>
     </row>
-    <row r="106" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A106" s="65" t="s">
-        <v>114</v>
+    <row r="106" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A106" s="62" t="s">
+        <v>502</v>
       </c>
       <c r="B106" s="42" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C106" s="42" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D106" s="42"/>
-      <c r="E106" s="43" t="s">
-        <v>338</v>
+      <c r="E106" s="48" t="s">
+        <v>377</v>
       </c>
       <c r="F106" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G106" s="54" t="s">
-        <v>268</v>
+        <v>138</v>
+      </c>
+      <c r="G106" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="H106" s="44"/>
-      <c r="I106" s="63"/>
+      <c r="I106" s="45"/>
       <c r="J106" s="46"/>
       <c r="K106" s="46"/>
       <c r="L106" s="46"/>
@@ -32425,28 +32424,28 @@
       <c r="IV106" s="39"/>
       <c r="IW106" s="47"/>
     </row>
-    <row r="107" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A107" s="65" t="s">
-        <v>114</v>
+    <row r="107" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+      <c r="A107" s="64" t="s">
+        <v>513</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D107" s="42"/>
-      <c r="E107" s="43" t="s">
-        <v>389</v>
+      <c r="E107" s="48" t="s">
+        <v>366</v>
       </c>
       <c r="F107" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="G107" s="54" t="s">
-        <v>268</v>
+        <v>133</v>
+      </c>
+      <c r="G107" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="H107" s="44"/>
-      <c r="I107" s="63"/>
+      <c r="I107" s="45"/>
       <c r="J107" s="46"/>
       <c r="K107" s="46"/>
       <c r="L107" s="46"/>
@@ -32696,28 +32695,28 @@
       <c r="IV107" s="39"/>
       <c r="IW107" s="47"/>
     </row>
-    <row r="108" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A108" s="66" t="s">
-        <v>279</v>
-      </c>
-      <c r="B108" s="60" t="s">
-        <v>47</v>
+    <row r="108" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A108" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="42" t="s">
+        <v>118</v>
       </c>
       <c r="C108" s="42" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="D108" s="42"/>
-      <c r="E108" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F108" s="42"/>
+      <c r="E108" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="F108" s="42" t="s">
+        <v>120</v>
+      </c>
       <c r="G108" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H108" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="I108" s="45"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="63"/>
       <c r="J108" s="46"/>
       <c r="K108" s="46"/>
       <c r="L108" s="46"/>
@@ -32968,27 +32967,27 @@
       <c r="IW108" s="47"/>
     </row>
     <row r="109" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A109" s="66" t="s">
-        <v>279</v>
-      </c>
-      <c r="B109" s="60" t="s">
-        <v>48</v>
+      <c r="A109" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="42" t="s">
+        <v>115</v>
       </c>
       <c r="C109" s="42" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="D109" s="42"/>
-      <c r="E109" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F109" s="42"/>
+      <c r="E109" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="F109" s="42" t="s">
+        <v>117</v>
+      </c>
       <c r="G109" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H109" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="I109" s="45"/>
+      <c r="H109" s="44"/>
+      <c r="I109" s="63"/>
       <c r="J109" s="46"/>
       <c r="K109" s="46"/>
       <c r="L109" s="46"/>
@@ -33242,11 +33241,11 @@
       <c r="A110" s="66" t="s">
         <v>279</v>
       </c>
-      <c r="B110" s="42" t="s">
-        <v>51</v>
+      <c r="B110" s="60" t="s">
+        <v>47</v>
       </c>
       <c r="C110" s="42" t="s">
-        <v>349</v>
+        <v>257</v>
       </c>
       <c r="D110" s="42"/>
       <c r="E110" s="42" t="s">
@@ -33513,11 +33512,11 @@
       <c r="A111" s="66" t="s">
         <v>279</v>
       </c>
-      <c r="B111" s="42" t="s">
-        <v>50</v>
+      <c r="B111" s="60" t="s">
+        <v>48</v>
       </c>
       <c r="C111" s="42" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D111" s="42"/>
       <c r="E111" s="42" t="s">
@@ -33784,11 +33783,11 @@
       <c r="A112" s="66" t="s">
         <v>279</v>
       </c>
-      <c r="B112" s="60" t="s">
-        <v>49</v>
+      <c r="B112" s="42" t="s">
+        <v>51</v>
       </c>
       <c r="C112" s="42" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="D112" s="42"/>
       <c r="E112" s="42" t="s">
@@ -34052,27 +34051,25 @@
       <c r="IW112" s="47"/>
     </row>
     <row r="113" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A113" s="68" t="s">
-        <v>253</v>
+      <c r="A113" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="B113" s="42" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C113" s="42" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="D113" s="42"/>
       <c r="E113" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="F113" s="42" t="s">
-        <v>20</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F113" s="42"/>
       <c r="G113" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H113" s="44" t="s">
-        <v>251</v>
+      <c r="H113" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I113" s="45"/>
       <c r="J113" s="46"/>
@@ -34325,27 +34322,25 @@
       <c r="IW113" s="47"/>
     </row>
     <row r="114" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A114" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="B114" s="42" t="s">
-        <v>21</v>
+      <c r="A114" s="66" t="s">
+        <v>279</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>49</v>
       </c>
       <c r="C114" s="42" t="s">
-        <v>22</v>
+        <v>259</v>
       </c>
       <c r="D114" s="42"/>
       <c r="E114" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="F114" s="42" t="s">
-        <v>23</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F114" s="42"/>
       <c r="G114" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H114" s="44" t="s">
-        <v>251</v>
+      <c r="H114" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I114" s="45"/>
       <c r="J114" s="46"/>
@@ -34602,17 +34597,17 @@
         <v>253</v>
       </c>
       <c r="B115" s="42" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C115" s="42" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D115" s="42"/>
       <c r="E115" s="42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F115" s="42" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>268</v>
@@ -34874,18 +34869,18 @@
       <c r="A116" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="60" t="s">
-        <v>45</v>
+      <c r="B116" s="42" t="s">
+        <v>21</v>
       </c>
       <c r="C116" s="42" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D116" s="42"/>
       <c r="E116" s="42" t="s">
-        <v>342</v>
+        <v>242</v>
       </c>
       <c r="F116" s="42" t="s">
-        <v>322</v>
+        <v>23</v>
       </c>
       <c r="G116" s="54" t="s">
         <v>268</v>
@@ -35147,18 +35142,18 @@
       <c r="A117" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B117" s="60" t="s">
-        <v>43</v>
+      <c r="B117" s="42" t="s">
+        <v>15</v>
       </c>
       <c r="C117" s="42" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D117" s="42"/>
       <c r="E117" s="42" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F117" s="42" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="G117" s="54" t="s">
         <v>268</v>
@@ -35420,18 +35415,18 @@
       <c r="A118" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B118" s="42" t="s">
-        <v>51</v>
+      <c r="B118" s="60" t="s">
+        <v>45</v>
       </c>
       <c r="C118" s="42" t="s">
-        <v>323</v>
+        <v>46</v>
       </c>
       <c r="D118" s="42"/>
       <c r="E118" s="42" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="F118" s="42" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G118" s="54" t="s">
         <v>268</v>
@@ -35689,22 +35684,22 @@
       <c r="IV118" s="39"/>
       <c r="IW118" s="47"/>
     </row>
-    <row r="119" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A119" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B119" s="42" t="s">
-        <v>9</v>
+      <c r="B119" s="60" t="s">
+        <v>43</v>
       </c>
       <c r="C119" s="42" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D119" s="42"/>
       <c r="E119" s="42" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F119" s="42" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="G119" s="54" t="s">
         <v>268</v>
@@ -35962,22 +35957,22 @@
       <c r="IV119" s="39"/>
       <c r="IW119" s="47"/>
     </row>
-    <row r="120" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A120" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B120" s="42" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C120" s="42" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
       <c r="D120" s="42"/>
       <c r="E120" s="42" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="F120" s="42" t="s">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="G120" s="54" t="s">
         <v>268</v>
@@ -36224,23 +36219,34 @@
       <c r="IK120" s="46"/>
       <c r="IL120" s="46"/>
       <c r="IM120" s="46"/>
+      <c r="IN120" s="39"/>
+      <c r="IO120" s="39"/>
+      <c r="IP120" s="39"/>
+      <c r="IQ120" s="39"/>
+      <c r="IR120" s="39"/>
+      <c r="IS120" s="39"/>
+      <c r="IT120" s="39"/>
+      <c r="IU120" s="39"/>
+      <c r="IV120" s="39"/>
       <c r="IW120" s="47"/>
     </row>
-    <row r="121" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A121" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B121" s="60" t="s">
-        <v>41</v>
+      <c r="B121" s="42" t="s">
+        <v>9</v>
       </c>
       <c r="C121" s="42" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D121" s="42"/>
       <c r="E121" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F121" s="42"/>
+        <v>237</v>
+      </c>
+      <c r="F121" s="42" t="s">
+        <v>292</v>
+      </c>
       <c r="G121" s="54" t="s">
         <v>268</v>
       </c>
@@ -36486,23 +36492,34 @@
       <c r="IK121" s="46"/>
       <c r="IL121" s="46"/>
       <c r="IM121" s="46"/>
+      <c r="IN121" s="39"/>
+      <c r="IO121" s="39"/>
+      <c r="IP121" s="39"/>
+      <c r="IQ121" s="39"/>
+      <c r="IR121" s="39"/>
+      <c r="IS121" s="39"/>
+      <c r="IT121" s="39"/>
+      <c r="IU121" s="39"/>
+      <c r="IV121" s="39"/>
       <c r="IW121" s="47"/>
     </row>
     <row r="122" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A122" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B122" s="60" t="s">
-        <v>39</v>
+      <c r="B122" s="42" t="s">
+        <v>6</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="F122" s="42"/>
+        <v>236</v>
+      </c>
+      <c r="F122" s="42" t="s">
+        <v>8</v>
+      </c>
       <c r="G122" s="54" t="s">
         <v>268</v>
       </c>
@@ -36750,23 +36767,21 @@
       <c r="IM122" s="46"/>
       <c r="IW122" s="47"/>
     </row>
-    <row r="123" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A123" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B123" s="60" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C123" s="42" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D123" s="42"/>
       <c r="E123" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="F123" s="42" t="s">
-        <v>293</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F123" s="42"/>
       <c r="G123" s="54" t="s">
         <v>268</v>
       </c>
@@ -37014,23 +37029,21 @@
       <c r="IM123" s="46"/>
       <c r="IW123" s="47"/>
     </row>
-    <row r="124" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A124" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B124" s="42" t="s">
-        <v>2</v>
+      <c r="B124" s="60" t="s">
+        <v>39</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D124" s="42"/>
       <c r="E124" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="F124" s="42" t="s">
-        <v>295</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F124" s="42"/>
       <c r="G124" s="54" t="s">
         <v>268</v>
       </c>
@@ -37039,300 +37052,261 @@
       </c>
       <c r="I124" s="45"/>
       <c r="J124" s="46"/>
-      <c r="K124" s="69"/>
-      <c r="L124" s="69"/>
-      <c r="M124" s="69"/>
-      <c r="N124" s="69"/>
-      <c r="O124" s="69"/>
-      <c r="P124" s="69"/>
-      <c r="Q124" s="69"/>
-      <c r="R124" s="69"/>
-      <c r="S124" s="69"/>
-      <c r="T124" s="69"/>
-      <c r="U124" s="69"/>
-      <c r="V124" s="69"/>
-      <c r="W124" s="69"/>
-      <c r="X124" s="69"/>
-      <c r="Y124" s="69"/>
-      <c r="Z124" s="69"/>
-      <c r="AA124" s="69"/>
-      <c r="AB124" s="69"/>
-      <c r="AC124" s="69"/>
-      <c r="AD124" s="69"/>
-      <c r="AE124" s="69"/>
-      <c r="AF124" s="69"/>
-      <c r="AG124" s="69"/>
-      <c r="AH124" s="69"/>
-      <c r="AI124" s="69"/>
-      <c r="AJ124" s="69"/>
-      <c r="AK124" s="69"/>
-      <c r="AL124" s="69"/>
-      <c r="AM124" s="69"/>
-      <c r="AN124" s="69"/>
-      <c r="AO124" s="69"/>
-      <c r="AP124" s="69"/>
-      <c r="AQ124" s="69"/>
-      <c r="AR124" s="69"/>
-      <c r="AS124" s="69"/>
-      <c r="AT124" s="69"/>
-      <c r="AU124" s="69"/>
-      <c r="AV124" s="69"/>
-      <c r="AW124" s="69"/>
-      <c r="AX124" s="69"/>
-      <c r="AY124" s="69"/>
-      <c r="AZ124" s="69"/>
-      <c r="BA124" s="69"/>
-      <c r="BB124" s="69"/>
-      <c r="BC124" s="69"/>
-      <c r="BD124" s="69"/>
-      <c r="BE124" s="69"/>
-      <c r="BF124" s="69"/>
-      <c r="BG124" s="69"/>
-      <c r="BH124" s="69"/>
-      <c r="BI124" s="69"/>
-      <c r="BJ124" s="69"/>
-      <c r="BK124" s="69"/>
-      <c r="BL124" s="69"/>
-      <c r="BM124" s="69"/>
-      <c r="BN124" s="69"/>
-      <c r="BO124" s="69"/>
-      <c r="BP124" s="69"/>
-      <c r="BQ124" s="69"/>
-      <c r="BR124" s="69"/>
-      <c r="BS124" s="69"/>
-      <c r="BT124" s="69"/>
-      <c r="BU124" s="69"/>
-      <c r="BV124" s="69"/>
-      <c r="BW124" s="69"/>
-      <c r="BX124" s="69"/>
-      <c r="BY124" s="69"/>
-      <c r="BZ124" s="69"/>
-      <c r="CA124" s="69"/>
-      <c r="CB124" s="69"/>
-      <c r="CC124" s="69"/>
-      <c r="CD124" s="69"/>
-      <c r="CE124" s="69"/>
-      <c r="CF124" s="69"/>
-      <c r="CG124" s="69"/>
-      <c r="CH124" s="69"/>
-      <c r="CI124" s="69"/>
-      <c r="CJ124" s="69"/>
-      <c r="CK124" s="69"/>
-      <c r="CL124" s="69"/>
-      <c r="CM124" s="69"/>
-      <c r="CN124" s="69"/>
-      <c r="CO124" s="69"/>
-      <c r="CP124" s="69"/>
-      <c r="CQ124" s="69"/>
-      <c r="CR124" s="69"/>
-      <c r="CS124" s="69"/>
-      <c r="CT124" s="69"/>
-      <c r="CU124" s="69"/>
-      <c r="CV124" s="69"/>
-      <c r="CW124" s="69"/>
-      <c r="CX124" s="69"/>
-      <c r="CY124" s="69"/>
-      <c r="CZ124" s="69"/>
-      <c r="DA124" s="69"/>
-      <c r="DB124" s="69"/>
-      <c r="DC124" s="69"/>
-      <c r="DD124" s="69"/>
-      <c r="DE124" s="69"/>
-      <c r="DF124" s="69"/>
-      <c r="DG124" s="69"/>
-      <c r="DH124" s="69"/>
-      <c r="DI124" s="69"/>
-      <c r="DJ124" s="69"/>
-      <c r="DK124" s="69"/>
-      <c r="DL124" s="69"/>
-      <c r="DM124" s="69"/>
-      <c r="DN124" s="69"/>
-      <c r="DO124" s="69"/>
-      <c r="DP124" s="69"/>
-      <c r="DQ124" s="69"/>
-      <c r="DR124" s="69"/>
-      <c r="DS124" s="69"/>
-      <c r="DT124" s="69"/>
-      <c r="DU124" s="69"/>
-      <c r="DV124" s="69"/>
-      <c r="DW124" s="69"/>
-      <c r="DX124" s="69"/>
-      <c r="DY124" s="69"/>
-      <c r="DZ124" s="69"/>
-      <c r="EA124" s="69"/>
-      <c r="EB124" s="69"/>
-      <c r="EC124" s="69"/>
-      <c r="ED124" s="69"/>
-      <c r="EE124" s="69"/>
-      <c r="EF124" s="69"/>
-      <c r="EG124" s="69"/>
-      <c r="EH124" s="69"/>
-      <c r="EI124" s="69"/>
-      <c r="EJ124" s="69"/>
-      <c r="EK124" s="69"/>
-      <c r="EL124" s="69"/>
-      <c r="EM124" s="69"/>
-      <c r="EN124" s="69"/>
-      <c r="EO124" s="69"/>
-      <c r="EP124" s="69"/>
-      <c r="EQ124" s="69"/>
-      <c r="ER124" s="69"/>
-      <c r="ES124" s="69"/>
-      <c r="ET124" s="69"/>
-      <c r="EU124" s="69"/>
-      <c r="EV124" s="69"/>
-      <c r="EW124" s="69"/>
-      <c r="EX124" s="69"/>
-      <c r="EY124" s="69"/>
-      <c r="EZ124" s="69"/>
-      <c r="FA124" s="69"/>
-      <c r="FB124" s="69"/>
-      <c r="FC124" s="69"/>
-      <c r="FD124" s="69"/>
-      <c r="FE124" s="69"/>
-      <c r="FF124" s="69"/>
-      <c r="FG124" s="69"/>
-      <c r="FH124" s="69"/>
-      <c r="FI124" s="69"/>
-      <c r="FJ124" s="69"/>
-      <c r="FK124" s="69"/>
-      <c r="FL124" s="69"/>
-      <c r="FM124" s="69"/>
-      <c r="FN124" s="69"/>
-      <c r="FO124" s="69"/>
-      <c r="FP124" s="69"/>
-      <c r="FQ124" s="69"/>
-      <c r="FR124" s="69"/>
-      <c r="FS124" s="69"/>
-      <c r="FT124" s="69"/>
-      <c r="FU124" s="69"/>
-      <c r="FV124" s="69"/>
-      <c r="FW124" s="69"/>
-      <c r="FX124" s="69"/>
-      <c r="FY124" s="69"/>
-      <c r="FZ124" s="69"/>
-      <c r="GA124" s="69"/>
-      <c r="GB124" s="69"/>
-      <c r="GC124" s="69"/>
-      <c r="GD124" s="69"/>
-      <c r="GE124" s="69"/>
-      <c r="GF124" s="69"/>
-      <c r="GG124" s="69"/>
-      <c r="GH124" s="69"/>
-      <c r="GI124" s="69"/>
-      <c r="GJ124" s="69"/>
-      <c r="GK124" s="69"/>
-      <c r="GL124" s="69"/>
-      <c r="GM124" s="69"/>
-      <c r="GN124" s="69"/>
-      <c r="GO124" s="69"/>
-      <c r="GP124" s="69"/>
-      <c r="GQ124" s="69"/>
-      <c r="GR124" s="69"/>
-      <c r="GS124" s="69"/>
-      <c r="GT124" s="69"/>
-      <c r="GU124" s="69"/>
-      <c r="GV124" s="69"/>
-      <c r="GW124" s="69"/>
-      <c r="GX124" s="69"/>
-      <c r="GY124" s="69"/>
-      <c r="GZ124" s="69"/>
-      <c r="HA124" s="69"/>
-      <c r="HB124" s="69"/>
-      <c r="HC124" s="69"/>
-      <c r="HD124" s="69"/>
-      <c r="HE124" s="69"/>
-      <c r="HF124" s="69"/>
-      <c r="HG124" s="69"/>
-      <c r="HH124" s="69"/>
-      <c r="HI124" s="69"/>
-      <c r="HJ124" s="69"/>
-      <c r="HK124" s="69"/>
-      <c r="HL124" s="69"/>
-      <c r="HM124" s="69"/>
-      <c r="HN124" s="69"/>
-      <c r="HO124" s="69"/>
-      <c r="HP124" s="69"/>
-      <c r="HQ124" s="69"/>
-      <c r="HR124" s="69"/>
-      <c r="HS124" s="69"/>
-      <c r="HT124" s="69"/>
-      <c r="HU124" s="69"/>
-      <c r="HV124" s="69"/>
-      <c r="HW124" s="69"/>
-      <c r="HX124" s="69"/>
-      <c r="HY124" s="69"/>
-      <c r="HZ124" s="69"/>
-      <c r="IA124" s="69"/>
-      <c r="IB124" s="69"/>
-      <c r="IC124" s="69"/>
-      <c r="ID124" s="69"/>
-      <c r="IE124" s="69"/>
-      <c r="IF124" s="69"/>
-      <c r="IG124" s="69"/>
-      <c r="IH124" s="69"/>
-      <c r="II124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV124" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW124" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K124" s="46"/>
+      <c r="L124" s="46"/>
+      <c r="M124" s="46"/>
+      <c r="N124" s="46"/>
+      <c r="O124" s="46"/>
+      <c r="P124" s="46"/>
+      <c r="Q124" s="46"/>
+      <c r="R124" s="46"/>
+      <c r="S124" s="46"/>
+      <c r="T124" s="46"/>
+      <c r="U124" s="46"/>
+      <c r="V124" s="46"/>
+      <c r="W124" s="46"/>
+      <c r="X124" s="46"/>
+      <c r="Y124" s="46"/>
+      <c r="Z124" s="46"/>
+      <c r="AA124" s="46"/>
+      <c r="AB124" s="46"/>
+      <c r="AC124" s="46"/>
+      <c r="AD124" s="46"/>
+      <c r="AE124" s="46"/>
+      <c r="AF124" s="46"/>
+      <c r="AG124" s="46"/>
+      <c r="AH124" s="46"/>
+      <c r="AI124" s="46"/>
+      <c r="AJ124" s="46"/>
+      <c r="AK124" s="46"/>
+      <c r="AL124" s="46"/>
+      <c r="AM124" s="46"/>
+      <c r="AN124" s="46"/>
+      <c r="AO124" s="46"/>
+      <c r="AP124" s="46"/>
+      <c r="AQ124" s="46"/>
+      <c r="AR124" s="46"/>
+      <c r="AS124" s="46"/>
+      <c r="AT124" s="46"/>
+      <c r="AU124" s="46"/>
+      <c r="AV124" s="46"/>
+      <c r="AW124" s="46"/>
+      <c r="AX124" s="46"/>
+      <c r="AY124" s="46"/>
+      <c r="AZ124" s="46"/>
+      <c r="BA124" s="46"/>
+      <c r="BB124" s="46"/>
+      <c r="BC124" s="46"/>
+      <c r="BD124" s="46"/>
+      <c r="BE124" s="46"/>
+      <c r="BF124" s="46"/>
+      <c r="BG124" s="46"/>
+      <c r="BH124" s="46"/>
+      <c r="BI124" s="46"/>
+      <c r="BJ124" s="46"/>
+      <c r="BK124" s="46"/>
+      <c r="BL124" s="46"/>
+      <c r="BM124" s="46"/>
+      <c r="BN124" s="46"/>
+      <c r="BO124" s="46"/>
+      <c r="BP124" s="46"/>
+      <c r="BQ124" s="46"/>
+      <c r="BR124" s="46"/>
+      <c r="BS124" s="46"/>
+      <c r="BT124" s="46"/>
+      <c r="BU124" s="46"/>
+      <c r="BV124" s="46"/>
+      <c r="BW124" s="46"/>
+      <c r="BX124" s="46"/>
+      <c r="BY124" s="46"/>
+      <c r="BZ124" s="46"/>
+      <c r="CA124" s="46"/>
+      <c r="CB124" s="46"/>
+      <c r="CC124" s="46"/>
+      <c r="CD124" s="46"/>
+      <c r="CE124" s="46"/>
+      <c r="CF124" s="46"/>
+      <c r="CG124" s="46"/>
+      <c r="CH124" s="46"/>
+      <c r="CI124" s="46"/>
+      <c r="CJ124" s="46"/>
+      <c r="CK124" s="46"/>
+      <c r="CL124" s="46"/>
+      <c r="CM124" s="46"/>
+      <c r="CN124" s="46"/>
+      <c r="CO124" s="46"/>
+      <c r="CP124" s="46"/>
+      <c r="CQ124" s="46"/>
+      <c r="CR124" s="46"/>
+      <c r="CS124" s="46"/>
+      <c r="CT124" s="46"/>
+      <c r="CU124" s="46"/>
+      <c r="CV124" s="46"/>
+      <c r="CW124" s="46"/>
+      <c r="CX124" s="46"/>
+      <c r="CY124" s="46"/>
+      <c r="CZ124" s="46"/>
+      <c r="DA124" s="46"/>
+      <c r="DB124" s="46"/>
+      <c r="DC124" s="46"/>
+      <c r="DD124" s="46"/>
+      <c r="DE124" s="46"/>
+      <c r="DF124" s="46"/>
+      <c r="DG124" s="46"/>
+      <c r="DH124" s="46"/>
+      <c r="DI124" s="46"/>
+      <c r="DJ124" s="46"/>
+      <c r="DK124" s="46"/>
+      <c r="DL124" s="46"/>
+      <c r="DM124" s="46"/>
+      <c r="DN124" s="46"/>
+      <c r="DO124" s="46"/>
+      <c r="DP124" s="46"/>
+      <c r="DQ124" s="46"/>
+      <c r="DR124" s="46"/>
+      <c r="DS124" s="46"/>
+      <c r="DT124" s="46"/>
+      <c r="DU124" s="46"/>
+      <c r="DV124" s="46"/>
+      <c r="DW124" s="46"/>
+      <c r="DX124" s="46"/>
+      <c r="DY124" s="46"/>
+      <c r="DZ124" s="46"/>
+      <c r="EA124" s="46"/>
+      <c r="EB124" s="46"/>
+      <c r="EC124" s="46"/>
+      <c r="ED124" s="46"/>
+      <c r="EE124" s="46"/>
+      <c r="EF124" s="46"/>
+      <c r="EG124" s="46"/>
+      <c r="EH124" s="46"/>
+      <c r="EI124" s="46"/>
+      <c r="EJ124" s="46"/>
+      <c r="EK124" s="46"/>
+      <c r="EL124" s="46"/>
+      <c r="EM124" s="46"/>
+      <c r="EN124" s="46"/>
+      <c r="EO124" s="46"/>
+      <c r="EP124" s="46"/>
+      <c r="EQ124" s="46"/>
+      <c r="ER124" s="46"/>
+      <c r="ES124" s="46"/>
+      <c r="ET124" s="46"/>
+      <c r="EU124" s="46"/>
+      <c r="EV124" s="46"/>
+      <c r="EW124" s="46"/>
+      <c r="EX124" s="46"/>
+      <c r="EY124" s="46"/>
+      <c r="EZ124" s="46"/>
+      <c r="FA124" s="46"/>
+      <c r="FB124" s="46"/>
+      <c r="FC124" s="46"/>
+      <c r="FD124" s="46"/>
+      <c r="FE124" s="46"/>
+      <c r="FF124" s="46"/>
+      <c r="FG124" s="46"/>
+      <c r="FH124" s="46"/>
+      <c r="FI124" s="46"/>
+      <c r="FJ124" s="46"/>
+      <c r="FK124" s="46"/>
+      <c r="FL124" s="46"/>
+      <c r="FM124" s="46"/>
+      <c r="FN124" s="46"/>
+      <c r="FO124" s="46"/>
+      <c r="FP124" s="46"/>
+      <c r="FQ124" s="46"/>
+      <c r="FR124" s="46"/>
+      <c r="FS124" s="46"/>
+      <c r="FT124" s="46"/>
+      <c r="FU124" s="46"/>
+      <c r="FV124" s="46"/>
+      <c r="FW124" s="46"/>
+      <c r="FX124" s="46"/>
+      <c r="FY124" s="46"/>
+      <c r="FZ124" s="46"/>
+      <c r="GA124" s="46"/>
+      <c r="GB124" s="46"/>
+      <c r="GC124" s="46"/>
+      <c r="GD124" s="46"/>
+      <c r="GE124" s="46"/>
+      <c r="GF124" s="46"/>
+      <c r="GG124" s="46"/>
+      <c r="GH124" s="46"/>
+      <c r="GI124" s="46"/>
+      <c r="GJ124" s="46"/>
+      <c r="GK124" s="46"/>
+      <c r="GL124" s="46"/>
+      <c r="GM124" s="46"/>
+      <c r="GN124" s="46"/>
+      <c r="GO124" s="46"/>
+      <c r="GP124" s="46"/>
+      <c r="GQ124" s="46"/>
+      <c r="GR124" s="46"/>
+      <c r="GS124" s="46"/>
+      <c r="GT124" s="46"/>
+      <c r="GU124" s="46"/>
+      <c r="GV124" s="46"/>
+      <c r="GW124" s="46"/>
+      <c r="GX124" s="46"/>
+      <c r="GY124" s="46"/>
+      <c r="GZ124" s="46"/>
+      <c r="HA124" s="46"/>
+      <c r="HB124" s="46"/>
+      <c r="HC124" s="46"/>
+      <c r="HD124" s="46"/>
+      <c r="HE124" s="46"/>
+      <c r="HF124" s="46"/>
+      <c r="HG124" s="46"/>
+      <c r="HH124" s="46"/>
+      <c r="HI124" s="46"/>
+      <c r="HJ124" s="46"/>
+      <c r="HK124" s="46"/>
+      <c r="HL124" s="46"/>
+      <c r="HM124" s="46"/>
+      <c r="HN124" s="46"/>
+      <c r="HO124" s="46"/>
+      <c r="HP124" s="46"/>
+      <c r="HQ124" s="46"/>
+      <c r="HR124" s="46"/>
+      <c r="HS124" s="46"/>
+      <c r="HT124" s="46"/>
+      <c r="HU124" s="46"/>
+      <c r="HV124" s="46"/>
+      <c r="HW124" s="46"/>
+      <c r="HX124" s="46"/>
+      <c r="HY124" s="46"/>
+      <c r="HZ124" s="46"/>
+      <c r="IA124" s="46"/>
+      <c r="IB124" s="46"/>
+      <c r="IC124" s="46"/>
+      <c r="ID124" s="46"/>
+      <c r="IE124" s="46"/>
+      <c r="IF124" s="46"/>
+      <c r="IG124" s="46"/>
+      <c r="IH124" s="46"/>
+      <c r="II124" s="46"/>
+      <c r="IJ124" s="46"/>
+      <c r="IK124" s="46"/>
+      <c r="IL124" s="46"/>
+      <c r="IM124" s="46"/>
+      <c r="IW124" s="47"/>
     </row>
-    <row r="125" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
       <c r="A125" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B125" s="42" t="s">
-        <v>13</v>
+      <c r="B125" s="60" t="s">
+        <v>4</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D125" s="42"/>
       <c r="E125" s="42" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F125" s="42" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="G125" s="54" t="s">
         <v>268</v>
@@ -37342,300 +37316,261 @@
       </c>
       <c r="I125" s="45"/>
       <c r="J125" s="46"/>
-      <c r="K125" s="69"/>
-      <c r="L125" s="69"/>
-      <c r="M125" s="69"/>
-      <c r="N125" s="69"/>
-      <c r="O125" s="69"/>
-      <c r="P125" s="69"/>
-      <c r="Q125" s="69"/>
-      <c r="R125" s="69"/>
-      <c r="S125" s="69"/>
-      <c r="T125" s="69"/>
-      <c r="U125" s="69"/>
-      <c r="V125" s="69"/>
-      <c r="W125" s="69"/>
-      <c r="X125" s="69"/>
-      <c r="Y125" s="69"/>
-      <c r="Z125" s="69"/>
-      <c r="AA125" s="69"/>
-      <c r="AB125" s="69"/>
-      <c r="AC125" s="69"/>
-      <c r="AD125" s="69"/>
-      <c r="AE125" s="69"/>
-      <c r="AF125" s="69"/>
-      <c r="AG125" s="69"/>
-      <c r="AH125" s="69"/>
-      <c r="AI125" s="69"/>
-      <c r="AJ125" s="69"/>
-      <c r="AK125" s="69"/>
-      <c r="AL125" s="69"/>
-      <c r="AM125" s="69"/>
-      <c r="AN125" s="69"/>
-      <c r="AO125" s="69"/>
-      <c r="AP125" s="69"/>
-      <c r="AQ125" s="69"/>
-      <c r="AR125" s="69"/>
-      <c r="AS125" s="69"/>
-      <c r="AT125" s="69"/>
-      <c r="AU125" s="69"/>
-      <c r="AV125" s="69"/>
-      <c r="AW125" s="69"/>
-      <c r="AX125" s="69"/>
-      <c r="AY125" s="69"/>
-      <c r="AZ125" s="69"/>
-      <c r="BA125" s="69"/>
-      <c r="BB125" s="69"/>
-      <c r="BC125" s="69"/>
-      <c r="BD125" s="69"/>
-      <c r="BE125" s="69"/>
-      <c r="BF125" s="69"/>
-      <c r="BG125" s="69"/>
-      <c r="BH125" s="69"/>
-      <c r="BI125" s="69"/>
-      <c r="BJ125" s="69"/>
-      <c r="BK125" s="69"/>
-      <c r="BL125" s="69"/>
-      <c r="BM125" s="69"/>
-      <c r="BN125" s="69"/>
-      <c r="BO125" s="69"/>
-      <c r="BP125" s="69"/>
-      <c r="BQ125" s="69"/>
-      <c r="BR125" s="69"/>
-      <c r="BS125" s="69"/>
-      <c r="BT125" s="69"/>
-      <c r="BU125" s="69"/>
-      <c r="BV125" s="69"/>
-      <c r="BW125" s="69"/>
-      <c r="BX125" s="69"/>
-      <c r="BY125" s="69"/>
-      <c r="BZ125" s="69"/>
-      <c r="CA125" s="69"/>
-      <c r="CB125" s="69"/>
-      <c r="CC125" s="69"/>
-      <c r="CD125" s="69"/>
-      <c r="CE125" s="69"/>
-      <c r="CF125" s="69"/>
-      <c r="CG125" s="69"/>
-      <c r="CH125" s="69"/>
-      <c r="CI125" s="69"/>
-      <c r="CJ125" s="69"/>
-      <c r="CK125" s="69"/>
-      <c r="CL125" s="69"/>
-      <c r="CM125" s="69"/>
-      <c r="CN125" s="69"/>
-      <c r="CO125" s="69"/>
-      <c r="CP125" s="69"/>
-      <c r="CQ125" s="69"/>
-      <c r="CR125" s="69"/>
-      <c r="CS125" s="69"/>
-      <c r="CT125" s="69"/>
-      <c r="CU125" s="69"/>
-      <c r="CV125" s="69"/>
-      <c r="CW125" s="69"/>
-      <c r="CX125" s="69"/>
-      <c r="CY125" s="69"/>
-      <c r="CZ125" s="69"/>
-      <c r="DA125" s="69"/>
-      <c r="DB125" s="69"/>
-      <c r="DC125" s="69"/>
-      <c r="DD125" s="69"/>
-      <c r="DE125" s="69"/>
-      <c r="DF125" s="69"/>
-      <c r="DG125" s="69"/>
-      <c r="DH125" s="69"/>
-      <c r="DI125" s="69"/>
-      <c r="DJ125" s="69"/>
-      <c r="DK125" s="69"/>
-      <c r="DL125" s="69"/>
-      <c r="DM125" s="69"/>
-      <c r="DN125" s="69"/>
-      <c r="DO125" s="69"/>
-      <c r="DP125" s="69"/>
-      <c r="DQ125" s="69"/>
-      <c r="DR125" s="69"/>
-      <c r="DS125" s="69"/>
-      <c r="DT125" s="69"/>
-      <c r="DU125" s="69"/>
-      <c r="DV125" s="69"/>
-      <c r="DW125" s="69"/>
-      <c r="DX125" s="69"/>
-      <c r="DY125" s="69"/>
-      <c r="DZ125" s="69"/>
-      <c r="EA125" s="69"/>
-      <c r="EB125" s="69"/>
-      <c r="EC125" s="69"/>
-      <c r="ED125" s="69"/>
-      <c r="EE125" s="69"/>
-      <c r="EF125" s="69"/>
-      <c r="EG125" s="69"/>
-      <c r="EH125" s="69"/>
-      <c r="EI125" s="69"/>
-      <c r="EJ125" s="69"/>
-      <c r="EK125" s="69"/>
-      <c r="EL125" s="69"/>
-      <c r="EM125" s="69"/>
-      <c r="EN125" s="69"/>
-      <c r="EO125" s="69"/>
-      <c r="EP125" s="69"/>
-      <c r="EQ125" s="69"/>
-      <c r="ER125" s="69"/>
-      <c r="ES125" s="69"/>
-      <c r="ET125" s="69"/>
-      <c r="EU125" s="69"/>
-      <c r="EV125" s="69"/>
-      <c r="EW125" s="69"/>
-      <c r="EX125" s="69"/>
-      <c r="EY125" s="69"/>
-      <c r="EZ125" s="69"/>
-      <c r="FA125" s="69"/>
-      <c r="FB125" s="69"/>
-      <c r="FC125" s="69"/>
-      <c r="FD125" s="69"/>
-      <c r="FE125" s="69"/>
-      <c r="FF125" s="69"/>
-      <c r="FG125" s="69"/>
-      <c r="FH125" s="69"/>
-      <c r="FI125" s="69"/>
-      <c r="FJ125" s="69"/>
-      <c r="FK125" s="69"/>
-      <c r="FL125" s="69"/>
-      <c r="FM125" s="69"/>
-      <c r="FN125" s="69"/>
-      <c r="FO125" s="69"/>
-      <c r="FP125" s="69"/>
-      <c r="FQ125" s="69"/>
-      <c r="FR125" s="69"/>
-      <c r="FS125" s="69"/>
-      <c r="FT125" s="69"/>
-      <c r="FU125" s="69"/>
-      <c r="FV125" s="69"/>
-      <c r="FW125" s="69"/>
-      <c r="FX125" s="69"/>
-      <c r="FY125" s="69"/>
-      <c r="FZ125" s="69"/>
-      <c r="GA125" s="69"/>
-      <c r="GB125" s="69"/>
-      <c r="GC125" s="69"/>
-      <c r="GD125" s="69"/>
-      <c r="GE125" s="69"/>
-      <c r="GF125" s="69"/>
-      <c r="GG125" s="69"/>
-      <c r="GH125" s="69"/>
-      <c r="GI125" s="69"/>
-      <c r="GJ125" s="69"/>
-      <c r="GK125" s="69"/>
-      <c r="GL125" s="69"/>
-      <c r="GM125" s="69"/>
-      <c r="GN125" s="69"/>
-      <c r="GO125" s="69"/>
-      <c r="GP125" s="69"/>
-      <c r="GQ125" s="69"/>
-      <c r="GR125" s="69"/>
-      <c r="GS125" s="69"/>
-      <c r="GT125" s="69"/>
-      <c r="GU125" s="69"/>
-      <c r="GV125" s="69"/>
-      <c r="GW125" s="69"/>
-      <c r="GX125" s="69"/>
-      <c r="GY125" s="69"/>
-      <c r="GZ125" s="69"/>
-      <c r="HA125" s="69"/>
-      <c r="HB125" s="69"/>
-      <c r="HC125" s="69"/>
-      <c r="HD125" s="69"/>
-      <c r="HE125" s="69"/>
-      <c r="HF125" s="69"/>
-      <c r="HG125" s="69"/>
-      <c r="HH125" s="69"/>
-      <c r="HI125" s="69"/>
-      <c r="HJ125" s="69"/>
-      <c r="HK125" s="69"/>
-      <c r="HL125" s="69"/>
-      <c r="HM125" s="69"/>
-      <c r="HN125" s="69"/>
-      <c r="HO125" s="69"/>
-      <c r="HP125" s="69"/>
-      <c r="HQ125" s="69"/>
-      <c r="HR125" s="69"/>
-      <c r="HS125" s="69"/>
-      <c r="HT125" s="69"/>
-      <c r="HU125" s="69"/>
-      <c r="HV125" s="69"/>
-      <c r="HW125" s="69"/>
-      <c r="HX125" s="69"/>
-      <c r="HY125" s="69"/>
-      <c r="HZ125" s="69"/>
-      <c r="IA125" s="69"/>
-      <c r="IB125" s="69"/>
-      <c r="IC125" s="69"/>
-      <c r="ID125" s="69"/>
-      <c r="IE125" s="69"/>
-      <c r="IF125" s="69"/>
-      <c r="IG125" s="69"/>
-      <c r="IH125" s="69"/>
-      <c r="II125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV125" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW125" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K125" s="46"/>
+      <c r="L125" s="46"/>
+      <c r="M125" s="46"/>
+      <c r="N125" s="46"/>
+      <c r="O125" s="46"/>
+      <c r="P125" s="46"/>
+      <c r="Q125" s="46"/>
+      <c r="R125" s="46"/>
+      <c r="S125" s="46"/>
+      <c r="T125" s="46"/>
+      <c r="U125" s="46"/>
+      <c r="V125" s="46"/>
+      <c r="W125" s="46"/>
+      <c r="X125" s="46"/>
+      <c r="Y125" s="46"/>
+      <c r="Z125" s="46"/>
+      <c r="AA125" s="46"/>
+      <c r="AB125" s="46"/>
+      <c r="AC125" s="46"/>
+      <c r="AD125" s="46"/>
+      <c r="AE125" s="46"/>
+      <c r="AF125" s="46"/>
+      <c r="AG125" s="46"/>
+      <c r="AH125" s="46"/>
+      <c r="AI125" s="46"/>
+      <c r="AJ125" s="46"/>
+      <c r="AK125" s="46"/>
+      <c r="AL125" s="46"/>
+      <c r="AM125" s="46"/>
+      <c r="AN125" s="46"/>
+      <c r="AO125" s="46"/>
+      <c r="AP125" s="46"/>
+      <c r="AQ125" s="46"/>
+      <c r="AR125" s="46"/>
+      <c r="AS125" s="46"/>
+      <c r="AT125" s="46"/>
+      <c r="AU125" s="46"/>
+      <c r="AV125" s="46"/>
+      <c r="AW125" s="46"/>
+      <c r="AX125" s="46"/>
+      <c r="AY125" s="46"/>
+      <c r="AZ125" s="46"/>
+      <c r="BA125" s="46"/>
+      <c r="BB125" s="46"/>
+      <c r="BC125" s="46"/>
+      <c r="BD125" s="46"/>
+      <c r="BE125" s="46"/>
+      <c r="BF125" s="46"/>
+      <c r="BG125" s="46"/>
+      <c r="BH125" s="46"/>
+      <c r="BI125" s="46"/>
+      <c r="BJ125" s="46"/>
+      <c r="BK125" s="46"/>
+      <c r="BL125" s="46"/>
+      <c r="BM125" s="46"/>
+      <c r="BN125" s="46"/>
+      <c r="BO125" s="46"/>
+      <c r="BP125" s="46"/>
+      <c r="BQ125" s="46"/>
+      <c r="BR125" s="46"/>
+      <c r="BS125" s="46"/>
+      <c r="BT125" s="46"/>
+      <c r="BU125" s="46"/>
+      <c r="BV125" s="46"/>
+      <c r="BW125" s="46"/>
+      <c r="BX125" s="46"/>
+      <c r="BY125" s="46"/>
+      <c r="BZ125" s="46"/>
+      <c r="CA125" s="46"/>
+      <c r="CB125" s="46"/>
+      <c r="CC125" s="46"/>
+      <c r="CD125" s="46"/>
+      <c r="CE125" s="46"/>
+      <c r="CF125" s="46"/>
+      <c r="CG125" s="46"/>
+      <c r="CH125" s="46"/>
+      <c r="CI125" s="46"/>
+      <c r="CJ125" s="46"/>
+      <c r="CK125" s="46"/>
+      <c r="CL125" s="46"/>
+      <c r="CM125" s="46"/>
+      <c r="CN125" s="46"/>
+      <c r="CO125" s="46"/>
+      <c r="CP125" s="46"/>
+      <c r="CQ125" s="46"/>
+      <c r="CR125" s="46"/>
+      <c r="CS125" s="46"/>
+      <c r="CT125" s="46"/>
+      <c r="CU125" s="46"/>
+      <c r="CV125" s="46"/>
+      <c r="CW125" s="46"/>
+      <c r="CX125" s="46"/>
+      <c r="CY125" s="46"/>
+      <c r="CZ125" s="46"/>
+      <c r="DA125" s="46"/>
+      <c r="DB125" s="46"/>
+      <c r="DC125" s="46"/>
+      <c r="DD125" s="46"/>
+      <c r="DE125" s="46"/>
+      <c r="DF125" s="46"/>
+      <c r="DG125" s="46"/>
+      <c r="DH125" s="46"/>
+      <c r="DI125" s="46"/>
+      <c r="DJ125" s="46"/>
+      <c r="DK125" s="46"/>
+      <c r="DL125" s="46"/>
+      <c r="DM125" s="46"/>
+      <c r="DN125" s="46"/>
+      <c r="DO125" s="46"/>
+      <c r="DP125" s="46"/>
+      <c r="DQ125" s="46"/>
+      <c r="DR125" s="46"/>
+      <c r="DS125" s="46"/>
+      <c r="DT125" s="46"/>
+      <c r="DU125" s="46"/>
+      <c r="DV125" s="46"/>
+      <c r="DW125" s="46"/>
+      <c r="DX125" s="46"/>
+      <c r="DY125" s="46"/>
+      <c r="DZ125" s="46"/>
+      <c r="EA125" s="46"/>
+      <c r="EB125" s="46"/>
+      <c r="EC125" s="46"/>
+      <c r="ED125" s="46"/>
+      <c r="EE125" s="46"/>
+      <c r="EF125" s="46"/>
+      <c r="EG125" s="46"/>
+      <c r="EH125" s="46"/>
+      <c r="EI125" s="46"/>
+      <c r="EJ125" s="46"/>
+      <c r="EK125" s="46"/>
+      <c r="EL125" s="46"/>
+      <c r="EM125" s="46"/>
+      <c r="EN125" s="46"/>
+      <c r="EO125" s="46"/>
+      <c r="EP125" s="46"/>
+      <c r="EQ125" s="46"/>
+      <c r="ER125" s="46"/>
+      <c r="ES125" s="46"/>
+      <c r="ET125" s="46"/>
+      <c r="EU125" s="46"/>
+      <c r="EV125" s="46"/>
+      <c r="EW125" s="46"/>
+      <c r="EX125" s="46"/>
+      <c r="EY125" s="46"/>
+      <c r="EZ125" s="46"/>
+      <c r="FA125" s="46"/>
+      <c r="FB125" s="46"/>
+      <c r="FC125" s="46"/>
+      <c r="FD125" s="46"/>
+      <c r="FE125" s="46"/>
+      <c r="FF125" s="46"/>
+      <c r="FG125" s="46"/>
+      <c r="FH125" s="46"/>
+      <c r="FI125" s="46"/>
+      <c r="FJ125" s="46"/>
+      <c r="FK125" s="46"/>
+      <c r="FL125" s="46"/>
+      <c r="FM125" s="46"/>
+      <c r="FN125" s="46"/>
+      <c r="FO125" s="46"/>
+      <c r="FP125" s="46"/>
+      <c r="FQ125" s="46"/>
+      <c r="FR125" s="46"/>
+      <c r="FS125" s="46"/>
+      <c r="FT125" s="46"/>
+      <c r="FU125" s="46"/>
+      <c r="FV125" s="46"/>
+      <c r="FW125" s="46"/>
+      <c r="FX125" s="46"/>
+      <c r="FY125" s="46"/>
+      <c r="FZ125" s="46"/>
+      <c r="GA125" s="46"/>
+      <c r="GB125" s="46"/>
+      <c r="GC125" s="46"/>
+      <c r="GD125" s="46"/>
+      <c r="GE125" s="46"/>
+      <c r="GF125" s="46"/>
+      <c r="GG125" s="46"/>
+      <c r="GH125" s="46"/>
+      <c r="GI125" s="46"/>
+      <c r="GJ125" s="46"/>
+      <c r="GK125" s="46"/>
+      <c r="GL125" s="46"/>
+      <c r="GM125" s="46"/>
+      <c r="GN125" s="46"/>
+      <c r="GO125" s="46"/>
+      <c r="GP125" s="46"/>
+      <c r="GQ125" s="46"/>
+      <c r="GR125" s="46"/>
+      <c r="GS125" s="46"/>
+      <c r="GT125" s="46"/>
+      <c r="GU125" s="46"/>
+      <c r="GV125" s="46"/>
+      <c r="GW125" s="46"/>
+      <c r="GX125" s="46"/>
+      <c r="GY125" s="46"/>
+      <c r="GZ125" s="46"/>
+      <c r="HA125" s="46"/>
+      <c r="HB125" s="46"/>
+      <c r="HC125" s="46"/>
+      <c r="HD125" s="46"/>
+      <c r="HE125" s="46"/>
+      <c r="HF125" s="46"/>
+      <c r="HG125" s="46"/>
+      <c r="HH125" s="46"/>
+      <c r="HI125" s="46"/>
+      <c r="HJ125" s="46"/>
+      <c r="HK125" s="46"/>
+      <c r="HL125" s="46"/>
+      <c r="HM125" s="46"/>
+      <c r="HN125" s="46"/>
+      <c r="HO125" s="46"/>
+      <c r="HP125" s="46"/>
+      <c r="HQ125" s="46"/>
+      <c r="HR125" s="46"/>
+      <c r="HS125" s="46"/>
+      <c r="HT125" s="46"/>
+      <c r="HU125" s="46"/>
+      <c r="HV125" s="46"/>
+      <c r="HW125" s="46"/>
+      <c r="HX125" s="46"/>
+      <c r="HY125" s="46"/>
+      <c r="HZ125" s="46"/>
+      <c r="IA125" s="46"/>
+      <c r="IB125" s="46"/>
+      <c r="IC125" s="46"/>
+      <c r="ID125" s="46"/>
+      <c r="IE125" s="46"/>
+      <c r="IF125" s="46"/>
+      <c r="IG125" s="46"/>
+      <c r="IH125" s="46"/>
+      <c r="II125" s="46"/>
+      <c r="IJ125" s="46"/>
+      <c r="IK125" s="46"/>
+      <c r="IL125" s="46"/>
+      <c r="IM125" s="46"/>
+      <c r="IW125" s="47"/>
     </row>
     <row r="126" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
       <c r="A126" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B126" s="42" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D126" s="42"/>
       <c r="E126" s="42" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="F126" s="42" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="G126" s="54" t="s">
         <v>268</v>
@@ -37928,23 +37863,23 @@
         <v>253</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="C127" s="61"/>
-      <c r="D127" s="42" t="s">
-        <v>302</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C127" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="42"/>
       <c r="E127" s="42" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="F127" s="42" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="G127" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H127" s="54" t="s">
-        <v>268</v>
+      <c r="H127" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="I127" s="45"/>
       <c r="J127" s="46"/>
@@ -38226,288 +38161,325 @@
         <v>112</v>
       </c>
     </row>
-    <row r="128" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A128" s="71" t="s">
-        <v>325</v>
+    <row r="128" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A128" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="C128" s="42" t="s">
-        <v>299</v>
+        <v>12</v>
       </c>
       <c r="D128" s="42"/>
       <c r="E128" s="42" t="s">
-        <v>304</v>
+        <v>238</v>
       </c>
       <c r="F128" s="42" t="s">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="G128" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H128" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I128" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="H128" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I128" s="45"/>
       <c r="J128" s="46"/>
-      <c r="K128" s="46"/>
-      <c r="L128" s="46"/>
-      <c r="M128" s="46"/>
-      <c r="N128" s="46"/>
-      <c r="O128" s="46"/>
-      <c r="P128" s="46"/>
-      <c r="Q128" s="46"/>
-      <c r="R128" s="46"/>
-      <c r="S128" s="46"/>
-      <c r="T128" s="46"/>
-      <c r="U128" s="46"/>
-      <c r="V128" s="46"/>
-      <c r="W128" s="46"/>
-      <c r="X128" s="46"/>
-      <c r="Y128" s="46"/>
-      <c r="Z128" s="46"/>
-      <c r="AA128" s="46"/>
-      <c r="AB128" s="46"/>
-      <c r="AC128" s="46"/>
-      <c r="AD128" s="46"/>
-      <c r="AE128" s="46"/>
-      <c r="AF128" s="46"/>
-      <c r="AG128" s="46"/>
-      <c r="AH128" s="46"/>
-      <c r="AI128" s="46"/>
-      <c r="AJ128" s="46"/>
-      <c r="AK128" s="46"/>
-      <c r="AL128" s="46"/>
-      <c r="AM128" s="46"/>
-      <c r="AN128" s="46"/>
-      <c r="AO128" s="46"/>
-      <c r="AP128" s="46"/>
-      <c r="AQ128" s="46"/>
-      <c r="AR128" s="46"/>
-      <c r="AS128" s="46"/>
-      <c r="AT128" s="46"/>
-      <c r="AU128" s="46"/>
-      <c r="AV128" s="46"/>
-      <c r="AW128" s="46"/>
-      <c r="AX128" s="46"/>
-      <c r="AY128" s="46"/>
-      <c r="AZ128" s="46"/>
-      <c r="BA128" s="46"/>
-      <c r="BB128" s="46"/>
-      <c r="BC128" s="46"/>
-      <c r="BD128" s="46"/>
-      <c r="BE128" s="46"/>
-      <c r="BF128" s="46"/>
-      <c r="BG128" s="46"/>
-      <c r="BH128" s="46"/>
-      <c r="BI128" s="46"/>
-      <c r="BJ128" s="46"/>
-      <c r="BK128" s="46"/>
-      <c r="BL128" s="46"/>
-      <c r="BM128" s="46"/>
-      <c r="BN128" s="46"/>
-      <c r="BO128" s="46"/>
-      <c r="BP128" s="46"/>
-      <c r="BQ128" s="46"/>
-      <c r="BR128" s="46"/>
-      <c r="BS128" s="46"/>
-      <c r="BT128" s="46"/>
-      <c r="BU128" s="46"/>
-      <c r="BV128" s="46"/>
-      <c r="BW128" s="46"/>
-      <c r="BX128" s="46"/>
-      <c r="BY128" s="46"/>
-      <c r="BZ128" s="46"/>
-      <c r="CA128" s="46"/>
-      <c r="CB128" s="46"/>
-      <c r="CC128" s="46"/>
-      <c r="CD128" s="46"/>
-      <c r="CE128" s="46"/>
-      <c r="CF128" s="46"/>
-      <c r="CG128" s="46"/>
-      <c r="CH128" s="46"/>
-      <c r="CI128" s="46"/>
-      <c r="CJ128" s="46"/>
-      <c r="CK128" s="46"/>
-      <c r="CL128" s="46"/>
-      <c r="CM128" s="46"/>
-      <c r="CN128" s="46"/>
-      <c r="CO128" s="46"/>
-      <c r="CP128" s="46"/>
-      <c r="CQ128" s="46"/>
-      <c r="CR128" s="46"/>
-      <c r="CS128" s="46"/>
-      <c r="CT128" s="46"/>
-      <c r="CU128" s="46"/>
-      <c r="CV128" s="46"/>
-      <c r="CW128" s="46"/>
-      <c r="CX128" s="46"/>
-      <c r="CY128" s="46"/>
-      <c r="CZ128" s="46"/>
-      <c r="DA128" s="46"/>
-      <c r="DB128" s="46"/>
-      <c r="DC128" s="46"/>
-      <c r="DD128" s="46"/>
-      <c r="DE128" s="46"/>
-      <c r="DF128" s="46"/>
-      <c r="DG128" s="46"/>
-      <c r="DH128" s="46"/>
-      <c r="DI128" s="46"/>
-      <c r="DJ128" s="46"/>
-      <c r="DK128" s="46"/>
-      <c r="DL128" s="46"/>
-      <c r="DM128" s="46"/>
-      <c r="DN128" s="46"/>
-      <c r="DO128" s="46"/>
-      <c r="DP128" s="46"/>
-      <c r="DQ128" s="46"/>
-      <c r="DR128" s="46"/>
-      <c r="DS128" s="46"/>
-      <c r="DT128" s="46"/>
-      <c r="DU128" s="46"/>
-      <c r="DV128" s="46"/>
-      <c r="DW128" s="46"/>
-      <c r="DX128" s="46"/>
-      <c r="DY128" s="46"/>
-      <c r="DZ128" s="46"/>
-      <c r="EA128" s="46"/>
-      <c r="EB128" s="46"/>
-      <c r="EC128" s="46"/>
-      <c r="ED128" s="46"/>
-      <c r="EE128" s="46"/>
-      <c r="EF128" s="46"/>
-      <c r="EG128" s="46"/>
-      <c r="EH128" s="46"/>
-      <c r="EI128" s="46"/>
-      <c r="EJ128" s="46"/>
-      <c r="EK128" s="46"/>
-      <c r="EL128" s="46"/>
-      <c r="EM128" s="46"/>
-      <c r="EN128" s="46"/>
-      <c r="EO128" s="46"/>
-      <c r="EP128" s="46"/>
-      <c r="EQ128" s="46"/>
-      <c r="ER128" s="46"/>
-      <c r="ES128" s="46"/>
-      <c r="ET128" s="46"/>
-      <c r="EU128" s="46"/>
-      <c r="EV128" s="46"/>
-      <c r="EW128" s="46"/>
-      <c r="EX128" s="46"/>
-      <c r="EY128" s="46"/>
-      <c r="EZ128" s="46"/>
-      <c r="FA128" s="46"/>
-      <c r="FB128" s="46"/>
-      <c r="FC128" s="46"/>
-      <c r="FD128" s="46"/>
-      <c r="FE128" s="46"/>
-      <c r="FF128" s="46"/>
-      <c r="FG128" s="46"/>
-      <c r="FH128" s="46"/>
-      <c r="FI128" s="46"/>
-      <c r="FJ128" s="46"/>
-      <c r="FK128" s="46"/>
-      <c r="FL128" s="46"/>
-      <c r="FM128" s="46"/>
-      <c r="FN128" s="46"/>
-      <c r="FO128" s="46"/>
-      <c r="FP128" s="46"/>
-      <c r="FQ128" s="46"/>
-      <c r="FR128" s="46"/>
-      <c r="FS128" s="46"/>
-      <c r="FT128" s="46"/>
-      <c r="FU128" s="46"/>
-      <c r="FV128" s="46"/>
-      <c r="FW128" s="46"/>
-      <c r="FX128" s="46"/>
-      <c r="FY128" s="46"/>
-      <c r="FZ128" s="46"/>
-      <c r="GA128" s="46"/>
-      <c r="GB128" s="46"/>
-      <c r="GC128" s="46"/>
-      <c r="GD128" s="46"/>
-      <c r="GE128" s="46"/>
-      <c r="GF128" s="46"/>
-      <c r="GG128" s="46"/>
-      <c r="GH128" s="46"/>
-      <c r="GI128" s="46"/>
-      <c r="GJ128" s="46"/>
-      <c r="GK128" s="46"/>
-      <c r="GL128" s="46"/>
-      <c r="GM128" s="46"/>
-      <c r="GN128" s="46"/>
-      <c r="GO128" s="46"/>
-      <c r="GP128" s="46"/>
-      <c r="GQ128" s="46"/>
-      <c r="GR128" s="46"/>
-      <c r="GS128" s="46"/>
-      <c r="GT128" s="46"/>
-      <c r="GU128" s="46"/>
-      <c r="GV128" s="46"/>
-      <c r="GW128" s="46"/>
-      <c r="GX128" s="46"/>
-      <c r="GY128" s="46"/>
-      <c r="GZ128" s="46"/>
-      <c r="HA128" s="46"/>
-      <c r="HB128" s="46"/>
-      <c r="HC128" s="46"/>
-      <c r="HD128" s="46"/>
-      <c r="HE128" s="46"/>
-      <c r="HF128" s="46"/>
-      <c r="HG128" s="46"/>
-      <c r="HH128" s="46"/>
-      <c r="HI128" s="46"/>
-      <c r="HJ128" s="46"/>
-      <c r="HK128" s="46"/>
-      <c r="HL128" s="46"/>
-      <c r="HM128" s="46"/>
-      <c r="HN128" s="46"/>
-      <c r="HO128" s="46"/>
-      <c r="HP128" s="46"/>
-      <c r="HQ128" s="46"/>
-      <c r="HR128" s="46"/>
-      <c r="HS128" s="46"/>
-      <c r="HT128" s="46"/>
-      <c r="HU128" s="46"/>
-      <c r="HV128" s="46"/>
-      <c r="HW128" s="46"/>
-      <c r="HX128" s="46"/>
-      <c r="HY128" s="46"/>
-      <c r="HZ128" s="46"/>
-      <c r="IA128" s="46"/>
-      <c r="IB128" s="46"/>
-      <c r="IC128" s="46"/>
-      <c r="ID128" s="46"/>
-      <c r="IE128" s="46"/>
-      <c r="IF128" s="46"/>
-      <c r="IG128" s="46"/>
-      <c r="IH128" s="46"/>
-      <c r="II128" s="46"/>
-      <c r="IJ128" s="46"/>
-      <c r="IK128" s="46"/>
-      <c r="IL128" s="46"/>
-      <c r="IM128" s="46"/>
-      <c r="IW128" s="47"/>
+      <c r="K128" s="69"/>
+      <c r="L128" s="69"/>
+      <c r="M128" s="69"/>
+      <c r="N128" s="69"/>
+      <c r="O128" s="69"/>
+      <c r="P128" s="69"/>
+      <c r="Q128" s="69"/>
+      <c r="R128" s="69"/>
+      <c r="S128" s="69"/>
+      <c r="T128" s="69"/>
+      <c r="U128" s="69"/>
+      <c r="V128" s="69"/>
+      <c r="W128" s="69"/>
+      <c r="X128" s="69"/>
+      <c r="Y128" s="69"/>
+      <c r="Z128" s="69"/>
+      <c r="AA128" s="69"/>
+      <c r="AB128" s="69"/>
+      <c r="AC128" s="69"/>
+      <c r="AD128" s="69"/>
+      <c r="AE128" s="69"/>
+      <c r="AF128" s="69"/>
+      <c r="AG128" s="69"/>
+      <c r="AH128" s="69"/>
+      <c r="AI128" s="69"/>
+      <c r="AJ128" s="69"/>
+      <c r="AK128" s="69"/>
+      <c r="AL128" s="69"/>
+      <c r="AM128" s="69"/>
+      <c r="AN128" s="69"/>
+      <c r="AO128" s="69"/>
+      <c r="AP128" s="69"/>
+      <c r="AQ128" s="69"/>
+      <c r="AR128" s="69"/>
+      <c r="AS128" s="69"/>
+      <c r="AT128" s="69"/>
+      <c r="AU128" s="69"/>
+      <c r="AV128" s="69"/>
+      <c r="AW128" s="69"/>
+      <c r="AX128" s="69"/>
+      <c r="AY128" s="69"/>
+      <c r="AZ128" s="69"/>
+      <c r="BA128" s="69"/>
+      <c r="BB128" s="69"/>
+      <c r="BC128" s="69"/>
+      <c r="BD128" s="69"/>
+      <c r="BE128" s="69"/>
+      <c r="BF128" s="69"/>
+      <c r="BG128" s="69"/>
+      <c r="BH128" s="69"/>
+      <c r="BI128" s="69"/>
+      <c r="BJ128" s="69"/>
+      <c r="BK128" s="69"/>
+      <c r="BL128" s="69"/>
+      <c r="BM128" s="69"/>
+      <c r="BN128" s="69"/>
+      <c r="BO128" s="69"/>
+      <c r="BP128" s="69"/>
+      <c r="BQ128" s="69"/>
+      <c r="BR128" s="69"/>
+      <c r="BS128" s="69"/>
+      <c r="BT128" s="69"/>
+      <c r="BU128" s="69"/>
+      <c r="BV128" s="69"/>
+      <c r="BW128" s="69"/>
+      <c r="BX128" s="69"/>
+      <c r="BY128" s="69"/>
+      <c r="BZ128" s="69"/>
+      <c r="CA128" s="69"/>
+      <c r="CB128" s="69"/>
+      <c r="CC128" s="69"/>
+      <c r="CD128" s="69"/>
+      <c r="CE128" s="69"/>
+      <c r="CF128" s="69"/>
+      <c r="CG128" s="69"/>
+      <c r="CH128" s="69"/>
+      <c r="CI128" s="69"/>
+      <c r="CJ128" s="69"/>
+      <c r="CK128" s="69"/>
+      <c r="CL128" s="69"/>
+      <c r="CM128" s="69"/>
+      <c r="CN128" s="69"/>
+      <c r="CO128" s="69"/>
+      <c r="CP128" s="69"/>
+      <c r="CQ128" s="69"/>
+      <c r="CR128" s="69"/>
+      <c r="CS128" s="69"/>
+      <c r="CT128" s="69"/>
+      <c r="CU128" s="69"/>
+      <c r="CV128" s="69"/>
+      <c r="CW128" s="69"/>
+      <c r="CX128" s="69"/>
+      <c r="CY128" s="69"/>
+      <c r="CZ128" s="69"/>
+      <c r="DA128" s="69"/>
+      <c r="DB128" s="69"/>
+      <c r="DC128" s="69"/>
+      <c r="DD128" s="69"/>
+      <c r="DE128" s="69"/>
+      <c r="DF128" s="69"/>
+      <c r="DG128" s="69"/>
+      <c r="DH128" s="69"/>
+      <c r="DI128" s="69"/>
+      <c r="DJ128" s="69"/>
+      <c r="DK128" s="69"/>
+      <c r="DL128" s="69"/>
+      <c r="DM128" s="69"/>
+      <c r="DN128" s="69"/>
+      <c r="DO128" s="69"/>
+      <c r="DP128" s="69"/>
+      <c r="DQ128" s="69"/>
+      <c r="DR128" s="69"/>
+      <c r="DS128" s="69"/>
+      <c r="DT128" s="69"/>
+      <c r="DU128" s="69"/>
+      <c r="DV128" s="69"/>
+      <c r="DW128" s="69"/>
+      <c r="DX128" s="69"/>
+      <c r="DY128" s="69"/>
+      <c r="DZ128" s="69"/>
+      <c r="EA128" s="69"/>
+      <c r="EB128" s="69"/>
+      <c r="EC128" s="69"/>
+      <c r="ED128" s="69"/>
+      <c r="EE128" s="69"/>
+      <c r="EF128" s="69"/>
+      <c r="EG128" s="69"/>
+      <c r="EH128" s="69"/>
+      <c r="EI128" s="69"/>
+      <c r="EJ128" s="69"/>
+      <c r="EK128" s="69"/>
+      <c r="EL128" s="69"/>
+      <c r="EM128" s="69"/>
+      <c r="EN128" s="69"/>
+      <c r="EO128" s="69"/>
+      <c r="EP128" s="69"/>
+      <c r="EQ128" s="69"/>
+      <c r="ER128" s="69"/>
+      <c r="ES128" s="69"/>
+      <c r="ET128" s="69"/>
+      <c r="EU128" s="69"/>
+      <c r="EV128" s="69"/>
+      <c r="EW128" s="69"/>
+      <c r="EX128" s="69"/>
+      <c r="EY128" s="69"/>
+      <c r="EZ128" s="69"/>
+      <c r="FA128" s="69"/>
+      <c r="FB128" s="69"/>
+      <c r="FC128" s="69"/>
+      <c r="FD128" s="69"/>
+      <c r="FE128" s="69"/>
+      <c r="FF128" s="69"/>
+      <c r="FG128" s="69"/>
+      <c r="FH128" s="69"/>
+      <c r="FI128" s="69"/>
+      <c r="FJ128" s="69"/>
+      <c r="FK128" s="69"/>
+      <c r="FL128" s="69"/>
+      <c r="FM128" s="69"/>
+      <c r="FN128" s="69"/>
+      <c r="FO128" s="69"/>
+      <c r="FP128" s="69"/>
+      <c r="FQ128" s="69"/>
+      <c r="FR128" s="69"/>
+      <c r="FS128" s="69"/>
+      <c r="FT128" s="69"/>
+      <c r="FU128" s="69"/>
+      <c r="FV128" s="69"/>
+      <c r="FW128" s="69"/>
+      <c r="FX128" s="69"/>
+      <c r="FY128" s="69"/>
+      <c r="FZ128" s="69"/>
+      <c r="GA128" s="69"/>
+      <c r="GB128" s="69"/>
+      <c r="GC128" s="69"/>
+      <c r="GD128" s="69"/>
+      <c r="GE128" s="69"/>
+      <c r="GF128" s="69"/>
+      <c r="GG128" s="69"/>
+      <c r="GH128" s="69"/>
+      <c r="GI128" s="69"/>
+      <c r="GJ128" s="69"/>
+      <c r="GK128" s="69"/>
+      <c r="GL128" s="69"/>
+      <c r="GM128" s="69"/>
+      <c r="GN128" s="69"/>
+      <c r="GO128" s="69"/>
+      <c r="GP128" s="69"/>
+      <c r="GQ128" s="69"/>
+      <c r="GR128" s="69"/>
+      <c r="GS128" s="69"/>
+      <c r="GT128" s="69"/>
+      <c r="GU128" s="69"/>
+      <c r="GV128" s="69"/>
+      <c r="GW128" s="69"/>
+      <c r="GX128" s="69"/>
+      <c r="GY128" s="69"/>
+      <c r="GZ128" s="69"/>
+      <c r="HA128" s="69"/>
+      <c r="HB128" s="69"/>
+      <c r="HC128" s="69"/>
+      <c r="HD128" s="69"/>
+      <c r="HE128" s="69"/>
+      <c r="HF128" s="69"/>
+      <c r="HG128" s="69"/>
+      <c r="HH128" s="69"/>
+      <c r="HI128" s="69"/>
+      <c r="HJ128" s="69"/>
+      <c r="HK128" s="69"/>
+      <c r="HL128" s="69"/>
+      <c r="HM128" s="69"/>
+      <c r="HN128" s="69"/>
+      <c r="HO128" s="69"/>
+      <c r="HP128" s="69"/>
+      <c r="HQ128" s="69"/>
+      <c r="HR128" s="69"/>
+      <c r="HS128" s="69"/>
+      <c r="HT128" s="69"/>
+      <c r="HU128" s="69"/>
+      <c r="HV128" s="69"/>
+      <c r="HW128" s="69"/>
+      <c r="HX128" s="69"/>
+      <c r="HY128" s="69"/>
+      <c r="HZ128" s="69"/>
+      <c r="IA128" s="69"/>
+      <c r="IB128" s="69"/>
+      <c r="IC128" s="69"/>
+      <c r="ID128" s="69"/>
+      <c r="IE128" s="69"/>
+      <c r="IF128" s="69"/>
+      <c r="IG128" s="69"/>
+      <c r="IH128" s="69"/>
+      <c r="II128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV128" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW128" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="129" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A129" s="71" t="s">
-        <v>325</v>
+    <row r="129" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A129" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="C129" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="D129" s="42"/>
+        <v>313</v>
+      </c>
+      <c r="C129" s="61"/>
+      <c r="D129" s="42" t="s">
+        <v>302</v>
+      </c>
       <c r="E129" s="42" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="F129" s="42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G129" s="54" t="s">
         <v>268</v>
@@ -38515,248 +38487,285 @@
       <c r="H129" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="I129" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="I129" s="45"/>
       <c r="J129" s="46"/>
-      <c r="K129" s="46"/>
-      <c r="L129" s="46"/>
-      <c r="M129" s="46"/>
-      <c r="N129" s="46"/>
-      <c r="O129" s="46"/>
-      <c r="P129" s="46"/>
-      <c r="Q129" s="46"/>
-      <c r="R129" s="46"/>
-      <c r="S129" s="46"/>
-      <c r="T129" s="46"/>
-      <c r="U129" s="46"/>
-      <c r="V129" s="46"/>
-      <c r="W129" s="46"/>
-      <c r="X129" s="46"/>
-      <c r="Y129" s="46"/>
-      <c r="Z129" s="46"/>
-      <c r="AA129" s="46"/>
-      <c r="AB129" s="46"/>
-      <c r="AC129" s="46"/>
-      <c r="AD129" s="46"/>
-      <c r="AE129" s="46"/>
-      <c r="AF129" s="46"/>
-      <c r="AG129" s="46"/>
-      <c r="AH129" s="46"/>
-      <c r="AI129" s="46"/>
-      <c r="AJ129" s="46"/>
-      <c r="AK129" s="46"/>
-      <c r="AL129" s="46"/>
-      <c r="AM129" s="46"/>
-      <c r="AN129" s="46"/>
-      <c r="AO129" s="46"/>
-      <c r="AP129" s="46"/>
-      <c r="AQ129" s="46"/>
-      <c r="AR129" s="46"/>
-      <c r="AS129" s="46"/>
-      <c r="AT129" s="46"/>
-      <c r="AU129" s="46"/>
-      <c r="AV129" s="46"/>
-      <c r="AW129" s="46"/>
-      <c r="AX129" s="46"/>
-      <c r="AY129" s="46"/>
-      <c r="AZ129" s="46"/>
-      <c r="BA129" s="46"/>
-      <c r="BB129" s="46"/>
-      <c r="BC129" s="46"/>
-      <c r="BD129" s="46"/>
-      <c r="BE129" s="46"/>
-      <c r="BF129" s="46"/>
-      <c r="BG129" s="46"/>
-      <c r="BH129" s="46"/>
-      <c r="BI129" s="46"/>
-      <c r="BJ129" s="46"/>
-      <c r="BK129" s="46"/>
-      <c r="BL129" s="46"/>
-      <c r="BM129" s="46"/>
-      <c r="BN129" s="46"/>
-      <c r="BO129" s="46"/>
-      <c r="BP129" s="46"/>
-      <c r="BQ129" s="46"/>
-      <c r="BR129" s="46"/>
-      <c r="BS129" s="46"/>
-      <c r="BT129" s="46"/>
-      <c r="BU129" s="46"/>
-      <c r="BV129" s="46"/>
-      <c r="BW129" s="46"/>
-      <c r="BX129" s="46"/>
-      <c r="BY129" s="46"/>
-      <c r="BZ129" s="46"/>
-      <c r="CA129" s="46"/>
-      <c r="CB129" s="46"/>
-      <c r="CC129" s="46"/>
-      <c r="CD129" s="46"/>
-      <c r="CE129" s="46"/>
-      <c r="CF129" s="46"/>
-      <c r="CG129" s="46"/>
-      <c r="CH129" s="46"/>
-      <c r="CI129" s="46"/>
-      <c r="CJ129" s="46"/>
-      <c r="CK129" s="46"/>
-      <c r="CL129" s="46"/>
-      <c r="CM129" s="46"/>
-      <c r="CN129" s="46"/>
-      <c r="CO129" s="46"/>
-      <c r="CP129" s="46"/>
-      <c r="CQ129" s="46"/>
-      <c r="CR129" s="46"/>
-      <c r="CS129" s="46"/>
-      <c r="CT129" s="46"/>
-      <c r="CU129" s="46"/>
-      <c r="CV129" s="46"/>
-      <c r="CW129" s="46"/>
-      <c r="CX129" s="46"/>
-      <c r="CY129" s="46"/>
-      <c r="CZ129" s="46"/>
-      <c r="DA129" s="46"/>
-      <c r="DB129" s="46"/>
-      <c r="DC129" s="46"/>
-      <c r="DD129" s="46"/>
-      <c r="DE129" s="46"/>
-      <c r="DF129" s="46"/>
-      <c r="DG129" s="46"/>
-      <c r="DH129" s="46"/>
-      <c r="DI129" s="46"/>
-      <c r="DJ129" s="46"/>
-      <c r="DK129" s="46"/>
-      <c r="DL129" s="46"/>
-      <c r="DM129" s="46"/>
-      <c r="DN129" s="46"/>
-      <c r="DO129" s="46"/>
-      <c r="DP129" s="46"/>
-      <c r="DQ129" s="46"/>
-      <c r="DR129" s="46"/>
-      <c r="DS129" s="46"/>
-      <c r="DT129" s="46"/>
-      <c r="DU129" s="46"/>
-      <c r="DV129" s="46"/>
-      <c r="DW129" s="46"/>
-      <c r="DX129" s="46"/>
-      <c r="DY129" s="46"/>
-      <c r="DZ129" s="46"/>
-      <c r="EA129" s="46"/>
-      <c r="EB129" s="46"/>
-      <c r="EC129" s="46"/>
-      <c r="ED129" s="46"/>
-      <c r="EE129" s="46"/>
-      <c r="EF129" s="46"/>
-      <c r="EG129" s="46"/>
-      <c r="EH129" s="46"/>
-      <c r="EI129" s="46"/>
-      <c r="EJ129" s="46"/>
-      <c r="EK129" s="46"/>
-      <c r="EL129" s="46"/>
-      <c r="EM129" s="46"/>
-      <c r="EN129" s="46"/>
-      <c r="EO129" s="46"/>
-      <c r="EP129" s="46"/>
-      <c r="EQ129" s="46"/>
-      <c r="ER129" s="46"/>
-      <c r="ES129" s="46"/>
-      <c r="ET129" s="46"/>
-      <c r="EU129" s="46"/>
-      <c r="EV129" s="46"/>
-      <c r="EW129" s="46"/>
-      <c r="EX129" s="46"/>
-      <c r="EY129" s="46"/>
-      <c r="EZ129" s="46"/>
-      <c r="FA129" s="46"/>
-      <c r="FB129" s="46"/>
-      <c r="FC129" s="46"/>
-      <c r="FD129" s="46"/>
-      <c r="FE129" s="46"/>
-      <c r="FF129" s="46"/>
-      <c r="FG129" s="46"/>
-      <c r="FH129" s="46"/>
-      <c r="FI129" s="46"/>
-      <c r="FJ129" s="46"/>
-      <c r="FK129" s="46"/>
-      <c r="FL129" s="46"/>
-      <c r="FM129" s="46"/>
-      <c r="FN129" s="46"/>
-      <c r="FO129" s="46"/>
-      <c r="FP129" s="46"/>
-      <c r="FQ129" s="46"/>
-      <c r="FR129" s="46"/>
-      <c r="FS129" s="46"/>
-      <c r="FT129" s="46"/>
-      <c r="FU129" s="46"/>
-      <c r="FV129" s="46"/>
-      <c r="FW129" s="46"/>
-      <c r="FX129" s="46"/>
-      <c r="FY129" s="46"/>
-      <c r="FZ129" s="46"/>
-      <c r="GA129" s="46"/>
-      <c r="GB129" s="46"/>
-      <c r="GC129" s="46"/>
-      <c r="GD129" s="46"/>
-      <c r="GE129" s="46"/>
-      <c r="GF129" s="46"/>
-      <c r="GG129" s="46"/>
-      <c r="GH129" s="46"/>
-      <c r="GI129" s="46"/>
-      <c r="GJ129" s="46"/>
-      <c r="GK129" s="46"/>
-      <c r="GL129" s="46"/>
-      <c r="GM129" s="46"/>
-      <c r="GN129" s="46"/>
-      <c r="GO129" s="46"/>
-      <c r="GP129" s="46"/>
-      <c r="GQ129" s="46"/>
-      <c r="GR129" s="46"/>
-      <c r="GS129" s="46"/>
-      <c r="GT129" s="46"/>
-      <c r="GU129" s="46"/>
-      <c r="GV129" s="46"/>
-      <c r="GW129" s="46"/>
-      <c r="GX129" s="46"/>
-      <c r="GY129" s="46"/>
-      <c r="GZ129" s="46"/>
-      <c r="HA129" s="46"/>
-      <c r="HB129" s="46"/>
-      <c r="HC129" s="46"/>
-      <c r="HD129" s="46"/>
-      <c r="HE129" s="46"/>
-      <c r="HF129" s="46"/>
-      <c r="HG129" s="46"/>
-      <c r="HH129" s="46"/>
-      <c r="HI129" s="46"/>
-      <c r="HJ129" s="46"/>
-      <c r="HK129" s="46"/>
-      <c r="HL129" s="46"/>
-      <c r="HM129" s="46"/>
-      <c r="HN129" s="46"/>
-      <c r="HO129" s="46"/>
-      <c r="HP129" s="46"/>
-      <c r="HQ129" s="46"/>
-      <c r="HR129" s="46"/>
-      <c r="HS129" s="46"/>
-      <c r="HT129" s="46"/>
-      <c r="HU129" s="46"/>
-      <c r="HV129" s="46"/>
-      <c r="HW129" s="46"/>
-      <c r="HX129" s="46"/>
-      <c r="HY129" s="46"/>
-      <c r="HZ129" s="46"/>
-      <c r="IA129" s="46"/>
-      <c r="IB129" s="46"/>
-      <c r="IC129" s="46"/>
-      <c r="ID129" s="46"/>
-      <c r="IE129" s="46"/>
-      <c r="IF129" s="46"/>
-      <c r="IG129" s="46"/>
-      <c r="IH129" s="46"/>
-      <c r="II129" s="46"/>
-      <c r="IJ129" s="46"/>
-      <c r="IK129" s="46"/>
-      <c r="IL129" s="46"/>
-      <c r="IM129" s="46"/>
-      <c r="IW129" s="47"/>
+      <c r="K129" s="69"/>
+      <c r="L129" s="69"/>
+      <c r="M129" s="69"/>
+      <c r="N129" s="69"/>
+      <c r="O129" s="69"/>
+      <c r="P129" s="69"/>
+      <c r="Q129" s="69"/>
+      <c r="R129" s="69"/>
+      <c r="S129" s="69"/>
+      <c r="T129" s="69"/>
+      <c r="U129" s="69"/>
+      <c r="V129" s="69"/>
+      <c r="W129" s="69"/>
+      <c r="X129" s="69"/>
+      <c r="Y129" s="69"/>
+      <c r="Z129" s="69"/>
+      <c r="AA129" s="69"/>
+      <c r="AB129" s="69"/>
+      <c r="AC129" s="69"/>
+      <c r="AD129" s="69"/>
+      <c r="AE129" s="69"/>
+      <c r="AF129" s="69"/>
+      <c r="AG129" s="69"/>
+      <c r="AH129" s="69"/>
+      <c r="AI129" s="69"/>
+      <c r="AJ129" s="69"/>
+      <c r="AK129" s="69"/>
+      <c r="AL129" s="69"/>
+      <c r="AM129" s="69"/>
+      <c r="AN129" s="69"/>
+      <c r="AO129" s="69"/>
+      <c r="AP129" s="69"/>
+      <c r="AQ129" s="69"/>
+      <c r="AR129" s="69"/>
+      <c r="AS129" s="69"/>
+      <c r="AT129" s="69"/>
+      <c r="AU129" s="69"/>
+      <c r="AV129" s="69"/>
+      <c r="AW129" s="69"/>
+      <c r="AX129" s="69"/>
+      <c r="AY129" s="69"/>
+      <c r="AZ129" s="69"/>
+      <c r="BA129" s="69"/>
+      <c r="BB129" s="69"/>
+      <c r="BC129" s="69"/>
+      <c r="BD129" s="69"/>
+      <c r="BE129" s="69"/>
+      <c r="BF129" s="69"/>
+      <c r="BG129" s="69"/>
+      <c r="BH129" s="69"/>
+      <c r="BI129" s="69"/>
+      <c r="BJ129" s="69"/>
+      <c r="BK129" s="69"/>
+      <c r="BL129" s="69"/>
+      <c r="BM129" s="69"/>
+      <c r="BN129" s="69"/>
+      <c r="BO129" s="69"/>
+      <c r="BP129" s="69"/>
+      <c r="BQ129" s="69"/>
+      <c r="BR129" s="69"/>
+      <c r="BS129" s="69"/>
+      <c r="BT129" s="69"/>
+      <c r="BU129" s="69"/>
+      <c r="BV129" s="69"/>
+      <c r="BW129" s="69"/>
+      <c r="BX129" s="69"/>
+      <c r="BY129" s="69"/>
+      <c r="BZ129" s="69"/>
+      <c r="CA129" s="69"/>
+      <c r="CB129" s="69"/>
+      <c r="CC129" s="69"/>
+      <c r="CD129" s="69"/>
+      <c r="CE129" s="69"/>
+      <c r="CF129" s="69"/>
+      <c r="CG129" s="69"/>
+      <c r="CH129" s="69"/>
+      <c r="CI129" s="69"/>
+      <c r="CJ129" s="69"/>
+      <c r="CK129" s="69"/>
+      <c r="CL129" s="69"/>
+      <c r="CM129" s="69"/>
+      <c r="CN129" s="69"/>
+      <c r="CO129" s="69"/>
+      <c r="CP129" s="69"/>
+      <c r="CQ129" s="69"/>
+      <c r="CR129" s="69"/>
+      <c r="CS129" s="69"/>
+      <c r="CT129" s="69"/>
+      <c r="CU129" s="69"/>
+      <c r="CV129" s="69"/>
+      <c r="CW129" s="69"/>
+      <c r="CX129" s="69"/>
+      <c r="CY129" s="69"/>
+      <c r="CZ129" s="69"/>
+      <c r="DA129" s="69"/>
+      <c r="DB129" s="69"/>
+      <c r="DC129" s="69"/>
+      <c r="DD129" s="69"/>
+      <c r="DE129" s="69"/>
+      <c r="DF129" s="69"/>
+      <c r="DG129" s="69"/>
+      <c r="DH129" s="69"/>
+      <c r="DI129" s="69"/>
+      <c r="DJ129" s="69"/>
+      <c r="DK129" s="69"/>
+      <c r="DL129" s="69"/>
+      <c r="DM129" s="69"/>
+      <c r="DN129" s="69"/>
+      <c r="DO129" s="69"/>
+      <c r="DP129" s="69"/>
+      <c r="DQ129" s="69"/>
+      <c r="DR129" s="69"/>
+      <c r="DS129" s="69"/>
+      <c r="DT129" s="69"/>
+      <c r="DU129" s="69"/>
+      <c r="DV129" s="69"/>
+      <c r="DW129" s="69"/>
+      <c r="DX129" s="69"/>
+      <c r="DY129" s="69"/>
+      <c r="DZ129" s="69"/>
+      <c r="EA129" s="69"/>
+      <c r="EB129" s="69"/>
+      <c r="EC129" s="69"/>
+      <c r="ED129" s="69"/>
+      <c r="EE129" s="69"/>
+      <c r="EF129" s="69"/>
+      <c r="EG129" s="69"/>
+      <c r="EH129" s="69"/>
+      <c r="EI129" s="69"/>
+      <c r="EJ129" s="69"/>
+      <c r="EK129" s="69"/>
+      <c r="EL129" s="69"/>
+      <c r="EM129" s="69"/>
+      <c r="EN129" s="69"/>
+      <c r="EO129" s="69"/>
+      <c r="EP129" s="69"/>
+      <c r="EQ129" s="69"/>
+      <c r="ER129" s="69"/>
+      <c r="ES129" s="69"/>
+      <c r="ET129" s="69"/>
+      <c r="EU129" s="69"/>
+      <c r="EV129" s="69"/>
+      <c r="EW129" s="69"/>
+      <c r="EX129" s="69"/>
+      <c r="EY129" s="69"/>
+      <c r="EZ129" s="69"/>
+      <c r="FA129" s="69"/>
+      <c r="FB129" s="69"/>
+      <c r="FC129" s="69"/>
+      <c r="FD129" s="69"/>
+      <c r="FE129" s="69"/>
+      <c r="FF129" s="69"/>
+      <c r="FG129" s="69"/>
+      <c r="FH129" s="69"/>
+      <c r="FI129" s="69"/>
+      <c r="FJ129" s="69"/>
+      <c r="FK129" s="69"/>
+      <c r="FL129" s="69"/>
+      <c r="FM129" s="69"/>
+      <c r="FN129" s="69"/>
+      <c r="FO129" s="69"/>
+      <c r="FP129" s="69"/>
+      <c r="FQ129" s="69"/>
+      <c r="FR129" s="69"/>
+      <c r="FS129" s="69"/>
+      <c r="FT129" s="69"/>
+      <c r="FU129" s="69"/>
+      <c r="FV129" s="69"/>
+      <c r="FW129" s="69"/>
+      <c r="FX129" s="69"/>
+      <c r="FY129" s="69"/>
+      <c r="FZ129" s="69"/>
+      <c r="GA129" s="69"/>
+      <c r="GB129" s="69"/>
+      <c r="GC129" s="69"/>
+      <c r="GD129" s="69"/>
+      <c r="GE129" s="69"/>
+      <c r="GF129" s="69"/>
+      <c r="GG129" s="69"/>
+      <c r="GH129" s="69"/>
+      <c r="GI129" s="69"/>
+      <c r="GJ129" s="69"/>
+      <c r="GK129" s="69"/>
+      <c r="GL129" s="69"/>
+      <c r="GM129" s="69"/>
+      <c r="GN129" s="69"/>
+      <c r="GO129" s="69"/>
+      <c r="GP129" s="69"/>
+      <c r="GQ129" s="69"/>
+      <c r="GR129" s="69"/>
+      <c r="GS129" s="69"/>
+      <c r="GT129" s="69"/>
+      <c r="GU129" s="69"/>
+      <c r="GV129" s="69"/>
+      <c r="GW129" s="69"/>
+      <c r="GX129" s="69"/>
+      <c r="GY129" s="69"/>
+      <c r="GZ129" s="69"/>
+      <c r="HA129" s="69"/>
+      <c r="HB129" s="69"/>
+      <c r="HC129" s="69"/>
+      <c r="HD129" s="69"/>
+      <c r="HE129" s="69"/>
+      <c r="HF129" s="69"/>
+      <c r="HG129" s="69"/>
+      <c r="HH129" s="69"/>
+      <c r="HI129" s="69"/>
+      <c r="HJ129" s="69"/>
+      <c r="HK129" s="69"/>
+      <c r="HL129" s="69"/>
+      <c r="HM129" s="69"/>
+      <c r="HN129" s="69"/>
+      <c r="HO129" s="69"/>
+      <c r="HP129" s="69"/>
+      <c r="HQ129" s="69"/>
+      <c r="HR129" s="69"/>
+      <c r="HS129" s="69"/>
+      <c r="HT129" s="69"/>
+      <c r="HU129" s="69"/>
+      <c r="HV129" s="69"/>
+      <c r="HW129" s="69"/>
+      <c r="HX129" s="69"/>
+      <c r="HY129" s="69"/>
+      <c r="HZ129" s="69"/>
+      <c r="IA129" s="69"/>
+      <c r="IB129" s="69"/>
+      <c r="IC129" s="69"/>
+      <c r="ID129" s="69"/>
+      <c r="IE129" s="69"/>
+      <c r="IF129" s="69"/>
+      <c r="IG129" s="69"/>
+      <c r="IH129" s="69"/>
+      <c r="II129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV129" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW129" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="130" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A130" s="71" t="s">
@@ -38766,14 +38775,14 @@
         <v>314</v>
       </c>
       <c r="C130" s="42" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D130" s="42"/>
       <c r="E130" s="42" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F130" s="42" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G130" s="54" t="s">
         <v>268</v>
@@ -39032,14 +39041,14 @@
         <v>314</v>
       </c>
       <c r="C131" s="42" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D131" s="42"/>
       <c r="E131" s="42" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F131" s="42" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="G131" s="54" t="s">
         <v>268</v>
@@ -39298,14 +39307,14 @@
         <v>314</v>
       </c>
       <c r="C132" s="42" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="D132" s="42"/>
       <c r="E132" s="42" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F132" s="42" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G132" s="54" t="s">
         <v>268</v>
@@ -39564,14 +39573,14 @@
         <v>314</v>
       </c>
       <c r="C133" s="42" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D133" s="42"/>
       <c r="E133" s="42" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F133" s="42" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G133" s="54" t="s">
         <v>268</v>
@@ -39822,22 +39831,22 @@
       <c r="IM133" s="46"/>
       <c r="IW133" s="47"/>
     </row>
-    <row r="134" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A134" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B134" s="42" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="C134" s="42" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="F134" s="42" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="G134" s="54" t="s">
         <v>268</v>
@@ -40088,22 +40097,22 @@
       <c r="IM134" s="46"/>
       <c r="IW134" s="47"/>
     </row>
-    <row r="135" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A135" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B135" s="42" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="C135" s="42" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="D135" s="42"/>
       <c r="E135" s="42" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="F135" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G135" s="54" t="s">
         <v>268</v>
@@ -40352,33 +40361,24 @@
       <c r="IK135" s="46"/>
       <c r="IL135" s="46"/>
       <c r="IM135" s="46"/>
-      <c r="IN135" s="39"/>
-      <c r="IO135" s="39"/>
-      <c r="IP135" s="39"/>
-      <c r="IQ135" s="39"/>
-      <c r="IR135" s="39"/>
-      <c r="IS135" s="39"/>
-      <c r="IT135" s="39"/>
-      <c r="IU135" s="39"/>
-      <c r="IV135" s="39"/>
       <c r="IW135" s="47"/>
     </row>
-    <row r="136" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
       <c r="A136" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B136" s="42" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C136" s="42" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D136" s="42"/>
       <c r="E136" s="42" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="F136" s="42" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>268</v>
@@ -40627,33 +40627,24 @@
       <c r="IK136" s="46"/>
       <c r="IL136" s="46"/>
       <c r="IM136" s="46"/>
-      <c r="IN136" s="39"/>
-      <c r="IO136" s="39"/>
-      <c r="IP136" s="39"/>
-      <c r="IQ136" s="39"/>
-      <c r="IR136" s="39"/>
-      <c r="IS136" s="39"/>
-      <c r="IT136" s="39"/>
-      <c r="IU136" s="39"/>
-      <c r="IV136" s="39"/>
       <c r="IW136" s="47"/>
     </row>
-    <row r="137" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A137" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B137" s="42" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C137" s="42" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D137" s="42"/>
       <c r="E137" s="42" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F137" s="42" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="G137" s="54" t="s">
         <v>268</v>
@@ -40918,17 +40909,17 @@
         <v>325</v>
       </c>
       <c r="B138" s="42" t="s">
-        <v>11</v>
+        <v>276</v>
       </c>
       <c r="C138" s="42" t="s">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="42" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="F138" s="42" t="s">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="G138" s="54" t="s">
         <v>268</v>
@@ -41188,30 +41179,32 @@
       <c r="IV138" s="39"/>
       <c r="IW138" s="47"/>
     </row>
-    <row r="139" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A139" s="68" t="s">
-        <v>343</v>
+    <row r="139" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+      <c r="A139" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B139" s="42" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="C139" s="42" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42" t="s">
-        <v>339</v>
+        <v>262</v>
       </c>
       <c r="F139" s="42" t="s">
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="G139" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H139" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I139" s="45"/>
+      <c r="H139" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I139" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J139" s="46"/>
       <c r="K139" s="46"/>
       <c r="L139" s="46"/>
@@ -41462,29 +41455,31 @@
       <c r="IW139" s="47"/>
     </row>
     <row r="140" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A140" s="68" t="s">
-        <v>343</v>
+      <c r="A140" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B140" s="42" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C140" s="42" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="42" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="F140" s="42" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G140" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H140" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I140" s="45"/>
+      <c r="H140" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I140" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J140" s="46"/>
       <c r="K140" s="46"/>
       <c r="L140" s="46"/>
@@ -41734,22 +41729,22 @@
       <c r="IV140" s="39"/>
       <c r="IW140" s="47"/>
     </row>
-    <row r="141" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A141" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B141" s="42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C141" s="42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D141" s="42"/>
       <c r="E141" s="42" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F141" s="42" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G141" s="54" t="s">
         <v>268</v>
@@ -41996,24 +41991,33 @@
       <c r="IK141" s="46"/>
       <c r="IL141" s="46"/>
       <c r="IM141" s="46"/>
+      <c r="IN141" s="39"/>
+      <c r="IO141" s="39"/>
+      <c r="IP141" s="39"/>
+      <c r="IQ141" s="39"/>
+      <c r="IR141" s="39"/>
+      <c r="IS141" s="39"/>
+      <c r="IT141" s="39"/>
+      <c r="IU141" s="39"/>
+      <c r="IV141" s="39"/>
       <c r="IW141" s="47"/>
     </row>
-    <row r="142" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A142" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B142" s="42" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C142" s="42" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D142" s="42"/>
       <c r="E142" s="42" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F142" s="42" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G142" s="54" t="s">
         <v>268</v>
@@ -42260,23 +42264,33 @@
       <c r="IK142" s="46"/>
       <c r="IL142" s="46"/>
       <c r="IM142" s="46"/>
+      <c r="IN142" s="39"/>
+      <c r="IO142" s="39"/>
+      <c r="IP142" s="39"/>
+      <c r="IQ142" s="39"/>
+      <c r="IR142" s="39"/>
+      <c r="IS142" s="39"/>
+      <c r="IT142" s="39"/>
+      <c r="IU142" s="39"/>
+      <c r="IV142" s="39"/>
+      <c r="IW142" s="47"/>
     </row>
     <row r="143" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A143" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B143" s="42" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C143" s="42" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D143" s="42"/>
       <c r="E143" s="42" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F143" s="42" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G143" s="54" t="s">
         <v>268</v>
@@ -42523,23 +42537,24 @@
       <c r="IK143" s="46"/>
       <c r="IL143" s="46"/>
       <c r="IM143" s="46"/>
+      <c r="IW143" s="47"/>
     </row>
     <row r="144" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A144" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B144" s="42" t="s">
-        <v>320</v>
+        <v>27</v>
       </c>
       <c r="C144" s="42" t="s">
-        <v>278</v>
+        <v>28</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F144" s="42" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G144" s="54" t="s">
         <v>268</v>
@@ -42788,19 +42803,29 @@
       <c r="IM144" s="46"/>
     </row>
     <row r="145" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A145" s="72"/>
-      <c r="B145" s="73"/>
-      <c r="C145" s="73"/>
-      <c r="D145" s="73"/>
-      <c r="E145" s="73"/>
-      <c r="F145" s="46"/>
-      <c r="G145" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="H145" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="I145" s="76"/>
+      <c r="A145" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B145" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D145" s="42"/>
+      <c r="E145" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F145" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="G145" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="H145" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I145" s="45"/>
       <c r="J145" s="46"/>
       <c r="K145" s="46"/>
       <c r="L145" s="46"/>
@@ -43039,23 +43064,31 @@
       <c r="IK145" s="46"/>
       <c r="IL145" s="46"/>
       <c r="IM145" s="46"/>
-      <c r="IW145" s="47"/>
     </row>
-    <row r="146" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="B146" s="73"/>
-      <c r="C146" s="73"/>
-      <c r="D146" s="73"/>
-      <c r="E146" s="73"/>
-      <c r="F146" s="46"/>
-      <c r="G146" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="H146" s="79" t="s">
-        <v>344</v>
-      </c>
-      <c r="I146" s="80" t="s">
+    <row r="146" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A146" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="C146" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="D146" s="42"/>
+      <c r="E146" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="F146" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="G146" s="54" t="s">
         <v>268</v>
       </c>
+      <c r="H146" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I146" s="45"/>
       <c r="J146" s="46"/>
       <c r="K146" s="46"/>
       <c r="L146" s="46"/>
@@ -43294,32 +43327,21 @@
       <c r="IK146" s="46"/>
       <c r="IL146" s="46"/>
       <c r="IM146" s="46"/>
-      <c r="IN146" s="39"/>
-      <c r="IO146" s="39"/>
-      <c r="IP146" s="39"/>
-      <c r="IQ146" s="39"/>
-      <c r="IR146" s="39"/>
-      <c r="IS146" s="39"/>
-      <c r="IT146" s="39"/>
-      <c r="IU146" s="39"/>
-      <c r="IV146" s="39"/>
-      <c r="IW146" s="47"/>
     </row>
-    <row r="147" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A147" s="72"/>
       <c r="B147" s="73"/>
       <c r="C147" s="73"/>
       <c r="D147" s="73"/>
       <c r="E147" s="73"/>
       <c r="F147" s="46"/>
-      <c r="G147" s="78" t="s">
-        <v>285</v>
-      </c>
-      <c r="H147" s="79" t="s">
-        <v>345</v>
-      </c>
-      <c r="I147" s="81" t="s">
-        <v>250</v>
-      </c>
+      <c r="G147" s="74" t="s">
+        <v>282</v>
+      </c>
+      <c r="H147" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="I147" s="76"/>
       <c r="J147" s="46"/>
       <c r="K147" s="46"/>
       <c r="L147" s="46"/>
@@ -43558,31 +43580,22 @@
       <c r="IK147" s="46"/>
       <c r="IL147" s="46"/>
       <c r="IM147" s="46"/>
-      <c r="IN147" s="39"/>
-      <c r="IO147" s="39"/>
-      <c r="IP147" s="39"/>
-      <c r="IQ147" s="39"/>
-      <c r="IR147" s="39"/>
-      <c r="IS147" s="39"/>
-      <c r="IT147" s="39"/>
-      <c r="IU147" s="39"/>
-      <c r="IV147" s="39"/>
       <c r="IW147" s="47"/>
     </row>
-    <row r="148" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="B148" s="73"/>
       <c r="C148" s="73"/>
       <c r="D148" s="73"/>
       <c r="E148" s="73"/>
       <c r="F148" s="46"/>
       <c r="G148" s="78" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H148" s="79" t="s">
-        <v>287</v>
-      </c>
-      <c r="I148" s="82" t="s">
-        <v>251</v>
+        <v>344</v>
+      </c>
+      <c r="I148" s="80" t="s">
+        <v>268</v>
       </c>
       <c r="J148" s="46"/>
       <c r="K148" s="46"/>
@@ -43840,13 +43853,13 @@
       <c r="E149" s="73"/>
       <c r="F149" s="46"/>
       <c r="G149" s="78" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H149" s="79" t="s">
-        <v>289</v>
-      </c>
-      <c r="I149" s="83" t="s">
-        <v>272</v>
+        <v>345</v>
+      </c>
+      <c r="I149" s="81" t="s">
+        <v>250</v>
       </c>
       <c r="J149" s="46"/>
       <c r="K149" s="46"/>
@@ -44097,28 +44110,550 @@
       <c r="IV149" s="39"/>
       <c r="IW149" s="47"/>
     </row>
-    <row r="150" spans="1:257" s="90" customFormat="1" ht="46" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="84"/>
-      <c r="B150" s="85"/>
-      <c r="C150" s="85"/>
-      <c r="D150" s="86"/>
-      <c r="E150" s="85"/>
-      <c r="F150" s="85"/>
-      <c r="G150" s="87" t="s">
+    <row r="150" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+      <c r="B150" s="73"/>
+      <c r="C150" s="73"/>
+      <c r="D150" s="73"/>
+      <c r="E150" s="73"/>
+      <c r="F150" s="46"/>
+      <c r="G150" s="78" t="s">
+        <v>286</v>
+      </c>
+      <c r="H150" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="I150" s="82" t="s">
+        <v>251</v>
+      </c>
+      <c r="J150" s="46"/>
+      <c r="K150" s="46"/>
+      <c r="L150" s="46"/>
+      <c r="M150" s="46"/>
+      <c r="N150" s="46"/>
+      <c r="O150" s="46"/>
+      <c r="P150" s="46"/>
+      <c r="Q150" s="46"/>
+      <c r="R150" s="46"/>
+      <c r="S150" s="46"/>
+      <c r="T150" s="46"/>
+      <c r="U150" s="46"/>
+      <c r="V150" s="46"/>
+      <c r="W150" s="46"/>
+      <c r="X150" s="46"/>
+      <c r="Y150" s="46"/>
+      <c r="Z150" s="46"/>
+      <c r="AA150" s="46"/>
+      <c r="AB150" s="46"/>
+      <c r="AC150" s="46"/>
+      <c r="AD150" s="46"/>
+      <c r="AE150" s="46"/>
+      <c r="AF150" s="46"/>
+      <c r="AG150" s="46"/>
+      <c r="AH150" s="46"/>
+      <c r="AI150" s="46"/>
+      <c r="AJ150" s="46"/>
+      <c r="AK150" s="46"/>
+      <c r="AL150" s="46"/>
+      <c r="AM150" s="46"/>
+      <c r="AN150" s="46"/>
+      <c r="AO150" s="46"/>
+      <c r="AP150" s="46"/>
+      <c r="AQ150" s="46"/>
+      <c r="AR150" s="46"/>
+      <c r="AS150" s="46"/>
+      <c r="AT150" s="46"/>
+      <c r="AU150" s="46"/>
+      <c r="AV150" s="46"/>
+      <c r="AW150" s="46"/>
+      <c r="AX150" s="46"/>
+      <c r="AY150" s="46"/>
+      <c r="AZ150" s="46"/>
+      <c r="BA150" s="46"/>
+      <c r="BB150" s="46"/>
+      <c r="BC150" s="46"/>
+      <c r="BD150" s="46"/>
+      <c r="BE150" s="46"/>
+      <c r="BF150" s="46"/>
+      <c r="BG150" s="46"/>
+      <c r="BH150" s="46"/>
+      <c r="BI150" s="46"/>
+      <c r="BJ150" s="46"/>
+      <c r="BK150" s="46"/>
+      <c r="BL150" s="46"/>
+      <c r="BM150" s="46"/>
+      <c r="BN150" s="46"/>
+      <c r="BO150" s="46"/>
+      <c r="BP150" s="46"/>
+      <c r="BQ150" s="46"/>
+      <c r="BR150" s="46"/>
+      <c r="BS150" s="46"/>
+      <c r="BT150" s="46"/>
+      <c r="BU150" s="46"/>
+      <c r="BV150" s="46"/>
+      <c r="BW150" s="46"/>
+      <c r="BX150" s="46"/>
+      <c r="BY150" s="46"/>
+      <c r="BZ150" s="46"/>
+      <c r="CA150" s="46"/>
+      <c r="CB150" s="46"/>
+      <c r="CC150" s="46"/>
+      <c r="CD150" s="46"/>
+      <c r="CE150" s="46"/>
+      <c r="CF150" s="46"/>
+      <c r="CG150" s="46"/>
+      <c r="CH150" s="46"/>
+      <c r="CI150" s="46"/>
+      <c r="CJ150" s="46"/>
+      <c r="CK150" s="46"/>
+      <c r="CL150" s="46"/>
+      <c r="CM150" s="46"/>
+      <c r="CN150" s="46"/>
+      <c r="CO150" s="46"/>
+      <c r="CP150" s="46"/>
+      <c r="CQ150" s="46"/>
+      <c r="CR150" s="46"/>
+      <c r="CS150" s="46"/>
+      <c r="CT150" s="46"/>
+      <c r="CU150" s="46"/>
+      <c r="CV150" s="46"/>
+      <c r="CW150" s="46"/>
+      <c r="CX150" s="46"/>
+      <c r="CY150" s="46"/>
+      <c r="CZ150" s="46"/>
+      <c r="DA150" s="46"/>
+      <c r="DB150" s="46"/>
+      <c r="DC150" s="46"/>
+      <c r="DD150" s="46"/>
+      <c r="DE150" s="46"/>
+      <c r="DF150" s="46"/>
+      <c r="DG150" s="46"/>
+      <c r="DH150" s="46"/>
+      <c r="DI150" s="46"/>
+      <c r="DJ150" s="46"/>
+      <c r="DK150" s="46"/>
+      <c r="DL150" s="46"/>
+      <c r="DM150" s="46"/>
+      <c r="DN150" s="46"/>
+      <c r="DO150" s="46"/>
+      <c r="DP150" s="46"/>
+      <c r="DQ150" s="46"/>
+      <c r="DR150" s="46"/>
+      <c r="DS150" s="46"/>
+      <c r="DT150" s="46"/>
+      <c r="DU150" s="46"/>
+      <c r="DV150" s="46"/>
+      <c r="DW150" s="46"/>
+      <c r="DX150" s="46"/>
+      <c r="DY150" s="46"/>
+      <c r="DZ150" s="46"/>
+      <c r="EA150" s="46"/>
+      <c r="EB150" s="46"/>
+      <c r="EC150" s="46"/>
+      <c r="ED150" s="46"/>
+      <c r="EE150" s="46"/>
+      <c r="EF150" s="46"/>
+      <c r="EG150" s="46"/>
+      <c r="EH150" s="46"/>
+      <c r="EI150" s="46"/>
+      <c r="EJ150" s="46"/>
+      <c r="EK150" s="46"/>
+      <c r="EL150" s="46"/>
+      <c r="EM150" s="46"/>
+      <c r="EN150" s="46"/>
+      <c r="EO150" s="46"/>
+      <c r="EP150" s="46"/>
+      <c r="EQ150" s="46"/>
+      <c r="ER150" s="46"/>
+      <c r="ES150" s="46"/>
+      <c r="ET150" s="46"/>
+      <c r="EU150" s="46"/>
+      <c r="EV150" s="46"/>
+      <c r="EW150" s="46"/>
+      <c r="EX150" s="46"/>
+      <c r="EY150" s="46"/>
+      <c r="EZ150" s="46"/>
+      <c r="FA150" s="46"/>
+      <c r="FB150" s="46"/>
+      <c r="FC150" s="46"/>
+      <c r="FD150" s="46"/>
+      <c r="FE150" s="46"/>
+      <c r="FF150" s="46"/>
+      <c r="FG150" s="46"/>
+      <c r="FH150" s="46"/>
+      <c r="FI150" s="46"/>
+      <c r="FJ150" s="46"/>
+      <c r="FK150" s="46"/>
+      <c r="FL150" s="46"/>
+      <c r="FM150" s="46"/>
+      <c r="FN150" s="46"/>
+      <c r="FO150" s="46"/>
+      <c r="FP150" s="46"/>
+      <c r="FQ150" s="46"/>
+      <c r="FR150" s="46"/>
+      <c r="FS150" s="46"/>
+      <c r="FT150" s="46"/>
+      <c r="FU150" s="46"/>
+      <c r="FV150" s="46"/>
+      <c r="FW150" s="46"/>
+      <c r="FX150" s="46"/>
+      <c r="FY150" s="46"/>
+      <c r="FZ150" s="46"/>
+      <c r="GA150" s="46"/>
+      <c r="GB150" s="46"/>
+      <c r="GC150" s="46"/>
+      <c r="GD150" s="46"/>
+      <c r="GE150" s="46"/>
+      <c r="GF150" s="46"/>
+      <c r="GG150" s="46"/>
+      <c r="GH150" s="46"/>
+      <c r="GI150" s="46"/>
+      <c r="GJ150" s="46"/>
+      <c r="GK150" s="46"/>
+      <c r="GL150" s="46"/>
+      <c r="GM150" s="46"/>
+      <c r="GN150" s="46"/>
+      <c r="GO150" s="46"/>
+      <c r="GP150" s="46"/>
+      <c r="GQ150" s="46"/>
+      <c r="GR150" s="46"/>
+      <c r="GS150" s="46"/>
+      <c r="GT150" s="46"/>
+      <c r="GU150" s="46"/>
+      <c r="GV150" s="46"/>
+      <c r="GW150" s="46"/>
+      <c r="GX150" s="46"/>
+      <c r="GY150" s="46"/>
+      <c r="GZ150" s="46"/>
+      <c r="HA150" s="46"/>
+      <c r="HB150" s="46"/>
+      <c r="HC150" s="46"/>
+      <c r="HD150" s="46"/>
+      <c r="HE150" s="46"/>
+      <c r="HF150" s="46"/>
+      <c r="HG150" s="46"/>
+      <c r="HH150" s="46"/>
+      <c r="HI150" s="46"/>
+      <c r="HJ150" s="46"/>
+      <c r="HK150" s="46"/>
+      <c r="HL150" s="46"/>
+      <c r="HM150" s="46"/>
+      <c r="HN150" s="46"/>
+      <c r="HO150" s="46"/>
+      <c r="HP150" s="46"/>
+      <c r="HQ150" s="46"/>
+      <c r="HR150" s="46"/>
+      <c r="HS150" s="46"/>
+      <c r="HT150" s="46"/>
+      <c r="HU150" s="46"/>
+      <c r="HV150" s="46"/>
+      <c r="HW150" s="46"/>
+      <c r="HX150" s="46"/>
+      <c r="HY150" s="46"/>
+      <c r="HZ150" s="46"/>
+      <c r="IA150" s="46"/>
+      <c r="IB150" s="46"/>
+      <c r="IC150" s="46"/>
+      <c r="ID150" s="46"/>
+      <c r="IE150" s="46"/>
+      <c r="IF150" s="46"/>
+      <c r="IG150" s="46"/>
+      <c r="IH150" s="46"/>
+      <c r="II150" s="46"/>
+      <c r="IJ150" s="46"/>
+      <c r="IK150" s="46"/>
+      <c r="IL150" s="46"/>
+      <c r="IM150" s="46"/>
+      <c r="IN150" s="39"/>
+      <c r="IO150" s="39"/>
+      <c r="IP150" s="39"/>
+      <c r="IQ150" s="39"/>
+      <c r="IR150" s="39"/>
+      <c r="IS150" s="39"/>
+      <c r="IT150" s="39"/>
+      <c r="IU150" s="39"/>
+      <c r="IV150" s="39"/>
+      <c r="IW150" s="47"/>
+    </row>
+    <row r="151" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+      <c r="B151" s="73"/>
+      <c r="C151" s="73"/>
+      <c r="D151" s="73"/>
+      <c r="E151" s="73"/>
+      <c r="F151" s="46"/>
+      <c r="G151" s="78" t="s">
+        <v>288</v>
+      </c>
+      <c r="H151" s="79" t="s">
+        <v>289</v>
+      </c>
+      <c r="I151" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="J151" s="46"/>
+      <c r="K151" s="46"/>
+      <c r="L151" s="46"/>
+      <c r="M151" s="46"/>
+      <c r="N151" s="46"/>
+      <c r="O151" s="46"/>
+      <c r="P151" s="46"/>
+      <c r="Q151" s="46"/>
+      <c r="R151" s="46"/>
+      <c r="S151" s="46"/>
+      <c r="T151" s="46"/>
+      <c r="U151" s="46"/>
+      <c r="V151" s="46"/>
+      <c r="W151" s="46"/>
+      <c r="X151" s="46"/>
+      <c r="Y151" s="46"/>
+      <c r="Z151" s="46"/>
+      <c r="AA151" s="46"/>
+      <c r="AB151" s="46"/>
+      <c r="AC151" s="46"/>
+      <c r="AD151" s="46"/>
+      <c r="AE151" s="46"/>
+      <c r="AF151" s="46"/>
+      <c r="AG151" s="46"/>
+      <c r="AH151" s="46"/>
+      <c r="AI151" s="46"/>
+      <c r="AJ151" s="46"/>
+      <c r="AK151" s="46"/>
+      <c r="AL151" s="46"/>
+      <c r="AM151" s="46"/>
+      <c r="AN151" s="46"/>
+      <c r="AO151" s="46"/>
+      <c r="AP151" s="46"/>
+      <c r="AQ151" s="46"/>
+      <c r="AR151" s="46"/>
+      <c r="AS151" s="46"/>
+      <c r="AT151" s="46"/>
+      <c r="AU151" s="46"/>
+      <c r="AV151" s="46"/>
+      <c r="AW151" s="46"/>
+      <c r="AX151" s="46"/>
+      <c r="AY151" s="46"/>
+      <c r="AZ151" s="46"/>
+      <c r="BA151" s="46"/>
+      <c r="BB151" s="46"/>
+      <c r="BC151" s="46"/>
+      <c r="BD151" s="46"/>
+      <c r="BE151" s="46"/>
+      <c r="BF151" s="46"/>
+      <c r="BG151" s="46"/>
+      <c r="BH151" s="46"/>
+      <c r="BI151" s="46"/>
+      <c r="BJ151" s="46"/>
+      <c r="BK151" s="46"/>
+      <c r="BL151" s="46"/>
+      <c r="BM151" s="46"/>
+      <c r="BN151" s="46"/>
+      <c r="BO151" s="46"/>
+      <c r="BP151" s="46"/>
+      <c r="BQ151" s="46"/>
+      <c r="BR151" s="46"/>
+      <c r="BS151" s="46"/>
+      <c r="BT151" s="46"/>
+      <c r="BU151" s="46"/>
+      <c r="BV151" s="46"/>
+      <c r="BW151" s="46"/>
+      <c r="BX151" s="46"/>
+      <c r="BY151" s="46"/>
+      <c r="BZ151" s="46"/>
+      <c r="CA151" s="46"/>
+      <c r="CB151" s="46"/>
+      <c r="CC151" s="46"/>
+      <c r="CD151" s="46"/>
+      <c r="CE151" s="46"/>
+      <c r="CF151" s="46"/>
+      <c r="CG151" s="46"/>
+      <c r="CH151" s="46"/>
+      <c r="CI151" s="46"/>
+      <c r="CJ151" s="46"/>
+      <c r="CK151" s="46"/>
+      <c r="CL151" s="46"/>
+      <c r="CM151" s="46"/>
+      <c r="CN151" s="46"/>
+      <c r="CO151" s="46"/>
+      <c r="CP151" s="46"/>
+      <c r="CQ151" s="46"/>
+      <c r="CR151" s="46"/>
+      <c r="CS151" s="46"/>
+      <c r="CT151" s="46"/>
+      <c r="CU151" s="46"/>
+      <c r="CV151" s="46"/>
+      <c r="CW151" s="46"/>
+      <c r="CX151" s="46"/>
+      <c r="CY151" s="46"/>
+      <c r="CZ151" s="46"/>
+      <c r="DA151" s="46"/>
+      <c r="DB151" s="46"/>
+      <c r="DC151" s="46"/>
+      <c r="DD151" s="46"/>
+      <c r="DE151" s="46"/>
+      <c r="DF151" s="46"/>
+      <c r="DG151" s="46"/>
+      <c r="DH151" s="46"/>
+      <c r="DI151" s="46"/>
+      <c r="DJ151" s="46"/>
+      <c r="DK151" s="46"/>
+      <c r="DL151" s="46"/>
+      <c r="DM151" s="46"/>
+      <c r="DN151" s="46"/>
+      <c r="DO151" s="46"/>
+      <c r="DP151" s="46"/>
+      <c r="DQ151" s="46"/>
+      <c r="DR151" s="46"/>
+      <c r="DS151" s="46"/>
+      <c r="DT151" s="46"/>
+      <c r="DU151" s="46"/>
+      <c r="DV151" s="46"/>
+      <c r="DW151" s="46"/>
+      <c r="DX151" s="46"/>
+      <c r="DY151" s="46"/>
+      <c r="DZ151" s="46"/>
+      <c r="EA151" s="46"/>
+      <c r="EB151" s="46"/>
+      <c r="EC151" s="46"/>
+      <c r="ED151" s="46"/>
+      <c r="EE151" s="46"/>
+      <c r="EF151" s="46"/>
+      <c r="EG151" s="46"/>
+      <c r="EH151" s="46"/>
+      <c r="EI151" s="46"/>
+      <c r="EJ151" s="46"/>
+      <c r="EK151" s="46"/>
+      <c r="EL151" s="46"/>
+      <c r="EM151" s="46"/>
+      <c r="EN151" s="46"/>
+      <c r="EO151" s="46"/>
+      <c r="EP151" s="46"/>
+      <c r="EQ151" s="46"/>
+      <c r="ER151" s="46"/>
+      <c r="ES151" s="46"/>
+      <c r="ET151" s="46"/>
+      <c r="EU151" s="46"/>
+      <c r="EV151" s="46"/>
+      <c r="EW151" s="46"/>
+      <c r="EX151" s="46"/>
+      <c r="EY151" s="46"/>
+      <c r="EZ151" s="46"/>
+      <c r="FA151" s="46"/>
+      <c r="FB151" s="46"/>
+      <c r="FC151" s="46"/>
+      <c r="FD151" s="46"/>
+      <c r="FE151" s="46"/>
+      <c r="FF151" s="46"/>
+      <c r="FG151" s="46"/>
+      <c r="FH151" s="46"/>
+      <c r="FI151" s="46"/>
+      <c r="FJ151" s="46"/>
+      <c r="FK151" s="46"/>
+      <c r="FL151" s="46"/>
+      <c r="FM151" s="46"/>
+      <c r="FN151" s="46"/>
+      <c r="FO151" s="46"/>
+      <c r="FP151" s="46"/>
+      <c r="FQ151" s="46"/>
+      <c r="FR151" s="46"/>
+      <c r="FS151" s="46"/>
+      <c r="FT151" s="46"/>
+      <c r="FU151" s="46"/>
+      <c r="FV151" s="46"/>
+      <c r="FW151" s="46"/>
+      <c r="FX151" s="46"/>
+      <c r="FY151" s="46"/>
+      <c r="FZ151" s="46"/>
+      <c r="GA151" s="46"/>
+      <c r="GB151" s="46"/>
+      <c r="GC151" s="46"/>
+      <c r="GD151" s="46"/>
+      <c r="GE151" s="46"/>
+      <c r="GF151" s="46"/>
+      <c r="GG151" s="46"/>
+      <c r="GH151" s="46"/>
+      <c r="GI151" s="46"/>
+      <c r="GJ151" s="46"/>
+      <c r="GK151" s="46"/>
+      <c r="GL151" s="46"/>
+      <c r="GM151" s="46"/>
+      <c r="GN151" s="46"/>
+      <c r="GO151" s="46"/>
+      <c r="GP151" s="46"/>
+      <c r="GQ151" s="46"/>
+      <c r="GR151" s="46"/>
+      <c r="GS151" s="46"/>
+      <c r="GT151" s="46"/>
+      <c r="GU151" s="46"/>
+      <c r="GV151" s="46"/>
+      <c r="GW151" s="46"/>
+      <c r="GX151" s="46"/>
+      <c r="GY151" s="46"/>
+      <c r="GZ151" s="46"/>
+      <c r="HA151" s="46"/>
+      <c r="HB151" s="46"/>
+      <c r="HC151" s="46"/>
+      <c r="HD151" s="46"/>
+      <c r="HE151" s="46"/>
+      <c r="HF151" s="46"/>
+      <c r="HG151" s="46"/>
+      <c r="HH151" s="46"/>
+      <c r="HI151" s="46"/>
+      <c r="HJ151" s="46"/>
+      <c r="HK151" s="46"/>
+      <c r="HL151" s="46"/>
+      <c r="HM151" s="46"/>
+      <c r="HN151" s="46"/>
+      <c r="HO151" s="46"/>
+      <c r="HP151" s="46"/>
+      <c r="HQ151" s="46"/>
+      <c r="HR151" s="46"/>
+      <c r="HS151" s="46"/>
+      <c r="HT151" s="46"/>
+      <c r="HU151" s="46"/>
+      <c r="HV151" s="46"/>
+      <c r="HW151" s="46"/>
+      <c r="HX151" s="46"/>
+      <c r="HY151" s="46"/>
+      <c r="HZ151" s="46"/>
+      <c r="IA151" s="46"/>
+      <c r="IB151" s="46"/>
+      <c r="IC151" s="46"/>
+      <c r="ID151" s="46"/>
+      <c r="IE151" s="46"/>
+      <c r="IF151" s="46"/>
+      <c r="IG151" s="46"/>
+      <c r="IH151" s="46"/>
+      <c r="II151" s="46"/>
+      <c r="IJ151" s="46"/>
+      <c r="IK151" s="46"/>
+      <c r="IL151" s="46"/>
+      <c r="IM151" s="46"/>
+      <c r="IN151" s="39"/>
+      <c r="IO151" s="39"/>
+      <c r="IP151" s="39"/>
+      <c r="IQ151" s="39"/>
+      <c r="IR151" s="39"/>
+      <c r="IS151" s="39"/>
+      <c r="IT151" s="39"/>
+      <c r="IU151" s="39"/>
+      <c r="IV151" s="39"/>
+      <c r="IW151" s="47"/>
+    </row>
+    <row r="152" spans="1:257" s="90" customFormat="1" ht="46" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="84"/>
+      <c r="B152" s="85"/>
+      <c r="C152" s="85"/>
+      <c r="D152" s="86"/>
+      <c r="E152" s="85"/>
+      <c r="F152" s="85"/>
+      <c r="G152" s="87" t="s">
         <v>290</v>
       </c>
-      <c r="H150" s="88" t="s">
+      <c r="H152" s="88" t="s">
         <v>291</v>
       </c>
-      <c r="I150" s="89" t="s">
+      <c r="I152" s="89" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="151" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A151" s="84"/>
-    </row>
-    <row r="152" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A152" s="84"/>
     </row>
     <row r="153" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A153" s="84"/>
@@ -44150,13 +44685,19 @@
     <row r="162" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A162" s="84"/>
     </row>
-    <row r="163" spans="1:9" ht="15" x14ac:dyDescent="0.15">
-      <c r="H163" s="90"/>
-      <c r="I163" s="90"/>
+    <row r="163" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A163" s="84"/>
+    </row>
+    <row r="164" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A164" s="84"/>
+    </row>
+    <row r="165" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="H165" s="90"/>
+      <c r="I165" s="90"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
-    <sortCondition ref="A1:A163"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I166">
+    <sortCondition ref="A1:A166"/>
   </sortState>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
@@ -44601,7 +45142,7 @@
       <c r="B35" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="C35" s="92" t="s">
+      <c r="C35" s="97" t="s">
         <v>195</v>
       </c>
       <c r="D35" s="7"/>
@@ -44612,7 +45153,7 @@
       <c r="B36" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C36" s="93"/>
+      <c r="C36" s="98"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
@@ -44621,7 +45162,7 @@
       <c r="B37" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="93"/>
+      <c r="C37" s="98"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
@@ -44630,7 +45171,7 @@
       <c r="B38" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="C38" s="94"/>
+      <c r="C38" s="99"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>

--- a/SlotTemplate_AudioSpec.xlsx
+++ b/SlotTemplate_AudioSpec.xlsx
@@ -5,10 +5,10 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valsamp/Documents/GitHub/igtinteractive/playa-slot-template-tumbling-reels-audio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valsamp/Documents/GitHub/igtinteractive/slot-template-audio-howler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA1FEB1-A6A4-E844-A825-EC34D9DA2DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29D740E-9833-C242-816D-4A41E10D10A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="560">
   <si>
     <t>EVENT</t>
   </si>
@@ -1785,12 +1785,41 @@
   <si>
     <t>onBonusSymbolWinS15</t>
   </si>
+  <si>
+    <t>REMOVED</t>
+  </si>
+  <si>
+    <t>onBonusSymbolLandB01_4</t>
+  </si>
+  <si>
+    <t>onBonusSymbolLandB01_5</t>
+  </si>
+  <si>
+    <t>SymbolB01Land4</t>
+  </si>
+  <si>
+    <t>SymbolB01Land5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SymbolB01Land4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SymbolB01Land5
+</t>
+  </si>
+  <si>
+    <t>onSymbolLandB01_4</t>
+  </si>
+  <si>
+    <t>onSymbolLandB01_5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1959,8 +1988,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2072,8 +2108,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2338,8 +2379,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2348,8 +2404,9 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2608,6 +2665,9 @@
     <xf numFmtId="49" fontId="9" fillId="7" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2617,15 +2677,16 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="20" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="20% - Accent1" xfId="4" builtinId="30"/>
     <cellStyle name="20% - Accent6" xfId="5" builtinId="50"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Input" xfId="6" builtinId="20"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3818,7 +3879,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IW155"/>
+  <dimension ref="A1:IW159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.1640625" style="77" bestFit="1" customWidth="1"/>
@@ -11389,7 +11450,7 @@
       <c r="C29" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="D29" s="99"/>
+      <c r="D29" s="96"/>
       <c r="E29" s="48" t="s">
         <v>364</v>
       </c>
@@ -12457,26 +12518,26 @@
       <c r="IV32" s="39"/>
       <c r="IW32" s="47"/>
     </row>
-    <row r="33" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A33" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="49" t="s">
-        <v>430</v>
+      <c r="B33" s="42"/>
+      <c r="C33" s="59" t="s">
+        <v>558</v>
+      </c>
+      <c r="D33" s="61"/>
+      <c r="E33" s="43" t="s">
+        <v>556</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="58"/>
       <c r="J33" s="46"/>
       <c r="K33" s="46"/>
       <c r="L33" s="46"/>
@@ -12726,20 +12787,20 @@
       <c r="IV33" s="39"/>
       <c r="IW33" s="47"/>
     </row>
-    <row r="34" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A34" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B34" s="42"/>
-      <c r="C34" s="57" t="s">
-        <v>528</v>
-      </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="48" t="s">
-        <v>445</v>
+      <c r="C34" s="59" t="s">
+        <v>559</v>
+      </c>
+      <c r="D34" s="61"/>
+      <c r="E34" s="43" t="s">
+        <v>557</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="G34" s="44" t="s">
         <v>251</v>
@@ -12995,26 +13056,26 @@
       <c r="IV34" s="39"/>
       <c r="IW34" s="47"/>
     </row>
-    <row r="35" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:257" ht="75" x14ac:dyDescent="0.15">
       <c r="A35" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="42"/>
+      <c r="B35" s="60"/>
       <c r="C35" s="42" t="s">
-        <v>74</v>
+        <v>429</v>
       </c>
       <c r="D35" s="42"/>
-      <c r="E35" s="43" t="s">
-        <v>449</v>
+      <c r="E35" s="49" t="s">
+        <v>430</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>532</v>
+        <v>425</v>
       </c>
       <c r="G35" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H35" s="44"/>
-      <c r="I35" s="58"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
       <c r="J35" s="46"/>
       <c r="K35" s="46"/>
       <c r="L35" s="46"/>
@@ -13269,15 +13330,15 @@
         <v>248</v>
       </c>
       <c r="B36" s="42"/>
-      <c r="C36" s="42" t="s">
-        <v>70</v>
+      <c r="C36" s="57" t="s">
+        <v>528</v>
       </c>
       <c r="D36" s="42"/>
-      <c r="E36" s="43" t="s">
-        <v>450</v>
+      <c r="E36" s="48" t="s">
+        <v>445</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="G36" s="44" t="s">
         <v>251</v>
@@ -13533,28 +13594,26 @@
       <c r="IV36" s="39"/>
       <c r="IW36" s="47"/>
     </row>
-    <row r="37" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A37" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B37" s="42"/>
       <c r="C37" s="42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" s="42"/>
       <c r="E37" s="43" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="G37" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H37" s="44"/>
-      <c r="I37" s="58" t="s">
-        <v>78</v>
-      </c>
+      <c r="I37" s="58"/>
       <c r="J37" s="46"/>
       <c r="K37" s="46"/>
       <c r="L37" s="46"/>
@@ -13804,20 +13863,20 @@
       <c r="IV37" s="39"/>
       <c r="IW37" s="47"/>
     </row>
-    <row r="38" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A38" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="42" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D38" s="42"/>
       <c r="E38" s="43" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>515</v>
+        <v>440</v>
       </c>
       <c r="G38" s="44" t="s">
         <v>251</v>
@@ -14073,26 +14132,28 @@
       <c r="IV38" s="39"/>
       <c r="IW38" s="47"/>
     </row>
-    <row r="39" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:257" ht="60" x14ac:dyDescent="0.15">
       <c r="A39" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="42" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D39" s="42"/>
       <c r="E39" s="43" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G39" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H39" s="44"/>
-      <c r="I39" s="58"/>
+      <c r="I39" s="58" t="s">
+        <v>78</v>
+      </c>
       <c r="J39" s="46"/>
       <c r="K39" s="46"/>
       <c r="L39" s="46"/>
@@ -14348,14 +14409,14 @@
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D40" s="42"/>
       <c r="E40" s="43" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G40" s="44" t="s">
         <v>251</v>
@@ -14617,14 +14678,14 @@
       </c>
       <c r="B41" s="42"/>
       <c r="C41" s="42" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="43" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G41" s="44" t="s">
         <v>251</v>
@@ -14886,14 +14947,14 @@
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="42" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D42" s="42"/>
       <c r="E42" s="43" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G42" s="44" t="s">
         <v>251</v>
@@ -15155,14 +15216,14 @@
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D43" s="42"/>
       <c r="E43" s="43" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F43" s="42" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G43" s="44" t="s">
         <v>251</v>
@@ -15424,14 +15485,14 @@
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="42" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D44" s="42"/>
       <c r="E44" s="43" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F44" s="42" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G44" s="44" t="s">
         <v>251</v>
@@ -15693,14 +15754,14 @@
       </c>
       <c r="B45" s="42"/>
       <c r="C45" s="42" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D45" s="42"/>
       <c r="E45" s="43" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G45" s="44" t="s">
         <v>251</v>
@@ -15962,14 +16023,14 @@
       </c>
       <c r="B46" s="42"/>
       <c r="C46" s="42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D46" s="42"/>
       <c r="E46" s="43" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G46" s="44" t="s">
         <v>251</v>
@@ -16231,14 +16292,14 @@
       </c>
       <c r="B47" s="42"/>
       <c r="C47" s="42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D47" s="42"/>
       <c r="E47" s="43" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="G47" s="44" t="s">
         <v>251</v>
@@ -16500,14 +16561,14 @@
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42" t="s">
-        <v>504</v>
+        <v>93</v>
       </c>
       <c r="D48" s="42"/>
       <c r="E48" s="43" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="G48" s="44" t="s">
         <v>251</v>
@@ -16769,14 +16830,14 @@
       </c>
       <c r="B49" s="42"/>
       <c r="C49" s="42" t="s">
-        <v>505</v>
+        <v>94</v>
       </c>
       <c r="D49" s="42"/>
       <c r="E49" s="43" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G49" s="44" t="s">
         <v>251</v>
@@ -17038,14 +17099,14 @@
       </c>
       <c r="B50" s="42"/>
       <c r="C50" s="42" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D50" s="42"/>
       <c r="E50" s="43" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G50" s="44" t="s">
         <v>251</v>
@@ -17307,14 +17368,14 @@
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D51" s="42"/>
       <c r="E51" s="43" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F51" s="42" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G51" s="44" t="s">
         <v>251</v>
@@ -17570,20 +17631,20 @@
       <c r="IV51" s="39"/>
       <c r="IW51" s="47"/>
     </row>
-    <row r="52" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="56" t="s">
         <v>248</v>
       </c>
       <c r="B52" s="42"/>
       <c r="C52" s="42" t="s">
-        <v>75</v>
+        <v>506</v>
       </c>
       <c r="D52" s="42"/>
-      <c r="E52" s="48" t="s">
-        <v>462</v>
+      <c r="E52" s="43" t="s">
+        <v>497</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G52" s="44" t="s">
         <v>251</v>
@@ -17839,26 +17900,26 @@
       <c r="IV52" s="39"/>
       <c r="IW52" s="47"/>
     </row>
-    <row r="53" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A53" s="62" t="s">
-        <v>122</v>
+    <row r="53" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A53" s="56" t="s">
+        <v>248</v>
       </c>
       <c r="B53" s="42"/>
       <c r="C53" s="42" t="s">
-        <v>108</v>
+        <v>507</v>
       </c>
       <c r="D53" s="42"/>
-      <c r="E53" s="48" t="s">
-        <v>350</v>
+      <c r="E53" s="43" t="s">
+        <v>498</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>412</v>
+        <v>503</v>
       </c>
       <c r="G53" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
+      <c r="I53" s="58"/>
       <c r="J53" s="46"/>
       <c r="K53" s="46"/>
       <c r="L53" s="46"/>
@@ -18109,25 +18170,25 @@
       <c r="IW53" s="47"/>
     </row>
     <row r="54" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A54" s="62" t="s">
-        <v>122</v>
+      <c r="A54" s="56" t="s">
+        <v>248</v>
       </c>
       <c r="B54" s="42"/>
       <c r="C54" s="42" t="s">
-        <v>466</v>
+        <v>75</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="48" t="s">
-        <v>381</v>
+        <v>462</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="G54" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H54" s="44"/>
-      <c r="I54" s="63"/>
+      <c r="I54" s="58"/>
       <c r="J54" s="46"/>
       <c r="K54" s="46"/>
       <c r="L54" s="46"/>
@@ -18377,22 +18438,20 @@
       <c r="IV54" s="39"/>
       <c r="IW54" s="47"/>
     </row>
-    <row r="55" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A55" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="42" t="s">
-        <v>136</v>
-      </c>
+      <c r="B55" s="42"/>
       <c r="C55" s="42" t="s">
-        <v>473</v>
+        <v>108</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="48" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="F55" s="42" t="s">
-        <v>138</v>
+        <v>412</v>
       </c>
       <c r="G55" s="44" t="s">
         <v>251</v>
@@ -18652,24 +18711,22 @@
       <c r="A56" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B56" s="42" t="s">
-        <v>128</v>
-      </c>
+      <c r="B56" s="42"/>
       <c r="C56" s="42" t="s">
-        <v>378</v>
+        <v>466</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="48" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>130</v>
+        <v>468</v>
       </c>
       <c r="G56" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H56" s="44"/>
-      <c r="I56" s="45"/>
+      <c r="I56" s="63"/>
       <c r="J56" s="46"/>
       <c r="K56" s="46"/>
       <c r="L56" s="46"/>
@@ -18919,22 +18976,22 @@
       <c r="IV56" s="39"/>
       <c r="IW56" s="47"/>
     </row>
-    <row r="57" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="62" t="s">
         <v>122</v>
       </c>
       <c r="B57" s="42" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>372</v>
+        <v>473</v>
       </c>
       <c r="D57" s="42"/>
       <c r="E57" s="48" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G57" s="44" t="s">
         <v>251</v>
@@ -19198,11 +19255,11 @@
         <v>128</v>
       </c>
       <c r="C58" s="42" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D58" s="42"/>
       <c r="E58" s="48" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F58" s="42" t="s">
         <v>130</v>
@@ -19461,7 +19518,7 @@
       <c r="IV58" s="39"/>
       <c r="IW58" s="47"/>
     </row>
-    <row r="59" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A59" s="62" t="s">
         <v>122</v>
       </c>
@@ -19469,11 +19526,11 @@
         <v>128</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D59" s="42"/>
       <c r="E59" s="48" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F59" s="42" t="s">
         <v>130</v>
@@ -19732,20 +19789,22 @@
       <c r="IV59" s="39"/>
       <c r="IW59" s="47"/>
     </row>
-    <row r="60" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A60" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="42"/>
+      <c r="B60" s="42" t="s">
+        <v>128</v>
+      </c>
       <c r="C60" s="42" t="s">
-        <v>474</v>
+        <v>375</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="48" t="s">
-        <v>475</v>
+        <v>376</v>
       </c>
       <c r="F60" s="42" t="s">
-        <v>477</v>
+        <v>130</v>
       </c>
       <c r="G60" s="44" t="s">
         <v>251</v>
@@ -20001,20 +20060,22 @@
       <c r="IV60" s="39"/>
       <c r="IW60" s="47"/>
     </row>
-    <row r="61" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:257" ht="45" x14ac:dyDescent="0.15">
       <c r="A61" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="42"/>
+      <c r="B61" s="42" t="s">
+        <v>128</v>
+      </c>
       <c r="C61" s="42" t="s">
-        <v>469</v>
+        <v>371</v>
       </c>
       <c r="D61" s="42"/>
       <c r="E61" s="48" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F61" s="42" t="s">
-        <v>470</v>
+        <v>130</v>
       </c>
       <c r="G61" s="44" t="s">
         <v>251</v>
@@ -20270,26 +20331,26 @@
       <c r="IV61" s="39"/>
       <c r="IW61" s="47"/>
     </row>
-    <row r="62" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="62" t="s">
         <v>122</v>
       </c>
       <c r="B62" s="42"/>
       <c r="C62" s="42" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D62" s="42"/>
-      <c r="E62" s="43" t="s">
-        <v>370</v>
+      <c r="E62" s="48" t="s">
+        <v>475</v>
       </c>
       <c r="F62" s="42" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G62" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H62" s="44"/>
-      <c r="I62" s="63"/>
+      <c r="I62" s="45"/>
       <c r="J62" s="46"/>
       <c r="K62" s="46"/>
       <c r="L62" s="46"/>
@@ -20543,24 +20604,22 @@
       <c r="A63" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="42" t="s">
-        <v>110</v>
-      </c>
+      <c r="B63" s="42"/>
       <c r="C63" s="42" t="s">
-        <v>111</v>
+        <v>469</v>
       </c>
       <c r="D63" s="42"/>
       <c r="E63" s="48" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="F63" s="42" t="s">
-        <v>109</v>
+        <v>470</v>
       </c>
       <c r="G63" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H63" s="44"/>
-      <c r="I63" s="63"/>
+      <c r="I63" s="45"/>
       <c r="J63" s="46"/>
       <c r="K63" s="46"/>
       <c r="L63" s="46"/>
@@ -20810,28 +20869,26 @@
       <c r="IV63" s="39"/>
       <c r="IW63" s="47"/>
     </row>
-    <row r="64" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A64" s="64" t="s">
-        <v>388</v>
-      </c>
-      <c r="B64" s="42" t="s">
-        <v>131</v>
-      </c>
+    <row r="64" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A64" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" s="42"/>
       <c r="C64" s="42" t="s">
-        <v>533</v>
+        <v>471</v>
       </c>
       <c r="D64" s="42"/>
-      <c r="E64" s="48" t="s">
-        <v>389</v>
+      <c r="E64" s="43" t="s">
+        <v>370</v>
       </c>
       <c r="F64" s="42" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G64" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H64" s="44"/>
-      <c r="I64" s="45"/>
+      <c r="I64" s="63"/>
       <c r="J64" s="46"/>
       <c r="K64" s="46"/>
       <c r="L64" s="46"/>
@@ -21081,28 +21138,28 @@
       <c r="IV64" s="39"/>
       <c r="IW64" s="47"/>
     </row>
-    <row r="65" spans="1:257" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="64" t="s">
-        <v>388</v>
+    <row r="65" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A65" s="62" t="s">
+        <v>122</v>
       </c>
       <c r="B65" s="42" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>534</v>
+        <v>111</v>
       </c>
       <c r="D65" s="42"/>
       <c r="E65" s="48" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F65" s="42" t="s">
-        <v>481</v>
+        <v>109</v>
       </c>
       <c r="G65" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H65" s="44"/>
-      <c r="I65" s="45"/>
+      <c r="I65" s="63"/>
       <c r="J65" s="46"/>
       <c r="K65" s="46"/>
       <c r="L65" s="46"/>
@@ -21352,7 +21409,7 @@
       <c r="IV65" s="39"/>
       <c r="IW65" s="47"/>
     </row>
-    <row r="66" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="64" t="s">
         <v>388</v>
       </c>
@@ -21360,14 +21417,14 @@
         <v>131</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G66" s="44" t="s">
         <v>251</v>
@@ -21623,28 +21680,28 @@
       <c r="IV66" s="39"/>
       <c r="IW66" s="47"/>
     </row>
-    <row r="67" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:257" ht="31" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="64" t="s">
         <v>388</v>
       </c>
       <c r="B67" s="42" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="C67" s="42" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D67" s="42"/>
       <c r="E67" s="48" t="s">
-        <v>482</v>
+        <v>391</v>
       </c>
       <c r="F67" s="42" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="G67" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H67" s="44"/>
-      <c r="I67" s="58"/>
+      <c r="I67" s="45"/>
       <c r="J67" s="46"/>
       <c r="K67" s="46"/>
       <c r="L67" s="46"/>
@@ -21894,28 +21951,28 @@
       <c r="IV67" s="39"/>
       <c r="IW67" s="47"/>
     </row>
-    <row r="68" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="64" t="s">
         <v>388</v>
       </c>
       <c r="B68" s="42" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D68" s="42"/>
       <c r="E68" s="48" t="s">
-        <v>483</v>
+        <v>390</v>
       </c>
       <c r="F68" s="42" t="s">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="G68" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H68" s="44"/>
-      <c r="I68" s="58"/>
+      <c r="I68" s="45"/>
       <c r="J68" s="46"/>
       <c r="K68" s="46"/>
       <c r="L68" s="46"/>
@@ -22165,28 +22222,28 @@
       <c r="IV68" s="39"/>
       <c r="IW68" s="47"/>
     </row>
-    <row r="69" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="64" t="s">
         <v>388</v>
       </c>
       <c r="B69" s="42" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="D69" s="42"/>
       <c r="E69" s="48" t="s">
-        <v>484</v>
+        <v>554</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="G69" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H69" s="44"/>
-      <c r="I69" s="58"/>
+      <c r="I69" s="45"/>
       <c r="J69" s="46"/>
       <c r="K69" s="46"/>
       <c r="L69" s="46"/>
@@ -22436,28 +22493,28 @@
       <c r="IV69" s="39"/>
       <c r="IW69" s="47"/>
     </row>
-    <row r="70" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:257" ht="76" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="64" t="s">
         <v>388</v>
       </c>
       <c r="B70" s="42" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="D70" s="42"/>
       <c r="E70" s="48" t="s">
-        <v>485</v>
+        <v>555</v>
       </c>
       <c r="F70" s="42" t="s">
-        <v>84</v>
+        <v>480</v>
       </c>
       <c r="G70" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H70" s="44"/>
-      <c r="I70" s="58"/>
+      <c r="I70" s="45"/>
       <c r="J70" s="46"/>
       <c r="K70" s="46"/>
       <c r="L70" s="46"/>
@@ -22715,14 +22772,14 @@
         <v>380</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D71" s="42"/>
       <c r="E71" s="48" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F71" s="42" t="s">
-        <v>86</v>
+        <v>508</v>
       </c>
       <c r="G71" s="44" t="s">
         <v>251</v>
@@ -22986,14 +23043,14 @@
         <v>380</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D72" s="42"/>
       <c r="E72" s="48" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G72" s="44" t="s">
         <v>251</v>
@@ -23257,14 +23314,14 @@
         <v>380</v>
       </c>
       <c r="C73" s="42" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D73" s="42"/>
       <c r="E73" s="48" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F73" s="42" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G73" s="44" t="s">
         <v>251</v>
@@ -23528,11 +23585,11 @@
         <v>380</v>
       </c>
       <c r="C74" s="42" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D74" s="42"/>
       <c r="E74" s="48" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F74" s="42" t="s">
         <v>84</v>
@@ -23799,11 +23856,11 @@
         <v>380</v>
       </c>
       <c r="C75" s="42" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D75" s="42"/>
       <c r="E75" s="48" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F75" s="42" t="s">
         <v>86</v>
@@ -24070,11 +24127,11 @@
         <v>380</v>
       </c>
       <c r="C76" s="42" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D76" s="42"/>
       <c r="E76" s="48" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F76" s="42" t="s">
         <v>88</v>
@@ -24341,14 +24398,14 @@
         <v>380</v>
       </c>
       <c r="C77" s="42" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D77" s="42"/>
       <c r="E77" s="48" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F77" s="42" t="s">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="G77" s="44" t="s">
         <v>251</v>
@@ -24612,14 +24669,14 @@
         <v>380</v>
       </c>
       <c r="C78" s="42" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D78" s="42"/>
       <c r="E78" s="48" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="F78" s="42" t="s">
-        <v>499</v>
+        <v>84</v>
       </c>
       <c r="G78" s="44" t="s">
         <v>251</v>
@@ -24883,14 +24940,14 @@
         <v>380</v>
       </c>
       <c r="C79" s="42" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D79" s="42"/>
       <c r="E79" s="48" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="F79" s="42" t="s">
-        <v>501</v>
+        <v>86</v>
       </c>
       <c r="G79" s="44" t="s">
         <v>251</v>
@@ -25154,14 +25211,14 @@
         <v>380</v>
       </c>
       <c r="C80" s="42" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D80" s="42"/>
       <c r="E80" s="48" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="F80" s="42" t="s">
-        <v>502</v>
+        <v>88</v>
       </c>
       <c r="G80" s="44" t="s">
         <v>251</v>
@@ -25425,14 +25482,14 @@
         <v>380</v>
       </c>
       <c r="C81" s="42" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D81" s="42"/>
       <c r="E81" s="48" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="F81" s="42" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G81" s="44" t="s">
         <v>251</v>
@@ -25689,29 +25746,27 @@
       <c r="IW81" s="47"/>
     </row>
     <row r="82" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A82" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="B82" s="42"/>
+      <c r="A82" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B82" s="42" t="s">
+        <v>380</v>
+      </c>
       <c r="C82" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D82" s="42" t="s">
-        <v>369</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="D82" s="42"/>
       <c r="E82" s="48" t="s">
-        <v>427</v>
+        <v>509</v>
       </c>
       <c r="F82" s="42" t="s">
-        <v>415</v>
+        <v>499</v>
       </c>
       <c r="G82" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H82" s="44"/>
-      <c r="I82" s="45" t="s">
-        <v>428</v>
-      </c>
+      <c r="I82" s="58"/>
       <c r="J82" s="46"/>
       <c r="K82" s="46"/>
       <c r="L82" s="46"/>
@@ -25961,28 +26016,28 @@
       <c r="IV82" s="39"/>
       <c r="IW82" s="47"/>
     </row>
-    <row r="83" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A83" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="B83" s="42"/>
+    <row r="83" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A83" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B83" s="42" t="s">
+        <v>380</v>
+      </c>
       <c r="C83" s="42" t="s">
-        <v>59</v>
+        <v>548</v>
       </c>
       <c r="D83" s="42"/>
-      <c r="E83" s="43" t="s">
-        <v>392</v>
+      <c r="E83" s="48" t="s">
+        <v>510</v>
       </c>
       <c r="F83" s="42" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
       <c r="G83" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H83" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I83" s="45"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="58"/>
       <c r="J83" s="46"/>
       <c r="K83" s="46"/>
       <c r="L83" s="46"/>
@@ -26232,26 +26287,28 @@
       <c r="IV83" s="39"/>
       <c r="IW83" s="47"/>
     </row>
-    <row r="84" spans="1:257" ht="75" x14ac:dyDescent="0.15">
-      <c r="A84" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="B84" s="42"/>
-      <c r="C84" s="57" t="s">
-        <v>169</v>
+    <row r="84" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A84" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B84" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="C84" s="42" t="s">
+        <v>549</v>
       </c>
       <c r="D84" s="42"/>
       <c r="E84" s="48" t="s">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="F84" s="42" t="s">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="G84" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H84" s="44"/>
-      <c r="I84" s="45"/>
+      <c r="I84" s="58"/>
       <c r="J84" s="46"/>
       <c r="K84" s="46"/>
       <c r="L84" s="46"/>
@@ -26502,21 +26559,21 @@
       <c r="IW84" s="47"/>
     </row>
     <row r="85" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A85" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="B85" s="42"/>
-      <c r="C85" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D85" s="93" t="s">
-        <v>363</v>
-      </c>
+      <c r="A85" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B85" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="C85" s="42" t="s">
+        <v>550</v>
+      </c>
+      <c r="D85" s="42"/>
       <c r="E85" s="48" t="s">
-        <v>363</v>
+        <v>512</v>
       </c>
       <c r="F85" s="42" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
       <c r="G85" s="44" t="s">
         <v>251</v>
@@ -26773,27 +26830,29 @@
       <c r="IW85" s="47"/>
     </row>
     <row r="86" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A86" s="56" t="s">
-        <v>446</v>
+      <c r="A86" s="41" t="s">
+        <v>443</v>
       </c>
       <c r="B86" s="42"/>
-      <c r="C86" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="D86" s="93" t="s">
-        <v>364</v>
+      <c r="C86" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D86" s="42" t="s">
+        <v>369</v>
       </c>
       <c r="E86" s="48" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="F86" s="42" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G86" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H86" s="44"/>
-      <c r="I86" s="58"/>
+      <c r="I86" s="45" t="s">
+        <v>428</v>
+      </c>
       <c r="J86" s="46"/>
       <c r="K86" s="46"/>
       <c r="L86" s="46"/>
@@ -27044,27 +27103,27 @@
       <c r="IW86" s="47"/>
     </row>
     <row r="87" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A87" s="56" t="s">
-        <v>446</v>
+      <c r="A87" s="41" t="s">
+        <v>443</v>
       </c>
       <c r="B87" s="42"/>
-      <c r="C87" s="57" t="s">
-        <v>367</v>
-      </c>
-      <c r="D87" s="42" t="s">
-        <v>362</v>
-      </c>
-      <c r="E87" s="48" t="s">
-        <v>362</v>
+      <c r="C87" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="42"/>
+      <c r="E87" s="43" t="s">
+        <v>392</v>
       </c>
       <c r="F87" s="42" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="G87" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H87" s="44"/>
-      <c r="I87" s="58"/>
+      <c r="H87" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I87" s="45"/>
       <c r="J87" s="46"/>
       <c r="K87" s="46"/>
       <c r="L87" s="46"/>
@@ -27314,28 +27373,26 @@
       <c r="IV87" s="39"/>
       <c r="IW87" s="47"/>
     </row>
-    <row r="88" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A88" s="56" t="s">
-        <v>446</v>
+    <row r="88" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+      <c r="A88" s="41" t="s">
+        <v>443</v>
       </c>
       <c r="B88" s="42"/>
       <c r="C88" s="57" t="s">
-        <v>360</v>
-      </c>
-      <c r="D88" s="42" t="s">
-        <v>361</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="D88" s="42"/>
       <c r="E88" s="48" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F88" s="42" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="G88" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H88" s="44"/>
-      <c r="I88" s="58"/>
+      <c r="I88" s="45"/>
       <c r="J88" s="46"/>
       <c r="K88" s="46"/>
       <c r="L88" s="46"/>
@@ -27585,22 +27642,22 @@
       <c r="IV88" s="39"/>
       <c r="IW88" s="47"/>
     </row>
-    <row r="89" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A89" s="56" t="s">
         <v>446</v>
       </c>
       <c r="B89" s="42"/>
-      <c r="C89" s="59" t="s">
-        <v>365</v>
-      </c>
-      <c r="D89" s="42" t="s">
-        <v>386</v>
+      <c r="C89" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D89" s="93" t="s">
+        <v>363</v>
       </c>
       <c r="E89" s="48" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F89" s="42" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G89" s="44" t="s">
         <v>251</v>
@@ -27856,20 +27913,22 @@
       <c r="IV89" s="39"/>
       <c r="IW89" s="47"/>
     </row>
-    <row r="90" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A90" s="56" t="s">
         <v>446</v>
       </c>
       <c r="B90" s="42"/>
-      <c r="C90" s="59" t="s">
-        <v>384</v>
-      </c>
-      <c r="D90" s="42"/>
+      <c r="C90" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D90" s="93" t="s">
+        <v>364</v>
+      </c>
       <c r="E90" s="48" t="s">
-        <v>465</v>
+        <v>364</v>
       </c>
       <c r="F90" s="42" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G90" s="44" t="s">
         <v>251</v>
@@ -28125,26 +28184,28 @@
       <c r="IV90" s="39"/>
       <c r="IW90" s="47"/>
     </row>
-    <row r="91" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A91" s="56" t="s">
         <v>446</v>
       </c>
-      <c r="B91" s="60"/>
-      <c r="C91" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="D91" s="42"/>
-      <c r="E91" s="49" t="s">
-        <v>383</v>
+      <c r="B91" s="42"/>
+      <c r="C91" s="57" t="s">
+        <v>367</v>
+      </c>
+      <c r="D91" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="E91" s="48" t="s">
+        <v>362</v>
       </c>
       <c r="F91" s="42" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G91" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="58"/>
       <c r="J91" s="46"/>
       <c r="K91" s="46"/>
       <c r="L91" s="46"/>
@@ -28394,26 +28455,28 @@
       <c r="IV91" s="39"/>
       <c r="IW91" s="47"/>
     </row>
-    <row r="92" spans="1:257" ht="17" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A92" s="56" t="s">
         <v>446</v>
       </c>
-      <c r="B92" s="95"/>
-      <c r="C92" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="D92" s="95"/>
-      <c r="E92" s="95" t="s">
-        <v>445</v>
-      </c>
-      <c r="F92" s="95" t="s">
-        <v>439</v>
+      <c r="B92" s="42"/>
+      <c r="C92" s="57" t="s">
+        <v>360</v>
+      </c>
+      <c r="D92" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="E92" s="48" t="s">
+        <v>361</v>
+      </c>
+      <c r="F92" s="42" t="s">
+        <v>421</v>
       </c>
       <c r="G92" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H92" s="94"/>
-      <c r="I92" s="95"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="58"/>
       <c r="J92" s="46"/>
       <c r="K92" s="46"/>
       <c r="L92" s="46"/>
@@ -28663,26 +28726,30 @@
       <c r="IV92" s="39"/>
       <c r="IW92" s="47"/>
     </row>
-    <row r="93" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A93" s="62" t="s">
-        <v>467</v>
+    <row r="93" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+      <c r="A93" s="56" t="s">
+        <v>446</v>
       </c>
       <c r="B93" s="42"/>
-      <c r="C93" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="D93" s="42"/>
+      <c r="C93" s="59" t="s">
+        <v>365</v>
+      </c>
+      <c r="D93" s="42" t="s">
+        <v>386</v>
+      </c>
       <c r="E93" s="48" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="F93" s="42" t="s">
-        <v>468</v>
-      </c>
-      <c r="G93" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="H93" s="44"/>
-      <c r="I93" s="63"/>
+        <v>422</v>
+      </c>
+      <c r="G93" s="100" t="s">
+        <v>551</v>
+      </c>
+      <c r="H93" s="100" t="s">
+        <v>551</v>
+      </c>
+      <c r="I93" s="58"/>
       <c r="J93" s="46"/>
       <c r="K93" s="46"/>
       <c r="L93" s="46"/>
@@ -28933,25 +29000,25 @@
       <c r="IW93" s="47"/>
     </row>
     <row r="94" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A94" s="62" t="s">
-        <v>467</v>
+      <c r="A94" s="56" t="s">
+        <v>446</v>
       </c>
       <c r="B94" s="42"/>
-      <c r="C94" s="42" t="s">
-        <v>127</v>
+      <c r="C94" s="59" t="s">
+        <v>384</v>
       </c>
       <c r="D94" s="42"/>
       <c r="E94" s="48" t="s">
-        <v>368</v>
+        <v>465</v>
       </c>
       <c r="F94" s="42" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="G94" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H94" s="44"/>
-      <c r="I94" s="45"/>
+      <c r="I94" s="58"/>
       <c r="J94" s="46"/>
       <c r="K94" s="46"/>
       <c r="L94" s="46"/>
@@ -29201,26 +29268,26 @@
       <c r="IV94" s="39"/>
       <c r="IW94" s="47"/>
     </row>
-    <row r="95" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A95" s="62" t="s">
-        <v>467</v>
-      </c>
-      <c r="B95" s="42"/>
+    <row r="95" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+      <c r="A95" s="56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B95" s="60"/>
       <c r="C95" s="42" t="s">
-        <v>124</v>
+        <v>382</v>
       </c>
       <c r="D95" s="42"/>
-      <c r="E95" s="43" t="s">
-        <v>370</v>
+      <c r="E95" s="49" t="s">
+        <v>383</v>
       </c>
       <c r="F95" s="42" t="s">
-        <v>472</v>
+        <v>424</v>
       </c>
       <c r="G95" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H95" s="44"/>
-      <c r="I95" s="63"/>
+      <c r="H95" s="45"/>
+      <c r="I95" s="45"/>
       <c r="J95" s="46"/>
       <c r="K95" s="46"/>
       <c r="L95" s="46"/>
@@ -29470,28 +29537,26 @@
       <c r="IV95" s="39"/>
       <c r="IW95" s="47"/>
     </row>
-    <row r="96" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A96" s="62" t="s">
-        <v>467</v>
-      </c>
-      <c r="B96" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C96" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="D96" s="42"/>
-      <c r="E96" s="48" t="s">
-        <v>377</v>
-      </c>
-      <c r="F96" s="42" t="s">
-        <v>138</v>
+    <row r="96" spans="1:257" ht="17" x14ac:dyDescent="0.15">
+      <c r="A96" s="56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B96" s="95"/>
+      <c r="C96" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" s="95"/>
+      <c r="E96" s="95" t="s">
+        <v>445</v>
+      </c>
+      <c r="F96" s="95" t="s">
+        <v>439</v>
       </c>
       <c r="G96" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="H96" s="44"/>
-      <c r="I96" s="45"/>
+      <c r="H96" s="94"/>
+      <c r="I96" s="95"/>
       <c r="J96" s="46"/>
       <c r="K96" s="46"/>
       <c r="L96" s="46"/>
@@ -29741,28 +29806,26 @@
       <c r="IV96" s="39"/>
       <c r="IW96" s="47"/>
     </row>
-    <row r="97" spans="1:257" ht="75" x14ac:dyDescent="0.15">
-      <c r="A97" s="64" t="s">
-        <v>478</v>
-      </c>
-      <c r="B97" s="42" t="s">
-        <v>131</v>
-      </c>
+    <row r="97" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A97" s="62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B97" s="42"/>
       <c r="C97" s="42" t="s">
-        <v>132</v>
+        <v>385</v>
       </c>
       <c r="D97" s="42"/>
       <c r="E97" s="48" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="F97" s="42" t="s">
-        <v>133</v>
+        <v>468</v>
       </c>
       <c r="G97" s="44" t="s">
         <v>251</v>
       </c>
       <c r="H97" s="44"/>
-      <c r="I97" s="45"/>
+      <c r="I97" s="63"/>
       <c r="J97" s="46"/>
       <c r="K97" s="46"/>
       <c r="L97" s="46"/>
@@ -30013,27 +30076,25 @@
       <c r="IW97" s="47"/>
     </row>
     <row r="98" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="A98" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="B98" s="42" t="s">
-        <v>118</v>
-      </c>
+      <c r="A98" s="62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B98" s="42"/>
       <c r="C98" s="42" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D98" s="42"/>
-      <c r="E98" s="43" t="s">
-        <v>338</v>
+      <c r="E98" s="48" t="s">
+        <v>368</v>
       </c>
       <c r="F98" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="G98" s="54" t="s">
-        <v>268</v>
+        <v>470</v>
+      </c>
+      <c r="G98" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="H98" s="44"/>
-      <c r="I98" s="63"/>
+      <c r="I98" s="45"/>
       <c r="J98" s="46"/>
       <c r="K98" s="46"/>
       <c r="L98" s="46"/>
@@ -30283,25 +30344,23 @@
       <c r="IV98" s="39"/>
       <c r="IW98" s="47"/>
     </row>
-    <row r="99" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A99" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="B99" s="42" t="s">
-        <v>115</v>
-      </c>
+    <row r="99" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A99" s="62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B99" s="42"/>
       <c r="C99" s="42" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D99" s="42"/>
       <c r="E99" s="43" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F99" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="G99" s="54" t="s">
-        <v>268</v>
+        <v>472</v>
+      </c>
+      <c r="G99" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="H99" s="44"/>
       <c r="I99" s="63"/>
@@ -30555,26 +30614,26 @@
       <c r="IW99" s="47"/>
     </row>
     <row r="100" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A100" s="66" t="s">
-        <v>279</v>
-      </c>
-      <c r="B100" s="60" t="s">
-        <v>47</v>
+      <c r="A100" s="62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B100" s="42" t="s">
+        <v>136</v>
       </c>
       <c r="C100" s="42" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="D100" s="42"/>
-      <c r="E100" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F100" s="42"/>
-      <c r="G100" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="H100" s="67" t="s">
-        <v>250</v>
-      </c>
+      <c r="E100" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="F100" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G100" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="H100" s="44"/>
       <c r="I100" s="45"/>
       <c r="J100" s="46"/>
       <c r="K100" s="46"/>
@@ -30825,26 +30884,28 @@
       <c r="IV100" s="39"/>
       <c r="IW100" s="47"/>
     </row>
-    <row r="101" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A101" s="66" t="s">
-        <v>279</v>
-      </c>
-      <c r="B101" s="60" t="s">
-        <v>48</v>
+    <row r="101" spans="1:257" ht="75" x14ac:dyDescent="0.15">
+      <c r="A101" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="B101" s="42" t="s">
+        <v>131</v>
       </c>
       <c r="C101" s="42" t="s">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="D101" s="42"/>
-      <c r="E101" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F101" s="42"/>
-      <c r="G101" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="H101" s="67" t="s">
-        <v>250</v>
+      <c r="E101" s="48" t="s">
+        <v>366</v>
+      </c>
+      <c r="F101" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="G101" s="100" t="s">
+        <v>551</v>
+      </c>
+      <c r="H101" s="100" t="s">
+        <v>551</v>
       </c>
       <c r="I101" s="45"/>
       <c r="J101" s="46"/>
@@ -31096,28 +31157,28 @@
       <c r="IV101" s="39"/>
       <c r="IW101" s="47"/>
     </row>
-    <row r="102" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A102" s="66" t="s">
-        <v>279</v>
+    <row r="102" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="A102" s="65" t="s">
+        <v>114</v>
       </c>
       <c r="B102" s="42" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="C102" s="42" t="s">
-        <v>349</v>
+        <v>119</v>
       </c>
       <c r="D102" s="42"/>
-      <c r="E102" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F102" s="42"/>
+      <c r="E102" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="F102" s="42" t="s">
+        <v>120</v>
+      </c>
       <c r="G102" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H102" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="I102" s="45"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="63"/>
       <c r="J102" s="46"/>
       <c r="K102" s="46"/>
       <c r="L102" s="46"/>
@@ -31368,27 +31429,27 @@
       <c r="IW102" s="47"/>
     </row>
     <row r="103" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A103" s="66" t="s">
-        <v>279</v>
+      <c r="A103" s="65" t="s">
+        <v>114</v>
       </c>
       <c r="B103" s="42" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="D103" s="42"/>
-      <c r="E103" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="F103" s="42"/>
+      <c r="E103" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="F103" s="42" t="s">
+        <v>117</v>
+      </c>
       <c r="G103" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H103" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="I103" s="45"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="63"/>
       <c r="J103" s="46"/>
       <c r="K103" s="46"/>
       <c r="L103" s="46"/>
@@ -31643,10 +31704,10 @@
         <v>279</v>
       </c>
       <c r="B104" s="60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C104" s="42" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D104" s="42"/>
       <c r="E104" s="42" t="s">
@@ -31910,27 +31971,25 @@
       <c r="IW104" s="47"/>
     </row>
     <row r="105" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A105" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="B105" s="42" t="s">
-        <v>18</v>
+      <c r="A105" s="66" t="s">
+        <v>279</v>
+      </c>
+      <c r="B105" s="60" t="s">
+        <v>48</v>
       </c>
       <c r="C105" s="42" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="D105" s="42"/>
       <c r="E105" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="F105" s="42" t="s">
-        <v>20</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F105" s="42"/>
       <c r="G105" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H105" s="44" t="s">
-        <v>251</v>
+      <c r="H105" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I105" s="45"/>
       <c r="J105" s="46"/>
@@ -32183,27 +32242,25 @@
       <c r="IW105" s="47"/>
     </row>
     <row r="106" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A106" s="68" t="s">
-        <v>253</v>
+      <c r="A106" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="B106" s="42" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C106" s="42" t="s">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="D106" s="42"/>
       <c r="E106" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="F106" s="42" t="s">
-        <v>23</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F106" s="42"/>
       <c r="G106" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H106" s="44" t="s">
-        <v>251</v>
+      <c r="H106" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I106" s="45"/>
       <c r="J106" s="46"/>
@@ -32456,27 +32513,25 @@
       <c r="IW106" s="47"/>
     </row>
     <row r="107" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A107" s="68" t="s">
-        <v>253</v>
+      <c r="A107" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="D107" s="42"/>
       <c r="E107" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="F107" s="42" t="s">
-        <v>17</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F107" s="42"/>
       <c r="G107" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H107" s="44" t="s">
-        <v>251</v>
+      <c r="H107" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I107" s="45"/>
       <c r="J107" s="46"/>
@@ -32729,27 +32784,25 @@
       <c r="IW107" s="47"/>
     </row>
     <row r="108" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A108" s="68" t="s">
-        <v>253</v>
+      <c r="A108" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="B108" s="60" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C108" s="42" t="s">
-        <v>46</v>
+        <v>259</v>
       </c>
       <c r="D108" s="42"/>
       <c r="E108" s="42" t="s">
         <v>342</v>
       </c>
-      <c r="F108" s="42" t="s">
-        <v>322</v>
-      </c>
+      <c r="F108" s="42"/>
       <c r="G108" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H108" s="44" t="s">
-        <v>251</v>
+      <c r="H108" s="67" t="s">
+        <v>250</v>
       </c>
       <c r="I108" s="45"/>
       <c r="J108" s="46"/>
@@ -33005,18 +33058,18 @@
       <c r="A109" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B109" s="60" t="s">
-        <v>43</v>
+      <c r="B109" s="42" t="s">
+        <v>18</v>
       </c>
       <c r="C109" s="42" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D109" s="42"/>
       <c r="E109" s="42" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F109" s="42" t="s">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="G109" s="54" t="s">
         <v>268</v>
@@ -33279,17 +33332,17 @@
         <v>253</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C110" s="42" t="s">
-        <v>323</v>
+        <v>22</v>
       </c>
       <c r="D110" s="42"/>
       <c r="E110" s="42" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="F110" s="42" t="s">
-        <v>330</v>
+        <v>23</v>
       </c>
       <c r="G110" s="54" t="s">
         <v>268</v>
@@ -33547,22 +33600,22 @@
       <c r="IV110" s="39"/>
       <c r="IW110" s="47"/>
     </row>
-    <row r="111" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A111" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B111" s="42" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C111" s="42" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D111" s="42"/>
       <c r="E111" s="42" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F111" s="42" t="s">
-        <v>292</v>
+        <v>17</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>268</v>
@@ -33820,22 +33873,22 @@
       <c r="IV111" s="39"/>
       <c r="IW111" s="47"/>
     </row>
-    <row r="112" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A112" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B112" s="42" t="s">
-        <v>6</v>
+      <c r="B112" s="60" t="s">
+        <v>45</v>
       </c>
       <c r="C112" s="42" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="D112" s="42"/>
       <c r="E112" s="42" t="s">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="F112" s="42" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>268</v>
@@ -34082,23 +34135,34 @@
       <c r="IK112" s="46"/>
       <c r="IL112" s="46"/>
       <c r="IM112" s="46"/>
+      <c r="IN112" s="39"/>
+      <c r="IO112" s="39"/>
+      <c r="IP112" s="39"/>
+      <c r="IQ112" s="39"/>
+      <c r="IR112" s="39"/>
+      <c r="IS112" s="39"/>
+      <c r="IT112" s="39"/>
+      <c r="IU112" s="39"/>
+      <c r="IV112" s="39"/>
       <c r="IW112" s="47"/>
     </row>
-    <row r="113" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A113" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B113" s="60" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C113" s="42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D113" s="42"/>
       <c r="E113" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F113" s="42"/>
+        <v>245</v>
+      </c>
+      <c r="F113" s="42" t="s">
+        <v>281</v>
+      </c>
       <c r="G113" s="54" t="s">
         <v>268</v>
       </c>
@@ -34344,23 +34408,34 @@
       <c r="IK113" s="46"/>
       <c r="IL113" s="46"/>
       <c r="IM113" s="46"/>
+      <c r="IN113" s="39"/>
+      <c r="IO113" s="39"/>
+      <c r="IP113" s="39"/>
+      <c r="IQ113" s="39"/>
+      <c r="IR113" s="39"/>
+      <c r="IS113" s="39"/>
+      <c r="IT113" s="39"/>
+      <c r="IU113" s="39"/>
+      <c r="IV113" s="39"/>
       <c r="IW113" s="47"/>
     </row>
-    <row r="114" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A114" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="60" t="s">
-        <v>39</v>
+      <c r="B114" s="42" t="s">
+        <v>51</v>
       </c>
       <c r="C114" s="42" t="s">
-        <v>40</v>
+        <v>323</v>
       </c>
       <c r="D114" s="42"/>
       <c r="E114" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="F114" s="42"/>
+        <v>324</v>
+      </c>
+      <c r="F114" s="42" t="s">
+        <v>330</v>
+      </c>
       <c r="G114" s="54" t="s">
         <v>268</v>
       </c>
@@ -34606,24 +34681,33 @@
       <c r="IK114" s="46"/>
       <c r="IL114" s="46"/>
       <c r="IM114" s="46"/>
+      <c r="IN114" s="39"/>
+      <c r="IO114" s="39"/>
+      <c r="IP114" s="39"/>
+      <c r="IQ114" s="39"/>
+      <c r="IR114" s="39"/>
+      <c r="IS114" s="39"/>
+      <c r="IT114" s="39"/>
+      <c r="IU114" s="39"/>
+      <c r="IV114" s="39"/>
       <c r="IW114" s="47"/>
     </row>
-    <row r="115" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:257" ht="30" x14ac:dyDescent="0.15">
       <c r="A115" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B115" s="60" t="s">
-        <v>4</v>
+      <c r="B115" s="42" t="s">
+        <v>9</v>
       </c>
       <c r="C115" s="42" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D115" s="42"/>
       <c r="E115" s="42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F115" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>268</v>
@@ -34870,24 +34954,33 @@
       <c r="IK115" s="46"/>
       <c r="IL115" s="46"/>
       <c r="IM115" s="46"/>
+      <c r="IN115" s="39"/>
+      <c r="IO115" s="39"/>
+      <c r="IP115" s="39"/>
+      <c r="IQ115" s="39"/>
+      <c r="IR115" s="39"/>
+      <c r="IS115" s="39"/>
+      <c r="IT115" s="39"/>
+      <c r="IU115" s="39"/>
+      <c r="IV115" s="39"/>
       <c r="IW115" s="47"/>
     </row>
-    <row r="116" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A116" s="68" t="s">
         <v>253</v>
       </c>
       <c r="B116" s="42" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C116" s="42" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D116" s="42"/>
       <c r="E116" s="42" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="F116" s="42" t="s">
-        <v>295</v>
+        <v>8</v>
       </c>
       <c r="G116" s="54" t="s">
         <v>268</v>
@@ -34897,301 +34990,260 @@
       </c>
       <c r="I116" s="45"/>
       <c r="J116" s="46"/>
-      <c r="K116" s="69"/>
-      <c r="L116" s="69"/>
-      <c r="M116" s="69"/>
-      <c r="N116" s="69"/>
-      <c r="O116" s="69"/>
-      <c r="P116" s="69"/>
-      <c r="Q116" s="69"/>
-      <c r="R116" s="69"/>
-      <c r="S116" s="69"/>
-      <c r="T116" s="69"/>
-      <c r="U116" s="69"/>
-      <c r="V116" s="69"/>
-      <c r="W116" s="69"/>
-      <c r="X116" s="69"/>
-      <c r="Y116" s="69"/>
-      <c r="Z116" s="69"/>
-      <c r="AA116" s="69"/>
-      <c r="AB116" s="69"/>
-      <c r="AC116" s="69"/>
-      <c r="AD116" s="69"/>
-      <c r="AE116" s="69"/>
-      <c r="AF116" s="69"/>
-      <c r="AG116" s="69"/>
-      <c r="AH116" s="69"/>
-      <c r="AI116" s="69"/>
-      <c r="AJ116" s="69"/>
-      <c r="AK116" s="69"/>
-      <c r="AL116" s="69"/>
-      <c r="AM116" s="69"/>
-      <c r="AN116" s="69"/>
-      <c r="AO116" s="69"/>
-      <c r="AP116" s="69"/>
-      <c r="AQ116" s="69"/>
-      <c r="AR116" s="69"/>
-      <c r="AS116" s="69"/>
-      <c r="AT116" s="69"/>
-      <c r="AU116" s="69"/>
-      <c r="AV116" s="69"/>
-      <c r="AW116" s="69"/>
-      <c r="AX116" s="69"/>
-      <c r="AY116" s="69"/>
-      <c r="AZ116" s="69"/>
-      <c r="BA116" s="69"/>
-      <c r="BB116" s="69"/>
-      <c r="BC116" s="69"/>
-      <c r="BD116" s="69"/>
-      <c r="BE116" s="69"/>
-      <c r="BF116" s="69"/>
-      <c r="BG116" s="69"/>
-      <c r="BH116" s="69"/>
-      <c r="BI116" s="69"/>
-      <c r="BJ116" s="69"/>
-      <c r="BK116" s="69"/>
-      <c r="BL116" s="69"/>
-      <c r="BM116" s="69"/>
-      <c r="BN116" s="69"/>
-      <c r="BO116" s="69"/>
-      <c r="BP116" s="69"/>
-      <c r="BQ116" s="69"/>
-      <c r="BR116" s="69"/>
-      <c r="BS116" s="69"/>
-      <c r="BT116" s="69"/>
-      <c r="BU116" s="69"/>
-      <c r="BV116" s="69"/>
-      <c r="BW116" s="69"/>
-      <c r="BX116" s="69"/>
-      <c r="BY116" s="69"/>
-      <c r="BZ116" s="69"/>
-      <c r="CA116" s="69"/>
-      <c r="CB116" s="69"/>
-      <c r="CC116" s="69"/>
-      <c r="CD116" s="69"/>
-      <c r="CE116" s="69"/>
-      <c r="CF116" s="69"/>
-      <c r="CG116" s="69"/>
-      <c r="CH116" s="69"/>
-      <c r="CI116" s="69"/>
-      <c r="CJ116" s="69"/>
-      <c r="CK116" s="69"/>
-      <c r="CL116" s="69"/>
-      <c r="CM116" s="69"/>
-      <c r="CN116" s="69"/>
-      <c r="CO116" s="69"/>
-      <c r="CP116" s="69"/>
-      <c r="CQ116" s="69"/>
-      <c r="CR116" s="69"/>
-      <c r="CS116" s="69"/>
-      <c r="CT116" s="69"/>
-      <c r="CU116" s="69"/>
-      <c r="CV116" s="69"/>
-      <c r="CW116" s="69"/>
-      <c r="CX116" s="69"/>
-      <c r="CY116" s="69"/>
-      <c r="CZ116" s="69"/>
-      <c r="DA116" s="69"/>
-      <c r="DB116" s="69"/>
-      <c r="DC116" s="69"/>
-      <c r="DD116" s="69"/>
-      <c r="DE116" s="69"/>
-      <c r="DF116" s="69"/>
-      <c r="DG116" s="69"/>
-      <c r="DH116" s="69"/>
-      <c r="DI116" s="69"/>
-      <c r="DJ116" s="69"/>
-      <c r="DK116" s="69"/>
-      <c r="DL116" s="69"/>
-      <c r="DM116" s="69"/>
-      <c r="DN116" s="69"/>
-      <c r="DO116" s="69"/>
-      <c r="DP116" s="69"/>
-      <c r="DQ116" s="69"/>
-      <c r="DR116" s="69"/>
-      <c r="DS116" s="69"/>
-      <c r="DT116" s="69"/>
-      <c r="DU116" s="69"/>
-      <c r="DV116" s="69"/>
-      <c r="DW116" s="69"/>
-      <c r="DX116" s="69"/>
-      <c r="DY116" s="69"/>
-      <c r="DZ116" s="69"/>
-      <c r="EA116" s="69"/>
-      <c r="EB116" s="69"/>
-      <c r="EC116" s="69"/>
-      <c r="ED116" s="69"/>
-      <c r="EE116" s="69"/>
-      <c r="EF116" s="69"/>
-      <c r="EG116" s="69"/>
-      <c r="EH116" s="69"/>
-      <c r="EI116" s="69"/>
-      <c r="EJ116" s="69"/>
-      <c r="EK116" s="69"/>
-      <c r="EL116" s="69"/>
-      <c r="EM116" s="69"/>
-      <c r="EN116" s="69"/>
-      <c r="EO116" s="69"/>
-      <c r="EP116" s="69"/>
-      <c r="EQ116" s="69"/>
-      <c r="ER116" s="69"/>
-      <c r="ES116" s="69"/>
-      <c r="ET116" s="69"/>
-      <c r="EU116" s="69"/>
-      <c r="EV116" s="69"/>
-      <c r="EW116" s="69"/>
-      <c r="EX116" s="69"/>
-      <c r="EY116" s="69"/>
-      <c r="EZ116" s="69"/>
-      <c r="FA116" s="69"/>
-      <c r="FB116" s="69"/>
-      <c r="FC116" s="69"/>
-      <c r="FD116" s="69"/>
-      <c r="FE116" s="69"/>
-      <c r="FF116" s="69"/>
-      <c r="FG116" s="69"/>
-      <c r="FH116" s="69"/>
-      <c r="FI116" s="69"/>
-      <c r="FJ116" s="69"/>
-      <c r="FK116" s="69"/>
-      <c r="FL116" s="69"/>
-      <c r="FM116" s="69"/>
-      <c r="FN116" s="69"/>
-      <c r="FO116" s="69"/>
-      <c r="FP116" s="69"/>
-      <c r="FQ116" s="69"/>
-      <c r="FR116" s="69"/>
-      <c r="FS116" s="69"/>
-      <c r="FT116" s="69"/>
-      <c r="FU116" s="69"/>
-      <c r="FV116" s="69"/>
-      <c r="FW116" s="69"/>
-      <c r="FX116" s="69"/>
-      <c r="FY116" s="69"/>
-      <c r="FZ116" s="69"/>
-      <c r="GA116" s="69"/>
-      <c r="GB116" s="69"/>
-      <c r="GC116" s="69"/>
-      <c r="GD116" s="69"/>
-      <c r="GE116" s="69"/>
-      <c r="GF116" s="69"/>
-      <c r="GG116" s="69"/>
-      <c r="GH116" s="69"/>
-      <c r="GI116" s="69"/>
-      <c r="GJ116" s="69"/>
-      <c r="GK116" s="69"/>
-      <c r="GL116" s="69"/>
-      <c r="GM116" s="69"/>
-      <c r="GN116" s="69"/>
-      <c r="GO116" s="69"/>
-      <c r="GP116" s="69"/>
-      <c r="GQ116" s="69"/>
-      <c r="GR116" s="69"/>
-      <c r="GS116" s="69"/>
-      <c r="GT116" s="69"/>
-      <c r="GU116" s="69"/>
-      <c r="GV116" s="69"/>
-      <c r="GW116" s="69"/>
-      <c r="GX116" s="69"/>
-      <c r="GY116" s="69"/>
-      <c r="GZ116" s="69"/>
-      <c r="HA116" s="69"/>
-      <c r="HB116" s="69"/>
-      <c r="HC116" s="69"/>
-      <c r="HD116" s="69"/>
-      <c r="HE116" s="69"/>
-      <c r="HF116" s="69"/>
-      <c r="HG116" s="69"/>
-      <c r="HH116" s="69"/>
-      <c r="HI116" s="69"/>
-      <c r="HJ116" s="69"/>
-      <c r="HK116" s="69"/>
-      <c r="HL116" s="69"/>
-      <c r="HM116" s="69"/>
-      <c r="HN116" s="69"/>
-      <c r="HO116" s="69"/>
-      <c r="HP116" s="69"/>
-      <c r="HQ116" s="69"/>
-      <c r="HR116" s="69"/>
-      <c r="HS116" s="69"/>
-      <c r="HT116" s="69"/>
-      <c r="HU116" s="69"/>
-      <c r="HV116" s="69"/>
-      <c r="HW116" s="69"/>
-      <c r="HX116" s="69"/>
-      <c r="HY116" s="69"/>
-      <c r="HZ116" s="69"/>
-      <c r="IA116" s="69"/>
-      <c r="IB116" s="69"/>
-      <c r="IC116" s="69"/>
-      <c r="ID116" s="69"/>
-      <c r="IE116" s="69"/>
-      <c r="IF116" s="69"/>
-      <c r="IG116" s="69"/>
-      <c r="IH116" s="69"/>
-      <c r="II116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV116" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW116" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K116" s="46"/>
+      <c r="L116" s="46"/>
+      <c r="M116" s="46"/>
+      <c r="N116" s="46"/>
+      <c r="O116" s="46"/>
+      <c r="P116" s="46"/>
+      <c r="Q116" s="46"/>
+      <c r="R116" s="46"/>
+      <c r="S116" s="46"/>
+      <c r="T116" s="46"/>
+      <c r="U116" s="46"/>
+      <c r="V116" s="46"/>
+      <c r="W116" s="46"/>
+      <c r="X116" s="46"/>
+      <c r="Y116" s="46"/>
+      <c r="Z116" s="46"/>
+      <c r="AA116" s="46"/>
+      <c r="AB116" s="46"/>
+      <c r="AC116" s="46"/>
+      <c r="AD116" s="46"/>
+      <c r="AE116" s="46"/>
+      <c r="AF116" s="46"/>
+      <c r="AG116" s="46"/>
+      <c r="AH116" s="46"/>
+      <c r="AI116" s="46"/>
+      <c r="AJ116" s="46"/>
+      <c r="AK116" s="46"/>
+      <c r="AL116" s="46"/>
+      <c r="AM116" s="46"/>
+      <c r="AN116" s="46"/>
+      <c r="AO116" s="46"/>
+      <c r="AP116" s="46"/>
+      <c r="AQ116" s="46"/>
+      <c r="AR116" s="46"/>
+      <c r="AS116" s="46"/>
+      <c r="AT116" s="46"/>
+      <c r="AU116" s="46"/>
+      <c r="AV116" s="46"/>
+      <c r="AW116" s="46"/>
+      <c r="AX116" s="46"/>
+      <c r="AY116" s="46"/>
+      <c r="AZ116" s="46"/>
+      <c r="BA116" s="46"/>
+      <c r="BB116" s="46"/>
+      <c r="BC116" s="46"/>
+      <c r="BD116" s="46"/>
+      <c r="BE116" s="46"/>
+      <c r="BF116" s="46"/>
+      <c r="BG116" s="46"/>
+      <c r="BH116" s="46"/>
+      <c r="BI116" s="46"/>
+      <c r="BJ116" s="46"/>
+      <c r="BK116" s="46"/>
+      <c r="BL116" s="46"/>
+      <c r="BM116" s="46"/>
+      <c r="BN116" s="46"/>
+      <c r="BO116" s="46"/>
+      <c r="BP116" s="46"/>
+      <c r="BQ116" s="46"/>
+      <c r="BR116" s="46"/>
+      <c r="BS116" s="46"/>
+      <c r="BT116" s="46"/>
+      <c r="BU116" s="46"/>
+      <c r="BV116" s="46"/>
+      <c r="BW116" s="46"/>
+      <c r="BX116" s="46"/>
+      <c r="BY116" s="46"/>
+      <c r="BZ116" s="46"/>
+      <c r="CA116" s="46"/>
+      <c r="CB116" s="46"/>
+      <c r="CC116" s="46"/>
+      <c r="CD116" s="46"/>
+      <c r="CE116" s="46"/>
+      <c r="CF116" s="46"/>
+      <c r="CG116" s="46"/>
+      <c r="CH116" s="46"/>
+      <c r="CI116" s="46"/>
+      <c r="CJ116" s="46"/>
+      <c r="CK116" s="46"/>
+      <c r="CL116" s="46"/>
+      <c r="CM116" s="46"/>
+      <c r="CN116" s="46"/>
+      <c r="CO116" s="46"/>
+      <c r="CP116" s="46"/>
+      <c r="CQ116" s="46"/>
+      <c r="CR116" s="46"/>
+      <c r="CS116" s="46"/>
+      <c r="CT116" s="46"/>
+      <c r="CU116" s="46"/>
+      <c r="CV116" s="46"/>
+      <c r="CW116" s="46"/>
+      <c r="CX116" s="46"/>
+      <c r="CY116" s="46"/>
+      <c r="CZ116" s="46"/>
+      <c r="DA116" s="46"/>
+      <c r="DB116" s="46"/>
+      <c r="DC116" s="46"/>
+      <c r="DD116" s="46"/>
+      <c r="DE116" s="46"/>
+      <c r="DF116" s="46"/>
+      <c r="DG116" s="46"/>
+      <c r="DH116" s="46"/>
+      <c r="DI116" s="46"/>
+      <c r="DJ116" s="46"/>
+      <c r="DK116" s="46"/>
+      <c r="DL116" s="46"/>
+      <c r="DM116" s="46"/>
+      <c r="DN116" s="46"/>
+      <c r="DO116" s="46"/>
+      <c r="DP116" s="46"/>
+      <c r="DQ116" s="46"/>
+      <c r="DR116" s="46"/>
+      <c r="DS116" s="46"/>
+      <c r="DT116" s="46"/>
+      <c r="DU116" s="46"/>
+      <c r="DV116" s="46"/>
+      <c r="DW116" s="46"/>
+      <c r="DX116" s="46"/>
+      <c r="DY116" s="46"/>
+      <c r="DZ116" s="46"/>
+      <c r="EA116" s="46"/>
+      <c r="EB116" s="46"/>
+      <c r="EC116" s="46"/>
+      <c r="ED116" s="46"/>
+      <c r="EE116" s="46"/>
+      <c r="EF116" s="46"/>
+      <c r="EG116" s="46"/>
+      <c r="EH116" s="46"/>
+      <c r="EI116" s="46"/>
+      <c r="EJ116" s="46"/>
+      <c r="EK116" s="46"/>
+      <c r="EL116" s="46"/>
+      <c r="EM116" s="46"/>
+      <c r="EN116" s="46"/>
+      <c r="EO116" s="46"/>
+      <c r="EP116" s="46"/>
+      <c r="EQ116" s="46"/>
+      <c r="ER116" s="46"/>
+      <c r="ES116" s="46"/>
+      <c r="ET116" s="46"/>
+      <c r="EU116" s="46"/>
+      <c r="EV116" s="46"/>
+      <c r="EW116" s="46"/>
+      <c r="EX116" s="46"/>
+      <c r="EY116" s="46"/>
+      <c r="EZ116" s="46"/>
+      <c r="FA116" s="46"/>
+      <c r="FB116" s="46"/>
+      <c r="FC116" s="46"/>
+      <c r="FD116" s="46"/>
+      <c r="FE116" s="46"/>
+      <c r="FF116" s="46"/>
+      <c r="FG116" s="46"/>
+      <c r="FH116" s="46"/>
+      <c r="FI116" s="46"/>
+      <c r="FJ116" s="46"/>
+      <c r="FK116" s="46"/>
+      <c r="FL116" s="46"/>
+      <c r="FM116" s="46"/>
+      <c r="FN116" s="46"/>
+      <c r="FO116" s="46"/>
+      <c r="FP116" s="46"/>
+      <c r="FQ116" s="46"/>
+      <c r="FR116" s="46"/>
+      <c r="FS116" s="46"/>
+      <c r="FT116" s="46"/>
+      <c r="FU116" s="46"/>
+      <c r="FV116" s="46"/>
+      <c r="FW116" s="46"/>
+      <c r="FX116" s="46"/>
+      <c r="FY116" s="46"/>
+      <c r="FZ116" s="46"/>
+      <c r="GA116" s="46"/>
+      <c r="GB116" s="46"/>
+      <c r="GC116" s="46"/>
+      <c r="GD116" s="46"/>
+      <c r="GE116" s="46"/>
+      <c r="GF116" s="46"/>
+      <c r="GG116" s="46"/>
+      <c r="GH116" s="46"/>
+      <c r="GI116" s="46"/>
+      <c r="GJ116" s="46"/>
+      <c r="GK116" s="46"/>
+      <c r="GL116" s="46"/>
+      <c r="GM116" s="46"/>
+      <c r="GN116" s="46"/>
+      <c r="GO116" s="46"/>
+      <c r="GP116" s="46"/>
+      <c r="GQ116" s="46"/>
+      <c r="GR116" s="46"/>
+      <c r="GS116" s="46"/>
+      <c r="GT116" s="46"/>
+      <c r="GU116" s="46"/>
+      <c r="GV116" s="46"/>
+      <c r="GW116" s="46"/>
+      <c r="GX116" s="46"/>
+      <c r="GY116" s="46"/>
+      <c r="GZ116" s="46"/>
+      <c r="HA116" s="46"/>
+      <c r="HB116" s="46"/>
+      <c r="HC116" s="46"/>
+      <c r="HD116" s="46"/>
+      <c r="HE116" s="46"/>
+      <c r="HF116" s="46"/>
+      <c r="HG116" s="46"/>
+      <c r="HH116" s="46"/>
+      <c r="HI116" s="46"/>
+      <c r="HJ116" s="46"/>
+      <c r="HK116" s="46"/>
+      <c r="HL116" s="46"/>
+      <c r="HM116" s="46"/>
+      <c r="HN116" s="46"/>
+      <c r="HO116" s="46"/>
+      <c r="HP116" s="46"/>
+      <c r="HQ116" s="46"/>
+      <c r="HR116" s="46"/>
+      <c r="HS116" s="46"/>
+      <c r="HT116" s="46"/>
+      <c r="HU116" s="46"/>
+      <c r="HV116" s="46"/>
+      <c r="HW116" s="46"/>
+      <c r="HX116" s="46"/>
+      <c r="HY116" s="46"/>
+      <c r="HZ116" s="46"/>
+      <c r="IA116" s="46"/>
+      <c r="IB116" s="46"/>
+      <c r="IC116" s="46"/>
+      <c r="ID116" s="46"/>
+      <c r="IE116" s="46"/>
+      <c r="IF116" s="46"/>
+      <c r="IG116" s="46"/>
+      <c r="IH116" s="46"/>
+      <c r="II116" s="46"/>
+      <c r="IJ116" s="46"/>
+      <c r="IK116" s="46"/>
+      <c r="IL116" s="46"/>
+      <c r="IM116" s="46"/>
+      <c r="IW116" s="47"/>
     </row>
-    <row r="117" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A117" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B117" s="42" t="s">
-        <v>13</v>
+      <c r="B117" s="60" t="s">
+        <v>41</v>
       </c>
       <c r="C117" s="42" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D117" s="42"/>
       <c r="E117" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="F117" s="42" t="s">
-        <v>326</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F117" s="42"/>
       <c r="G117" s="54" t="s">
         <v>268</v>
       </c>
@@ -35200,301 +35252,260 @@
       </c>
       <c r="I117" s="45"/>
       <c r="J117" s="46"/>
-      <c r="K117" s="69"/>
-      <c r="L117" s="69"/>
-      <c r="M117" s="69"/>
-      <c r="N117" s="69"/>
-      <c r="O117" s="69"/>
-      <c r="P117" s="69"/>
-      <c r="Q117" s="69"/>
-      <c r="R117" s="69"/>
-      <c r="S117" s="69"/>
-      <c r="T117" s="69"/>
-      <c r="U117" s="69"/>
-      <c r="V117" s="69"/>
-      <c r="W117" s="69"/>
-      <c r="X117" s="69"/>
-      <c r="Y117" s="69"/>
-      <c r="Z117" s="69"/>
-      <c r="AA117" s="69"/>
-      <c r="AB117" s="69"/>
-      <c r="AC117" s="69"/>
-      <c r="AD117" s="69"/>
-      <c r="AE117" s="69"/>
-      <c r="AF117" s="69"/>
-      <c r="AG117" s="69"/>
-      <c r="AH117" s="69"/>
-      <c r="AI117" s="69"/>
-      <c r="AJ117" s="69"/>
-      <c r="AK117" s="69"/>
-      <c r="AL117" s="69"/>
-      <c r="AM117" s="69"/>
-      <c r="AN117" s="69"/>
-      <c r="AO117" s="69"/>
-      <c r="AP117" s="69"/>
-      <c r="AQ117" s="69"/>
-      <c r="AR117" s="69"/>
-      <c r="AS117" s="69"/>
-      <c r="AT117" s="69"/>
-      <c r="AU117" s="69"/>
-      <c r="AV117" s="69"/>
-      <c r="AW117" s="69"/>
-      <c r="AX117" s="69"/>
-      <c r="AY117" s="69"/>
-      <c r="AZ117" s="69"/>
-      <c r="BA117" s="69"/>
-      <c r="BB117" s="69"/>
-      <c r="BC117" s="69"/>
-      <c r="BD117" s="69"/>
-      <c r="BE117" s="69"/>
-      <c r="BF117" s="69"/>
-      <c r="BG117" s="69"/>
-      <c r="BH117" s="69"/>
-      <c r="BI117" s="69"/>
-      <c r="BJ117" s="69"/>
-      <c r="BK117" s="69"/>
-      <c r="BL117" s="69"/>
-      <c r="BM117" s="69"/>
-      <c r="BN117" s="69"/>
-      <c r="BO117" s="69"/>
-      <c r="BP117" s="69"/>
-      <c r="BQ117" s="69"/>
-      <c r="BR117" s="69"/>
-      <c r="BS117" s="69"/>
-      <c r="BT117" s="69"/>
-      <c r="BU117" s="69"/>
-      <c r="BV117" s="69"/>
-      <c r="BW117" s="69"/>
-      <c r="BX117" s="69"/>
-      <c r="BY117" s="69"/>
-      <c r="BZ117" s="69"/>
-      <c r="CA117" s="69"/>
-      <c r="CB117" s="69"/>
-      <c r="CC117" s="69"/>
-      <c r="CD117" s="69"/>
-      <c r="CE117" s="69"/>
-      <c r="CF117" s="69"/>
-      <c r="CG117" s="69"/>
-      <c r="CH117" s="69"/>
-      <c r="CI117" s="69"/>
-      <c r="CJ117" s="69"/>
-      <c r="CK117" s="69"/>
-      <c r="CL117" s="69"/>
-      <c r="CM117" s="69"/>
-      <c r="CN117" s="69"/>
-      <c r="CO117" s="69"/>
-      <c r="CP117" s="69"/>
-      <c r="CQ117" s="69"/>
-      <c r="CR117" s="69"/>
-      <c r="CS117" s="69"/>
-      <c r="CT117" s="69"/>
-      <c r="CU117" s="69"/>
-      <c r="CV117" s="69"/>
-      <c r="CW117" s="69"/>
-      <c r="CX117" s="69"/>
-      <c r="CY117" s="69"/>
-      <c r="CZ117" s="69"/>
-      <c r="DA117" s="69"/>
-      <c r="DB117" s="69"/>
-      <c r="DC117" s="69"/>
-      <c r="DD117" s="69"/>
-      <c r="DE117" s="69"/>
-      <c r="DF117" s="69"/>
-      <c r="DG117" s="69"/>
-      <c r="DH117" s="69"/>
-      <c r="DI117" s="69"/>
-      <c r="DJ117" s="69"/>
-      <c r="DK117" s="69"/>
-      <c r="DL117" s="69"/>
-      <c r="DM117" s="69"/>
-      <c r="DN117" s="69"/>
-      <c r="DO117" s="69"/>
-      <c r="DP117" s="69"/>
-      <c r="DQ117" s="69"/>
-      <c r="DR117" s="69"/>
-      <c r="DS117" s="69"/>
-      <c r="DT117" s="69"/>
-      <c r="DU117" s="69"/>
-      <c r="DV117" s="69"/>
-      <c r="DW117" s="69"/>
-      <c r="DX117" s="69"/>
-      <c r="DY117" s="69"/>
-      <c r="DZ117" s="69"/>
-      <c r="EA117" s="69"/>
-      <c r="EB117" s="69"/>
-      <c r="EC117" s="69"/>
-      <c r="ED117" s="69"/>
-      <c r="EE117" s="69"/>
-      <c r="EF117" s="69"/>
-      <c r="EG117" s="69"/>
-      <c r="EH117" s="69"/>
-      <c r="EI117" s="69"/>
-      <c r="EJ117" s="69"/>
-      <c r="EK117" s="69"/>
-      <c r="EL117" s="69"/>
-      <c r="EM117" s="69"/>
-      <c r="EN117" s="69"/>
-      <c r="EO117" s="69"/>
-      <c r="EP117" s="69"/>
-      <c r="EQ117" s="69"/>
-      <c r="ER117" s="69"/>
-      <c r="ES117" s="69"/>
-      <c r="ET117" s="69"/>
-      <c r="EU117" s="69"/>
-      <c r="EV117" s="69"/>
-      <c r="EW117" s="69"/>
-      <c r="EX117" s="69"/>
-      <c r="EY117" s="69"/>
-      <c r="EZ117" s="69"/>
-      <c r="FA117" s="69"/>
-      <c r="FB117" s="69"/>
-      <c r="FC117" s="69"/>
-      <c r="FD117" s="69"/>
-      <c r="FE117" s="69"/>
-      <c r="FF117" s="69"/>
-      <c r="FG117" s="69"/>
-      <c r="FH117" s="69"/>
-      <c r="FI117" s="69"/>
-      <c r="FJ117" s="69"/>
-      <c r="FK117" s="69"/>
-      <c r="FL117" s="69"/>
-      <c r="FM117" s="69"/>
-      <c r="FN117" s="69"/>
-      <c r="FO117" s="69"/>
-      <c r="FP117" s="69"/>
-      <c r="FQ117" s="69"/>
-      <c r="FR117" s="69"/>
-      <c r="FS117" s="69"/>
-      <c r="FT117" s="69"/>
-      <c r="FU117" s="69"/>
-      <c r="FV117" s="69"/>
-      <c r="FW117" s="69"/>
-      <c r="FX117" s="69"/>
-      <c r="FY117" s="69"/>
-      <c r="FZ117" s="69"/>
-      <c r="GA117" s="69"/>
-      <c r="GB117" s="69"/>
-      <c r="GC117" s="69"/>
-      <c r="GD117" s="69"/>
-      <c r="GE117" s="69"/>
-      <c r="GF117" s="69"/>
-      <c r="GG117" s="69"/>
-      <c r="GH117" s="69"/>
-      <c r="GI117" s="69"/>
-      <c r="GJ117" s="69"/>
-      <c r="GK117" s="69"/>
-      <c r="GL117" s="69"/>
-      <c r="GM117" s="69"/>
-      <c r="GN117" s="69"/>
-      <c r="GO117" s="69"/>
-      <c r="GP117" s="69"/>
-      <c r="GQ117" s="69"/>
-      <c r="GR117" s="69"/>
-      <c r="GS117" s="69"/>
-      <c r="GT117" s="69"/>
-      <c r="GU117" s="69"/>
-      <c r="GV117" s="69"/>
-      <c r="GW117" s="69"/>
-      <c r="GX117" s="69"/>
-      <c r="GY117" s="69"/>
-      <c r="GZ117" s="69"/>
-      <c r="HA117" s="69"/>
-      <c r="HB117" s="69"/>
-      <c r="HC117" s="69"/>
-      <c r="HD117" s="69"/>
-      <c r="HE117" s="69"/>
-      <c r="HF117" s="69"/>
-      <c r="HG117" s="69"/>
-      <c r="HH117" s="69"/>
-      <c r="HI117" s="69"/>
-      <c r="HJ117" s="69"/>
-      <c r="HK117" s="69"/>
-      <c r="HL117" s="69"/>
-      <c r="HM117" s="69"/>
-      <c r="HN117" s="69"/>
-      <c r="HO117" s="69"/>
-      <c r="HP117" s="69"/>
-      <c r="HQ117" s="69"/>
-      <c r="HR117" s="69"/>
-      <c r="HS117" s="69"/>
-      <c r="HT117" s="69"/>
-      <c r="HU117" s="69"/>
-      <c r="HV117" s="69"/>
-      <c r="HW117" s="69"/>
-      <c r="HX117" s="69"/>
-      <c r="HY117" s="69"/>
-      <c r="HZ117" s="69"/>
-      <c r="IA117" s="69"/>
-      <c r="IB117" s="69"/>
-      <c r="IC117" s="69"/>
-      <c r="ID117" s="69"/>
-      <c r="IE117" s="69"/>
-      <c r="IF117" s="69"/>
-      <c r="IG117" s="69"/>
-      <c r="IH117" s="69"/>
-      <c r="II117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV117" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW117" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K117" s="46"/>
+      <c r="L117" s="46"/>
+      <c r="M117" s="46"/>
+      <c r="N117" s="46"/>
+      <c r="O117" s="46"/>
+      <c r="P117" s="46"/>
+      <c r="Q117" s="46"/>
+      <c r="R117" s="46"/>
+      <c r="S117" s="46"/>
+      <c r="T117" s="46"/>
+      <c r="U117" s="46"/>
+      <c r="V117" s="46"/>
+      <c r="W117" s="46"/>
+      <c r="X117" s="46"/>
+      <c r="Y117" s="46"/>
+      <c r="Z117" s="46"/>
+      <c r="AA117" s="46"/>
+      <c r="AB117" s="46"/>
+      <c r="AC117" s="46"/>
+      <c r="AD117" s="46"/>
+      <c r="AE117" s="46"/>
+      <c r="AF117" s="46"/>
+      <c r="AG117" s="46"/>
+      <c r="AH117" s="46"/>
+      <c r="AI117" s="46"/>
+      <c r="AJ117" s="46"/>
+      <c r="AK117" s="46"/>
+      <c r="AL117" s="46"/>
+      <c r="AM117" s="46"/>
+      <c r="AN117" s="46"/>
+      <c r="AO117" s="46"/>
+      <c r="AP117" s="46"/>
+      <c r="AQ117" s="46"/>
+      <c r="AR117" s="46"/>
+      <c r="AS117" s="46"/>
+      <c r="AT117" s="46"/>
+      <c r="AU117" s="46"/>
+      <c r="AV117" s="46"/>
+      <c r="AW117" s="46"/>
+      <c r="AX117" s="46"/>
+      <c r="AY117" s="46"/>
+      <c r="AZ117" s="46"/>
+      <c r="BA117" s="46"/>
+      <c r="BB117" s="46"/>
+      <c r="BC117" s="46"/>
+      <c r="BD117" s="46"/>
+      <c r="BE117" s="46"/>
+      <c r="BF117" s="46"/>
+      <c r="BG117" s="46"/>
+      <c r="BH117" s="46"/>
+      <c r="BI117" s="46"/>
+      <c r="BJ117" s="46"/>
+      <c r="BK117" s="46"/>
+      <c r="BL117" s="46"/>
+      <c r="BM117" s="46"/>
+      <c r="BN117" s="46"/>
+      <c r="BO117" s="46"/>
+      <c r="BP117" s="46"/>
+      <c r="BQ117" s="46"/>
+      <c r="BR117" s="46"/>
+      <c r="BS117" s="46"/>
+      <c r="BT117" s="46"/>
+      <c r="BU117" s="46"/>
+      <c r="BV117" s="46"/>
+      <c r="BW117" s="46"/>
+      <c r="BX117" s="46"/>
+      <c r="BY117" s="46"/>
+      <c r="BZ117" s="46"/>
+      <c r="CA117" s="46"/>
+      <c r="CB117" s="46"/>
+      <c r="CC117" s="46"/>
+      <c r="CD117" s="46"/>
+      <c r="CE117" s="46"/>
+      <c r="CF117" s="46"/>
+      <c r="CG117" s="46"/>
+      <c r="CH117" s="46"/>
+      <c r="CI117" s="46"/>
+      <c r="CJ117" s="46"/>
+      <c r="CK117" s="46"/>
+      <c r="CL117" s="46"/>
+      <c r="CM117" s="46"/>
+      <c r="CN117" s="46"/>
+      <c r="CO117" s="46"/>
+      <c r="CP117" s="46"/>
+      <c r="CQ117" s="46"/>
+      <c r="CR117" s="46"/>
+      <c r="CS117" s="46"/>
+      <c r="CT117" s="46"/>
+      <c r="CU117" s="46"/>
+      <c r="CV117" s="46"/>
+      <c r="CW117" s="46"/>
+      <c r="CX117" s="46"/>
+      <c r="CY117" s="46"/>
+      <c r="CZ117" s="46"/>
+      <c r="DA117" s="46"/>
+      <c r="DB117" s="46"/>
+      <c r="DC117" s="46"/>
+      <c r="DD117" s="46"/>
+      <c r="DE117" s="46"/>
+      <c r="DF117" s="46"/>
+      <c r="DG117" s="46"/>
+      <c r="DH117" s="46"/>
+      <c r="DI117" s="46"/>
+      <c r="DJ117" s="46"/>
+      <c r="DK117" s="46"/>
+      <c r="DL117" s="46"/>
+      <c r="DM117" s="46"/>
+      <c r="DN117" s="46"/>
+      <c r="DO117" s="46"/>
+      <c r="DP117" s="46"/>
+      <c r="DQ117" s="46"/>
+      <c r="DR117" s="46"/>
+      <c r="DS117" s="46"/>
+      <c r="DT117" s="46"/>
+      <c r="DU117" s="46"/>
+      <c r="DV117" s="46"/>
+      <c r="DW117" s="46"/>
+      <c r="DX117" s="46"/>
+      <c r="DY117" s="46"/>
+      <c r="DZ117" s="46"/>
+      <c r="EA117" s="46"/>
+      <c r="EB117" s="46"/>
+      <c r="EC117" s="46"/>
+      <c r="ED117" s="46"/>
+      <c r="EE117" s="46"/>
+      <c r="EF117" s="46"/>
+      <c r="EG117" s="46"/>
+      <c r="EH117" s="46"/>
+      <c r="EI117" s="46"/>
+      <c r="EJ117" s="46"/>
+      <c r="EK117" s="46"/>
+      <c r="EL117" s="46"/>
+      <c r="EM117" s="46"/>
+      <c r="EN117" s="46"/>
+      <c r="EO117" s="46"/>
+      <c r="EP117" s="46"/>
+      <c r="EQ117" s="46"/>
+      <c r="ER117" s="46"/>
+      <c r="ES117" s="46"/>
+      <c r="ET117" s="46"/>
+      <c r="EU117" s="46"/>
+      <c r="EV117" s="46"/>
+      <c r="EW117" s="46"/>
+      <c r="EX117" s="46"/>
+      <c r="EY117" s="46"/>
+      <c r="EZ117" s="46"/>
+      <c r="FA117" s="46"/>
+      <c r="FB117" s="46"/>
+      <c r="FC117" s="46"/>
+      <c r="FD117" s="46"/>
+      <c r="FE117" s="46"/>
+      <c r="FF117" s="46"/>
+      <c r="FG117" s="46"/>
+      <c r="FH117" s="46"/>
+      <c r="FI117" s="46"/>
+      <c r="FJ117" s="46"/>
+      <c r="FK117" s="46"/>
+      <c r="FL117" s="46"/>
+      <c r="FM117" s="46"/>
+      <c r="FN117" s="46"/>
+      <c r="FO117" s="46"/>
+      <c r="FP117" s="46"/>
+      <c r="FQ117" s="46"/>
+      <c r="FR117" s="46"/>
+      <c r="FS117" s="46"/>
+      <c r="FT117" s="46"/>
+      <c r="FU117" s="46"/>
+      <c r="FV117" s="46"/>
+      <c r="FW117" s="46"/>
+      <c r="FX117" s="46"/>
+      <c r="FY117" s="46"/>
+      <c r="FZ117" s="46"/>
+      <c r="GA117" s="46"/>
+      <c r="GB117" s="46"/>
+      <c r="GC117" s="46"/>
+      <c r="GD117" s="46"/>
+      <c r="GE117" s="46"/>
+      <c r="GF117" s="46"/>
+      <c r="GG117" s="46"/>
+      <c r="GH117" s="46"/>
+      <c r="GI117" s="46"/>
+      <c r="GJ117" s="46"/>
+      <c r="GK117" s="46"/>
+      <c r="GL117" s="46"/>
+      <c r="GM117" s="46"/>
+      <c r="GN117" s="46"/>
+      <c r="GO117" s="46"/>
+      <c r="GP117" s="46"/>
+      <c r="GQ117" s="46"/>
+      <c r="GR117" s="46"/>
+      <c r="GS117" s="46"/>
+      <c r="GT117" s="46"/>
+      <c r="GU117" s="46"/>
+      <c r="GV117" s="46"/>
+      <c r="GW117" s="46"/>
+      <c r="GX117" s="46"/>
+      <c r="GY117" s="46"/>
+      <c r="GZ117" s="46"/>
+      <c r="HA117" s="46"/>
+      <c r="HB117" s="46"/>
+      <c r="HC117" s="46"/>
+      <c r="HD117" s="46"/>
+      <c r="HE117" s="46"/>
+      <c r="HF117" s="46"/>
+      <c r="HG117" s="46"/>
+      <c r="HH117" s="46"/>
+      <c r="HI117" s="46"/>
+      <c r="HJ117" s="46"/>
+      <c r="HK117" s="46"/>
+      <c r="HL117" s="46"/>
+      <c r="HM117" s="46"/>
+      <c r="HN117" s="46"/>
+      <c r="HO117" s="46"/>
+      <c r="HP117" s="46"/>
+      <c r="HQ117" s="46"/>
+      <c r="HR117" s="46"/>
+      <c r="HS117" s="46"/>
+      <c r="HT117" s="46"/>
+      <c r="HU117" s="46"/>
+      <c r="HV117" s="46"/>
+      <c r="HW117" s="46"/>
+      <c r="HX117" s="46"/>
+      <c r="HY117" s="46"/>
+      <c r="HZ117" s="46"/>
+      <c r="IA117" s="46"/>
+      <c r="IB117" s="46"/>
+      <c r="IC117" s="46"/>
+      <c r="ID117" s="46"/>
+      <c r="IE117" s="46"/>
+      <c r="IF117" s="46"/>
+      <c r="IG117" s="46"/>
+      <c r="IH117" s="46"/>
+      <c r="II117" s="46"/>
+      <c r="IJ117" s="46"/>
+      <c r="IK117" s="46"/>
+      <c r="IL117" s="46"/>
+      <c r="IM117" s="46"/>
+      <c r="IW117" s="47"/>
     </row>
-    <row r="118" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A118" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B118" s="42" t="s">
-        <v>11</v>
+      <c r="B118" s="60" t="s">
+        <v>39</v>
       </c>
       <c r="C118" s="42" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D118" s="42"/>
       <c r="E118" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="F118" s="42" t="s">
-        <v>214</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F118" s="42"/>
       <c r="G118" s="54" t="s">
         <v>268</v>
       </c>
@@ -35503,1401 +35514,1434 @@
       </c>
       <c r="I118" s="45"/>
       <c r="J118" s="46"/>
-      <c r="K118" s="69"/>
-      <c r="L118" s="69"/>
-      <c r="M118" s="69"/>
-      <c r="N118" s="69"/>
-      <c r="O118" s="69"/>
-      <c r="P118" s="69"/>
-      <c r="Q118" s="69"/>
-      <c r="R118" s="69"/>
-      <c r="S118" s="69"/>
-      <c r="T118" s="69"/>
-      <c r="U118" s="69"/>
-      <c r="V118" s="69"/>
-      <c r="W118" s="69"/>
-      <c r="X118" s="69"/>
-      <c r="Y118" s="69"/>
-      <c r="Z118" s="69"/>
-      <c r="AA118" s="69"/>
-      <c r="AB118" s="69"/>
-      <c r="AC118" s="69"/>
-      <c r="AD118" s="69"/>
-      <c r="AE118" s="69"/>
-      <c r="AF118" s="69"/>
-      <c r="AG118" s="69"/>
-      <c r="AH118" s="69"/>
-      <c r="AI118" s="69"/>
-      <c r="AJ118" s="69"/>
-      <c r="AK118" s="69"/>
-      <c r="AL118" s="69"/>
-      <c r="AM118" s="69"/>
-      <c r="AN118" s="69"/>
-      <c r="AO118" s="69"/>
-      <c r="AP118" s="69"/>
-      <c r="AQ118" s="69"/>
-      <c r="AR118" s="69"/>
-      <c r="AS118" s="69"/>
-      <c r="AT118" s="69"/>
-      <c r="AU118" s="69"/>
-      <c r="AV118" s="69"/>
-      <c r="AW118" s="69"/>
-      <c r="AX118" s="69"/>
-      <c r="AY118" s="69"/>
-      <c r="AZ118" s="69"/>
-      <c r="BA118" s="69"/>
-      <c r="BB118" s="69"/>
-      <c r="BC118" s="69"/>
-      <c r="BD118" s="69"/>
-      <c r="BE118" s="69"/>
-      <c r="BF118" s="69"/>
-      <c r="BG118" s="69"/>
-      <c r="BH118" s="69"/>
-      <c r="BI118" s="69"/>
-      <c r="BJ118" s="69"/>
-      <c r="BK118" s="69"/>
-      <c r="BL118" s="69"/>
-      <c r="BM118" s="69"/>
-      <c r="BN118" s="69"/>
-      <c r="BO118" s="69"/>
-      <c r="BP118" s="69"/>
-      <c r="BQ118" s="69"/>
-      <c r="BR118" s="69"/>
-      <c r="BS118" s="69"/>
-      <c r="BT118" s="69"/>
-      <c r="BU118" s="69"/>
-      <c r="BV118" s="69"/>
-      <c r="BW118" s="69"/>
-      <c r="BX118" s="69"/>
-      <c r="BY118" s="69"/>
-      <c r="BZ118" s="69"/>
-      <c r="CA118" s="69"/>
-      <c r="CB118" s="69"/>
-      <c r="CC118" s="69"/>
-      <c r="CD118" s="69"/>
-      <c r="CE118" s="69"/>
-      <c r="CF118" s="69"/>
-      <c r="CG118" s="69"/>
-      <c r="CH118" s="69"/>
-      <c r="CI118" s="69"/>
-      <c r="CJ118" s="69"/>
-      <c r="CK118" s="69"/>
-      <c r="CL118" s="69"/>
-      <c r="CM118" s="69"/>
-      <c r="CN118" s="69"/>
-      <c r="CO118" s="69"/>
-      <c r="CP118" s="69"/>
-      <c r="CQ118" s="69"/>
-      <c r="CR118" s="69"/>
-      <c r="CS118" s="69"/>
-      <c r="CT118" s="69"/>
-      <c r="CU118" s="69"/>
-      <c r="CV118" s="69"/>
-      <c r="CW118" s="69"/>
-      <c r="CX118" s="69"/>
-      <c r="CY118" s="69"/>
-      <c r="CZ118" s="69"/>
-      <c r="DA118" s="69"/>
-      <c r="DB118" s="69"/>
-      <c r="DC118" s="69"/>
-      <c r="DD118" s="69"/>
-      <c r="DE118" s="69"/>
-      <c r="DF118" s="69"/>
-      <c r="DG118" s="69"/>
-      <c r="DH118" s="69"/>
-      <c r="DI118" s="69"/>
-      <c r="DJ118" s="69"/>
-      <c r="DK118" s="69"/>
-      <c r="DL118" s="69"/>
-      <c r="DM118" s="69"/>
-      <c r="DN118" s="69"/>
-      <c r="DO118" s="69"/>
-      <c r="DP118" s="69"/>
-      <c r="DQ118" s="69"/>
-      <c r="DR118" s="69"/>
-      <c r="DS118" s="69"/>
-      <c r="DT118" s="69"/>
-      <c r="DU118" s="69"/>
-      <c r="DV118" s="69"/>
-      <c r="DW118" s="69"/>
-      <c r="DX118" s="69"/>
-      <c r="DY118" s="69"/>
-      <c r="DZ118" s="69"/>
-      <c r="EA118" s="69"/>
-      <c r="EB118" s="69"/>
-      <c r="EC118" s="69"/>
-      <c r="ED118" s="69"/>
-      <c r="EE118" s="69"/>
-      <c r="EF118" s="69"/>
-      <c r="EG118" s="69"/>
-      <c r="EH118" s="69"/>
-      <c r="EI118" s="69"/>
-      <c r="EJ118" s="69"/>
-      <c r="EK118" s="69"/>
-      <c r="EL118" s="69"/>
-      <c r="EM118" s="69"/>
-      <c r="EN118" s="69"/>
-      <c r="EO118" s="69"/>
-      <c r="EP118" s="69"/>
-      <c r="EQ118" s="69"/>
-      <c r="ER118" s="69"/>
-      <c r="ES118" s="69"/>
-      <c r="ET118" s="69"/>
-      <c r="EU118" s="69"/>
-      <c r="EV118" s="69"/>
-      <c r="EW118" s="69"/>
-      <c r="EX118" s="69"/>
-      <c r="EY118" s="69"/>
-      <c r="EZ118" s="69"/>
-      <c r="FA118" s="69"/>
-      <c r="FB118" s="69"/>
-      <c r="FC118" s="69"/>
-      <c r="FD118" s="69"/>
-      <c r="FE118" s="69"/>
-      <c r="FF118" s="69"/>
-      <c r="FG118" s="69"/>
-      <c r="FH118" s="69"/>
-      <c r="FI118" s="69"/>
-      <c r="FJ118" s="69"/>
-      <c r="FK118" s="69"/>
-      <c r="FL118" s="69"/>
-      <c r="FM118" s="69"/>
-      <c r="FN118" s="69"/>
-      <c r="FO118" s="69"/>
-      <c r="FP118" s="69"/>
-      <c r="FQ118" s="69"/>
-      <c r="FR118" s="69"/>
-      <c r="FS118" s="69"/>
-      <c r="FT118" s="69"/>
-      <c r="FU118" s="69"/>
-      <c r="FV118" s="69"/>
-      <c r="FW118" s="69"/>
-      <c r="FX118" s="69"/>
-      <c r="FY118" s="69"/>
-      <c r="FZ118" s="69"/>
-      <c r="GA118" s="69"/>
-      <c r="GB118" s="69"/>
-      <c r="GC118" s="69"/>
-      <c r="GD118" s="69"/>
-      <c r="GE118" s="69"/>
-      <c r="GF118" s="69"/>
-      <c r="GG118" s="69"/>
-      <c r="GH118" s="69"/>
-      <c r="GI118" s="69"/>
-      <c r="GJ118" s="69"/>
-      <c r="GK118" s="69"/>
-      <c r="GL118" s="69"/>
-      <c r="GM118" s="69"/>
-      <c r="GN118" s="69"/>
-      <c r="GO118" s="69"/>
-      <c r="GP118" s="69"/>
-      <c r="GQ118" s="69"/>
-      <c r="GR118" s="69"/>
-      <c r="GS118" s="69"/>
-      <c r="GT118" s="69"/>
-      <c r="GU118" s="69"/>
-      <c r="GV118" s="69"/>
-      <c r="GW118" s="69"/>
-      <c r="GX118" s="69"/>
-      <c r="GY118" s="69"/>
-      <c r="GZ118" s="69"/>
-      <c r="HA118" s="69"/>
-      <c r="HB118" s="69"/>
-      <c r="HC118" s="69"/>
-      <c r="HD118" s="69"/>
-      <c r="HE118" s="69"/>
-      <c r="HF118" s="69"/>
-      <c r="HG118" s="69"/>
-      <c r="HH118" s="69"/>
-      <c r="HI118" s="69"/>
-      <c r="HJ118" s="69"/>
-      <c r="HK118" s="69"/>
-      <c r="HL118" s="69"/>
-      <c r="HM118" s="69"/>
-      <c r="HN118" s="69"/>
-      <c r="HO118" s="69"/>
-      <c r="HP118" s="69"/>
-      <c r="HQ118" s="69"/>
-      <c r="HR118" s="69"/>
-      <c r="HS118" s="69"/>
-      <c r="HT118" s="69"/>
-      <c r="HU118" s="69"/>
-      <c r="HV118" s="69"/>
-      <c r="HW118" s="69"/>
-      <c r="HX118" s="69"/>
-      <c r="HY118" s="69"/>
-      <c r="HZ118" s="69"/>
-      <c r="IA118" s="69"/>
-      <c r="IB118" s="69"/>
-      <c r="IC118" s="69"/>
-      <c r="ID118" s="69"/>
-      <c r="IE118" s="69"/>
-      <c r="IF118" s="69"/>
-      <c r="IG118" s="69"/>
-      <c r="IH118" s="69"/>
-      <c r="II118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV118" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW118" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K118" s="46"/>
+      <c r="L118" s="46"/>
+      <c r="M118" s="46"/>
+      <c r="N118" s="46"/>
+      <c r="O118" s="46"/>
+      <c r="P118" s="46"/>
+      <c r="Q118" s="46"/>
+      <c r="R118" s="46"/>
+      <c r="S118" s="46"/>
+      <c r="T118" s="46"/>
+      <c r="U118" s="46"/>
+      <c r="V118" s="46"/>
+      <c r="W118" s="46"/>
+      <c r="X118" s="46"/>
+      <c r="Y118" s="46"/>
+      <c r="Z118" s="46"/>
+      <c r="AA118" s="46"/>
+      <c r="AB118" s="46"/>
+      <c r="AC118" s="46"/>
+      <c r="AD118" s="46"/>
+      <c r="AE118" s="46"/>
+      <c r="AF118" s="46"/>
+      <c r="AG118" s="46"/>
+      <c r="AH118" s="46"/>
+      <c r="AI118" s="46"/>
+      <c r="AJ118" s="46"/>
+      <c r="AK118" s="46"/>
+      <c r="AL118" s="46"/>
+      <c r="AM118" s="46"/>
+      <c r="AN118" s="46"/>
+      <c r="AO118" s="46"/>
+      <c r="AP118" s="46"/>
+      <c r="AQ118" s="46"/>
+      <c r="AR118" s="46"/>
+      <c r="AS118" s="46"/>
+      <c r="AT118" s="46"/>
+      <c r="AU118" s="46"/>
+      <c r="AV118" s="46"/>
+      <c r="AW118" s="46"/>
+      <c r="AX118" s="46"/>
+      <c r="AY118" s="46"/>
+      <c r="AZ118" s="46"/>
+      <c r="BA118" s="46"/>
+      <c r="BB118" s="46"/>
+      <c r="BC118" s="46"/>
+      <c r="BD118" s="46"/>
+      <c r="BE118" s="46"/>
+      <c r="BF118" s="46"/>
+      <c r="BG118" s="46"/>
+      <c r="BH118" s="46"/>
+      <c r="BI118" s="46"/>
+      <c r="BJ118" s="46"/>
+      <c r="BK118" s="46"/>
+      <c r="BL118" s="46"/>
+      <c r="BM118" s="46"/>
+      <c r="BN118" s="46"/>
+      <c r="BO118" s="46"/>
+      <c r="BP118" s="46"/>
+      <c r="BQ118" s="46"/>
+      <c r="BR118" s="46"/>
+      <c r="BS118" s="46"/>
+      <c r="BT118" s="46"/>
+      <c r="BU118" s="46"/>
+      <c r="BV118" s="46"/>
+      <c r="BW118" s="46"/>
+      <c r="BX118" s="46"/>
+      <c r="BY118" s="46"/>
+      <c r="BZ118" s="46"/>
+      <c r="CA118" s="46"/>
+      <c r="CB118" s="46"/>
+      <c r="CC118" s="46"/>
+      <c r="CD118" s="46"/>
+      <c r="CE118" s="46"/>
+      <c r="CF118" s="46"/>
+      <c r="CG118" s="46"/>
+      <c r="CH118" s="46"/>
+      <c r="CI118" s="46"/>
+      <c r="CJ118" s="46"/>
+      <c r="CK118" s="46"/>
+      <c r="CL118" s="46"/>
+      <c r="CM118" s="46"/>
+      <c r="CN118" s="46"/>
+      <c r="CO118" s="46"/>
+      <c r="CP118" s="46"/>
+      <c r="CQ118" s="46"/>
+      <c r="CR118" s="46"/>
+      <c r="CS118" s="46"/>
+      <c r="CT118" s="46"/>
+      <c r="CU118" s="46"/>
+      <c r="CV118" s="46"/>
+      <c r="CW118" s="46"/>
+      <c r="CX118" s="46"/>
+      <c r="CY118" s="46"/>
+      <c r="CZ118" s="46"/>
+      <c r="DA118" s="46"/>
+      <c r="DB118" s="46"/>
+      <c r="DC118" s="46"/>
+      <c r="DD118" s="46"/>
+      <c r="DE118" s="46"/>
+      <c r="DF118" s="46"/>
+      <c r="DG118" s="46"/>
+      <c r="DH118" s="46"/>
+      <c r="DI118" s="46"/>
+      <c r="DJ118" s="46"/>
+      <c r="DK118" s="46"/>
+      <c r="DL118" s="46"/>
+      <c r="DM118" s="46"/>
+      <c r="DN118" s="46"/>
+      <c r="DO118" s="46"/>
+      <c r="DP118" s="46"/>
+      <c r="DQ118" s="46"/>
+      <c r="DR118" s="46"/>
+      <c r="DS118" s="46"/>
+      <c r="DT118" s="46"/>
+      <c r="DU118" s="46"/>
+      <c r="DV118" s="46"/>
+      <c r="DW118" s="46"/>
+      <c r="DX118" s="46"/>
+      <c r="DY118" s="46"/>
+      <c r="DZ118" s="46"/>
+      <c r="EA118" s="46"/>
+      <c r="EB118" s="46"/>
+      <c r="EC118" s="46"/>
+      <c r="ED118" s="46"/>
+      <c r="EE118" s="46"/>
+      <c r="EF118" s="46"/>
+      <c r="EG118" s="46"/>
+      <c r="EH118" s="46"/>
+      <c r="EI118" s="46"/>
+      <c r="EJ118" s="46"/>
+      <c r="EK118" s="46"/>
+      <c r="EL118" s="46"/>
+      <c r="EM118" s="46"/>
+      <c r="EN118" s="46"/>
+      <c r="EO118" s="46"/>
+      <c r="EP118" s="46"/>
+      <c r="EQ118" s="46"/>
+      <c r="ER118" s="46"/>
+      <c r="ES118" s="46"/>
+      <c r="ET118" s="46"/>
+      <c r="EU118" s="46"/>
+      <c r="EV118" s="46"/>
+      <c r="EW118" s="46"/>
+      <c r="EX118" s="46"/>
+      <c r="EY118" s="46"/>
+      <c r="EZ118" s="46"/>
+      <c r="FA118" s="46"/>
+      <c r="FB118" s="46"/>
+      <c r="FC118" s="46"/>
+      <c r="FD118" s="46"/>
+      <c r="FE118" s="46"/>
+      <c r="FF118" s="46"/>
+      <c r="FG118" s="46"/>
+      <c r="FH118" s="46"/>
+      <c r="FI118" s="46"/>
+      <c r="FJ118" s="46"/>
+      <c r="FK118" s="46"/>
+      <c r="FL118" s="46"/>
+      <c r="FM118" s="46"/>
+      <c r="FN118" s="46"/>
+      <c r="FO118" s="46"/>
+      <c r="FP118" s="46"/>
+      <c r="FQ118" s="46"/>
+      <c r="FR118" s="46"/>
+      <c r="FS118" s="46"/>
+      <c r="FT118" s="46"/>
+      <c r="FU118" s="46"/>
+      <c r="FV118" s="46"/>
+      <c r="FW118" s="46"/>
+      <c r="FX118" s="46"/>
+      <c r="FY118" s="46"/>
+      <c r="FZ118" s="46"/>
+      <c r="GA118" s="46"/>
+      <c r="GB118" s="46"/>
+      <c r="GC118" s="46"/>
+      <c r="GD118" s="46"/>
+      <c r="GE118" s="46"/>
+      <c r="GF118" s="46"/>
+      <c r="GG118" s="46"/>
+      <c r="GH118" s="46"/>
+      <c r="GI118" s="46"/>
+      <c r="GJ118" s="46"/>
+      <c r="GK118" s="46"/>
+      <c r="GL118" s="46"/>
+      <c r="GM118" s="46"/>
+      <c r="GN118" s="46"/>
+      <c r="GO118" s="46"/>
+      <c r="GP118" s="46"/>
+      <c r="GQ118" s="46"/>
+      <c r="GR118" s="46"/>
+      <c r="GS118" s="46"/>
+      <c r="GT118" s="46"/>
+      <c r="GU118" s="46"/>
+      <c r="GV118" s="46"/>
+      <c r="GW118" s="46"/>
+      <c r="GX118" s="46"/>
+      <c r="GY118" s="46"/>
+      <c r="GZ118" s="46"/>
+      <c r="HA118" s="46"/>
+      <c r="HB118" s="46"/>
+      <c r="HC118" s="46"/>
+      <c r="HD118" s="46"/>
+      <c r="HE118" s="46"/>
+      <c r="HF118" s="46"/>
+      <c r="HG118" s="46"/>
+      <c r="HH118" s="46"/>
+      <c r="HI118" s="46"/>
+      <c r="HJ118" s="46"/>
+      <c r="HK118" s="46"/>
+      <c r="HL118" s="46"/>
+      <c r="HM118" s="46"/>
+      <c r="HN118" s="46"/>
+      <c r="HO118" s="46"/>
+      <c r="HP118" s="46"/>
+      <c r="HQ118" s="46"/>
+      <c r="HR118" s="46"/>
+      <c r="HS118" s="46"/>
+      <c r="HT118" s="46"/>
+      <c r="HU118" s="46"/>
+      <c r="HV118" s="46"/>
+      <c r="HW118" s="46"/>
+      <c r="HX118" s="46"/>
+      <c r="HY118" s="46"/>
+      <c r="HZ118" s="46"/>
+      <c r="IA118" s="46"/>
+      <c r="IB118" s="46"/>
+      <c r="IC118" s="46"/>
+      <c r="ID118" s="46"/>
+      <c r="IE118" s="46"/>
+      <c r="IF118" s="46"/>
+      <c r="IG118" s="46"/>
+      <c r="IH118" s="46"/>
+      <c r="II118" s="46"/>
+      <c r="IJ118" s="46"/>
+      <c r="IK118" s="46"/>
+      <c r="IL118" s="46"/>
+      <c r="IM118" s="46"/>
+      <c r="IW118" s="47"/>
     </row>
-    <row r="119" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
       <c r="A119" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="B119" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="C119" s="61"/>
-      <c r="D119" s="42" t="s">
-        <v>302</v>
-      </c>
+      <c r="B119" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="42"/>
       <c r="E119" s="42" t="s">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="F119" s="42" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G119" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H119" s="54" t="s">
-        <v>268</v>
+      <c r="H119" s="44" t="s">
+        <v>251</v>
       </c>
       <c r="I119" s="45"/>
       <c r="J119" s="46"/>
-      <c r="K119" s="69"/>
-      <c r="L119" s="69"/>
-      <c r="M119" s="69"/>
-      <c r="N119" s="69"/>
-      <c r="O119" s="69"/>
-      <c r="P119" s="69"/>
-      <c r="Q119" s="69"/>
-      <c r="R119" s="69"/>
-      <c r="S119" s="69"/>
-      <c r="T119" s="69"/>
-      <c r="U119" s="69"/>
-      <c r="V119" s="69"/>
-      <c r="W119" s="69"/>
-      <c r="X119" s="69"/>
-      <c r="Y119" s="69"/>
-      <c r="Z119" s="69"/>
-      <c r="AA119" s="69"/>
-      <c r="AB119" s="69"/>
-      <c r="AC119" s="69"/>
-      <c r="AD119" s="69"/>
-      <c r="AE119" s="69"/>
-      <c r="AF119" s="69"/>
-      <c r="AG119" s="69"/>
-      <c r="AH119" s="69"/>
-      <c r="AI119" s="69"/>
-      <c r="AJ119" s="69"/>
-      <c r="AK119" s="69"/>
-      <c r="AL119" s="69"/>
-      <c r="AM119" s="69"/>
-      <c r="AN119" s="69"/>
-      <c r="AO119" s="69"/>
-      <c r="AP119" s="69"/>
-      <c r="AQ119" s="69"/>
-      <c r="AR119" s="69"/>
-      <c r="AS119" s="69"/>
-      <c r="AT119" s="69"/>
-      <c r="AU119" s="69"/>
-      <c r="AV119" s="69"/>
-      <c r="AW119" s="69"/>
-      <c r="AX119" s="69"/>
-      <c r="AY119" s="69"/>
-      <c r="AZ119" s="69"/>
-      <c r="BA119" s="69"/>
-      <c r="BB119" s="69"/>
-      <c r="BC119" s="69"/>
-      <c r="BD119" s="69"/>
-      <c r="BE119" s="69"/>
-      <c r="BF119" s="69"/>
-      <c r="BG119" s="69"/>
-      <c r="BH119" s="69"/>
-      <c r="BI119" s="69"/>
-      <c r="BJ119" s="69"/>
-      <c r="BK119" s="69"/>
-      <c r="BL119" s="69"/>
-      <c r="BM119" s="69"/>
-      <c r="BN119" s="69"/>
-      <c r="BO119" s="69"/>
-      <c r="BP119" s="69"/>
-      <c r="BQ119" s="69"/>
-      <c r="BR119" s="69"/>
-      <c r="BS119" s="69"/>
-      <c r="BT119" s="69"/>
-      <c r="BU119" s="69"/>
-      <c r="BV119" s="69"/>
-      <c r="BW119" s="69"/>
-      <c r="BX119" s="69"/>
-      <c r="BY119" s="69"/>
-      <c r="BZ119" s="69"/>
-      <c r="CA119" s="69"/>
-      <c r="CB119" s="69"/>
-      <c r="CC119" s="69"/>
-      <c r="CD119" s="69"/>
-      <c r="CE119" s="69"/>
-      <c r="CF119" s="69"/>
-      <c r="CG119" s="69"/>
-      <c r="CH119" s="69"/>
-      <c r="CI119" s="69"/>
-      <c r="CJ119" s="69"/>
-      <c r="CK119" s="69"/>
-      <c r="CL119" s="69"/>
-      <c r="CM119" s="69"/>
-      <c r="CN119" s="69"/>
-      <c r="CO119" s="69"/>
-      <c r="CP119" s="69"/>
-      <c r="CQ119" s="69"/>
-      <c r="CR119" s="69"/>
-      <c r="CS119" s="69"/>
-      <c r="CT119" s="69"/>
-      <c r="CU119" s="69"/>
-      <c r="CV119" s="69"/>
-      <c r="CW119" s="69"/>
-      <c r="CX119" s="69"/>
-      <c r="CY119" s="69"/>
-      <c r="CZ119" s="69"/>
-      <c r="DA119" s="69"/>
-      <c r="DB119" s="69"/>
-      <c r="DC119" s="69"/>
-      <c r="DD119" s="69"/>
-      <c r="DE119" s="69"/>
-      <c r="DF119" s="69"/>
-      <c r="DG119" s="69"/>
-      <c r="DH119" s="69"/>
-      <c r="DI119" s="69"/>
-      <c r="DJ119" s="69"/>
-      <c r="DK119" s="69"/>
-      <c r="DL119" s="69"/>
-      <c r="DM119" s="69"/>
-      <c r="DN119" s="69"/>
-      <c r="DO119" s="69"/>
-      <c r="DP119" s="69"/>
-      <c r="DQ119" s="69"/>
-      <c r="DR119" s="69"/>
-      <c r="DS119" s="69"/>
-      <c r="DT119" s="69"/>
-      <c r="DU119" s="69"/>
-      <c r="DV119" s="69"/>
-      <c r="DW119" s="69"/>
-      <c r="DX119" s="69"/>
-      <c r="DY119" s="69"/>
-      <c r="DZ119" s="69"/>
-      <c r="EA119" s="69"/>
-      <c r="EB119" s="69"/>
-      <c r="EC119" s="69"/>
-      <c r="ED119" s="69"/>
-      <c r="EE119" s="69"/>
-      <c r="EF119" s="69"/>
-      <c r="EG119" s="69"/>
-      <c r="EH119" s="69"/>
-      <c r="EI119" s="69"/>
-      <c r="EJ119" s="69"/>
-      <c r="EK119" s="69"/>
-      <c r="EL119" s="69"/>
-      <c r="EM119" s="69"/>
-      <c r="EN119" s="69"/>
-      <c r="EO119" s="69"/>
-      <c r="EP119" s="69"/>
-      <c r="EQ119" s="69"/>
-      <c r="ER119" s="69"/>
-      <c r="ES119" s="69"/>
-      <c r="ET119" s="69"/>
-      <c r="EU119" s="69"/>
-      <c r="EV119" s="69"/>
-      <c r="EW119" s="69"/>
-      <c r="EX119" s="69"/>
-      <c r="EY119" s="69"/>
-      <c r="EZ119" s="69"/>
-      <c r="FA119" s="69"/>
-      <c r="FB119" s="69"/>
-      <c r="FC119" s="69"/>
-      <c r="FD119" s="69"/>
-      <c r="FE119" s="69"/>
-      <c r="FF119" s="69"/>
-      <c r="FG119" s="69"/>
-      <c r="FH119" s="69"/>
-      <c r="FI119" s="69"/>
-      <c r="FJ119" s="69"/>
-      <c r="FK119" s="69"/>
-      <c r="FL119" s="69"/>
-      <c r="FM119" s="69"/>
-      <c r="FN119" s="69"/>
-      <c r="FO119" s="69"/>
-      <c r="FP119" s="69"/>
-      <c r="FQ119" s="69"/>
-      <c r="FR119" s="69"/>
-      <c r="FS119" s="69"/>
-      <c r="FT119" s="69"/>
-      <c r="FU119" s="69"/>
-      <c r="FV119" s="69"/>
-      <c r="FW119" s="69"/>
-      <c r="FX119" s="69"/>
-      <c r="FY119" s="69"/>
-      <c r="FZ119" s="69"/>
-      <c r="GA119" s="69"/>
-      <c r="GB119" s="69"/>
-      <c r="GC119" s="69"/>
-      <c r="GD119" s="69"/>
-      <c r="GE119" s="69"/>
-      <c r="GF119" s="69"/>
-      <c r="GG119" s="69"/>
-      <c r="GH119" s="69"/>
-      <c r="GI119" s="69"/>
-      <c r="GJ119" s="69"/>
-      <c r="GK119" s="69"/>
-      <c r="GL119" s="69"/>
-      <c r="GM119" s="69"/>
-      <c r="GN119" s="69"/>
-      <c r="GO119" s="69"/>
-      <c r="GP119" s="69"/>
-      <c r="GQ119" s="69"/>
-      <c r="GR119" s="69"/>
-      <c r="GS119" s="69"/>
-      <c r="GT119" s="69"/>
-      <c r="GU119" s="69"/>
-      <c r="GV119" s="69"/>
-      <c r="GW119" s="69"/>
-      <c r="GX119" s="69"/>
-      <c r="GY119" s="69"/>
-      <c r="GZ119" s="69"/>
-      <c r="HA119" s="69"/>
-      <c r="HB119" s="69"/>
-      <c r="HC119" s="69"/>
-      <c r="HD119" s="69"/>
-      <c r="HE119" s="69"/>
-      <c r="HF119" s="69"/>
-      <c r="HG119" s="69"/>
-      <c r="HH119" s="69"/>
-      <c r="HI119" s="69"/>
-      <c r="HJ119" s="69"/>
-      <c r="HK119" s="69"/>
-      <c r="HL119" s="69"/>
-      <c r="HM119" s="69"/>
-      <c r="HN119" s="69"/>
-      <c r="HO119" s="69"/>
-      <c r="HP119" s="69"/>
-      <c r="HQ119" s="69"/>
-      <c r="HR119" s="69"/>
-      <c r="HS119" s="69"/>
-      <c r="HT119" s="69"/>
-      <c r="HU119" s="69"/>
-      <c r="HV119" s="69"/>
-      <c r="HW119" s="69"/>
-      <c r="HX119" s="69"/>
-      <c r="HY119" s="69"/>
-      <c r="HZ119" s="69"/>
-      <c r="IA119" s="69"/>
-      <c r="IB119" s="69"/>
-      <c r="IC119" s="69"/>
-      <c r="ID119" s="69"/>
-      <c r="IE119" s="69"/>
-      <c r="IF119" s="69"/>
-      <c r="IG119" s="69"/>
-      <c r="IH119" s="69"/>
-      <c r="II119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IJ119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IK119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IL119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IM119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IN119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IO119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IP119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IQ119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IR119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IS119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IT119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IU119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IV119" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="IW119" s="70" t="s">
-        <v>112</v>
-      </c>
+      <c r="K119" s="46"/>
+      <c r="L119" s="46"/>
+      <c r="M119" s="46"/>
+      <c r="N119" s="46"/>
+      <c r="O119" s="46"/>
+      <c r="P119" s="46"/>
+      <c r="Q119" s="46"/>
+      <c r="R119" s="46"/>
+      <c r="S119" s="46"/>
+      <c r="T119" s="46"/>
+      <c r="U119" s="46"/>
+      <c r="V119" s="46"/>
+      <c r="W119" s="46"/>
+      <c r="X119" s="46"/>
+      <c r="Y119" s="46"/>
+      <c r="Z119" s="46"/>
+      <c r="AA119" s="46"/>
+      <c r="AB119" s="46"/>
+      <c r="AC119" s="46"/>
+      <c r="AD119" s="46"/>
+      <c r="AE119" s="46"/>
+      <c r="AF119" s="46"/>
+      <c r="AG119" s="46"/>
+      <c r="AH119" s="46"/>
+      <c r="AI119" s="46"/>
+      <c r="AJ119" s="46"/>
+      <c r="AK119" s="46"/>
+      <c r="AL119" s="46"/>
+      <c r="AM119" s="46"/>
+      <c r="AN119" s="46"/>
+      <c r="AO119" s="46"/>
+      <c r="AP119" s="46"/>
+      <c r="AQ119" s="46"/>
+      <c r="AR119" s="46"/>
+      <c r="AS119" s="46"/>
+      <c r="AT119" s="46"/>
+      <c r="AU119" s="46"/>
+      <c r="AV119" s="46"/>
+      <c r="AW119" s="46"/>
+      <c r="AX119" s="46"/>
+      <c r="AY119" s="46"/>
+      <c r="AZ119" s="46"/>
+      <c r="BA119" s="46"/>
+      <c r="BB119" s="46"/>
+      <c r="BC119" s="46"/>
+      <c r="BD119" s="46"/>
+      <c r="BE119" s="46"/>
+      <c r="BF119" s="46"/>
+      <c r="BG119" s="46"/>
+      <c r="BH119" s="46"/>
+      <c r="BI119" s="46"/>
+      <c r="BJ119" s="46"/>
+      <c r="BK119" s="46"/>
+      <c r="BL119" s="46"/>
+      <c r="BM119" s="46"/>
+      <c r="BN119" s="46"/>
+      <c r="BO119" s="46"/>
+      <c r="BP119" s="46"/>
+      <c r="BQ119" s="46"/>
+      <c r="BR119" s="46"/>
+      <c r="BS119" s="46"/>
+      <c r="BT119" s="46"/>
+      <c r="BU119" s="46"/>
+      <c r="BV119" s="46"/>
+      <c r="BW119" s="46"/>
+      <c r="BX119" s="46"/>
+      <c r="BY119" s="46"/>
+      <c r="BZ119" s="46"/>
+      <c r="CA119" s="46"/>
+      <c r="CB119" s="46"/>
+      <c r="CC119" s="46"/>
+      <c r="CD119" s="46"/>
+      <c r="CE119" s="46"/>
+      <c r="CF119" s="46"/>
+      <c r="CG119" s="46"/>
+      <c r="CH119" s="46"/>
+      <c r="CI119" s="46"/>
+      <c r="CJ119" s="46"/>
+      <c r="CK119" s="46"/>
+      <c r="CL119" s="46"/>
+      <c r="CM119" s="46"/>
+      <c r="CN119" s="46"/>
+      <c r="CO119" s="46"/>
+      <c r="CP119" s="46"/>
+      <c r="CQ119" s="46"/>
+      <c r="CR119" s="46"/>
+      <c r="CS119" s="46"/>
+      <c r="CT119" s="46"/>
+      <c r="CU119" s="46"/>
+      <c r="CV119" s="46"/>
+      <c r="CW119" s="46"/>
+      <c r="CX119" s="46"/>
+      <c r="CY119" s="46"/>
+      <c r="CZ119" s="46"/>
+      <c r="DA119" s="46"/>
+      <c r="DB119" s="46"/>
+      <c r="DC119" s="46"/>
+      <c r="DD119" s="46"/>
+      <c r="DE119" s="46"/>
+      <c r="DF119" s="46"/>
+      <c r="DG119" s="46"/>
+      <c r="DH119" s="46"/>
+      <c r="DI119" s="46"/>
+      <c r="DJ119" s="46"/>
+      <c r="DK119" s="46"/>
+      <c r="DL119" s="46"/>
+      <c r="DM119" s="46"/>
+      <c r="DN119" s="46"/>
+      <c r="DO119" s="46"/>
+      <c r="DP119" s="46"/>
+      <c r="DQ119" s="46"/>
+      <c r="DR119" s="46"/>
+      <c r="DS119" s="46"/>
+      <c r="DT119" s="46"/>
+      <c r="DU119" s="46"/>
+      <c r="DV119" s="46"/>
+      <c r="DW119" s="46"/>
+      <c r="DX119" s="46"/>
+      <c r="DY119" s="46"/>
+      <c r="DZ119" s="46"/>
+      <c r="EA119" s="46"/>
+      <c r="EB119" s="46"/>
+      <c r="EC119" s="46"/>
+      <c r="ED119" s="46"/>
+      <c r="EE119" s="46"/>
+      <c r="EF119" s="46"/>
+      <c r="EG119" s="46"/>
+      <c r="EH119" s="46"/>
+      <c r="EI119" s="46"/>
+      <c r="EJ119" s="46"/>
+      <c r="EK119" s="46"/>
+      <c r="EL119" s="46"/>
+      <c r="EM119" s="46"/>
+      <c r="EN119" s="46"/>
+      <c r="EO119" s="46"/>
+      <c r="EP119" s="46"/>
+      <c r="EQ119" s="46"/>
+      <c r="ER119" s="46"/>
+      <c r="ES119" s="46"/>
+      <c r="ET119" s="46"/>
+      <c r="EU119" s="46"/>
+      <c r="EV119" s="46"/>
+      <c r="EW119" s="46"/>
+      <c r="EX119" s="46"/>
+      <c r="EY119" s="46"/>
+      <c r="EZ119" s="46"/>
+      <c r="FA119" s="46"/>
+      <c r="FB119" s="46"/>
+      <c r="FC119" s="46"/>
+      <c r="FD119" s="46"/>
+      <c r="FE119" s="46"/>
+      <c r="FF119" s="46"/>
+      <c r="FG119" s="46"/>
+      <c r="FH119" s="46"/>
+      <c r="FI119" s="46"/>
+      <c r="FJ119" s="46"/>
+      <c r="FK119" s="46"/>
+      <c r="FL119" s="46"/>
+      <c r="FM119" s="46"/>
+      <c r="FN119" s="46"/>
+      <c r="FO119" s="46"/>
+      <c r="FP119" s="46"/>
+      <c r="FQ119" s="46"/>
+      <c r="FR119" s="46"/>
+      <c r="FS119" s="46"/>
+      <c r="FT119" s="46"/>
+      <c r="FU119" s="46"/>
+      <c r="FV119" s="46"/>
+      <c r="FW119" s="46"/>
+      <c r="FX119" s="46"/>
+      <c r="FY119" s="46"/>
+      <c r="FZ119" s="46"/>
+      <c r="GA119" s="46"/>
+      <c r="GB119" s="46"/>
+      <c r="GC119" s="46"/>
+      <c r="GD119" s="46"/>
+      <c r="GE119" s="46"/>
+      <c r="GF119" s="46"/>
+      <c r="GG119" s="46"/>
+      <c r="GH119" s="46"/>
+      <c r="GI119" s="46"/>
+      <c r="GJ119" s="46"/>
+      <c r="GK119" s="46"/>
+      <c r="GL119" s="46"/>
+      <c r="GM119" s="46"/>
+      <c r="GN119" s="46"/>
+      <c r="GO119" s="46"/>
+      <c r="GP119" s="46"/>
+      <c r="GQ119" s="46"/>
+      <c r="GR119" s="46"/>
+      <c r="GS119" s="46"/>
+      <c r="GT119" s="46"/>
+      <c r="GU119" s="46"/>
+      <c r="GV119" s="46"/>
+      <c r="GW119" s="46"/>
+      <c r="GX119" s="46"/>
+      <c r="GY119" s="46"/>
+      <c r="GZ119" s="46"/>
+      <c r="HA119" s="46"/>
+      <c r="HB119" s="46"/>
+      <c r="HC119" s="46"/>
+      <c r="HD119" s="46"/>
+      <c r="HE119" s="46"/>
+      <c r="HF119" s="46"/>
+      <c r="HG119" s="46"/>
+      <c r="HH119" s="46"/>
+      <c r="HI119" s="46"/>
+      <c r="HJ119" s="46"/>
+      <c r="HK119" s="46"/>
+      <c r="HL119" s="46"/>
+      <c r="HM119" s="46"/>
+      <c r="HN119" s="46"/>
+      <c r="HO119" s="46"/>
+      <c r="HP119" s="46"/>
+      <c r="HQ119" s="46"/>
+      <c r="HR119" s="46"/>
+      <c r="HS119" s="46"/>
+      <c r="HT119" s="46"/>
+      <c r="HU119" s="46"/>
+      <c r="HV119" s="46"/>
+      <c r="HW119" s="46"/>
+      <c r="HX119" s="46"/>
+      <c r="HY119" s="46"/>
+      <c r="HZ119" s="46"/>
+      <c r="IA119" s="46"/>
+      <c r="IB119" s="46"/>
+      <c r="IC119" s="46"/>
+      <c r="ID119" s="46"/>
+      <c r="IE119" s="46"/>
+      <c r="IF119" s="46"/>
+      <c r="IG119" s="46"/>
+      <c r="IH119" s="46"/>
+      <c r="II119" s="46"/>
+      <c r="IJ119" s="46"/>
+      <c r="IK119" s="46"/>
+      <c r="IL119" s="46"/>
+      <c r="IM119" s="46"/>
+      <c r="IW119" s="47"/>
     </row>
-    <row r="120" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A120" s="71" t="s">
-        <v>325</v>
+    <row r="120" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A120" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B120" s="42" t="s">
-        <v>314</v>
+        <v>2</v>
       </c>
       <c r="C120" s="42" t="s">
-        <v>299</v>
+        <v>3</v>
       </c>
       <c r="D120" s="42"/>
       <c r="E120" s="42" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F120" s="42" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G120" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H120" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I120" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="H120" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I120" s="45"/>
       <c r="J120" s="46"/>
-      <c r="K120" s="46"/>
-      <c r="L120" s="46"/>
-      <c r="M120" s="46"/>
-      <c r="N120" s="46"/>
-      <c r="O120" s="46"/>
-      <c r="P120" s="46"/>
-      <c r="Q120" s="46"/>
-      <c r="R120" s="46"/>
-      <c r="S120" s="46"/>
-      <c r="T120" s="46"/>
-      <c r="U120" s="46"/>
-      <c r="V120" s="46"/>
-      <c r="W120" s="46"/>
-      <c r="X120" s="46"/>
-      <c r="Y120" s="46"/>
-      <c r="Z120" s="46"/>
-      <c r="AA120" s="46"/>
-      <c r="AB120" s="46"/>
-      <c r="AC120" s="46"/>
-      <c r="AD120" s="46"/>
-      <c r="AE120" s="46"/>
-      <c r="AF120" s="46"/>
-      <c r="AG120" s="46"/>
-      <c r="AH120" s="46"/>
-      <c r="AI120" s="46"/>
-      <c r="AJ120" s="46"/>
-      <c r="AK120" s="46"/>
-      <c r="AL120" s="46"/>
-      <c r="AM120" s="46"/>
-      <c r="AN120" s="46"/>
-      <c r="AO120" s="46"/>
-      <c r="AP120" s="46"/>
-      <c r="AQ120" s="46"/>
-      <c r="AR120" s="46"/>
-      <c r="AS120" s="46"/>
-      <c r="AT120" s="46"/>
-      <c r="AU120" s="46"/>
-      <c r="AV120" s="46"/>
-      <c r="AW120" s="46"/>
-      <c r="AX120" s="46"/>
-      <c r="AY120" s="46"/>
-      <c r="AZ120" s="46"/>
-      <c r="BA120" s="46"/>
-      <c r="BB120" s="46"/>
-      <c r="BC120" s="46"/>
-      <c r="BD120" s="46"/>
-      <c r="BE120" s="46"/>
-      <c r="BF120" s="46"/>
-      <c r="BG120" s="46"/>
-      <c r="BH120" s="46"/>
-      <c r="BI120" s="46"/>
-      <c r="BJ120" s="46"/>
-      <c r="BK120" s="46"/>
-      <c r="BL120" s="46"/>
-      <c r="BM120" s="46"/>
-      <c r="BN120" s="46"/>
-      <c r="BO120" s="46"/>
-      <c r="BP120" s="46"/>
-      <c r="BQ120" s="46"/>
-      <c r="BR120" s="46"/>
-      <c r="BS120" s="46"/>
-      <c r="BT120" s="46"/>
-      <c r="BU120" s="46"/>
-      <c r="BV120" s="46"/>
-      <c r="BW120" s="46"/>
-      <c r="BX120" s="46"/>
-      <c r="BY120" s="46"/>
-      <c r="BZ120" s="46"/>
-      <c r="CA120" s="46"/>
-      <c r="CB120" s="46"/>
-      <c r="CC120" s="46"/>
-      <c r="CD120" s="46"/>
-      <c r="CE120" s="46"/>
-      <c r="CF120" s="46"/>
-      <c r="CG120" s="46"/>
-      <c r="CH120" s="46"/>
-      <c r="CI120" s="46"/>
-      <c r="CJ120" s="46"/>
-      <c r="CK120" s="46"/>
-      <c r="CL120" s="46"/>
-      <c r="CM120" s="46"/>
-      <c r="CN120" s="46"/>
-      <c r="CO120" s="46"/>
-      <c r="CP120" s="46"/>
-      <c r="CQ120" s="46"/>
-      <c r="CR120" s="46"/>
-      <c r="CS120" s="46"/>
-      <c r="CT120" s="46"/>
-      <c r="CU120" s="46"/>
-      <c r="CV120" s="46"/>
-      <c r="CW120" s="46"/>
-      <c r="CX120" s="46"/>
-      <c r="CY120" s="46"/>
-      <c r="CZ120" s="46"/>
-      <c r="DA120" s="46"/>
-      <c r="DB120" s="46"/>
-      <c r="DC120" s="46"/>
-      <c r="DD120" s="46"/>
-      <c r="DE120" s="46"/>
-      <c r="DF120" s="46"/>
-      <c r="DG120" s="46"/>
-      <c r="DH120" s="46"/>
-      <c r="DI120" s="46"/>
-      <c r="DJ120" s="46"/>
-      <c r="DK120" s="46"/>
-      <c r="DL120" s="46"/>
-      <c r="DM120" s="46"/>
-      <c r="DN120" s="46"/>
-      <c r="DO120" s="46"/>
-      <c r="DP120" s="46"/>
-      <c r="DQ120" s="46"/>
-      <c r="DR120" s="46"/>
-      <c r="DS120" s="46"/>
-      <c r="DT120" s="46"/>
-      <c r="DU120" s="46"/>
-      <c r="DV120" s="46"/>
-      <c r="DW120" s="46"/>
-      <c r="DX120" s="46"/>
-      <c r="DY120" s="46"/>
-      <c r="DZ120" s="46"/>
-      <c r="EA120" s="46"/>
-      <c r="EB120" s="46"/>
-      <c r="EC120" s="46"/>
-      <c r="ED120" s="46"/>
-      <c r="EE120" s="46"/>
-      <c r="EF120" s="46"/>
-      <c r="EG120" s="46"/>
-      <c r="EH120" s="46"/>
-      <c r="EI120" s="46"/>
-      <c r="EJ120" s="46"/>
-      <c r="EK120" s="46"/>
-      <c r="EL120" s="46"/>
-      <c r="EM120" s="46"/>
-      <c r="EN120" s="46"/>
-      <c r="EO120" s="46"/>
-      <c r="EP120" s="46"/>
-      <c r="EQ120" s="46"/>
-      <c r="ER120" s="46"/>
-      <c r="ES120" s="46"/>
-      <c r="ET120" s="46"/>
-      <c r="EU120" s="46"/>
-      <c r="EV120" s="46"/>
-      <c r="EW120" s="46"/>
-      <c r="EX120" s="46"/>
-      <c r="EY120" s="46"/>
-      <c r="EZ120" s="46"/>
-      <c r="FA120" s="46"/>
-      <c r="FB120" s="46"/>
-      <c r="FC120" s="46"/>
-      <c r="FD120" s="46"/>
-      <c r="FE120" s="46"/>
-      <c r="FF120" s="46"/>
-      <c r="FG120" s="46"/>
-      <c r="FH120" s="46"/>
-      <c r="FI120" s="46"/>
-      <c r="FJ120" s="46"/>
-      <c r="FK120" s="46"/>
-      <c r="FL120" s="46"/>
-      <c r="FM120" s="46"/>
-      <c r="FN120" s="46"/>
-      <c r="FO120" s="46"/>
-      <c r="FP120" s="46"/>
-      <c r="FQ120" s="46"/>
-      <c r="FR120" s="46"/>
-      <c r="FS120" s="46"/>
-      <c r="FT120" s="46"/>
-      <c r="FU120" s="46"/>
-      <c r="FV120" s="46"/>
-      <c r="FW120" s="46"/>
-      <c r="FX120" s="46"/>
-      <c r="FY120" s="46"/>
-      <c r="FZ120" s="46"/>
-      <c r="GA120" s="46"/>
-      <c r="GB120" s="46"/>
-      <c r="GC120" s="46"/>
-      <c r="GD120" s="46"/>
-      <c r="GE120" s="46"/>
-      <c r="GF120" s="46"/>
-      <c r="GG120" s="46"/>
-      <c r="GH120" s="46"/>
-      <c r="GI120" s="46"/>
-      <c r="GJ120" s="46"/>
-      <c r="GK120" s="46"/>
-      <c r="GL120" s="46"/>
-      <c r="GM120" s="46"/>
-      <c r="GN120" s="46"/>
-      <c r="GO120" s="46"/>
-      <c r="GP120" s="46"/>
-      <c r="GQ120" s="46"/>
-      <c r="GR120" s="46"/>
-      <c r="GS120" s="46"/>
-      <c r="GT120" s="46"/>
-      <c r="GU120" s="46"/>
-      <c r="GV120" s="46"/>
-      <c r="GW120" s="46"/>
-      <c r="GX120" s="46"/>
-      <c r="GY120" s="46"/>
-      <c r="GZ120" s="46"/>
-      <c r="HA120" s="46"/>
-      <c r="HB120" s="46"/>
-      <c r="HC120" s="46"/>
-      <c r="HD120" s="46"/>
-      <c r="HE120" s="46"/>
-      <c r="HF120" s="46"/>
-      <c r="HG120" s="46"/>
-      <c r="HH120" s="46"/>
-      <c r="HI120" s="46"/>
-      <c r="HJ120" s="46"/>
-      <c r="HK120" s="46"/>
-      <c r="HL120" s="46"/>
-      <c r="HM120" s="46"/>
-      <c r="HN120" s="46"/>
-      <c r="HO120" s="46"/>
-      <c r="HP120" s="46"/>
-      <c r="HQ120" s="46"/>
-      <c r="HR120" s="46"/>
-      <c r="HS120" s="46"/>
-      <c r="HT120" s="46"/>
-      <c r="HU120" s="46"/>
-      <c r="HV120" s="46"/>
-      <c r="HW120" s="46"/>
-      <c r="HX120" s="46"/>
-      <c r="HY120" s="46"/>
-      <c r="HZ120" s="46"/>
-      <c r="IA120" s="46"/>
-      <c r="IB120" s="46"/>
-      <c r="IC120" s="46"/>
-      <c r="ID120" s="46"/>
-      <c r="IE120" s="46"/>
-      <c r="IF120" s="46"/>
-      <c r="IG120" s="46"/>
-      <c r="IH120" s="46"/>
-      <c r="II120" s="46"/>
-      <c r="IJ120" s="46"/>
-      <c r="IK120" s="46"/>
-      <c r="IL120" s="46"/>
-      <c r="IM120" s="46"/>
-      <c r="IW120" s="47"/>
+      <c r="K120" s="69"/>
+      <c r="L120" s="69"/>
+      <c r="M120" s="69"/>
+      <c r="N120" s="69"/>
+      <c r="O120" s="69"/>
+      <c r="P120" s="69"/>
+      <c r="Q120" s="69"/>
+      <c r="R120" s="69"/>
+      <c r="S120" s="69"/>
+      <c r="T120" s="69"/>
+      <c r="U120" s="69"/>
+      <c r="V120" s="69"/>
+      <c r="W120" s="69"/>
+      <c r="X120" s="69"/>
+      <c r="Y120" s="69"/>
+      <c r="Z120" s="69"/>
+      <c r="AA120" s="69"/>
+      <c r="AB120" s="69"/>
+      <c r="AC120" s="69"/>
+      <c r="AD120" s="69"/>
+      <c r="AE120" s="69"/>
+      <c r="AF120" s="69"/>
+      <c r="AG120" s="69"/>
+      <c r="AH120" s="69"/>
+      <c r="AI120" s="69"/>
+      <c r="AJ120" s="69"/>
+      <c r="AK120" s="69"/>
+      <c r="AL120" s="69"/>
+      <c r="AM120" s="69"/>
+      <c r="AN120" s="69"/>
+      <c r="AO120" s="69"/>
+      <c r="AP120" s="69"/>
+      <c r="AQ120" s="69"/>
+      <c r="AR120" s="69"/>
+      <c r="AS120" s="69"/>
+      <c r="AT120" s="69"/>
+      <c r="AU120" s="69"/>
+      <c r="AV120" s="69"/>
+      <c r="AW120" s="69"/>
+      <c r="AX120" s="69"/>
+      <c r="AY120" s="69"/>
+      <c r="AZ120" s="69"/>
+      <c r="BA120" s="69"/>
+      <c r="BB120" s="69"/>
+      <c r="BC120" s="69"/>
+      <c r="BD120" s="69"/>
+      <c r="BE120" s="69"/>
+      <c r="BF120" s="69"/>
+      <c r="BG120" s="69"/>
+      <c r="BH120" s="69"/>
+      <c r="BI120" s="69"/>
+      <c r="BJ120" s="69"/>
+      <c r="BK120" s="69"/>
+      <c r="BL120" s="69"/>
+      <c r="BM120" s="69"/>
+      <c r="BN120" s="69"/>
+      <c r="BO120" s="69"/>
+      <c r="BP120" s="69"/>
+      <c r="BQ120" s="69"/>
+      <c r="BR120" s="69"/>
+      <c r="BS120" s="69"/>
+      <c r="BT120" s="69"/>
+      <c r="BU120" s="69"/>
+      <c r="BV120" s="69"/>
+      <c r="BW120" s="69"/>
+      <c r="BX120" s="69"/>
+      <c r="BY120" s="69"/>
+      <c r="BZ120" s="69"/>
+      <c r="CA120" s="69"/>
+      <c r="CB120" s="69"/>
+      <c r="CC120" s="69"/>
+      <c r="CD120" s="69"/>
+      <c r="CE120" s="69"/>
+      <c r="CF120" s="69"/>
+      <c r="CG120" s="69"/>
+      <c r="CH120" s="69"/>
+      <c r="CI120" s="69"/>
+      <c r="CJ120" s="69"/>
+      <c r="CK120" s="69"/>
+      <c r="CL120" s="69"/>
+      <c r="CM120" s="69"/>
+      <c r="CN120" s="69"/>
+      <c r="CO120" s="69"/>
+      <c r="CP120" s="69"/>
+      <c r="CQ120" s="69"/>
+      <c r="CR120" s="69"/>
+      <c r="CS120" s="69"/>
+      <c r="CT120" s="69"/>
+      <c r="CU120" s="69"/>
+      <c r="CV120" s="69"/>
+      <c r="CW120" s="69"/>
+      <c r="CX120" s="69"/>
+      <c r="CY120" s="69"/>
+      <c r="CZ120" s="69"/>
+      <c r="DA120" s="69"/>
+      <c r="DB120" s="69"/>
+      <c r="DC120" s="69"/>
+      <c r="DD120" s="69"/>
+      <c r="DE120" s="69"/>
+      <c r="DF120" s="69"/>
+      <c r="DG120" s="69"/>
+      <c r="DH120" s="69"/>
+      <c r="DI120" s="69"/>
+      <c r="DJ120" s="69"/>
+      <c r="DK120" s="69"/>
+      <c r="DL120" s="69"/>
+      <c r="DM120" s="69"/>
+      <c r="DN120" s="69"/>
+      <c r="DO120" s="69"/>
+      <c r="DP120" s="69"/>
+      <c r="DQ120" s="69"/>
+      <c r="DR120" s="69"/>
+      <c r="DS120" s="69"/>
+      <c r="DT120" s="69"/>
+      <c r="DU120" s="69"/>
+      <c r="DV120" s="69"/>
+      <c r="DW120" s="69"/>
+      <c r="DX120" s="69"/>
+      <c r="DY120" s="69"/>
+      <c r="DZ120" s="69"/>
+      <c r="EA120" s="69"/>
+      <c r="EB120" s="69"/>
+      <c r="EC120" s="69"/>
+      <c r="ED120" s="69"/>
+      <c r="EE120" s="69"/>
+      <c r="EF120" s="69"/>
+      <c r="EG120" s="69"/>
+      <c r="EH120" s="69"/>
+      <c r="EI120" s="69"/>
+      <c r="EJ120" s="69"/>
+      <c r="EK120" s="69"/>
+      <c r="EL120" s="69"/>
+      <c r="EM120" s="69"/>
+      <c r="EN120" s="69"/>
+      <c r="EO120" s="69"/>
+      <c r="EP120" s="69"/>
+      <c r="EQ120" s="69"/>
+      <c r="ER120" s="69"/>
+      <c r="ES120" s="69"/>
+      <c r="ET120" s="69"/>
+      <c r="EU120" s="69"/>
+      <c r="EV120" s="69"/>
+      <c r="EW120" s="69"/>
+      <c r="EX120" s="69"/>
+      <c r="EY120" s="69"/>
+      <c r="EZ120" s="69"/>
+      <c r="FA120" s="69"/>
+      <c r="FB120" s="69"/>
+      <c r="FC120" s="69"/>
+      <c r="FD120" s="69"/>
+      <c r="FE120" s="69"/>
+      <c r="FF120" s="69"/>
+      <c r="FG120" s="69"/>
+      <c r="FH120" s="69"/>
+      <c r="FI120" s="69"/>
+      <c r="FJ120" s="69"/>
+      <c r="FK120" s="69"/>
+      <c r="FL120" s="69"/>
+      <c r="FM120" s="69"/>
+      <c r="FN120" s="69"/>
+      <c r="FO120" s="69"/>
+      <c r="FP120" s="69"/>
+      <c r="FQ120" s="69"/>
+      <c r="FR120" s="69"/>
+      <c r="FS120" s="69"/>
+      <c r="FT120" s="69"/>
+      <c r="FU120" s="69"/>
+      <c r="FV120" s="69"/>
+      <c r="FW120" s="69"/>
+      <c r="FX120" s="69"/>
+      <c r="FY120" s="69"/>
+      <c r="FZ120" s="69"/>
+      <c r="GA120" s="69"/>
+      <c r="GB120" s="69"/>
+      <c r="GC120" s="69"/>
+      <c r="GD120" s="69"/>
+      <c r="GE120" s="69"/>
+      <c r="GF120" s="69"/>
+      <c r="GG120" s="69"/>
+      <c r="GH120" s="69"/>
+      <c r="GI120" s="69"/>
+      <c r="GJ120" s="69"/>
+      <c r="GK120" s="69"/>
+      <c r="GL120" s="69"/>
+      <c r="GM120" s="69"/>
+      <c r="GN120" s="69"/>
+      <c r="GO120" s="69"/>
+      <c r="GP120" s="69"/>
+      <c r="GQ120" s="69"/>
+      <c r="GR120" s="69"/>
+      <c r="GS120" s="69"/>
+      <c r="GT120" s="69"/>
+      <c r="GU120" s="69"/>
+      <c r="GV120" s="69"/>
+      <c r="GW120" s="69"/>
+      <c r="GX120" s="69"/>
+      <c r="GY120" s="69"/>
+      <c r="GZ120" s="69"/>
+      <c r="HA120" s="69"/>
+      <c r="HB120" s="69"/>
+      <c r="HC120" s="69"/>
+      <c r="HD120" s="69"/>
+      <c r="HE120" s="69"/>
+      <c r="HF120" s="69"/>
+      <c r="HG120" s="69"/>
+      <c r="HH120" s="69"/>
+      <c r="HI120" s="69"/>
+      <c r="HJ120" s="69"/>
+      <c r="HK120" s="69"/>
+      <c r="HL120" s="69"/>
+      <c r="HM120" s="69"/>
+      <c r="HN120" s="69"/>
+      <c r="HO120" s="69"/>
+      <c r="HP120" s="69"/>
+      <c r="HQ120" s="69"/>
+      <c r="HR120" s="69"/>
+      <c r="HS120" s="69"/>
+      <c r="HT120" s="69"/>
+      <c r="HU120" s="69"/>
+      <c r="HV120" s="69"/>
+      <c r="HW120" s="69"/>
+      <c r="HX120" s="69"/>
+      <c r="HY120" s="69"/>
+      <c r="HZ120" s="69"/>
+      <c r="IA120" s="69"/>
+      <c r="IB120" s="69"/>
+      <c r="IC120" s="69"/>
+      <c r="ID120" s="69"/>
+      <c r="IE120" s="69"/>
+      <c r="IF120" s="69"/>
+      <c r="IG120" s="69"/>
+      <c r="IH120" s="69"/>
+      <c r="II120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV120" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW120" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="121" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A121" s="71" t="s">
-        <v>325</v>
+    <row r="121" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A121" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="C121" s="42" t="s">
-        <v>298</v>
+        <v>14</v>
       </c>
       <c r="D121" s="42"/>
       <c r="E121" s="42" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="F121" s="42" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="G121" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H121" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I121" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="H121" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I121" s="45"/>
       <c r="J121" s="46"/>
-      <c r="K121" s="46"/>
-      <c r="L121" s="46"/>
-      <c r="M121" s="46"/>
-      <c r="N121" s="46"/>
-      <c r="O121" s="46"/>
-      <c r="P121" s="46"/>
-      <c r="Q121" s="46"/>
-      <c r="R121" s="46"/>
-      <c r="S121" s="46"/>
-      <c r="T121" s="46"/>
-      <c r="U121" s="46"/>
-      <c r="V121" s="46"/>
-      <c r="W121" s="46"/>
-      <c r="X121" s="46"/>
-      <c r="Y121" s="46"/>
-      <c r="Z121" s="46"/>
-      <c r="AA121" s="46"/>
-      <c r="AB121" s="46"/>
-      <c r="AC121" s="46"/>
-      <c r="AD121" s="46"/>
-      <c r="AE121" s="46"/>
-      <c r="AF121" s="46"/>
-      <c r="AG121" s="46"/>
-      <c r="AH121" s="46"/>
-      <c r="AI121" s="46"/>
-      <c r="AJ121" s="46"/>
-      <c r="AK121" s="46"/>
-      <c r="AL121" s="46"/>
-      <c r="AM121" s="46"/>
-      <c r="AN121" s="46"/>
-      <c r="AO121" s="46"/>
-      <c r="AP121" s="46"/>
-      <c r="AQ121" s="46"/>
-      <c r="AR121" s="46"/>
-      <c r="AS121" s="46"/>
-      <c r="AT121" s="46"/>
-      <c r="AU121" s="46"/>
-      <c r="AV121" s="46"/>
-      <c r="AW121" s="46"/>
-      <c r="AX121" s="46"/>
-      <c r="AY121" s="46"/>
-      <c r="AZ121" s="46"/>
-      <c r="BA121" s="46"/>
-      <c r="BB121" s="46"/>
-      <c r="BC121" s="46"/>
-      <c r="BD121" s="46"/>
-      <c r="BE121" s="46"/>
-      <c r="BF121" s="46"/>
-      <c r="BG121" s="46"/>
-      <c r="BH121" s="46"/>
-      <c r="BI121" s="46"/>
-      <c r="BJ121" s="46"/>
-      <c r="BK121" s="46"/>
-      <c r="BL121" s="46"/>
-      <c r="BM121" s="46"/>
-      <c r="BN121" s="46"/>
-      <c r="BO121" s="46"/>
-      <c r="BP121" s="46"/>
-      <c r="BQ121" s="46"/>
-      <c r="BR121" s="46"/>
-      <c r="BS121" s="46"/>
-      <c r="BT121" s="46"/>
-      <c r="BU121" s="46"/>
-      <c r="BV121" s="46"/>
-      <c r="BW121" s="46"/>
-      <c r="BX121" s="46"/>
-      <c r="BY121" s="46"/>
-      <c r="BZ121" s="46"/>
-      <c r="CA121" s="46"/>
-      <c r="CB121" s="46"/>
-      <c r="CC121" s="46"/>
-      <c r="CD121" s="46"/>
-      <c r="CE121" s="46"/>
-      <c r="CF121" s="46"/>
-      <c r="CG121" s="46"/>
-      <c r="CH121" s="46"/>
-      <c r="CI121" s="46"/>
-      <c r="CJ121" s="46"/>
-      <c r="CK121" s="46"/>
-      <c r="CL121" s="46"/>
-      <c r="CM121" s="46"/>
-      <c r="CN121" s="46"/>
-      <c r="CO121" s="46"/>
-      <c r="CP121" s="46"/>
-      <c r="CQ121" s="46"/>
-      <c r="CR121" s="46"/>
-      <c r="CS121" s="46"/>
-      <c r="CT121" s="46"/>
-      <c r="CU121" s="46"/>
-      <c r="CV121" s="46"/>
-      <c r="CW121" s="46"/>
-      <c r="CX121" s="46"/>
-      <c r="CY121" s="46"/>
-      <c r="CZ121" s="46"/>
-      <c r="DA121" s="46"/>
-      <c r="DB121" s="46"/>
-      <c r="DC121" s="46"/>
-      <c r="DD121" s="46"/>
-      <c r="DE121" s="46"/>
-      <c r="DF121" s="46"/>
-      <c r="DG121" s="46"/>
-      <c r="DH121" s="46"/>
-      <c r="DI121" s="46"/>
-      <c r="DJ121" s="46"/>
-      <c r="DK121" s="46"/>
-      <c r="DL121" s="46"/>
-      <c r="DM121" s="46"/>
-      <c r="DN121" s="46"/>
-      <c r="DO121" s="46"/>
-      <c r="DP121" s="46"/>
-      <c r="DQ121" s="46"/>
-      <c r="DR121" s="46"/>
-      <c r="DS121" s="46"/>
-      <c r="DT121" s="46"/>
-      <c r="DU121" s="46"/>
-      <c r="DV121" s="46"/>
-      <c r="DW121" s="46"/>
-      <c r="DX121" s="46"/>
-      <c r="DY121" s="46"/>
-      <c r="DZ121" s="46"/>
-      <c r="EA121" s="46"/>
-      <c r="EB121" s="46"/>
-      <c r="EC121" s="46"/>
-      <c r="ED121" s="46"/>
-      <c r="EE121" s="46"/>
-      <c r="EF121" s="46"/>
-      <c r="EG121" s="46"/>
-      <c r="EH121" s="46"/>
-      <c r="EI121" s="46"/>
-      <c r="EJ121" s="46"/>
-      <c r="EK121" s="46"/>
-      <c r="EL121" s="46"/>
-      <c r="EM121" s="46"/>
-      <c r="EN121" s="46"/>
-      <c r="EO121" s="46"/>
-      <c r="EP121" s="46"/>
-      <c r="EQ121" s="46"/>
-      <c r="ER121" s="46"/>
-      <c r="ES121" s="46"/>
-      <c r="ET121" s="46"/>
-      <c r="EU121" s="46"/>
-      <c r="EV121" s="46"/>
-      <c r="EW121" s="46"/>
-      <c r="EX121" s="46"/>
-      <c r="EY121" s="46"/>
-      <c r="EZ121" s="46"/>
-      <c r="FA121" s="46"/>
-      <c r="FB121" s="46"/>
-      <c r="FC121" s="46"/>
-      <c r="FD121" s="46"/>
-      <c r="FE121" s="46"/>
-      <c r="FF121" s="46"/>
-      <c r="FG121" s="46"/>
-      <c r="FH121" s="46"/>
-      <c r="FI121" s="46"/>
-      <c r="FJ121" s="46"/>
-      <c r="FK121" s="46"/>
-      <c r="FL121" s="46"/>
-      <c r="FM121" s="46"/>
-      <c r="FN121" s="46"/>
-      <c r="FO121" s="46"/>
-      <c r="FP121" s="46"/>
-      <c r="FQ121" s="46"/>
-      <c r="FR121" s="46"/>
-      <c r="FS121" s="46"/>
-      <c r="FT121" s="46"/>
-      <c r="FU121" s="46"/>
-      <c r="FV121" s="46"/>
-      <c r="FW121" s="46"/>
-      <c r="FX121" s="46"/>
-      <c r="FY121" s="46"/>
-      <c r="FZ121" s="46"/>
-      <c r="GA121" s="46"/>
-      <c r="GB121" s="46"/>
-      <c r="GC121" s="46"/>
-      <c r="GD121" s="46"/>
-      <c r="GE121" s="46"/>
-      <c r="GF121" s="46"/>
-      <c r="GG121" s="46"/>
-      <c r="GH121" s="46"/>
-      <c r="GI121" s="46"/>
-      <c r="GJ121" s="46"/>
-      <c r="GK121" s="46"/>
-      <c r="GL121" s="46"/>
-      <c r="GM121" s="46"/>
-      <c r="GN121" s="46"/>
-      <c r="GO121" s="46"/>
-      <c r="GP121" s="46"/>
-      <c r="GQ121" s="46"/>
-      <c r="GR121" s="46"/>
-      <c r="GS121" s="46"/>
-      <c r="GT121" s="46"/>
-      <c r="GU121" s="46"/>
-      <c r="GV121" s="46"/>
-      <c r="GW121" s="46"/>
-      <c r="GX121" s="46"/>
-      <c r="GY121" s="46"/>
-      <c r="GZ121" s="46"/>
-      <c r="HA121" s="46"/>
-      <c r="HB121" s="46"/>
-      <c r="HC121" s="46"/>
-      <c r="HD121" s="46"/>
-      <c r="HE121" s="46"/>
-      <c r="HF121" s="46"/>
-      <c r="HG121" s="46"/>
-      <c r="HH121" s="46"/>
-      <c r="HI121" s="46"/>
-      <c r="HJ121" s="46"/>
-      <c r="HK121" s="46"/>
-      <c r="HL121" s="46"/>
-      <c r="HM121" s="46"/>
-      <c r="HN121" s="46"/>
-      <c r="HO121" s="46"/>
-      <c r="HP121" s="46"/>
-      <c r="HQ121" s="46"/>
-      <c r="HR121" s="46"/>
-      <c r="HS121" s="46"/>
-      <c r="HT121" s="46"/>
-      <c r="HU121" s="46"/>
-      <c r="HV121" s="46"/>
-      <c r="HW121" s="46"/>
-      <c r="HX121" s="46"/>
-      <c r="HY121" s="46"/>
-      <c r="HZ121" s="46"/>
-      <c r="IA121" s="46"/>
-      <c r="IB121" s="46"/>
-      <c r="IC121" s="46"/>
-      <c r="ID121" s="46"/>
-      <c r="IE121" s="46"/>
-      <c r="IF121" s="46"/>
-      <c r="IG121" s="46"/>
-      <c r="IH121" s="46"/>
-      <c r="II121" s="46"/>
-      <c r="IJ121" s="46"/>
-      <c r="IK121" s="46"/>
-      <c r="IL121" s="46"/>
-      <c r="IM121" s="46"/>
-      <c r="IW121" s="47"/>
+      <c r="K121" s="69"/>
+      <c r="L121" s="69"/>
+      <c r="M121" s="69"/>
+      <c r="N121" s="69"/>
+      <c r="O121" s="69"/>
+      <c r="P121" s="69"/>
+      <c r="Q121" s="69"/>
+      <c r="R121" s="69"/>
+      <c r="S121" s="69"/>
+      <c r="T121" s="69"/>
+      <c r="U121" s="69"/>
+      <c r="V121" s="69"/>
+      <c r="W121" s="69"/>
+      <c r="X121" s="69"/>
+      <c r="Y121" s="69"/>
+      <c r="Z121" s="69"/>
+      <c r="AA121" s="69"/>
+      <c r="AB121" s="69"/>
+      <c r="AC121" s="69"/>
+      <c r="AD121" s="69"/>
+      <c r="AE121" s="69"/>
+      <c r="AF121" s="69"/>
+      <c r="AG121" s="69"/>
+      <c r="AH121" s="69"/>
+      <c r="AI121" s="69"/>
+      <c r="AJ121" s="69"/>
+      <c r="AK121" s="69"/>
+      <c r="AL121" s="69"/>
+      <c r="AM121" s="69"/>
+      <c r="AN121" s="69"/>
+      <c r="AO121" s="69"/>
+      <c r="AP121" s="69"/>
+      <c r="AQ121" s="69"/>
+      <c r="AR121" s="69"/>
+      <c r="AS121" s="69"/>
+      <c r="AT121" s="69"/>
+      <c r="AU121" s="69"/>
+      <c r="AV121" s="69"/>
+      <c r="AW121" s="69"/>
+      <c r="AX121" s="69"/>
+      <c r="AY121" s="69"/>
+      <c r="AZ121" s="69"/>
+      <c r="BA121" s="69"/>
+      <c r="BB121" s="69"/>
+      <c r="BC121" s="69"/>
+      <c r="BD121" s="69"/>
+      <c r="BE121" s="69"/>
+      <c r="BF121" s="69"/>
+      <c r="BG121" s="69"/>
+      <c r="BH121" s="69"/>
+      <c r="BI121" s="69"/>
+      <c r="BJ121" s="69"/>
+      <c r="BK121" s="69"/>
+      <c r="BL121" s="69"/>
+      <c r="BM121" s="69"/>
+      <c r="BN121" s="69"/>
+      <c r="BO121" s="69"/>
+      <c r="BP121" s="69"/>
+      <c r="BQ121" s="69"/>
+      <c r="BR121" s="69"/>
+      <c r="BS121" s="69"/>
+      <c r="BT121" s="69"/>
+      <c r="BU121" s="69"/>
+      <c r="BV121" s="69"/>
+      <c r="BW121" s="69"/>
+      <c r="BX121" s="69"/>
+      <c r="BY121" s="69"/>
+      <c r="BZ121" s="69"/>
+      <c r="CA121" s="69"/>
+      <c r="CB121" s="69"/>
+      <c r="CC121" s="69"/>
+      <c r="CD121" s="69"/>
+      <c r="CE121" s="69"/>
+      <c r="CF121" s="69"/>
+      <c r="CG121" s="69"/>
+      <c r="CH121" s="69"/>
+      <c r="CI121" s="69"/>
+      <c r="CJ121" s="69"/>
+      <c r="CK121" s="69"/>
+      <c r="CL121" s="69"/>
+      <c r="CM121" s="69"/>
+      <c r="CN121" s="69"/>
+      <c r="CO121" s="69"/>
+      <c r="CP121" s="69"/>
+      <c r="CQ121" s="69"/>
+      <c r="CR121" s="69"/>
+      <c r="CS121" s="69"/>
+      <c r="CT121" s="69"/>
+      <c r="CU121" s="69"/>
+      <c r="CV121" s="69"/>
+      <c r="CW121" s="69"/>
+      <c r="CX121" s="69"/>
+      <c r="CY121" s="69"/>
+      <c r="CZ121" s="69"/>
+      <c r="DA121" s="69"/>
+      <c r="DB121" s="69"/>
+      <c r="DC121" s="69"/>
+      <c r="DD121" s="69"/>
+      <c r="DE121" s="69"/>
+      <c r="DF121" s="69"/>
+      <c r="DG121" s="69"/>
+      <c r="DH121" s="69"/>
+      <c r="DI121" s="69"/>
+      <c r="DJ121" s="69"/>
+      <c r="DK121" s="69"/>
+      <c r="DL121" s="69"/>
+      <c r="DM121" s="69"/>
+      <c r="DN121" s="69"/>
+      <c r="DO121" s="69"/>
+      <c r="DP121" s="69"/>
+      <c r="DQ121" s="69"/>
+      <c r="DR121" s="69"/>
+      <c r="DS121" s="69"/>
+      <c r="DT121" s="69"/>
+      <c r="DU121" s="69"/>
+      <c r="DV121" s="69"/>
+      <c r="DW121" s="69"/>
+      <c r="DX121" s="69"/>
+      <c r="DY121" s="69"/>
+      <c r="DZ121" s="69"/>
+      <c r="EA121" s="69"/>
+      <c r="EB121" s="69"/>
+      <c r="EC121" s="69"/>
+      <c r="ED121" s="69"/>
+      <c r="EE121" s="69"/>
+      <c r="EF121" s="69"/>
+      <c r="EG121" s="69"/>
+      <c r="EH121" s="69"/>
+      <c r="EI121" s="69"/>
+      <c r="EJ121" s="69"/>
+      <c r="EK121" s="69"/>
+      <c r="EL121" s="69"/>
+      <c r="EM121" s="69"/>
+      <c r="EN121" s="69"/>
+      <c r="EO121" s="69"/>
+      <c r="EP121" s="69"/>
+      <c r="EQ121" s="69"/>
+      <c r="ER121" s="69"/>
+      <c r="ES121" s="69"/>
+      <c r="ET121" s="69"/>
+      <c r="EU121" s="69"/>
+      <c r="EV121" s="69"/>
+      <c r="EW121" s="69"/>
+      <c r="EX121" s="69"/>
+      <c r="EY121" s="69"/>
+      <c r="EZ121" s="69"/>
+      <c r="FA121" s="69"/>
+      <c r="FB121" s="69"/>
+      <c r="FC121" s="69"/>
+      <c r="FD121" s="69"/>
+      <c r="FE121" s="69"/>
+      <c r="FF121" s="69"/>
+      <c r="FG121" s="69"/>
+      <c r="FH121" s="69"/>
+      <c r="FI121" s="69"/>
+      <c r="FJ121" s="69"/>
+      <c r="FK121" s="69"/>
+      <c r="FL121" s="69"/>
+      <c r="FM121" s="69"/>
+      <c r="FN121" s="69"/>
+      <c r="FO121" s="69"/>
+      <c r="FP121" s="69"/>
+      <c r="FQ121" s="69"/>
+      <c r="FR121" s="69"/>
+      <c r="FS121" s="69"/>
+      <c r="FT121" s="69"/>
+      <c r="FU121" s="69"/>
+      <c r="FV121" s="69"/>
+      <c r="FW121" s="69"/>
+      <c r="FX121" s="69"/>
+      <c r="FY121" s="69"/>
+      <c r="FZ121" s="69"/>
+      <c r="GA121" s="69"/>
+      <c r="GB121" s="69"/>
+      <c r="GC121" s="69"/>
+      <c r="GD121" s="69"/>
+      <c r="GE121" s="69"/>
+      <c r="GF121" s="69"/>
+      <c r="GG121" s="69"/>
+      <c r="GH121" s="69"/>
+      <c r="GI121" s="69"/>
+      <c r="GJ121" s="69"/>
+      <c r="GK121" s="69"/>
+      <c r="GL121" s="69"/>
+      <c r="GM121" s="69"/>
+      <c r="GN121" s="69"/>
+      <c r="GO121" s="69"/>
+      <c r="GP121" s="69"/>
+      <c r="GQ121" s="69"/>
+      <c r="GR121" s="69"/>
+      <c r="GS121" s="69"/>
+      <c r="GT121" s="69"/>
+      <c r="GU121" s="69"/>
+      <c r="GV121" s="69"/>
+      <c r="GW121" s="69"/>
+      <c r="GX121" s="69"/>
+      <c r="GY121" s="69"/>
+      <c r="GZ121" s="69"/>
+      <c r="HA121" s="69"/>
+      <c r="HB121" s="69"/>
+      <c r="HC121" s="69"/>
+      <c r="HD121" s="69"/>
+      <c r="HE121" s="69"/>
+      <c r="HF121" s="69"/>
+      <c r="HG121" s="69"/>
+      <c r="HH121" s="69"/>
+      <c r="HI121" s="69"/>
+      <c r="HJ121" s="69"/>
+      <c r="HK121" s="69"/>
+      <c r="HL121" s="69"/>
+      <c r="HM121" s="69"/>
+      <c r="HN121" s="69"/>
+      <c r="HO121" s="69"/>
+      <c r="HP121" s="69"/>
+      <c r="HQ121" s="69"/>
+      <c r="HR121" s="69"/>
+      <c r="HS121" s="69"/>
+      <c r="HT121" s="69"/>
+      <c r="HU121" s="69"/>
+      <c r="HV121" s="69"/>
+      <c r="HW121" s="69"/>
+      <c r="HX121" s="69"/>
+      <c r="HY121" s="69"/>
+      <c r="HZ121" s="69"/>
+      <c r="IA121" s="69"/>
+      <c r="IB121" s="69"/>
+      <c r="IC121" s="69"/>
+      <c r="ID121" s="69"/>
+      <c r="IE121" s="69"/>
+      <c r="IF121" s="69"/>
+      <c r="IG121" s="69"/>
+      <c r="IH121" s="69"/>
+      <c r="II121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV121" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW121" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="122" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A122" s="71" t="s">
-        <v>325</v>
+    <row r="122" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A122" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B122" s="42" t="s">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42" t="s">
-        <v>308</v>
+        <v>238</v>
       </c>
       <c r="F122" s="42" t="s">
-        <v>309</v>
+        <v>214</v>
       </c>
       <c r="G122" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H122" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I122" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="H122" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I122" s="45"/>
       <c r="J122" s="46"/>
-      <c r="K122" s="46"/>
-      <c r="L122" s="46"/>
-      <c r="M122" s="46"/>
-      <c r="N122" s="46"/>
-      <c r="O122" s="46"/>
-      <c r="P122" s="46"/>
-      <c r="Q122" s="46"/>
-      <c r="R122" s="46"/>
-      <c r="S122" s="46"/>
-      <c r="T122" s="46"/>
-      <c r="U122" s="46"/>
-      <c r="V122" s="46"/>
-      <c r="W122" s="46"/>
-      <c r="X122" s="46"/>
-      <c r="Y122" s="46"/>
-      <c r="Z122" s="46"/>
-      <c r="AA122" s="46"/>
-      <c r="AB122" s="46"/>
-      <c r="AC122" s="46"/>
-      <c r="AD122" s="46"/>
-      <c r="AE122" s="46"/>
-      <c r="AF122" s="46"/>
-      <c r="AG122" s="46"/>
-      <c r="AH122" s="46"/>
-      <c r="AI122" s="46"/>
-      <c r="AJ122" s="46"/>
-      <c r="AK122" s="46"/>
-      <c r="AL122" s="46"/>
-      <c r="AM122" s="46"/>
-      <c r="AN122" s="46"/>
-      <c r="AO122" s="46"/>
-      <c r="AP122" s="46"/>
-      <c r="AQ122" s="46"/>
-      <c r="AR122" s="46"/>
-      <c r="AS122" s="46"/>
-      <c r="AT122" s="46"/>
-      <c r="AU122" s="46"/>
-      <c r="AV122" s="46"/>
-      <c r="AW122" s="46"/>
-      <c r="AX122" s="46"/>
-      <c r="AY122" s="46"/>
-      <c r="AZ122" s="46"/>
-      <c r="BA122" s="46"/>
-      <c r="BB122" s="46"/>
-      <c r="BC122" s="46"/>
-      <c r="BD122" s="46"/>
-      <c r="BE122" s="46"/>
-      <c r="BF122" s="46"/>
-      <c r="BG122" s="46"/>
-      <c r="BH122" s="46"/>
-      <c r="BI122" s="46"/>
-      <c r="BJ122" s="46"/>
-      <c r="BK122" s="46"/>
-      <c r="BL122" s="46"/>
-      <c r="BM122" s="46"/>
-      <c r="BN122" s="46"/>
-      <c r="BO122" s="46"/>
-      <c r="BP122" s="46"/>
-      <c r="BQ122" s="46"/>
-      <c r="BR122" s="46"/>
-      <c r="BS122" s="46"/>
-      <c r="BT122" s="46"/>
-      <c r="BU122" s="46"/>
-      <c r="BV122" s="46"/>
-      <c r="BW122" s="46"/>
-      <c r="BX122" s="46"/>
-      <c r="BY122" s="46"/>
-      <c r="BZ122" s="46"/>
-      <c r="CA122" s="46"/>
-      <c r="CB122" s="46"/>
-      <c r="CC122" s="46"/>
-      <c r="CD122" s="46"/>
-      <c r="CE122" s="46"/>
-      <c r="CF122" s="46"/>
-      <c r="CG122" s="46"/>
-      <c r="CH122" s="46"/>
-      <c r="CI122" s="46"/>
-      <c r="CJ122" s="46"/>
-      <c r="CK122" s="46"/>
-      <c r="CL122" s="46"/>
-      <c r="CM122" s="46"/>
-      <c r="CN122" s="46"/>
-      <c r="CO122" s="46"/>
-      <c r="CP122" s="46"/>
-      <c r="CQ122" s="46"/>
-      <c r="CR122" s="46"/>
-      <c r="CS122" s="46"/>
-      <c r="CT122" s="46"/>
-      <c r="CU122" s="46"/>
-      <c r="CV122" s="46"/>
-      <c r="CW122" s="46"/>
-      <c r="CX122" s="46"/>
-      <c r="CY122" s="46"/>
-      <c r="CZ122" s="46"/>
-      <c r="DA122" s="46"/>
-      <c r="DB122" s="46"/>
-      <c r="DC122" s="46"/>
-      <c r="DD122" s="46"/>
-      <c r="DE122" s="46"/>
-      <c r="DF122" s="46"/>
-      <c r="DG122" s="46"/>
-      <c r="DH122" s="46"/>
-      <c r="DI122" s="46"/>
-      <c r="DJ122" s="46"/>
-      <c r="DK122" s="46"/>
-      <c r="DL122" s="46"/>
-      <c r="DM122" s="46"/>
-      <c r="DN122" s="46"/>
-      <c r="DO122" s="46"/>
-      <c r="DP122" s="46"/>
-      <c r="DQ122" s="46"/>
-      <c r="DR122" s="46"/>
-      <c r="DS122" s="46"/>
-      <c r="DT122" s="46"/>
-      <c r="DU122" s="46"/>
-      <c r="DV122" s="46"/>
-      <c r="DW122" s="46"/>
-      <c r="DX122" s="46"/>
-      <c r="DY122" s="46"/>
-      <c r="DZ122" s="46"/>
-      <c r="EA122" s="46"/>
-      <c r="EB122" s="46"/>
-      <c r="EC122" s="46"/>
-      <c r="ED122" s="46"/>
-      <c r="EE122" s="46"/>
-      <c r="EF122" s="46"/>
-      <c r="EG122" s="46"/>
-      <c r="EH122" s="46"/>
-      <c r="EI122" s="46"/>
-      <c r="EJ122" s="46"/>
-      <c r="EK122" s="46"/>
-      <c r="EL122" s="46"/>
-      <c r="EM122" s="46"/>
-      <c r="EN122" s="46"/>
-      <c r="EO122" s="46"/>
-      <c r="EP122" s="46"/>
-      <c r="EQ122" s="46"/>
-      <c r="ER122" s="46"/>
-      <c r="ES122" s="46"/>
-      <c r="ET122" s="46"/>
-      <c r="EU122" s="46"/>
-      <c r="EV122" s="46"/>
-      <c r="EW122" s="46"/>
-      <c r="EX122" s="46"/>
-      <c r="EY122" s="46"/>
-      <c r="EZ122" s="46"/>
-      <c r="FA122" s="46"/>
-      <c r="FB122" s="46"/>
-      <c r="FC122" s="46"/>
-      <c r="FD122" s="46"/>
-      <c r="FE122" s="46"/>
-      <c r="FF122" s="46"/>
-      <c r="FG122" s="46"/>
-      <c r="FH122" s="46"/>
-      <c r="FI122" s="46"/>
-      <c r="FJ122" s="46"/>
-      <c r="FK122" s="46"/>
-      <c r="FL122" s="46"/>
-      <c r="FM122" s="46"/>
-      <c r="FN122" s="46"/>
-      <c r="FO122" s="46"/>
-      <c r="FP122" s="46"/>
-      <c r="FQ122" s="46"/>
-      <c r="FR122" s="46"/>
-      <c r="FS122" s="46"/>
-      <c r="FT122" s="46"/>
-      <c r="FU122" s="46"/>
-      <c r="FV122" s="46"/>
-      <c r="FW122" s="46"/>
-      <c r="FX122" s="46"/>
-      <c r="FY122" s="46"/>
-      <c r="FZ122" s="46"/>
-      <c r="GA122" s="46"/>
-      <c r="GB122" s="46"/>
-      <c r="GC122" s="46"/>
-      <c r="GD122" s="46"/>
-      <c r="GE122" s="46"/>
-      <c r="GF122" s="46"/>
-      <c r="GG122" s="46"/>
-      <c r="GH122" s="46"/>
-      <c r="GI122" s="46"/>
-      <c r="GJ122" s="46"/>
-      <c r="GK122" s="46"/>
-      <c r="GL122" s="46"/>
-      <c r="GM122" s="46"/>
-      <c r="GN122" s="46"/>
-      <c r="GO122" s="46"/>
-      <c r="GP122" s="46"/>
-      <c r="GQ122" s="46"/>
-      <c r="GR122" s="46"/>
-      <c r="GS122" s="46"/>
-      <c r="GT122" s="46"/>
-      <c r="GU122" s="46"/>
-      <c r="GV122" s="46"/>
-      <c r="GW122" s="46"/>
-      <c r="GX122" s="46"/>
-      <c r="GY122" s="46"/>
-      <c r="GZ122" s="46"/>
-      <c r="HA122" s="46"/>
-      <c r="HB122" s="46"/>
-      <c r="HC122" s="46"/>
-      <c r="HD122" s="46"/>
-      <c r="HE122" s="46"/>
-      <c r="HF122" s="46"/>
-      <c r="HG122" s="46"/>
-      <c r="HH122" s="46"/>
-      <c r="HI122" s="46"/>
-      <c r="HJ122" s="46"/>
-      <c r="HK122" s="46"/>
-      <c r="HL122" s="46"/>
-      <c r="HM122" s="46"/>
-      <c r="HN122" s="46"/>
-      <c r="HO122" s="46"/>
-      <c r="HP122" s="46"/>
-      <c r="HQ122" s="46"/>
-      <c r="HR122" s="46"/>
-      <c r="HS122" s="46"/>
-      <c r="HT122" s="46"/>
-      <c r="HU122" s="46"/>
-      <c r="HV122" s="46"/>
-      <c r="HW122" s="46"/>
-      <c r="HX122" s="46"/>
-      <c r="HY122" s="46"/>
-      <c r="HZ122" s="46"/>
-      <c r="IA122" s="46"/>
-      <c r="IB122" s="46"/>
-      <c r="IC122" s="46"/>
-      <c r="ID122" s="46"/>
-      <c r="IE122" s="46"/>
-      <c r="IF122" s="46"/>
-      <c r="IG122" s="46"/>
-      <c r="IH122" s="46"/>
-      <c r="II122" s="46"/>
-      <c r="IJ122" s="46"/>
-      <c r="IK122" s="46"/>
-      <c r="IL122" s="46"/>
-      <c r="IM122" s="46"/>
-      <c r="IW122" s="47"/>
+      <c r="K122" s="69"/>
+      <c r="L122" s="69"/>
+      <c r="M122" s="69"/>
+      <c r="N122" s="69"/>
+      <c r="O122" s="69"/>
+      <c r="P122" s="69"/>
+      <c r="Q122" s="69"/>
+      <c r="R122" s="69"/>
+      <c r="S122" s="69"/>
+      <c r="T122" s="69"/>
+      <c r="U122" s="69"/>
+      <c r="V122" s="69"/>
+      <c r="W122" s="69"/>
+      <c r="X122" s="69"/>
+      <c r="Y122" s="69"/>
+      <c r="Z122" s="69"/>
+      <c r="AA122" s="69"/>
+      <c r="AB122" s="69"/>
+      <c r="AC122" s="69"/>
+      <c r="AD122" s="69"/>
+      <c r="AE122" s="69"/>
+      <c r="AF122" s="69"/>
+      <c r="AG122" s="69"/>
+      <c r="AH122" s="69"/>
+      <c r="AI122" s="69"/>
+      <c r="AJ122" s="69"/>
+      <c r="AK122" s="69"/>
+      <c r="AL122" s="69"/>
+      <c r="AM122" s="69"/>
+      <c r="AN122" s="69"/>
+      <c r="AO122" s="69"/>
+      <c r="AP122" s="69"/>
+      <c r="AQ122" s="69"/>
+      <c r="AR122" s="69"/>
+      <c r="AS122" s="69"/>
+      <c r="AT122" s="69"/>
+      <c r="AU122" s="69"/>
+      <c r="AV122" s="69"/>
+      <c r="AW122" s="69"/>
+      <c r="AX122" s="69"/>
+      <c r="AY122" s="69"/>
+      <c r="AZ122" s="69"/>
+      <c r="BA122" s="69"/>
+      <c r="BB122" s="69"/>
+      <c r="BC122" s="69"/>
+      <c r="BD122" s="69"/>
+      <c r="BE122" s="69"/>
+      <c r="BF122" s="69"/>
+      <c r="BG122" s="69"/>
+      <c r="BH122" s="69"/>
+      <c r="BI122" s="69"/>
+      <c r="BJ122" s="69"/>
+      <c r="BK122" s="69"/>
+      <c r="BL122" s="69"/>
+      <c r="BM122" s="69"/>
+      <c r="BN122" s="69"/>
+      <c r="BO122" s="69"/>
+      <c r="BP122" s="69"/>
+      <c r="BQ122" s="69"/>
+      <c r="BR122" s="69"/>
+      <c r="BS122" s="69"/>
+      <c r="BT122" s="69"/>
+      <c r="BU122" s="69"/>
+      <c r="BV122" s="69"/>
+      <c r="BW122" s="69"/>
+      <c r="BX122" s="69"/>
+      <c r="BY122" s="69"/>
+      <c r="BZ122" s="69"/>
+      <c r="CA122" s="69"/>
+      <c r="CB122" s="69"/>
+      <c r="CC122" s="69"/>
+      <c r="CD122" s="69"/>
+      <c r="CE122" s="69"/>
+      <c r="CF122" s="69"/>
+      <c r="CG122" s="69"/>
+      <c r="CH122" s="69"/>
+      <c r="CI122" s="69"/>
+      <c r="CJ122" s="69"/>
+      <c r="CK122" s="69"/>
+      <c r="CL122" s="69"/>
+      <c r="CM122" s="69"/>
+      <c r="CN122" s="69"/>
+      <c r="CO122" s="69"/>
+      <c r="CP122" s="69"/>
+      <c r="CQ122" s="69"/>
+      <c r="CR122" s="69"/>
+      <c r="CS122" s="69"/>
+      <c r="CT122" s="69"/>
+      <c r="CU122" s="69"/>
+      <c r="CV122" s="69"/>
+      <c r="CW122" s="69"/>
+      <c r="CX122" s="69"/>
+      <c r="CY122" s="69"/>
+      <c r="CZ122" s="69"/>
+      <c r="DA122" s="69"/>
+      <c r="DB122" s="69"/>
+      <c r="DC122" s="69"/>
+      <c r="DD122" s="69"/>
+      <c r="DE122" s="69"/>
+      <c r="DF122" s="69"/>
+      <c r="DG122" s="69"/>
+      <c r="DH122" s="69"/>
+      <c r="DI122" s="69"/>
+      <c r="DJ122" s="69"/>
+      <c r="DK122" s="69"/>
+      <c r="DL122" s="69"/>
+      <c r="DM122" s="69"/>
+      <c r="DN122" s="69"/>
+      <c r="DO122" s="69"/>
+      <c r="DP122" s="69"/>
+      <c r="DQ122" s="69"/>
+      <c r="DR122" s="69"/>
+      <c r="DS122" s="69"/>
+      <c r="DT122" s="69"/>
+      <c r="DU122" s="69"/>
+      <c r="DV122" s="69"/>
+      <c r="DW122" s="69"/>
+      <c r="DX122" s="69"/>
+      <c r="DY122" s="69"/>
+      <c r="DZ122" s="69"/>
+      <c r="EA122" s="69"/>
+      <c r="EB122" s="69"/>
+      <c r="EC122" s="69"/>
+      <c r="ED122" s="69"/>
+      <c r="EE122" s="69"/>
+      <c r="EF122" s="69"/>
+      <c r="EG122" s="69"/>
+      <c r="EH122" s="69"/>
+      <c r="EI122" s="69"/>
+      <c r="EJ122" s="69"/>
+      <c r="EK122" s="69"/>
+      <c r="EL122" s="69"/>
+      <c r="EM122" s="69"/>
+      <c r="EN122" s="69"/>
+      <c r="EO122" s="69"/>
+      <c r="EP122" s="69"/>
+      <c r="EQ122" s="69"/>
+      <c r="ER122" s="69"/>
+      <c r="ES122" s="69"/>
+      <c r="ET122" s="69"/>
+      <c r="EU122" s="69"/>
+      <c r="EV122" s="69"/>
+      <c r="EW122" s="69"/>
+      <c r="EX122" s="69"/>
+      <c r="EY122" s="69"/>
+      <c r="EZ122" s="69"/>
+      <c r="FA122" s="69"/>
+      <c r="FB122" s="69"/>
+      <c r="FC122" s="69"/>
+      <c r="FD122" s="69"/>
+      <c r="FE122" s="69"/>
+      <c r="FF122" s="69"/>
+      <c r="FG122" s="69"/>
+      <c r="FH122" s="69"/>
+      <c r="FI122" s="69"/>
+      <c r="FJ122" s="69"/>
+      <c r="FK122" s="69"/>
+      <c r="FL122" s="69"/>
+      <c r="FM122" s="69"/>
+      <c r="FN122" s="69"/>
+      <c r="FO122" s="69"/>
+      <c r="FP122" s="69"/>
+      <c r="FQ122" s="69"/>
+      <c r="FR122" s="69"/>
+      <c r="FS122" s="69"/>
+      <c r="FT122" s="69"/>
+      <c r="FU122" s="69"/>
+      <c r="FV122" s="69"/>
+      <c r="FW122" s="69"/>
+      <c r="FX122" s="69"/>
+      <c r="FY122" s="69"/>
+      <c r="FZ122" s="69"/>
+      <c r="GA122" s="69"/>
+      <c r="GB122" s="69"/>
+      <c r="GC122" s="69"/>
+      <c r="GD122" s="69"/>
+      <c r="GE122" s="69"/>
+      <c r="GF122" s="69"/>
+      <c r="GG122" s="69"/>
+      <c r="GH122" s="69"/>
+      <c r="GI122" s="69"/>
+      <c r="GJ122" s="69"/>
+      <c r="GK122" s="69"/>
+      <c r="GL122" s="69"/>
+      <c r="GM122" s="69"/>
+      <c r="GN122" s="69"/>
+      <c r="GO122" s="69"/>
+      <c r="GP122" s="69"/>
+      <c r="GQ122" s="69"/>
+      <c r="GR122" s="69"/>
+      <c r="GS122" s="69"/>
+      <c r="GT122" s="69"/>
+      <c r="GU122" s="69"/>
+      <c r="GV122" s="69"/>
+      <c r="GW122" s="69"/>
+      <c r="GX122" s="69"/>
+      <c r="GY122" s="69"/>
+      <c r="GZ122" s="69"/>
+      <c r="HA122" s="69"/>
+      <c r="HB122" s="69"/>
+      <c r="HC122" s="69"/>
+      <c r="HD122" s="69"/>
+      <c r="HE122" s="69"/>
+      <c r="HF122" s="69"/>
+      <c r="HG122" s="69"/>
+      <c r="HH122" s="69"/>
+      <c r="HI122" s="69"/>
+      <c r="HJ122" s="69"/>
+      <c r="HK122" s="69"/>
+      <c r="HL122" s="69"/>
+      <c r="HM122" s="69"/>
+      <c r="HN122" s="69"/>
+      <c r="HO122" s="69"/>
+      <c r="HP122" s="69"/>
+      <c r="HQ122" s="69"/>
+      <c r="HR122" s="69"/>
+      <c r="HS122" s="69"/>
+      <c r="HT122" s="69"/>
+      <c r="HU122" s="69"/>
+      <c r="HV122" s="69"/>
+      <c r="HW122" s="69"/>
+      <c r="HX122" s="69"/>
+      <c r="HY122" s="69"/>
+      <c r="HZ122" s="69"/>
+      <c r="IA122" s="69"/>
+      <c r="IB122" s="69"/>
+      <c r="IC122" s="69"/>
+      <c r="ID122" s="69"/>
+      <c r="IE122" s="69"/>
+      <c r="IF122" s="69"/>
+      <c r="IG122" s="69"/>
+      <c r="IH122" s="69"/>
+      <c r="II122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV122" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW122" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="123" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A123" s="71" t="s">
-        <v>325</v>
+    <row r="123" spans="1:257" s="39" customFormat="1" ht="90" x14ac:dyDescent="0.15">
+      <c r="A123" s="68" t="s">
+        <v>253</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="C123" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="D123" s="42"/>
+        <v>313</v>
+      </c>
+      <c r="C123" s="61"/>
+      <c r="D123" s="42" t="s">
+        <v>302</v>
+      </c>
       <c r="E123" s="42" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F123" s="42" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G123" s="54" t="s">
         <v>268</v>
@@ -36905,248 +36949,285 @@
       <c r="H123" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="I123" s="45" t="s">
-        <v>321</v>
-      </c>
+      <c r="I123" s="45"/>
       <c r="J123" s="46"/>
-      <c r="K123" s="46"/>
-      <c r="L123" s="46"/>
-      <c r="M123" s="46"/>
-      <c r="N123" s="46"/>
-      <c r="O123" s="46"/>
-      <c r="P123" s="46"/>
-      <c r="Q123" s="46"/>
-      <c r="R123" s="46"/>
-      <c r="S123" s="46"/>
-      <c r="T123" s="46"/>
-      <c r="U123" s="46"/>
-      <c r="V123" s="46"/>
-      <c r="W123" s="46"/>
-      <c r="X123" s="46"/>
-      <c r="Y123" s="46"/>
-      <c r="Z123" s="46"/>
-      <c r="AA123" s="46"/>
-      <c r="AB123" s="46"/>
-      <c r="AC123" s="46"/>
-      <c r="AD123" s="46"/>
-      <c r="AE123" s="46"/>
-      <c r="AF123" s="46"/>
-      <c r="AG123" s="46"/>
-      <c r="AH123" s="46"/>
-      <c r="AI123" s="46"/>
-      <c r="AJ123" s="46"/>
-      <c r="AK123" s="46"/>
-      <c r="AL123" s="46"/>
-      <c r="AM123" s="46"/>
-      <c r="AN123" s="46"/>
-      <c r="AO123" s="46"/>
-      <c r="AP123" s="46"/>
-      <c r="AQ123" s="46"/>
-      <c r="AR123" s="46"/>
-      <c r="AS123" s="46"/>
-      <c r="AT123" s="46"/>
-      <c r="AU123" s="46"/>
-      <c r="AV123" s="46"/>
-      <c r="AW123" s="46"/>
-      <c r="AX123" s="46"/>
-      <c r="AY123" s="46"/>
-      <c r="AZ123" s="46"/>
-      <c r="BA123" s="46"/>
-      <c r="BB123" s="46"/>
-      <c r="BC123" s="46"/>
-      <c r="BD123" s="46"/>
-      <c r="BE123" s="46"/>
-      <c r="BF123" s="46"/>
-      <c r="BG123" s="46"/>
-      <c r="BH123" s="46"/>
-      <c r="BI123" s="46"/>
-      <c r="BJ123" s="46"/>
-      <c r="BK123" s="46"/>
-      <c r="BL123" s="46"/>
-      <c r="BM123" s="46"/>
-      <c r="BN123" s="46"/>
-      <c r="BO123" s="46"/>
-      <c r="BP123" s="46"/>
-      <c r="BQ123" s="46"/>
-      <c r="BR123" s="46"/>
-      <c r="BS123" s="46"/>
-      <c r="BT123" s="46"/>
-      <c r="BU123" s="46"/>
-      <c r="BV123" s="46"/>
-      <c r="BW123" s="46"/>
-      <c r="BX123" s="46"/>
-      <c r="BY123" s="46"/>
-      <c r="BZ123" s="46"/>
-      <c r="CA123" s="46"/>
-      <c r="CB123" s="46"/>
-      <c r="CC123" s="46"/>
-      <c r="CD123" s="46"/>
-      <c r="CE123" s="46"/>
-      <c r="CF123" s="46"/>
-      <c r="CG123" s="46"/>
-      <c r="CH123" s="46"/>
-      <c r="CI123" s="46"/>
-      <c r="CJ123" s="46"/>
-      <c r="CK123" s="46"/>
-      <c r="CL123" s="46"/>
-      <c r="CM123" s="46"/>
-      <c r="CN123" s="46"/>
-      <c r="CO123" s="46"/>
-      <c r="CP123" s="46"/>
-      <c r="CQ123" s="46"/>
-      <c r="CR123" s="46"/>
-      <c r="CS123" s="46"/>
-      <c r="CT123" s="46"/>
-      <c r="CU123" s="46"/>
-      <c r="CV123" s="46"/>
-      <c r="CW123" s="46"/>
-      <c r="CX123" s="46"/>
-      <c r="CY123" s="46"/>
-      <c r="CZ123" s="46"/>
-      <c r="DA123" s="46"/>
-      <c r="DB123" s="46"/>
-      <c r="DC123" s="46"/>
-      <c r="DD123" s="46"/>
-      <c r="DE123" s="46"/>
-      <c r="DF123" s="46"/>
-      <c r="DG123" s="46"/>
-      <c r="DH123" s="46"/>
-      <c r="DI123" s="46"/>
-      <c r="DJ123" s="46"/>
-      <c r="DK123" s="46"/>
-      <c r="DL123" s="46"/>
-      <c r="DM123" s="46"/>
-      <c r="DN123" s="46"/>
-      <c r="DO123" s="46"/>
-      <c r="DP123" s="46"/>
-      <c r="DQ123" s="46"/>
-      <c r="DR123" s="46"/>
-      <c r="DS123" s="46"/>
-      <c r="DT123" s="46"/>
-      <c r="DU123" s="46"/>
-      <c r="DV123" s="46"/>
-      <c r="DW123" s="46"/>
-      <c r="DX123" s="46"/>
-      <c r="DY123" s="46"/>
-      <c r="DZ123" s="46"/>
-      <c r="EA123" s="46"/>
-      <c r="EB123" s="46"/>
-      <c r="EC123" s="46"/>
-      <c r="ED123" s="46"/>
-      <c r="EE123" s="46"/>
-      <c r="EF123" s="46"/>
-      <c r="EG123" s="46"/>
-      <c r="EH123" s="46"/>
-      <c r="EI123" s="46"/>
-      <c r="EJ123" s="46"/>
-      <c r="EK123" s="46"/>
-      <c r="EL123" s="46"/>
-      <c r="EM123" s="46"/>
-      <c r="EN123" s="46"/>
-      <c r="EO123" s="46"/>
-      <c r="EP123" s="46"/>
-      <c r="EQ123" s="46"/>
-      <c r="ER123" s="46"/>
-      <c r="ES123" s="46"/>
-      <c r="ET123" s="46"/>
-      <c r="EU123" s="46"/>
-      <c r="EV123" s="46"/>
-      <c r="EW123" s="46"/>
-      <c r="EX123" s="46"/>
-      <c r="EY123" s="46"/>
-      <c r="EZ123" s="46"/>
-      <c r="FA123" s="46"/>
-      <c r="FB123" s="46"/>
-      <c r="FC123" s="46"/>
-      <c r="FD123" s="46"/>
-      <c r="FE123" s="46"/>
-      <c r="FF123" s="46"/>
-      <c r="FG123" s="46"/>
-      <c r="FH123" s="46"/>
-      <c r="FI123" s="46"/>
-      <c r="FJ123" s="46"/>
-      <c r="FK123" s="46"/>
-      <c r="FL123" s="46"/>
-      <c r="FM123" s="46"/>
-      <c r="FN123" s="46"/>
-      <c r="FO123" s="46"/>
-      <c r="FP123" s="46"/>
-      <c r="FQ123" s="46"/>
-      <c r="FR123" s="46"/>
-      <c r="FS123" s="46"/>
-      <c r="FT123" s="46"/>
-      <c r="FU123" s="46"/>
-      <c r="FV123" s="46"/>
-      <c r="FW123" s="46"/>
-      <c r="FX123" s="46"/>
-      <c r="FY123" s="46"/>
-      <c r="FZ123" s="46"/>
-      <c r="GA123" s="46"/>
-      <c r="GB123" s="46"/>
-      <c r="GC123" s="46"/>
-      <c r="GD123" s="46"/>
-      <c r="GE123" s="46"/>
-      <c r="GF123" s="46"/>
-      <c r="GG123" s="46"/>
-      <c r="GH123" s="46"/>
-      <c r="GI123" s="46"/>
-      <c r="GJ123" s="46"/>
-      <c r="GK123" s="46"/>
-      <c r="GL123" s="46"/>
-      <c r="GM123" s="46"/>
-      <c r="GN123" s="46"/>
-      <c r="GO123" s="46"/>
-      <c r="GP123" s="46"/>
-      <c r="GQ123" s="46"/>
-      <c r="GR123" s="46"/>
-      <c r="GS123" s="46"/>
-      <c r="GT123" s="46"/>
-      <c r="GU123" s="46"/>
-      <c r="GV123" s="46"/>
-      <c r="GW123" s="46"/>
-      <c r="GX123" s="46"/>
-      <c r="GY123" s="46"/>
-      <c r="GZ123" s="46"/>
-      <c r="HA123" s="46"/>
-      <c r="HB123" s="46"/>
-      <c r="HC123" s="46"/>
-      <c r="HD123" s="46"/>
-      <c r="HE123" s="46"/>
-      <c r="HF123" s="46"/>
-      <c r="HG123" s="46"/>
-      <c r="HH123" s="46"/>
-      <c r="HI123" s="46"/>
-      <c r="HJ123" s="46"/>
-      <c r="HK123" s="46"/>
-      <c r="HL123" s="46"/>
-      <c r="HM123" s="46"/>
-      <c r="HN123" s="46"/>
-      <c r="HO123" s="46"/>
-      <c r="HP123" s="46"/>
-      <c r="HQ123" s="46"/>
-      <c r="HR123" s="46"/>
-      <c r="HS123" s="46"/>
-      <c r="HT123" s="46"/>
-      <c r="HU123" s="46"/>
-      <c r="HV123" s="46"/>
-      <c r="HW123" s="46"/>
-      <c r="HX123" s="46"/>
-      <c r="HY123" s="46"/>
-      <c r="HZ123" s="46"/>
-      <c r="IA123" s="46"/>
-      <c r="IB123" s="46"/>
-      <c r="IC123" s="46"/>
-      <c r="ID123" s="46"/>
-      <c r="IE123" s="46"/>
-      <c r="IF123" s="46"/>
-      <c r="IG123" s="46"/>
-      <c r="IH123" s="46"/>
-      <c r="II123" s="46"/>
-      <c r="IJ123" s="46"/>
-      <c r="IK123" s="46"/>
-      <c r="IL123" s="46"/>
-      <c r="IM123" s="46"/>
-      <c r="IW123" s="47"/>
+      <c r="K123" s="69"/>
+      <c r="L123" s="69"/>
+      <c r="M123" s="69"/>
+      <c r="N123" s="69"/>
+      <c r="O123" s="69"/>
+      <c r="P123" s="69"/>
+      <c r="Q123" s="69"/>
+      <c r="R123" s="69"/>
+      <c r="S123" s="69"/>
+      <c r="T123" s="69"/>
+      <c r="U123" s="69"/>
+      <c r="V123" s="69"/>
+      <c r="W123" s="69"/>
+      <c r="X123" s="69"/>
+      <c r="Y123" s="69"/>
+      <c r="Z123" s="69"/>
+      <c r="AA123" s="69"/>
+      <c r="AB123" s="69"/>
+      <c r="AC123" s="69"/>
+      <c r="AD123" s="69"/>
+      <c r="AE123" s="69"/>
+      <c r="AF123" s="69"/>
+      <c r="AG123" s="69"/>
+      <c r="AH123" s="69"/>
+      <c r="AI123" s="69"/>
+      <c r="AJ123" s="69"/>
+      <c r="AK123" s="69"/>
+      <c r="AL123" s="69"/>
+      <c r="AM123" s="69"/>
+      <c r="AN123" s="69"/>
+      <c r="AO123" s="69"/>
+      <c r="AP123" s="69"/>
+      <c r="AQ123" s="69"/>
+      <c r="AR123" s="69"/>
+      <c r="AS123" s="69"/>
+      <c r="AT123" s="69"/>
+      <c r="AU123" s="69"/>
+      <c r="AV123" s="69"/>
+      <c r="AW123" s="69"/>
+      <c r="AX123" s="69"/>
+      <c r="AY123" s="69"/>
+      <c r="AZ123" s="69"/>
+      <c r="BA123" s="69"/>
+      <c r="BB123" s="69"/>
+      <c r="BC123" s="69"/>
+      <c r="BD123" s="69"/>
+      <c r="BE123" s="69"/>
+      <c r="BF123" s="69"/>
+      <c r="BG123" s="69"/>
+      <c r="BH123" s="69"/>
+      <c r="BI123" s="69"/>
+      <c r="BJ123" s="69"/>
+      <c r="BK123" s="69"/>
+      <c r="BL123" s="69"/>
+      <c r="BM123" s="69"/>
+      <c r="BN123" s="69"/>
+      <c r="BO123" s="69"/>
+      <c r="BP123" s="69"/>
+      <c r="BQ123" s="69"/>
+      <c r="BR123" s="69"/>
+      <c r="BS123" s="69"/>
+      <c r="BT123" s="69"/>
+      <c r="BU123" s="69"/>
+      <c r="BV123" s="69"/>
+      <c r="BW123" s="69"/>
+      <c r="BX123" s="69"/>
+      <c r="BY123" s="69"/>
+      <c r="BZ123" s="69"/>
+      <c r="CA123" s="69"/>
+      <c r="CB123" s="69"/>
+      <c r="CC123" s="69"/>
+      <c r="CD123" s="69"/>
+      <c r="CE123" s="69"/>
+      <c r="CF123" s="69"/>
+      <c r="CG123" s="69"/>
+      <c r="CH123" s="69"/>
+      <c r="CI123" s="69"/>
+      <c r="CJ123" s="69"/>
+      <c r="CK123" s="69"/>
+      <c r="CL123" s="69"/>
+      <c r="CM123" s="69"/>
+      <c r="CN123" s="69"/>
+      <c r="CO123" s="69"/>
+      <c r="CP123" s="69"/>
+      <c r="CQ123" s="69"/>
+      <c r="CR123" s="69"/>
+      <c r="CS123" s="69"/>
+      <c r="CT123" s="69"/>
+      <c r="CU123" s="69"/>
+      <c r="CV123" s="69"/>
+      <c r="CW123" s="69"/>
+      <c r="CX123" s="69"/>
+      <c r="CY123" s="69"/>
+      <c r="CZ123" s="69"/>
+      <c r="DA123" s="69"/>
+      <c r="DB123" s="69"/>
+      <c r="DC123" s="69"/>
+      <c r="DD123" s="69"/>
+      <c r="DE123" s="69"/>
+      <c r="DF123" s="69"/>
+      <c r="DG123" s="69"/>
+      <c r="DH123" s="69"/>
+      <c r="DI123" s="69"/>
+      <c r="DJ123" s="69"/>
+      <c r="DK123" s="69"/>
+      <c r="DL123" s="69"/>
+      <c r="DM123" s="69"/>
+      <c r="DN123" s="69"/>
+      <c r="DO123" s="69"/>
+      <c r="DP123" s="69"/>
+      <c r="DQ123" s="69"/>
+      <c r="DR123" s="69"/>
+      <c r="DS123" s="69"/>
+      <c r="DT123" s="69"/>
+      <c r="DU123" s="69"/>
+      <c r="DV123" s="69"/>
+      <c r="DW123" s="69"/>
+      <c r="DX123" s="69"/>
+      <c r="DY123" s="69"/>
+      <c r="DZ123" s="69"/>
+      <c r="EA123" s="69"/>
+      <c r="EB123" s="69"/>
+      <c r="EC123" s="69"/>
+      <c r="ED123" s="69"/>
+      <c r="EE123" s="69"/>
+      <c r="EF123" s="69"/>
+      <c r="EG123" s="69"/>
+      <c r="EH123" s="69"/>
+      <c r="EI123" s="69"/>
+      <c r="EJ123" s="69"/>
+      <c r="EK123" s="69"/>
+      <c r="EL123" s="69"/>
+      <c r="EM123" s="69"/>
+      <c r="EN123" s="69"/>
+      <c r="EO123" s="69"/>
+      <c r="EP123" s="69"/>
+      <c r="EQ123" s="69"/>
+      <c r="ER123" s="69"/>
+      <c r="ES123" s="69"/>
+      <c r="ET123" s="69"/>
+      <c r="EU123" s="69"/>
+      <c r="EV123" s="69"/>
+      <c r="EW123" s="69"/>
+      <c r="EX123" s="69"/>
+      <c r="EY123" s="69"/>
+      <c r="EZ123" s="69"/>
+      <c r="FA123" s="69"/>
+      <c r="FB123" s="69"/>
+      <c r="FC123" s="69"/>
+      <c r="FD123" s="69"/>
+      <c r="FE123" s="69"/>
+      <c r="FF123" s="69"/>
+      <c r="FG123" s="69"/>
+      <c r="FH123" s="69"/>
+      <c r="FI123" s="69"/>
+      <c r="FJ123" s="69"/>
+      <c r="FK123" s="69"/>
+      <c r="FL123" s="69"/>
+      <c r="FM123" s="69"/>
+      <c r="FN123" s="69"/>
+      <c r="FO123" s="69"/>
+      <c r="FP123" s="69"/>
+      <c r="FQ123" s="69"/>
+      <c r="FR123" s="69"/>
+      <c r="FS123" s="69"/>
+      <c r="FT123" s="69"/>
+      <c r="FU123" s="69"/>
+      <c r="FV123" s="69"/>
+      <c r="FW123" s="69"/>
+      <c r="FX123" s="69"/>
+      <c r="FY123" s="69"/>
+      <c r="FZ123" s="69"/>
+      <c r="GA123" s="69"/>
+      <c r="GB123" s="69"/>
+      <c r="GC123" s="69"/>
+      <c r="GD123" s="69"/>
+      <c r="GE123" s="69"/>
+      <c r="GF123" s="69"/>
+      <c r="GG123" s="69"/>
+      <c r="GH123" s="69"/>
+      <c r="GI123" s="69"/>
+      <c r="GJ123" s="69"/>
+      <c r="GK123" s="69"/>
+      <c r="GL123" s="69"/>
+      <c r="GM123" s="69"/>
+      <c r="GN123" s="69"/>
+      <c r="GO123" s="69"/>
+      <c r="GP123" s="69"/>
+      <c r="GQ123" s="69"/>
+      <c r="GR123" s="69"/>
+      <c r="GS123" s="69"/>
+      <c r="GT123" s="69"/>
+      <c r="GU123" s="69"/>
+      <c r="GV123" s="69"/>
+      <c r="GW123" s="69"/>
+      <c r="GX123" s="69"/>
+      <c r="GY123" s="69"/>
+      <c r="GZ123" s="69"/>
+      <c r="HA123" s="69"/>
+      <c r="HB123" s="69"/>
+      <c r="HC123" s="69"/>
+      <c r="HD123" s="69"/>
+      <c r="HE123" s="69"/>
+      <c r="HF123" s="69"/>
+      <c r="HG123" s="69"/>
+      <c r="HH123" s="69"/>
+      <c r="HI123" s="69"/>
+      <c r="HJ123" s="69"/>
+      <c r="HK123" s="69"/>
+      <c r="HL123" s="69"/>
+      <c r="HM123" s="69"/>
+      <c r="HN123" s="69"/>
+      <c r="HO123" s="69"/>
+      <c r="HP123" s="69"/>
+      <c r="HQ123" s="69"/>
+      <c r="HR123" s="69"/>
+      <c r="HS123" s="69"/>
+      <c r="HT123" s="69"/>
+      <c r="HU123" s="69"/>
+      <c r="HV123" s="69"/>
+      <c r="HW123" s="69"/>
+      <c r="HX123" s="69"/>
+      <c r="HY123" s="69"/>
+      <c r="HZ123" s="69"/>
+      <c r="IA123" s="69"/>
+      <c r="IB123" s="69"/>
+      <c r="IC123" s="69"/>
+      <c r="ID123" s="69"/>
+      <c r="IE123" s="69"/>
+      <c r="IF123" s="69"/>
+      <c r="IG123" s="69"/>
+      <c r="IH123" s="69"/>
+      <c r="II123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IJ123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IK123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IL123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IM123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IN123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IO123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IP123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IQ123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IR123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IS123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IT123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IU123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IV123" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="IW123" s="70" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="124" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A124" s="71" t="s">
@@ -37156,14 +37237,14 @@
         <v>314</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D124" s="42"/>
       <c r="E124" s="42" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="F124" s="42" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>268</v>
@@ -37422,14 +37503,14 @@
         <v>314</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D125" s="42"/>
       <c r="E125" s="42" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F125" s="42" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G125" s="54" t="s">
         <v>268</v>
@@ -37680,22 +37761,22 @@
       <c r="IM125" s="46"/>
       <c r="IW125" s="47"/>
     </row>
-    <row r="126" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A126" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B126" s="42" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="D126" s="42"/>
       <c r="E126" s="42" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="F126" s="42" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="G126" s="54" t="s">
         <v>268</v>
@@ -37946,22 +38027,22 @@
       <c r="IM126" s="46"/>
       <c r="IW126" s="47"/>
     </row>
-    <row r="127" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A127" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="C127" s="42" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D127" s="42"/>
       <c r="E127" s="42" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="F127" s="42" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="G127" s="54" t="s">
         <v>268</v>
@@ -38210,33 +38291,24 @@
       <c r="IK127" s="46"/>
       <c r="IL127" s="46"/>
       <c r="IM127" s="46"/>
-      <c r="IN127" s="39"/>
-      <c r="IO127" s="39"/>
-      <c r="IP127" s="39"/>
-      <c r="IQ127" s="39"/>
-      <c r="IR127" s="39"/>
-      <c r="IS127" s="39"/>
-      <c r="IT127" s="39"/>
-      <c r="IU127" s="39"/>
-      <c r="IV127" s="39"/>
       <c r="IW127" s="47"/>
     </row>
-    <row r="128" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A128" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="C128" s="42" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="D128" s="42"/>
       <c r="E128" s="42" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="F128" s="42" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="G128" s="54" t="s">
         <v>268</v>
@@ -38485,33 +38557,24 @@
       <c r="IK128" s="46"/>
       <c r="IL128" s="46"/>
       <c r="IM128" s="46"/>
-      <c r="IN128" s="39"/>
-      <c r="IO128" s="39"/>
-      <c r="IP128" s="39"/>
-      <c r="IQ128" s="39"/>
-      <c r="IR128" s="39"/>
-      <c r="IS128" s="39"/>
-      <c r="IT128" s="39"/>
-      <c r="IU128" s="39"/>
-      <c r="IV128" s="39"/>
       <c r="IW128" s="47"/>
     </row>
-    <row r="129" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A129" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="C129" s="42" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="D129" s="42"/>
       <c r="E129" s="42" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="F129" s="42" t="s">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="G129" s="54" t="s">
         <v>268</v>
@@ -38760,33 +38823,24 @@
       <c r="IK129" s="46"/>
       <c r="IL129" s="46"/>
       <c r="IM129" s="46"/>
-      <c r="IN129" s="39"/>
-      <c r="IO129" s="39"/>
-      <c r="IP129" s="39"/>
-      <c r="IQ129" s="39"/>
-      <c r="IR129" s="39"/>
-      <c r="IS129" s="39"/>
-      <c r="IT129" s="39"/>
-      <c r="IU129" s="39"/>
-      <c r="IV129" s="39"/>
       <c r="IW129" s="47"/>
     </row>
-    <row r="130" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:257" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.15">
       <c r="A130" s="71" t="s">
         <v>325</v>
       </c>
       <c r="B130" s="42" t="s">
-        <v>11</v>
+        <v>267</v>
       </c>
       <c r="C130" s="42" t="s">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="D130" s="42"/>
       <c r="E130" s="42" t="s">
-        <v>327</v>
+        <v>266</v>
       </c>
       <c r="F130" s="42" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="G130" s="54" t="s">
         <v>268</v>
@@ -39035,41 +39089,34 @@
       <c r="IK130" s="46"/>
       <c r="IL130" s="46"/>
       <c r="IM130" s="46"/>
-      <c r="IN130" s="39"/>
-      <c r="IO130" s="39"/>
-      <c r="IP130" s="39"/>
-      <c r="IQ130" s="39"/>
-      <c r="IR130" s="39"/>
-      <c r="IS130" s="39"/>
-      <c r="IT130" s="39"/>
-      <c r="IU130" s="39"/>
-      <c r="IV130" s="39"/>
       <c r="IW130" s="47"/>
     </row>
     <row r="131" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A131" s="68" t="s">
-        <v>343</v>
+      <c r="A131" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B131" s="42" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="C131" s="42" t="s">
-        <v>37</v>
+        <v>255</v>
       </c>
       <c r="D131" s="42"/>
       <c r="E131" s="42" t="s">
-        <v>339</v>
+        <v>256</v>
       </c>
       <c r="F131" s="42" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="G131" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H131" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I131" s="45"/>
+      <c r="H131" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I131" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J131" s="46"/>
       <c r="K131" s="46"/>
       <c r="L131" s="46"/>
@@ -39320,29 +39367,31 @@
       <c r="IW131" s="47"/>
     </row>
     <row r="132" spans="1:257" ht="15" x14ac:dyDescent="0.15">
-      <c r="A132" s="68" t="s">
-        <v>343</v>
+      <c r="A132" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B132" s="42" t="s">
-        <v>30</v>
+        <v>276</v>
       </c>
       <c r="C132" s="42" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="D132" s="42"/>
       <c r="E132" s="42" t="s">
-        <v>340</v>
+        <v>275</v>
       </c>
       <c r="F132" s="42" t="s">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="G132" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H132" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I132" s="45"/>
+      <c r="H132" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I132" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J132" s="46"/>
       <c r="K132" s="46"/>
       <c r="L132" s="46"/>
@@ -39592,30 +39641,32 @@
       <c r="IV132" s="39"/>
       <c r="IW132" s="47"/>
     </row>
-    <row r="133" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A133" s="68" t="s">
-        <v>343</v>
+    <row r="133" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+      <c r="A133" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B133" s="42" t="s">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="C133" s="42" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
       <c r="D133" s="42"/>
       <c r="E133" s="42" t="s">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="F133" s="42" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="G133" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H133" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I133" s="45"/>
+      <c r="H133" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I133" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J133" s="46"/>
       <c r="K133" s="46"/>
       <c r="L133" s="46"/>
@@ -39854,32 +39905,43 @@
       <c r="IK133" s="46"/>
       <c r="IL133" s="46"/>
       <c r="IM133" s="46"/>
+      <c r="IN133" s="39"/>
+      <c r="IO133" s="39"/>
+      <c r="IP133" s="39"/>
+      <c r="IQ133" s="39"/>
+      <c r="IR133" s="39"/>
+      <c r="IS133" s="39"/>
+      <c r="IT133" s="39"/>
+      <c r="IU133" s="39"/>
+      <c r="IV133" s="39"/>
       <c r="IW133" s="47"/>
     </row>
-    <row r="134" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A134" s="68" t="s">
-        <v>343</v>
+    <row r="134" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="A134" s="71" t="s">
+        <v>325</v>
       </c>
       <c r="B134" s="42" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C134" s="42" t="s">
-        <v>28</v>
+        <v>328</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="F134" s="42" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G134" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H134" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I134" s="45"/>
+      <c r="H134" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="I134" s="45" t="s">
+        <v>321</v>
+      </c>
       <c r="J134" s="46"/>
       <c r="K134" s="46"/>
       <c r="L134" s="46"/>
@@ -40118,23 +40180,33 @@
       <c r="IK134" s="46"/>
       <c r="IL134" s="46"/>
       <c r="IM134" s="46"/>
+      <c r="IN134" s="39"/>
+      <c r="IO134" s="39"/>
+      <c r="IP134" s="39"/>
+      <c r="IQ134" s="39"/>
+      <c r="IR134" s="39"/>
+      <c r="IS134" s="39"/>
+      <c r="IT134" s="39"/>
+      <c r="IU134" s="39"/>
+      <c r="IV134" s="39"/>
+      <c r="IW134" s="47"/>
     </row>
-    <row r="135" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A135" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B135" s="42" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C135" s="42" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D135" s="42"/>
       <c r="E135" s="42" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F135" s="42" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G135" s="54" t="s">
         <v>268</v>
@@ -40381,23 +40453,33 @@
       <c r="IK135" s="46"/>
       <c r="IL135" s="46"/>
       <c r="IM135" s="46"/>
+      <c r="IN135" s="39"/>
+      <c r="IO135" s="39"/>
+      <c r="IP135" s="39"/>
+      <c r="IQ135" s="39"/>
+      <c r="IR135" s="39"/>
+      <c r="IS135" s="39"/>
+      <c r="IT135" s="39"/>
+      <c r="IU135" s="39"/>
+      <c r="IV135" s="39"/>
+      <c r="IW135" s="47"/>
     </row>
-    <row r="136" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:257" ht="15" x14ac:dyDescent="0.15">
       <c r="A136" s="68" t="s">
         <v>343</v>
       </c>
       <c r="B136" s="42" t="s">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="C136" s="42" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="D136" s="42"/>
       <c r="E136" s="42" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F136" s="42" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>268</v>
@@ -40644,21 +40726,41 @@
       <c r="IK136" s="46"/>
       <c r="IL136" s="46"/>
       <c r="IM136" s="46"/>
+      <c r="IN136" s="39"/>
+      <c r="IO136" s="39"/>
+      <c r="IP136" s="39"/>
+      <c r="IQ136" s="39"/>
+      <c r="IR136" s="39"/>
+      <c r="IS136" s="39"/>
+      <c r="IT136" s="39"/>
+      <c r="IU136" s="39"/>
+      <c r="IV136" s="39"/>
+      <c r="IW136" s="47"/>
     </row>
     <row r="137" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A137" s="72"/>
-      <c r="B137" s="73"/>
-      <c r="C137" s="73"/>
-      <c r="D137" s="73"/>
-      <c r="E137" s="73"/>
-      <c r="F137" s="46"/>
-      <c r="G137" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="H137" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="I137" s="76"/>
+      <c r="A137" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B137" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="42"/>
+      <c r="E137" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="F137" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="G137" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="H137" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I137" s="45"/>
       <c r="J137" s="46"/>
       <c r="K137" s="46"/>
       <c r="L137" s="46"/>
@@ -40899,21 +41001,30 @@
       <c r="IM137" s="46"/>
       <c r="IW137" s="47"/>
     </row>
-    <row r="138" spans="1:257" ht="30" x14ac:dyDescent="0.15">
-      <c r="B138" s="73"/>
-      <c r="C138" s="73"/>
-      <c r="D138" s="73"/>
-      <c r="E138" s="73"/>
-      <c r="F138" s="46"/>
-      <c r="G138" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="H138" s="79" t="s">
-        <v>344</v>
-      </c>
-      <c r="I138" s="80" t="s">
+    <row r="138" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A138" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C138" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="F138" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="G138" s="54" t="s">
         <v>268</v>
       </c>
+      <c r="H138" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I138" s="45"/>
       <c r="J138" s="46"/>
       <c r="K138" s="46"/>
       <c r="L138" s="46"/>
@@ -41152,32 +41263,31 @@
       <c r="IK138" s="46"/>
       <c r="IL138" s="46"/>
       <c r="IM138" s="46"/>
-      <c r="IN138" s="39"/>
-      <c r="IO138" s="39"/>
-      <c r="IP138" s="39"/>
-      <c r="IQ138" s="39"/>
-      <c r="IR138" s="39"/>
-      <c r="IS138" s="39"/>
-      <c r="IT138" s="39"/>
-      <c r="IU138" s="39"/>
-      <c r="IV138" s="39"/>
-      <c r="IW138" s="47"/>
     </row>
-    <row r="139" spans="1:257" ht="60" x14ac:dyDescent="0.15">
-      <c r="B139" s="73"/>
-      <c r="C139" s="73"/>
-      <c r="D139" s="73"/>
-      <c r="E139" s="73"/>
-      <c r="F139" s="46"/>
-      <c r="G139" s="78" t="s">
-        <v>285</v>
-      </c>
-      <c r="H139" s="79" t="s">
-        <v>345</v>
-      </c>
-      <c r="I139" s="81" t="s">
-        <v>250</v>
-      </c>
+    <row r="139" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A139" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B139" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F139" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="G139" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="H139" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="I139" s="45"/>
       <c r="J139" s="46"/>
       <c r="K139" s="46"/>
       <c r="L139" s="46"/>
@@ -41416,32 +41526,31 @@
       <c r="IK139" s="46"/>
       <c r="IL139" s="46"/>
       <c r="IM139" s="46"/>
-      <c r="IN139" s="39"/>
-      <c r="IO139" s="39"/>
-      <c r="IP139" s="39"/>
-      <c r="IQ139" s="39"/>
-      <c r="IR139" s="39"/>
-      <c r="IS139" s="39"/>
-      <c r="IT139" s="39"/>
-      <c r="IU139" s="39"/>
-      <c r="IV139" s="39"/>
-      <c r="IW139" s="47"/>
     </row>
-    <row r="140" spans="1:257" ht="45" x14ac:dyDescent="0.15">
-      <c r="B140" s="73"/>
-      <c r="C140" s="73"/>
-      <c r="D140" s="73"/>
-      <c r="E140" s="73"/>
-      <c r="F140" s="46"/>
-      <c r="G140" s="78" t="s">
-        <v>286</v>
-      </c>
-      <c r="H140" s="79" t="s">
-        <v>287</v>
-      </c>
-      <c r="I140" s="82" t="s">
+    <row r="140" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A140" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="C140" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="D140" s="42"/>
+      <c r="E140" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="F140" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="G140" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="H140" s="44" t="s">
         <v>251</v>
       </c>
+      <c r="I140" s="45"/>
       <c r="J140" s="46"/>
       <c r="K140" s="46"/>
       <c r="L140" s="46"/>
@@ -41680,32 +41789,21 @@
       <c r="IK140" s="46"/>
       <c r="IL140" s="46"/>
       <c r="IM140" s="46"/>
-      <c r="IN140" s="39"/>
-      <c r="IO140" s="39"/>
-      <c r="IP140" s="39"/>
-      <c r="IQ140" s="39"/>
-      <c r="IR140" s="39"/>
-      <c r="IS140" s="39"/>
-      <c r="IT140" s="39"/>
-      <c r="IU140" s="39"/>
-      <c r="IV140" s="39"/>
-      <c r="IW140" s="47"/>
     </row>
-    <row r="141" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:257" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A141" s="72"/>
       <c r="B141" s="73"/>
       <c r="C141" s="73"/>
       <c r="D141" s="73"/>
       <c r="E141" s="73"/>
       <c r="F141" s="46"/>
-      <c r="G141" s="78" t="s">
-        <v>288</v>
-      </c>
-      <c r="H141" s="79" t="s">
-        <v>289</v>
-      </c>
-      <c r="I141" s="83" t="s">
-        <v>272</v>
-      </c>
+      <c r="G141" s="74" t="s">
+        <v>282</v>
+      </c>
+      <c r="H141" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="I141" s="76"/>
       <c r="J141" s="46"/>
       <c r="K141" s="46"/>
       <c r="L141" s="46"/>
@@ -41944,77 +42042,1124 @@
       <c r="IK141" s="46"/>
       <c r="IL141" s="46"/>
       <c r="IM141" s="46"/>
-      <c r="IN141" s="39"/>
-      <c r="IO141" s="39"/>
-      <c r="IP141" s="39"/>
-      <c r="IQ141" s="39"/>
-      <c r="IR141" s="39"/>
-      <c r="IS141" s="39"/>
-      <c r="IT141" s="39"/>
-      <c r="IU141" s="39"/>
-      <c r="IV141" s="39"/>
       <c r="IW141" s="47"/>
     </row>
-    <row r="142" spans="1:257" s="90" customFormat="1" ht="46" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="84"/>
-      <c r="B142" s="85"/>
-      <c r="C142" s="85"/>
-      <c r="D142" s="86"/>
-      <c r="E142" s="85"/>
-      <c r="F142" s="85"/>
-      <c r="G142" s="87" t="s">
+    <row r="142" spans="1:257" ht="30" x14ac:dyDescent="0.15">
+      <c r="B142" s="73"/>
+      <c r="C142" s="73"/>
+      <c r="D142" s="73"/>
+      <c r="E142" s="73"/>
+      <c r="F142" s="46"/>
+      <c r="G142" s="78" t="s">
+        <v>284</v>
+      </c>
+      <c r="H142" s="79" t="s">
+        <v>344</v>
+      </c>
+      <c r="I142" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="J142" s="46"/>
+      <c r="K142" s="46"/>
+      <c r="L142" s="46"/>
+      <c r="M142" s="46"/>
+      <c r="N142" s="46"/>
+      <c r="O142" s="46"/>
+      <c r="P142" s="46"/>
+      <c r="Q142" s="46"/>
+      <c r="R142" s="46"/>
+      <c r="S142" s="46"/>
+      <c r="T142" s="46"/>
+      <c r="U142" s="46"/>
+      <c r="V142" s="46"/>
+      <c r="W142" s="46"/>
+      <c r="X142" s="46"/>
+      <c r="Y142" s="46"/>
+      <c r="Z142" s="46"/>
+      <c r="AA142" s="46"/>
+      <c r="AB142" s="46"/>
+      <c r="AC142" s="46"/>
+      <c r="AD142" s="46"/>
+      <c r="AE142" s="46"/>
+      <c r="AF142" s="46"/>
+      <c r="AG142" s="46"/>
+      <c r="AH142" s="46"/>
+      <c r="AI142" s="46"/>
+      <c r="AJ142" s="46"/>
+      <c r="AK142" s="46"/>
+      <c r="AL142" s="46"/>
+      <c r="AM142" s="46"/>
+      <c r="AN142" s="46"/>
+      <c r="AO142" s="46"/>
+      <c r="AP142" s="46"/>
+      <c r="AQ142" s="46"/>
+      <c r="AR142" s="46"/>
+      <c r="AS142" s="46"/>
+      <c r="AT142" s="46"/>
+      <c r="AU142" s="46"/>
+      <c r="AV142" s="46"/>
+      <c r="AW142" s="46"/>
+      <c r="AX142" s="46"/>
+      <c r="AY142" s="46"/>
+      <c r="AZ142" s="46"/>
+      <c r="BA142" s="46"/>
+      <c r="BB142" s="46"/>
+      <c r="BC142" s="46"/>
+      <c r="BD142" s="46"/>
+      <c r="BE142" s="46"/>
+      <c r="BF142" s="46"/>
+      <c r="BG142" s="46"/>
+      <c r="BH142" s="46"/>
+      <c r="BI142" s="46"/>
+      <c r="BJ142" s="46"/>
+      <c r="BK142" s="46"/>
+      <c r="BL142" s="46"/>
+      <c r="BM142" s="46"/>
+      <c r="BN142" s="46"/>
+      <c r="BO142" s="46"/>
+      <c r="BP142" s="46"/>
+      <c r="BQ142" s="46"/>
+      <c r="BR142" s="46"/>
+      <c r="BS142" s="46"/>
+      <c r="BT142" s="46"/>
+      <c r="BU142" s="46"/>
+      <c r="BV142" s="46"/>
+      <c r="BW142" s="46"/>
+      <c r="BX142" s="46"/>
+      <c r="BY142" s="46"/>
+      <c r="BZ142" s="46"/>
+      <c r="CA142" s="46"/>
+      <c r="CB142" s="46"/>
+      <c r="CC142" s="46"/>
+      <c r="CD142" s="46"/>
+      <c r="CE142" s="46"/>
+      <c r="CF142" s="46"/>
+      <c r="CG142" s="46"/>
+      <c r="CH142" s="46"/>
+      <c r="CI142" s="46"/>
+      <c r="CJ142" s="46"/>
+      <c r="CK142" s="46"/>
+      <c r="CL142" s="46"/>
+      <c r="CM142" s="46"/>
+      <c r="CN142" s="46"/>
+      <c r="CO142" s="46"/>
+      <c r="CP142" s="46"/>
+      <c r="CQ142" s="46"/>
+      <c r="CR142" s="46"/>
+      <c r="CS142" s="46"/>
+      <c r="CT142" s="46"/>
+      <c r="CU142" s="46"/>
+      <c r="CV142" s="46"/>
+      <c r="CW142" s="46"/>
+      <c r="CX142" s="46"/>
+      <c r="CY142" s="46"/>
+      <c r="CZ142" s="46"/>
+      <c r="DA142" s="46"/>
+      <c r="DB142" s="46"/>
+      <c r="DC142" s="46"/>
+      <c r="DD142" s="46"/>
+      <c r="DE142" s="46"/>
+      <c r="DF142" s="46"/>
+      <c r="DG142" s="46"/>
+      <c r="DH142" s="46"/>
+      <c r="DI142" s="46"/>
+      <c r="DJ142" s="46"/>
+      <c r="DK142" s="46"/>
+      <c r="DL142" s="46"/>
+      <c r="DM142" s="46"/>
+      <c r="DN142" s="46"/>
+      <c r="DO142" s="46"/>
+      <c r="DP142" s="46"/>
+      <c r="DQ142" s="46"/>
+      <c r="DR142" s="46"/>
+      <c r="DS142" s="46"/>
+      <c r="DT142" s="46"/>
+      <c r="DU142" s="46"/>
+      <c r="DV142" s="46"/>
+      <c r="DW142" s="46"/>
+      <c r="DX142" s="46"/>
+      <c r="DY142" s="46"/>
+      <c r="DZ142" s="46"/>
+      <c r="EA142" s="46"/>
+      <c r="EB142" s="46"/>
+      <c r="EC142" s="46"/>
+      <c r="ED142" s="46"/>
+      <c r="EE142" s="46"/>
+      <c r="EF142" s="46"/>
+      <c r="EG142" s="46"/>
+      <c r="EH142" s="46"/>
+      <c r="EI142" s="46"/>
+      <c r="EJ142" s="46"/>
+      <c r="EK142" s="46"/>
+      <c r="EL142" s="46"/>
+      <c r="EM142" s="46"/>
+      <c r="EN142" s="46"/>
+      <c r="EO142" s="46"/>
+      <c r="EP142" s="46"/>
+      <c r="EQ142" s="46"/>
+      <c r="ER142" s="46"/>
+      <c r="ES142" s="46"/>
+      <c r="ET142" s="46"/>
+      <c r="EU142" s="46"/>
+      <c r="EV142" s="46"/>
+      <c r="EW142" s="46"/>
+      <c r="EX142" s="46"/>
+      <c r="EY142" s="46"/>
+      <c r="EZ142" s="46"/>
+      <c r="FA142" s="46"/>
+      <c r="FB142" s="46"/>
+      <c r="FC142" s="46"/>
+      <c r="FD142" s="46"/>
+      <c r="FE142" s="46"/>
+      <c r="FF142" s="46"/>
+      <c r="FG142" s="46"/>
+      <c r="FH142" s="46"/>
+      <c r="FI142" s="46"/>
+      <c r="FJ142" s="46"/>
+      <c r="FK142" s="46"/>
+      <c r="FL142" s="46"/>
+      <c r="FM142" s="46"/>
+      <c r="FN142" s="46"/>
+      <c r="FO142" s="46"/>
+      <c r="FP142" s="46"/>
+      <c r="FQ142" s="46"/>
+      <c r="FR142" s="46"/>
+      <c r="FS142" s="46"/>
+      <c r="FT142" s="46"/>
+      <c r="FU142" s="46"/>
+      <c r="FV142" s="46"/>
+      <c r="FW142" s="46"/>
+      <c r="FX142" s="46"/>
+      <c r="FY142" s="46"/>
+      <c r="FZ142" s="46"/>
+      <c r="GA142" s="46"/>
+      <c r="GB142" s="46"/>
+      <c r="GC142" s="46"/>
+      <c r="GD142" s="46"/>
+      <c r="GE142" s="46"/>
+      <c r="GF142" s="46"/>
+      <c r="GG142" s="46"/>
+      <c r="GH142" s="46"/>
+      <c r="GI142" s="46"/>
+      <c r="GJ142" s="46"/>
+      <c r="GK142" s="46"/>
+      <c r="GL142" s="46"/>
+      <c r="GM142" s="46"/>
+      <c r="GN142" s="46"/>
+      <c r="GO142" s="46"/>
+      <c r="GP142" s="46"/>
+      <c r="GQ142" s="46"/>
+      <c r="GR142" s="46"/>
+      <c r="GS142" s="46"/>
+      <c r="GT142" s="46"/>
+      <c r="GU142" s="46"/>
+      <c r="GV142" s="46"/>
+      <c r="GW142" s="46"/>
+      <c r="GX142" s="46"/>
+      <c r="GY142" s="46"/>
+      <c r="GZ142" s="46"/>
+      <c r="HA142" s="46"/>
+      <c r="HB142" s="46"/>
+      <c r="HC142" s="46"/>
+      <c r="HD142" s="46"/>
+      <c r="HE142" s="46"/>
+      <c r="HF142" s="46"/>
+      <c r="HG142" s="46"/>
+      <c r="HH142" s="46"/>
+      <c r="HI142" s="46"/>
+      <c r="HJ142" s="46"/>
+      <c r="HK142" s="46"/>
+      <c r="HL142" s="46"/>
+      <c r="HM142" s="46"/>
+      <c r="HN142" s="46"/>
+      <c r="HO142" s="46"/>
+      <c r="HP142" s="46"/>
+      <c r="HQ142" s="46"/>
+      <c r="HR142" s="46"/>
+      <c r="HS142" s="46"/>
+      <c r="HT142" s="46"/>
+      <c r="HU142" s="46"/>
+      <c r="HV142" s="46"/>
+      <c r="HW142" s="46"/>
+      <c r="HX142" s="46"/>
+      <c r="HY142" s="46"/>
+      <c r="HZ142" s="46"/>
+      <c r="IA142" s="46"/>
+      <c r="IB142" s="46"/>
+      <c r="IC142" s="46"/>
+      <c r="ID142" s="46"/>
+      <c r="IE142" s="46"/>
+      <c r="IF142" s="46"/>
+      <c r="IG142" s="46"/>
+      <c r="IH142" s="46"/>
+      <c r="II142" s="46"/>
+      <c r="IJ142" s="46"/>
+      <c r="IK142" s="46"/>
+      <c r="IL142" s="46"/>
+      <c r="IM142" s="46"/>
+      <c r="IN142" s="39"/>
+      <c r="IO142" s="39"/>
+      <c r="IP142" s="39"/>
+      <c r="IQ142" s="39"/>
+      <c r="IR142" s="39"/>
+      <c r="IS142" s="39"/>
+      <c r="IT142" s="39"/>
+      <c r="IU142" s="39"/>
+      <c r="IV142" s="39"/>
+      <c r="IW142" s="47"/>
+    </row>
+    <row r="143" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+      <c r="B143" s="73"/>
+      <c r="C143" s="73"/>
+      <c r="D143" s="73"/>
+      <c r="E143" s="73"/>
+      <c r="F143" s="46"/>
+      <c r="G143" s="78" t="s">
+        <v>285</v>
+      </c>
+      <c r="H143" s="79" t="s">
+        <v>345</v>
+      </c>
+      <c r="I143" s="81" t="s">
+        <v>250</v>
+      </c>
+      <c r="J143" s="46"/>
+      <c r="K143" s="46"/>
+      <c r="L143" s="46"/>
+      <c r="M143" s="46"/>
+      <c r="N143" s="46"/>
+      <c r="O143" s="46"/>
+      <c r="P143" s="46"/>
+      <c r="Q143" s="46"/>
+      <c r="R143" s="46"/>
+      <c r="S143" s="46"/>
+      <c r="T143" s="46"/>
+      <c r="U143" s="46"/>
+      <c r="V143" s="46"/>
+      <c r="W143" s="46"/>
+      <c r="X143" s="46"/>
+      <c r="Y143" s="46"/>
+      <c r="Z143" s="46"/>
+      <c r="AA143" s="46"/>
+      <c r="AB143" s="46"/>
+      <c r="AC143" s="46"/>
+      <c r="AD143" s="46"/>
+      <c r="AE143" s="46"/>
+      <c r="AF143" s="46"/>
+      <c r="AG143" s="46"/>
+      <c r="AH143" s="46"/>
+      <c r="AI143" s="46"/>
+      <c r="AJ143" s="46"/>
+      <c r="AK143" s="46"/>
+      <c r="AL143" s="46"/>
+      <c r="AM143" s="46"/>
+      <c r="AN143" s="46"/>
+      <c r="AO143" s="46"/>
+      <c r="AP143" s="46"/>
+      <c r="AQ143" s="46"/>
+      <c r="AR143" s="46"/>
+      <c r="AS143" s="46"/>
+      <c r="AT143" s="46"/>
+      <c r="AU143" s="46"/>
+      <c r="AV143" s="46"/>
+      <c r="AW143" s="46"/>
+      <c r="AX143" s="46"/>
+      <c r="AY143" s="46"/>
+      <c r="AZ143" s="46"/>
+      <c r="BA143" s="46"/>
+      <c r="BB143" s="46"/>
+      <c r="BC143" s="46"/>
+      <c r="BD143" s="46"/>
+      <c r="BE143" s="46"/>
+      <c r="BF143" s="46"/>
+      <c r="BG143" s="46"/>
+      <c r="BH143" s="46"/>
+      <c r="BI143" s="46"/>
+      <c r="BJ143" s="46"/>
+      <c r="BK143" s="46"/>
+      <c r="BL143" s="46"/>
+      <c r="BM143" s="46"/>
+      <c r="BN143" s="46"/>
+      <c r="BO143" s="46"/>
+      <c r="BP143" s="46"/>
+      <c r="BQ143" s="46"/>
+      <c r="BR143" s="46"/>
+      <c r="BS143" s="46"/>
+      <c r="BT143" s="46"/>
+      <c r="BU143" s="46"/>
+      <c r="BV143" s="46"/>
+      <c r="BW143" s="46"/>
+      <c r="BX143" s="46"/>
+      <c r="BY143" s="46"/>
+      <c r="BZ143" s="46"/>
+      <c r="CA143" s="46"/>
+      <c r="CB143" s="46"/>
+      <c r="CC143" s="46"/>
+      <c r="CD143" s="46"/>
+      <c r="CE143" s="46"/>
+      <c r="CF143" s="46"/>
+      <c r="CG143" s="46"/>
+      <c r="CH143" s="46"/>
+      <c r="CI143" s="46"/>
+      <c r="CJ143" s="46"/>
+      <c r="CK143" s="46"/>
+      <c r="CL143" s="46"/>
+      <c r="CM143" s="46"/>
+      <c r="CN143" s="46"/>
+      <c r="CO143" s="46"/>
+      <c r="CP143" s="46"/>
+      <c r="CQ143" s="46"/>
+      <c r="CR143" s="46"/>
+      <c r="CS143" s="46"/>
+      <c r="CT143" s="46"/>
+      <c r="CU143" s="46"/>
+      <c r="CV143" s="46"/>
+      <c r="CW143" s="46"/>
+      <c r="CX143" s="46"/>
+      <c r="CY143" s="46"/>
+      <c r="CZ143" s="46"/>
+      <c r="DA143" s="46"/>
+      <c r="DB143" s="46"/>
+      <c r="DC143" s="46"/>
+      <c r="DD143" s="46"/>
+      <c r="DE143" s="46"/>
+      <c r="DF143" s="46"/>
+      <c r="DG143" s="46"/>
+      <c r="DH143" s="46"/>
+      <c r="DI143" s="46"/>
+      <c r="DJ143" s="46"/>
+      <c r="DK143" s="46"/>
+      <c r="DL143" s="46"/>
+      <c r="DM143" s="46"/>
+      <c r="DN143" s="46"/>
+      <c r="DO143" s="46"/>
+      <c r="DP143" s="46"/>
+      <c r="DQ143" s="46"/>
+      <c r="DR143" s="46"/>
+      <c r="DS143" s="46"/>
+      <c r="DT143" s="46"/>
+      <c r="DU143" s="46"/>
+      <c r="DV143" s="46"/>
+      <c r="DW143" s="46"/>
+      <c r="DX143" s="46"/>
+      <c r="DY143" s="46"/>
+      <c r="DZ143" s="46"/>
+      <c r="EA143" s="46"/>
+      <c r="EB143" s="46"/>
+      <c r="EC143" s="46"/>
+      <c r="ED143" s="46"/>
+      <c r="EE143" s="46"/>
+      <c r="EF143" s="46"/>
+      <c r="EG143" s="46"/>
+      <c r="EH143" s="46"/>
+      <c r="EI143" s="46"/>
+      <c r="EJ143" s="46"/>
+      <c r="EK143" s="46"/>
+      <c r="EL143" s="46"/>
+      <c r="EM143" s="46"/>
+      <c r="EN143" s="46"/>
+      <c r="EO143" s="46"/>
+      <c r="EP143" s="46"/>
+      <c r="EQ143" s="46"/>
+      <c r="ER143" s="46"/>
+      <c r="ES143" s="46"/>
+      <c r="ET143" s="46"/>
+      <c r="EU143" s="46"/>
+      <c r="EV143" s="46"/>
+      <c r="EW143" s="46"/>
+      <c r="EX143" s="46"/>
+      <c r="EY143" s="46"/>
+      <c r="EZ143" s="46"/>
+      <c r="FA143" s="46"/>
+      <c r="FB143" s="46"/>
+      <c r="FC143" s="46"/>
+      <c r="FD143" s="46"/>
+      <c r="FE143" s="46"/>
+      <c r="FF143" s="46"/>
+      <c r="FG143" s="46"/>
+      <c r="FH143" s="46"/>
+      <c r="FI143" s="46"/>
+      <c r="FJ143" s="46"/>
+      <c r="FK143" s="46"/>
+      <c r="FL143" s="46"/>
+      <c r="FM143" s="46"/>
+      <c r="FN143" s="46"/>
+      <c r="FO143" s="46"/>
+      <c r="FP143" s="46"/>
+      <c r="FQ143" s="46"/>
+      <c r="FR143" s="46"/>
+      <c r="FS143" s="46"/>
+      <c r="FT143" s="46"/>
+      <c r="FU143" s="46"/>
+      <c r="FV143" s="46"/>
+      <c r="FW143" s="46"/>
+      <c r="FX143" s="46"/>
+      <c r="FY143" s="46"/>
+      <c r="FZ143" s="46"/>
+      <c r="GA143" s="46"/>
+      <c r="GB143" s="46"/>
+      <c r="GC143" s="46"/>
+      <c r="GD143" s="46"/>
+      <c r="GE143" s="46"/>
+      <c r="GF143" s="46"/>
+      <c r="GG143" s="46"/>
+      <c r="GH143" s="46"/>
+      <c r="GI143" s="46"/>
+      <c r="GJ143" s="46"/>
+      <c r="GK143" s="46"/>
+      <c r="GL143" s="46"/>
+      <c r="GM143" s="46"/>
+      <c r="GN143" s="46"/>
+      <c r="GO143" s="46"/>
+      <c r="GP143" s="46"/>
+      <c r="GQ143" s="46"/>
+      <c r="GR143" s="46"/>
+      <c r="GS143" s="46"/>
+      <c r="GT143" s="46"/>
+      <c r="GU143" s="46"/>
+      <c r="GV143" s="46"/>
+      <c r="GW143" s="46"/>
+      <c r="GX143" s="46"/>
+      <c r="GY143" s="46"/>
+      <c r="GZ143" s="46"/>
+      <c r="HA143" s="46"/>
+      <c r="HB143" s="46"/>
+      <c r="HC143" s="46"/>
+      <c r="HD143" s="46"/>
+      <c r="HE143" s="46"/>
+      <c r="HF143" s="46"/>
+      <c r="HG143" s="46"/>
+      <c r="HH143" s="46"/>
+      <c r="HI143" s="46"/>
+      <c r="HJ143" s="46"/>
+      <c r="HK143" s="46"/>
+      <c r="HL143" s="46"/>
+      <c r="HM143" s="46"/>
+      <c r="HN143" s="46"/>
+      <c r="HO143" s="46"/>
+      <c r="HP143" s="46"/>
+      <c r="HQ143" s="46"/>
+      <c r="HR143" s="46"/>
+      <c r="HS143" s="46"/>
+      <c r="HT143" s="46"/>
+      <c r="HU143" s="46"/>
+      <c r="HV143" s="46"/>
+      <c r="HW143" s="46"/>
+      <c r="HX143" s="46"/>
+      <c r="HY143" s="46"/>
+      <c r="HZ143" s="46"/>
+      <c r="IA143" s="46"/>
+      <c r="IB143" s="46"/>
+      <c r="IC143" s="46"/>
+      <c r="ID143" s="46"/>
+      <c r="IE143" s="46"/>
+      <c r="IF143" s="46"/>
+      <c r="IG143" s="46"/>
+      <c r="IH143" s="46"/>
+      <c r="II143" s="46"/>
+      <c r="IJ143" s="46"/>
+      <c r="IK143" s="46"/>
+      <c r="IL143" s="46"/>
+      <c r="IM143" s="46"/>
+      <c r="IN143" s="39"/>
+      <c r="IO143" s="39"/>
+      <c r="IP143" s="39"/>
+      <c r="IQ143" s="39"/>
+      <c r="IR143" s="39"/>
+      <c r="IS143" s="39"/>
+      <c r="IT143" s="39"/>
+      <c r="IU143" s="39"/>
+      <c r="IV143" s="39"/>
+      <c r="IW143" s="47"/>
+    </row>
+    <row r="144" spans="1:257" ht="45" x14ac:dyDescent="0.15">
+      <c r="B144" s="73"/>
+      <c r="C144" s="73"/>
+      <c r="D144" s="73"/>
+      <c r="E144" s="73"/>
+      <c r="F144" s="46"/>
+      <c r="G144" s="78" t="s">
+        <v>286</v>
+      </c>
+      <c r="H144" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="I144" s="82" t="s">
+        <v>251</v>
+      </c>
+      <c r="J144" s="46"/>
+      <c r="K144" s="46"/>
+      <c r="L144" s="46"/>
+      <c r="M144" s="46"/>
+      <c r="N144" s="46"/>
+      <c r="O144" s="46"/>
+      <c r="P144" s="46"/>
+      <c r="Q144" s="46"/>
+      <c r="R144" s="46"/>
+      <c r="S144" s="46"/>
+      <c r="T144" s="46"/>
+      <c r="U144" s="46"/>
+      <c r="V144" s="46"/>
+      <c r="W144" s="46"/>
+      <c r="X144" s="46"/>
+      <c r="Y144" s="46"/>
+      <c r="Z144" s="46"/>
+      <c r="AA144" s="46"/>
+      <c r="AB144" s="46"/>
+      <c r="AC144" s="46"/>
+      <c r="AD144" s="46"/>
+      <c r="AE144" s="46"/>
+      <c r="AF144" s="46"/>
+      <c r="AG144" s="46"/>
+      <c r="AH144" s="46"/>
+      <c r="AI144" s="46"/>
+      <c r="AJ144" s="46"/>
+      <c r="AK144" s="46"/>
+      <c r="AL144" s="46"/>
+      <c r="AM144" s="46"/>
+      <c r="AN144" s="46"/>
+      <c r="AO144" s="46"/>
+      <c r="AP144" s="46"/>
+      <c r="AQ144" s="46"/>
+      <c r="AR144" s="46"/>
+      <c r="AS144" s="46"/>
+      <c r="AT144" s="46"/>
+      <c r="AU144" s="46"/>
+      <c r="AV144" s="46"/>
+      <c r="AW144" s="46"/>
+      <c r="AX144" s="46"/>
+      <c r="AY144" s="46"/>
+      <c r="AZ144" s="46"/>
+      <c r="BA144" s="46"/>
+      <c r="BB144" s="46"/>
+      <c r="BC144" s="46"/>
+      <c r="BD144" s="46"/>
+      <c r="BE144" s="46"/>
+      <c r="BF144" s="46"/>
+      <c r="BG144" s="46"/>
+      <c r="BH144" s="46"/>
+      <c r="BI144" s="46"/>
+      <c r="BJ144" s="46"/>
+      <c r="BK144" s="46"/>
+      <c r="BL144" s="46"/>
+      <c r="BM144" s="46"/>
+      <c r="BN144" s="46"/>
+      <c r="BO144" s="46"/>
+      <c r="BP144" s="46"/>
+      <c r="BQ144" s="46"/>
+      <c r="BR144" s="46"/>
+      <c r="BS144" s="46"/>
+      <c r="BT144" s="46"/>
+      <c r="BU144" s="46"/>
+      <c r="BV144" s="46"/>
+      <c r="BW144" s="46"/>
+      <c r="BX144" s="46"/>
+      <c r="BY144" s="46"/>
+      <c r="BZ144" s="46"/>
+      <c r="CA144" s="46"/>
+      <c r="CB144" s="46"/>
+      <c r="CC144" s="46"/>
+      <c r="CD144" s="46"/>
+      <c r="CE144" s="46"/>
+      <c r="CF144" s="46"/>
+      <c r="CG144" s="46"/>
+      <c r="CH144" s="46"/>
+      <c r="CI144" s="46"/>
+      <c r="CJ144" s="46"/>
+      <c r="CK144" s="46"/>
+      <c r="CL144" s="46"/>
+      <c r="CM144" s="46"/>
+      <c r="CN144" s="46"/>
+      <c r="CO144" s="46"/>
+      <c r="CP144" s="46"/>
+      <c r="CQ144" s="46"/>
+      <c r="CR144" s="46"/>
+      <c r="CS144" s="46"/>
+      <c r="CT144" s="46"/>
+      <c r="CU144" s="46"/>
+      <c r="CV144" s="46"/>
+      <c r="CW144" s="46"/>
+      <c r="CX144" s="46"/>
+      <c r="CY144" s="46"/>
+      <c r="CZ144" s="46"/>
+      <c r="DA144" s="46"/>
+      <c r="DB144" s="46"/>
+      <c r="DC144" s="46"/>
+      <c r="DD144" s="46"/>
+      <c r="DE144" s="46"/>
+      <c r="DF144" s="46"/>
+      <c r="DG144" s="46"/>
+      <c r="DH144" s="46"/>
+      <c r="DI144" s="46"/>
+      <c r="DJ144" s="46"/>
+      <c r="DK144" s="46"/>
+      <c r="DL144" s="46"/>
+      <c r="DM144" s="46"/>
+      <c r="DN144" s="46"/>
+      <c r="DO144" s="46"/>
+      <c r="DP144" s="46"/>
+      <c r="DQ144" s="46"/>
+      <c r="DR144" s="46"/>
+      <c r="DS144" s="46"/>
+      <c r="DT144" s="46"/>
+      <c r="DU144" s="46"/>
+      <c r="DV144" s="46"/>
+      <c r="DW144" s="46"/>
+      <c r="DX144" s="46"/>
+      <c r="DY144" s="46"/>
+      <c r="DZ144" s="46"/>
+      <c r="EA144" s="46"/>
+      <c r="EB144" s="46"/>
+      <c r="EC144" s="46"/>
+      <c r="ED144" s="46"/>
+      <c r="EE144" s="46"/>
+      <c r="EF144" s="46"/>
+      <c r="EG144" s="46"/>
+      <c r="EH144" s="46"/>
+      <c r="EI144" s="46"/>
+      <c r="EJ144" s="46"/>
+      <c r="EK144" s="46"/>
+      <c r="EL144" s="46"/>
+      <c r="EM144" s="46"/>
+      <c r="EN144" s="46"/>
+      <c r="EO144" s="46"/>
+      <c r="EP144" s="46"/>
+      <c r="EQ144" s="46"/>
+      <c r="ER144" s="46"/>
+      <c r="ES144" s="46"/>
+      <c r="ET144" s="46"/>
+      <c r="EU144" s="46"/>
+      <c r="EV144" s="46"/>
+      <c r="EW144" s="46"/>
+      <c r="EX144" s="46"/>
+      <c r="EY144" s="46"/>
+      <c r="EZ144" s="46"/>
+      <c r="FA144" s="46"/>
+      <c r="FB144" s="46"/>
+      <c r="FC144" s="46"/>
+      <c r="FD144" s="46"/>
+      <c r="FE144" s="46"/>
+      <c r="FF144" s="46"/>
+      <c r="FG144" s="46"/>
+      <c r="FH144" s="46"/>
+      <c r="FI144" s="46"/>
+      <c r="FJ144" s="46"/>
+      <c r="FK144" s="46"/>
+      <c r="FL144" s="46"/>
+      <c r="FM144" s="46"/>
+      <c r="FN144" s="46"/>
+      <c r="FO144" s="46"/>
+      <c r="FP144" s="46"/>
+      <c r="FQ144" s="46"/>
+      <c r="FR144" s="46"/>
+      <c r="FS144" s="46"/>
+      <c r="FT144" s="46"/>
+      <c r="FU144" s="46"/>
+      <c r="FV144" s="46"/>
+      <c r="FW144" s="46"/>
+      <c r="FX144" s="46"/>
+      <c r="FY144" s="46"/>
+      <c r="FZ144" s="46"/>
+      <c r="GA144" s="46"/>
+      <c r="GB144" s="46"/>
+      <c r="GC144" s="46"/>
+      <c r="GD144" s="46"/>
+      <c r="GE144" s="46"/>
+      <c r="GF144" s="46"/>
+      <c r="GG144" s="46"/>
+      <c r="GH144" s="46"/>
+      <c r="GI144" s="46"/>
+      <c r="GJ144" s="46"/>
+      <c r="GK144" s="46"/>
+      <c r="GL144" s="46"/>
+      <c r="GM144" s="46"/>
+      <c r="GN144" s="46"/>
+      <c r="GO144" s="46"/>
+      <c r="GP144" s="46"/>
+      <c r="GQ144" s="46"/>
+      <c r="GR144" s="46"/>
+      <c r="GS144" s="46"/>
+      <c r="GT144" s="46"/>
+      <c r="GU144" s="46"/>
+      <c r="GV144" s="46"/>
+      <c r="GW144" s="46"/>
+      <c r="GX144" s="46"/>
+      <c r="GY144" s="46"/>
+      <c r="GZ144" s="46"/>
+      <c r="HA144" s="46"/>
+      <c r="HB144" s="46"/>
+      <c r="HC144" s="46"/>
+      <c r="HD144" s="46"/>
+      <c r="HE144" s="46"/>
+      <c r="HF144" s="46"/>
+      <c r="HG144" s="46"/>
+      <c r="HH144" s="46"/>
+      <c r="HI144" s="46"/>
+      <c r="HJ144" s="46"/>
+      <c r="HK144" s="46"/>
+      <c r="HL144" s="46"/>
+      <c r="HM144" s="46"/>
+      <c r="HN144" s="46"/>
+      <c r="HO144" s="46"/>
+      <c r="HP144" s="46"/>
+      <c r="HQ144" s="46"/>
+      <c r="HR144" s="46"/>
+      <c r="HS144" s="46"/>
+      <c r="HT144" s="46"/>
+      <c r="HU144" s="46"/>
+      <c r="HV144" s="46"/>
+      <c r="HW144" s="46"/>
+      <c r="HX144" s="46"/>
+      <c r="HY144" s="46"/>
+      <c r="HZ144" s="46"/>
+      <c r="IA144" s="46"/>
+      <c r="IB144" s="46"/>
+      <c r="IC144" s="46"/>
+      <c r="ID144" s="46"/>
+      <c r="IE144" s="46"/>
+      <c r="IF144" s="46"/>
+      <c r="IG144" s="46"/>
+      <c r="IH144" s="46"/>
+      <c r="II144" s="46"/>
+      <c r="IJ144" s="46"/>
+      <c r="IK144" s="46"/>
+      <c r="IL144" s="46"/>
+      <c r="IM144" s="46"/>
+      <c r="IN144" s="39"/>
+      <c r="IO144" s="39"/>
+      <c r="IP144" s="39"/>
+      <c r="IQ144" s="39"/>
+      <c r="IR144" s="39"/>
+      <c r="IS144" s="39"/>
+      <c r="IT144" s="39"/>
+      <c r="IU144" s="39"/>
+      <c r="IV144" s="39"/>
+      <c r="IW144" s="47"/>
+    </row>
+    <row r="145" spans="1:257" ht="60" x14ac:dyDescent="0.15">
+      <c r="B145" s="73"/>
+      <c r="C145" s="73"/>
+      <c r="D145" s="73"/>
+      <c r="E145" s="73"/>
+      <c r="F145" s="46"/>
+      <c r="G145" s="78" t="s">
+        <v>288</v>
+      </c>
+      <c r="H145" s="79" t="s">
+        <v>289</v>
+      </c>
+      <c r="I145" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="J145" s="46"/>
+      <c r="K145" s="46"/>
+      <c r="L145" s="46"/>
+      <c r="M145" s="46"/>
+      <c r="N145" s="46"/>
+      <c r="O145" s="46"/>
+      <c r="P145" s="46"/>
+      <c r="Q145" s="46"/>
+      <c r="R145" s="46"/>
+      <c r="S145" s="46"/>
+      <c r="T145" s="46"/>
+      <c r="U145" s="46"/>
+      <c r="V145" s="46"/>
+      <c r="W145" s="46"/>
+      <c r="X145" s="46"/>
+      <c r="Y145" s="46"/>
+      <c r="Z145" s="46"/>
+      <c r="AA145" s="46"/>
+      <c r="AB145" s="46"/>
+      <c r="AC145" s="46"/>
+      <c r="AD145" s="46"/>
+      <c r="AE145" s="46"/>
+      <c r="AF145" s="46"/>
+      <c r="AG145" s="46"/>
+      <c r="AH145" s="46"/>
+      <c r="AI145" s="46"/>
+      <c r="AJ145" s="46"/>
+      <c r="AK145" s="46"/>
+      <c r="AL145" s="46"/>
+      <c r="AM145" s="46"/>
+      <c r="AN145" s="46"/>
+      <c r="AO145" s="46"/>
+      <c r="AP145" s="46"/>
+      <c r="AQ145" s="46"/>
+      <c r="AR145" s="46"/>
+      <c r="AS145" s="46"/>
+      <c r="AT145" s="46"/>
+      <c r="AU145" s="46"/>
+      <c r="AV145" s="46"/>
+      <c r="AW145" s="46"/>
+      <c r="AX145" s="46"/>
+      <c r="AY145" s="46"/>
+      <c r="AZ145" s="46"/>
+      <c r="BA145" s="46"/>
+      <c r="BB145" s="46"/>
+      <c r="BC145" s="46"/>
+      <c r="BD145" s="46"/>
+      <c r="BE145" s="46"/>
+      <c r="BF145" s="46"/>
+      <c r="BG145" s="46"/>
+      <c r="BH145" s="46"/>
+      <c r="BI145" s="46"/>
+      <c r="BJ145" s="46"/>
+      <c r="BK145" s="46"/>
+      <c r="BL145" s="46"/>
+      <c r="BM145" s="46"/>
+      <c r="BN145" s="46"/>
+      <c r="BO145" s="46"/>
+      <c r="BP145" s="46"/>
+      <c r="BQ145" s="46"/>
+      <c r="BR145" s="46"/>
+      <c r="BS145" s="46"/>
+      <c r="BT145" s="46"/>
+      <c r="BU145" s="46"/>
+      <c r="BV145" s="46"/>
+      <c r="BW145" s="46"/>
+      <c r="BX145" s="46"/>
+      <c r="BY145" s="46"/>
+      <c r="BZ145" s="46"/>
+      <c r="CA145" s="46"/>
+      <c r="CB145" s="46"/>
+      <c r="CC145" s="46"/>
+      <c r="CD145" s="46"/>
+      <c r="CE145" s="46"/>
+      <c r="CF145" s="46"/>
+      <c r="CG145" s="46"/>
+      <c r="CH145" s="46"/>
+      <c r="CI145" s="46"/>
+      <c r="CJ145" s="46"/>
+      <c r="CK145" s="46"/>
+      <c r="CL145" s="46"/>
+      <c r="CM145" s="46"/>
+      <c r="CN145" s="46"/>
+      <c r="CO145" s="46"/>
+      <c r="CP145" s="46"/>
+      <c r="CQ145" s="46"/>
+      <c r="CR145" s="46"/>
+      <c r="CS145" s="46"/>
+      <c r="CT145" s="46"/>
+      <c r="CU145" s="46"/>
+      <c r="CV145" s="46"/>
+      <c r="CW145" s="46"/>
+      <c r="CX145" s="46"/>
+      <c r="CY145" s="46"/>
+      <c r="CZ145" s="46"/>
+      <c r="DA145" s="46"/>
+      <c r="DB145" s="46"/>
+      <c r="DC145" s="46"/>
+      <c r="DD145" s="46"/>
+      <c r="DE145" s="46"/>
+      <c r="DF145" s="46"/>
+      <c r="DG145" s="46"/>
+      <c r="DH145" s="46"/>
+      <c r="DI145" s="46"/>
+      <c r="DJ145" s="46"/>
+      <c r="DK145" s="46"/>
+      <c r="DL145" s="46"/>
+      <c r="DM145" s="46"/>
+      <c r="DN145" s="46"/>
+      <c r="DO145" s="46"/>
+      <c r="DP145" s="46"/>
+      <c r="DQ145" s="46"/>
+      <c r="DR145" s="46"/>
+      <c r="DS145" s="46"/>
+      <c r="DT145" s="46"/>
+      <c r="DU145" s="46"/>
+      <c r="DV145" s="46"/>
+      <c r="DW145" s="46"/>
+      <c r="DX145" s="46"/>
+      <c r="DY145" s="46"/>
+      <c r="DZ145" s="46"/>
+      <c r="EA145" s="46"/>
+      <c r="EB145" s="46"/>
+      <c r="EC145" s="46"/>
+      <c r="ED145" s="46"/>
+      <c r="EE145" s="46"/>
+      <c r="EF145" s="46"/>
+      <c r="EG145" s="46"/>
+      <c r="EH145" s="46"/>
+      <c r="EI145" s="46"/>
+      <c r="EJ145" s="46"/>
+      <c r="EK145" s="46"/>
+      <c r="EL145" s="46"/>
+      <c r="EM145" s="46"/>
+      <c r="EN145" s="46"/>
+      <c r="EO145" s="46"/>
+      <c r="EP145" s="46"/>
+      <c r="EQ145" s="46"/>
+      <c r="ER145" s="46"/>
+      <c r="ES145" s="46"/>
+      <c r="ET145" s="46"/>
+      <c r="EU145" s="46"/>
+      <c r="EV145" s="46"/>
+      <c r="EW145" s="46"/>
+      <c r="EX145" s="46"/>
+      <c r="EY145" s="46"/>
+      <c r="EZ145" s="46"/>
+      <c r="FA145" s="46"/>
+      <c r="FB145" s="46"/>
+      <c r="FC145" s="46"/>
+      <c r="FD145" s="46"/>
+      <c r="FE145" s="46"/>
+      <c r="FF145" s="46"/>
+      <c r="FG145" s="46"/>
+      <c r="FH145" s="46"/>
+      <c r="FI145" s="46"/>
+      <c r="FJ145" s="46"/>
+      <c r="FK145" s="46"/>
+      <c r="FL145" s="46"/>
+      <c r="FM145" s="46"/>
+      <c r="FN145" s="46"/>
+      <c r="FO145" s="46"/>
+      <c r="FP145" s="46"/>
+      <c r="FQ145" s="46"/>
+      <c r="FR145" s="46"/>
+      <c r="FS145" s="46"/>
+      <c r="FT145" s="46"/>
+      <c r="FU145" s="46"/>
+      <c r="FV145" s="46"/>
+      <c r="FW145" s="46"/>
+      <c r="FX145" s="46"/>
+      <c r="FY145" s="46"/>
+      <c r="FZ145" s="46"/>
+      <c r="GA145" s="46"/>
+      <c r="GB145" s="46"/>
+      <c r="GC145" s="46"/>
+      <c r="GD145" s="46"/>
+      <c r="GE145" s="46"/>
+      <c r="GF145" s="46"/>
+      <c r="GG145" s="46"/>
+      <c r="GH145" s="46"/>
+      <c r="GI145" s="46"/>
+      <c r="GJ145" s="46"/>
+      <c r="GK145" s="46"/>
+      <c r="GL145" s="46"/>
+      <c r="GM145" s="46"/>
+      <c r="GN145" s="46"/>
+      <c r="GO145" s="46"/>
+      <c r="GP145" s="46"/>
+      <c r="GQ145" s="46"/>
+      <c r="GR145" s="46"/>
+      <c r="GS145" s="46"/>
+      <c r="GT145" s="46"/>
+      <c r="GU145" s="46"/>
+      <c r="GV145" s="46"/>
+      <c r="GW145" s="46"/>
+      <c r="GX145" s="46"/>
+      <c r="GY145" s="46"/>
+      <c r="GZ145" s="46"/>
+      <c r="HA145" s="46"/>
+      <c r="HB145" s="46"/>
+      <c r="HC145" s="46"/>
+      <c r="HD145" s="46"/>
+      <c r="HE145" s="46"/>
+      <c r="HF145" s="46"/>
+      <c r="HG145" s="46"/>
+      <c r="HH145" s="46"/>
+      <c r="HI145" s="46"/>
+      <c r="HJ145" s="46"/>
+      <c r="HK145" s="46"/>
+      <c r="HL145" s="46"/>
+      <c r="HM145" s="46"/>
+      <c r="HN145" s="46"/>
+      <c r="HO145" s="46"/>
+      <c r="HP145" s="46"/>
+      <c r="HQ145" s="46"/>
+      <c r="HR145" s="46"/>
+      <c r="HS145" s="46"/>
+      <c r="HT145" s="46"/>
+      <c r="HU145" s="46"/>
+      <c r="HV145" s="46"/>
+      <c r="HW145" s="46"/>
+      <c r="HX145" s="46"/>
+      <c r="HY145" s="46"/>
+      <c r="HZ145" s="46"/>
+      <c r="IA145" s="46"/>
+      <c r="IB145" s="46"/>
+      <c r="IC145" s="46"/>
+      <c r="ID145" s="46"/>
+      <c r="IE145" s="46"/>
+      <c r="IF145" s="46"/>
+      <c r="IG145" s="46"/>
+      <c r="IH145" s="46"/>
+      <c r="II145" s="46"/>
+      <c r="IJ145" s="46"/>
+      <c r="IK145" s="46"/>
+      <c r="IL145" s="46"/>
+      <c r="IM145" s="46"/>
+      <c r="IN145" s="39"/>
+      <c r="IO145" s="39"/>
+      <c r="IP145" s="39"/>
+      <c r="IQ145" s="39"/>
+      <c r="IR145" s="39"/>
+      <c r="IS145" s="39"/>
+      <c r="IT145" s="39"/>
+      <c r="IU145" s="39"/>
+      <c r="IV145" s="39"/>
+      <c r="IW145" s="47"/>
+    </row>
+    <row r="146" spans="1:257" s="90" customFormat="1" ht="46" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="84"/>
+      <c r="B146" s="85"/>
+      <c r="C146" s="85"/>
+      <c r="D146" s="86"/>
+      <c r="E146" s="85"/>
+      <c r="F146" s="85"/>
+      <c r="G146" s="87" t="s">
         <v>290</v>
       </c>
-      <c r="H142" s="88" t="s">
+      <c r="H146" s="88" t="s">
         <v>291</v>
       </c>
-      <c r="I142" s="89" t="s">
+      <c r="I146" s="89" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="143" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A143" s="84"/>
-    </row>
-    <row r="144" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A144" s="84"/>
-    </row>
-    <row r="145" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A145" s="84"/>
-    </row>
-    <row r="146" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
-      <c r="A146" s="84"/>
-    </row>
-    <row r="147" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A147" s="84"/>
     </row>
-    <row r="148" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A148" s="84"/>
     </row>
-    <row r="149" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A149" s="84"/>
     </row>
-    <row r="150" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A150" s="84"/>
     </row>
-    <row r="151" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A151" s="84"/>
     </row>
-    <row r="152" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A152" s="84"/>
     </row>
-    <row r="153" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A153" s="84"/>
     </row>
-    <row r="154" spans="1:9" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A154" s="84"/>
     </row>
-    <row r="155" spans="1:9" ht="15" x14ac:dyDescent="0.15">
-      <c r="H155" s="90"/>
-      <c r="I155" s="90"/>
+    <row r="155" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A155" s="84"/>
+    </row>
+    <row r="156" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A156" s="84"/>
+    </row>
+    <row r="157" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A157" s="84"/>
+    </row>
+    <row r="158" spans="1:257" s="90" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A158" s="84"/>
+    </row>
+    <row r="159" spans="1:257" ht="15" x14ac:dyDescent="0.15">
+      <c r="H159" s="90"/>
+      <c r="I159" s="90"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I156">
-    <sortCondition ref="A1:A156"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I160">
+    <sortCondition ref="A1:A160"/>
   </sortState>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
@@ -42459,7 +43604,7 @@
       <c r="B35" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="C35" s="96" t="s">
+      <c r="C35" s="97" t="s">
         <v>195</v>
       </c>
       <c r="D35" s="7"/>
@@ -42470,7 +43615,7 @@
       <c r="B36" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C36" s="97"/>
+      <c r="C36" s="98"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
@@ -42479,7 +43624,7 @@
       <c r="B37" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="97"/>
+      <c r="C37" s="98"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
@@ -42488,7 +43633,7 @@
       <c r="B38" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="C38" s="98"/>
+      <c r="C38" s="99"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
